--- a/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
+++ b/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA31FAB9-D951-4DC4-8E5C-5F990E9B84AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122D783-D101-471A-82A9-D7CF8CAF65C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3394" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3398" uniqueCount="33">
   <si>
     <t>План поставок ПОКОМ</t>
   </si>
@@ -435,7 +435,14 @@
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Обычный 2 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="484">
+  <dxfs count="485">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4205,7 +4212,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMD833"/>
+  <dimension ref="A1:AMD838"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
@@ -28068,512 +28075,636 @@
       <c r="J833" s="11"/>
       <c r="K833" s="12"/>
     </row>
+    <row r="834" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A834" s="1">
+        <v>830</v>
+      </c>
+      <c r="B834" s="7" t="str">
+        <f t="shared" ref="B834:B838" si="135">IF(C834&lt;&gt;"",TEXT(C834,"ДДД"),"")</f>
+        <v>Вт</v>
+      </c>
+      <c r="C834" s="8">
+        <v>46035</v>
+      </c>
+      <c r="D834" s="9">
+        <v>1100</v>
+      </c>
+      <c r="E834" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F834" s="11">
+        <f>2000+4800</f>
+        <v>6800</v>
+      </c>
+      <c r="G834" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H834" s="11">
+        <f>12400+6500</f>
+        <v>18900</v>
+      </c>
+      <c r="I834" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J834" s="11">
+        <f>7300+14000</f>
+        <v>21300</v>
+      </c>
+      <c r="K834" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="835" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A835" s="1">
+        <v>831</v>
+      </c>
+      <c r="B835" s="7" t="str">
+        <f t="shared" si="135"/>
+        <v>Ср</v>
+      </c>
+      <c r="C835" s="8">
+        <v>46036</v>
+      </c>
+      <c r="D835" s="9"/>
+      <c r="E835" s="10"/>
+      <c r="F835" s="11"/>
+      <c r="G835" s="12"/>
+      <c r="H835" s="11"/>
+      <c r="I835" s="12"/>
+      <c r="J835" s="11"/>
+      <c r="K835" s="12"/>
+    </row>
+    <row r="836" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A836" s="1">
+        <v>832</v>
+      </c>
+      <c r="B836" s="7" t="str">
+        <f t="shared" si="135"/>
+        <v>Чт</v>
+      </c>
+      <c r="C836" s="8">
+        <v>46037</v>
+      </c>
+      <c r="D836" s="9"/>
+      <c r="E836" s="10"/>
+      <c r="F836" s="11"/>
+      <c r="G836" s="12"/>
+      <c r="H836" s="11"/>
+      <c r="I836" s="12"/>
+      <c r="J836" s="11"/>
+      <c r="K836" s="12"/>
+    </row>
+    <row r="837" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A837" s="1">
+        <v>833</v>
+      </c>
+      <c r="B837" s="7" t="str">
+        <f t="shared" si="135"/>
+        <v>Пт</v>
+      </c>
+      <c r="C837" s="8">
+        <v>46038</v>
+      </c>
+      <c r="D837" s="9"/>
+      <c r="E837" s="10"/>
+      <c r="F837" s="11"/>
+      <c r="G837" s="12"/>
+      <c r="H837" s="11"/>
+      <c r="I837" s="12"/>
+      <c r="J837" s="11"/>
+      <c r="K837" s="12"/>
+    </row>
+    <row r="838" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A838" s="1">
+        <v>834</v>
+      </c>
+      <c r="B838" s="7" t="str">
+        <f t="shared" si="135"/>
+        <v>Сб</v>
+      </c>
+      <c r="C838" s="8">
+        <v>46039</v>
+      </c>
+      <c r="D838" s="9"/>
+      <c r="E838" s="10"/>
+      <c r="F838" s="11"/>
+      <c r="G838" s="12"/>
+      <c r="H838" s="11"/>
+      <c r="I838" s="12"/>
+      <c r="J838" s="11"/>
+      <c r="K838" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:E833">
-    <cfRule type="expression" dxfId="483" priority="708">
+  <conditionalFormatting sqref="B4:E838">
+    <cfRule type="expression" dxfId="484" priority="709">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:M683 B684:K833">
-    <cfRule type="expression" dxfId="482" priority="709">
+  <conditionalFormatting sqref="B4:M683 B684:K838">
+    <cfRule type="expression" dxfId="483" priority="710">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E678">
-    <cfRule type="expression" dxfId="481" priority="699">
+    <cfRule type="expression" dxfId="482" priority="700">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E693:E694">
-    <cfRule type="expression" dxfId="480" priority="686">
+    <cfRule type="expression" dxfId="481" priority="687">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E702">
-    <cfRule type="expression" dxfId="479" priority="673">
+    <cfRule type="expression" dxfId="480" priority="674">
       <formula>$C702=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E707">
-    <cfRule type="expression" dxfId="478" priority="669">
+    <cfRule type="expression" dxfId="479" priority="670">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709:E710">
-    <cfRule type="expression" dxfId="477" priority="661">
+    <cfRule type="expression" dxfId="478" priority="662">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E715">
-    <cfRule type="expression" dxfId="476" priority="657">
+    <cfRule type="expression" dxfId="477" priority="658">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E717:E718">
-    <cfRule type="expression" dxfId="475" priority="645">
+    <cfRule type="expression" dxfId="476" priority="646">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E723">
-    <cfRule type="expression" dxfId="474" priority="634">
+    <cfRule type="expression" dxfId="475" priority="635">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E725:E726">
-    <cfRule type="expression" dxfId="473" priority="611">
+    <cfRule type="expression" dxfId="474" priority="612">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E731">
-    <cfRule type="expression" dxfId="472" priority="599">
+    <cfRule type="expression" dxfId="473" priority="600">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E733:E734">
-    <cfRule type="expression" dxfId="471" priority="566">
+    <cfRule type="expression" dxfId="472" priority="567">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739">
-    <cfRule type="expression" dxfId="470" priority="534">
+    <cfRule type="expression" dxfId="471" priority="535">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E741:E742">
-    <cfRule type="expression" dxfId="469" priority="489">
+    <cfRule type="expression" dxfId="470" priority="490">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E747:E748">
-    <cfRule type="expression" dxfId="468" priority="426">
+    <cfRule type="expression" dxfId="469" priority="427">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E750">
-    <cfRule type="expression" dxfId="467" priority="410">
+    <cfRule type="expression" dxfId="468" priority="411">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="466" priority="384">
+    <cfRule type="expression" dxfId="467" priority="385">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E758">
-    <cfRule type="expression" dxfId="465" priority="336">
+    <cfRule type="expression" dxfId="466" priority="337">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E763">
-    <cfRule type="expression" dxfId="464" priority="309">
+    <cfRule type="expression" dxfId="465" priority="310">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E765:E766">
-    <cfRule type="expression" dxfId="463" priority="256">
+    <cfRule type="expression" dxfId="464" priority="257">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E771">
-    <cfRule type="expression" dxfId="462" priority="211">
+    <cfRule type="expression" dxfId="463" priority="212">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="461" priority="722">
+    <cfRule type="expression" dxfId="462" priority="723">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G661">
-    <cfRule type="expression" dxfId="460" priority="706">
+    <cfRule type="expression" dxfId="461" priority="707">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G670">
-    <cfRule type="expression" dxfId="459" priority="703">
+    <cfRule type="expression" dxfId="460" priority="704">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G678">
-    <cfRule type="expression" dxfId="458" priority="700">
+    <cfRule type="expression" dxfId="459" priority="701">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G686">
-    <cfRule type="expression" dxfId="457" priority="696">
+    <cfRule type="expression" dxfId="458" priority="697">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G691">
-    <cfRule type="expression" dxfId="456" priority="693">
+    <cfRule type="expression" dxfId="457" priority="694">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G693:G694">
-    <cfRule type="expression" dxfId="455" priority="685">
+    <cfRule type="expression" dxfId="456" priority="686">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G699">
-    <cfRule type="expression" dxfId="454" priority="682">
+    <cfRule type="expression" dxfId="455" priority="683">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701:G702">
-    <cfRule type="expression" dxfId="453" priority="674">
+    <cfRule type="expression" dxfId="454" priority="675">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G707">
-    <cfRule type="expression" dxfId="452" priority="670">
+    <cfRule type="expression" dxfId="453" priority="671">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G709:G710">
-    <cfRule type="expression" dxfId="451" priority="660">
+    <cfRule type="expression" dxfId="452" priority="661">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G715">
-    <cfRule type="expression" dxfId="450" priority="655">
+    <cfRule type="expression" dxfId="451" priority="656">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G717:G718">
-    <cfRule type="expression" dxfId="449" priority="642">
+    <cfRule type="expression" dxfId="450" priority="643">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G723">
-    <cfRule type="expression" dxfId="448" priority="631">
+    <cfRule type="expression" dxfId="449" priority="632">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G725:G726">
-    <cfRule type="expression" dxfId="447" priority="608">
+    <cfRule type="expression" dxfId="448" priority="609">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G731">
-    <cfRule type="expression" dxfId="446" priority="595">
+    <cfRule type="expression" dxfId="447" priority="596">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G733:G734">
-    <cfRule type="expression" dxfId="445" priority="560">
+    <cfRule type="expression" dxfId="446" priority="561">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739">
-    <cfRule type="expression" dxfId="444" priority="529">
+    <cfRule type="expression" dxfId="445" priority="530">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G741:G742">
-    <cfRule type="expression" dxfId="443" priority="483">
+    <cfRule type="expression" dxfId="444" priority="484">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G747">
-    <cfRule type="expression" dxfId="442" priority="446">
+    <cfRule type="expression" dxfId="443" priority="447">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="441" priority="403">
+    <cfRule type="expression" dxfId="442" priority="404">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="440" priority="378">
+    <cfRule type="expression" dxfId="441" priority="379">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G758">
-    <cfRule type="expression" dxfId="439" priority="329">
+    <cfRule type="expression" dxfId="440" priority="330">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763">
-    <cfRule type="expression" dxfId="438" priority="302">
+    <cfRule type="expression" dxfId="439" priority="303">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G765:G766">
-    <cfRule type="expression" dxfId="437" priority="243">
+    <cfRule type="expression" dxfId="438" priority="244">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G771">
-    <cfRule type="expression" dxfId="436" priority="204">
+    <cfRule type="expression" dxfId="437" priority="205">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H128:I129">
-    <cfRule type="expression" dxfId="435" priority="725">
+    <cfRule type="expression" dxfId="436" priority="726">
       <formula>$C128=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="expression" dxfId="434" priority="723">
+    <cfRule type="expression" dxfId="435" priority="724">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I661">
-    <cfRule type="expression" dxfId="433" priority="705">
+    <cfRule type="expression" dxfId="434" priority="706">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670">
-    <cfRule type="expression" dxfId="432" priority="702">
+    <cfRule type="expression" dxfId="433" priority="703">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I678">
-    <cfRule type="expression" dxfId="431" priority="698">
+    <cfRule type="expression" dxfId="432" priority="699">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I686">
-    <cfRule type="expression" dxfId="430" priority="695">
+    <cfRule type="expression" dxfId="431" priority="696">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I691">
-    <cfRule type="expression" dxfId="429" priority="692">
+    <cfRule type="expression" dxfId="430" priority="693">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I693:I694">
-    <cfRule type="expression" dxfId="428" priority="684">
+    <cfRule type="expression" dxfId="429" priority="685">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I699">
-    <cfRule type="expression" dxfId="427" priority="681">
+    <cfRule type="expression" dxfId="428" priority="682">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I701:I702">
-    <cfRule type="expression" dxfId="426" priority="675">
+    <cfRule type="expression" dxfId="427" priority="676">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I707">
-    <cfRule type="expression" dxfId="425" priority="672">
+    <cfRule type="expression" dxfId="426" priority="673">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I709:I710">
-    <cfRule type="expression" dxfId="424" priority="659">
+    <cfRule type="expression" dxfId="425" priority="660">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I715">
-    <cfRule type="expression" dxfId="423" priority="653">
+    <cfRule type="expression" dxfId="424" priority="654">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I717:I718">
-    <cfRule type="expression" dxfId="422" priority="639">
+    <cfRule type="expression" dxfId="423" priority="640">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I723:I726">
-    <cfRule type="expression" dxfId="421" priority="605">
+    <cfRule type="expression" dxfId="422" priority="606">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I731:I734">
-    <cfRule type="expression" dxfId="420" priority="554">
+    <cfRule type="expression" dxfId="421" priority="555">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I736">
-    <cfRule type="expression" dxfId="419" priority="543">
+    <cfRule type="expression" dxfId="420" priority="544">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I742">
-    <cfRule type="expression" dxfId="418" priority="477">
+    <cfRule type="expression" dxfId="419" priority="478">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I744">
-    <cfRule type="expression" dxfId="417" priority="461">
+    <cfRule type="expression" dxfId="418" priority="462">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I747:I748">
-    <cfRule type="expression" dxfId="416" priority="431">
+    <cfRule type="expression" dxfId="417" priority="432">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I750">
-    <cfRule type="expression" dxfId="415" priority="396">
+    <cfRule type="expression" dxfId="416" priority="397">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755:I756">
-    <cfRule type="expression" dxfId="414" priority="360">
+    <cfRule type="expression" dxfId="415" priority="361">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I758">
-    <cfRule type="expression" dxfId="413" priority="322">
+    <cfRule type="expression" dxfId="414" priority="323">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I763">
-    <cfRule type="expression" dxfId="412" priority="295">
+    <cfRule type="expression" dxfId="413" priority="296">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I765:I766">
-    <cfRule type="expression" dxfId="411" priority="230">
+    <cfRule type="expression" dxfId="412" priority="231">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I771:I772">
-    <cfRule type="expression" dxfId="410" priority="197">
+    <cfRule type="expression" dxfId="411" priority="198">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="409" priority="724">
+    <cfRule type="expression" dxfId="410" priority="725">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K661">
-    <cfRule type="expression" dxfId="408" priority="704">
+    <cfRule type="expression" dxfId="409" priority="705">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K670">
-    <cfRule type="expression" dxfId="407" priority="701">
+    <cfRule type="expression" dxfId="408" priority="702">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K678">
-    <cfRule type="expression" dxfId="406" priority="697">
+    <cfRule type="expression" dxfId="407" priority="698">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K686">
-    <cfRule type="expression" dxfId="405" priority="694">
+    <cfRule type="expression" dxfId="406" priority="695">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K691">
-    <cfRule type="expression" dxfId="404" priority="691">
+    <cfRule type="expression" dxfId="405" priority="692">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K693:K694">
-    <cfRule type="expression" dxfId="403" priority="683">
+    <cfRule type="expression" dxfId="404" priority="684">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K699">
-    <cfRule type="expression" dxfId="402" priority="680">
+    <cfRule type="expression" dxfId="403" priority="681">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701:K702">
-    <cfRule type="expression" dxfId="401" priority="676">
+    <cfRule type="expression" dxfId="402" priority="677">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K707">
-    <cfRule type="expression" dxfId="400" priority="671">
+    <cfRule type="expression" dxfId="401" priority="672">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K709:K710">
-    <cfRule type="expression" dxfId="399" priority="658">
+    <cfRule type="expression" dxfId="400" priority="659">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K715:K718">
-    <cfRule type="expression" dxfId="398" priority="636">
+    <cfRule type="expression" dxfId="399" priority="637">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K723">
-    <cfRule type="expression" dxfId="397" priority="625">
+    <cfRule type="expression" dxfId="398" priority="626">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K725:K726">
-    <cfRule type="expression" dxfId="396" priority="602">
+    <cfRule type="expression" dxfId="397" priority="603">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K731">
-    <cfRule type="expression" dxfId="395" priority="587">
+    <cfRule type="expression" dxfId="396" priority="588">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K733:K734">
-    <cfRule type="expression" dxfId="394" priority="548">
+    <cfRule type="expression" dxfId="395" priority="549">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K736">
-    <cfRule type="expression" dxfId="393" priority="538">
+    <cfRule type="expression" dxfId="394" priority="539">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K742">
-    <cfRule type="expression" dxfId="392" priority="466">
+    <cfRule type="expression" dxfId="393" priority="467">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K744">
-    <cfRule type="expression" dxfId="391" priority="456">
+    <cfRule type="expression" dxfId="392" priority="457">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K747">
-    <cfRule type="expression" dxfId="390" priority="436">
+    <cfRule type="expression" dxfId="391" priority="437">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K749:K750">
-    <cfRule type="expression" dxfId="389" priority="389">
+    <cfRule type="expression" dxfId="390" priority="390">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755:K756">
-    <cfRule type="expression" dxfId="388" priority="354">
+    <cfRule type="expression" dxfId="389" priority="355">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K758">
-    <cfRule type="expression" dxfId="387" priority="315">
+    <cfRule type="expression" dxfId="388" priority="316">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K763:K764">
-    <cfRule type="expression" dxfId="386" priority="288">
+    <cfRule type="expression" dxfId="387" priority="289">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766">
-    <cfRule type="expression" dxfId="385" priority="217">
+    <cfRule type="expression" dxfId="386" priority="218">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K771">
-    <cfRule type="expression" dxfId="384" priority="190">
+    <cfRule type="expression" dxfId="385" priority="191">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
+    <cfRule type="expression" dxfId="384" priority="190">
+      <formula>$C773=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G773">
     <cfRule type="expression" dxfId="383" priority="189">
       <formula>$C773=TODAY()</formula>
     </cfRule>
@@ -28583,7 +28714,7 @@
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G773">
+  <conditionalFormatting sqref="I773">
     <cfRule type="expression" dxfId="381" priority="187">
       <formula>$C773=TODAY()</formula>
     </cfRule>
@@ -28593,7 +28724,7 @@
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I773">
+  <conditionalFormatting sqref="K773">
     <cfRule type="expression" dxfId="379" priority="185">
       <formula>$C773=TODAY()</formula>
     </cfRule>
@@ -28603,29 +28734,29 @@
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K773">
+  <conditionalFormatting sqref="E774">
     <cfRule type="expression" dxfId="377" priority="183">
-      <formula>$C773=TODAY()</formula>
+      <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E774">
+  <conditionalFormatting sqref="G774">
     <cfRule type="expression" dxfId="376" priority="182">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G774">
+  <conditionalFormatting sqref="I774">
     <cfRule type="expression" dxfId="375" priority="181">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I774">
+  <conditionalFormatting sqref="K774">
     <cfRule type="expression" dxfId="374" priority="180">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K774">
+  <conditionalFormatting sqref="I776">
     <cfRule type="expression" dxfId="373" priority="179">
-      <formula>$C774=TODAY()</formula>
+      <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
@@ -28633,7 +28764,7 @@
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I776">
+  <conditionalFormatting sqref="K776">
     <cfRule type="expression" dxfId="371" priority="177">
       <formula>$C776=TODAY()</formula>
     </cfRule>
@@ -28643,12 +28774,12 @@
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K776">
+  <conditionalFormatting sqref="E779">
     <cfRule type="expression" dxfId="369" priority="175">
-      <formula>$C776=TODAY()</formula>
+      <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E779">
+  <conditionalFormatting sqref="G779">
     <cfRule type="expression" dxfId="368" priority="174">
       <formula>$C779=TODAY()</formula>
     </cfRule>
@@ -28658,7 +28789,7 @@
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G779">
+  <conditionalFormatting sqref="I779">
     <cfRule type="expression" dxfId="366" priority="172">
       <formula>$C779=TODAY()</formula>
     </cfRule>
@@ -28668,7 +28799,7 @@
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I779">
+  <conditionalFormatting sqref="K779">
     <cfRule type="expression" dxfId="364" priority="170">
       <formula>$C779=TODAY()</formula>
     </cfRule>
@@ -28678,9 +28809,9 @@
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K779">
+  <conditionalFormatting sqref="I780">
     <cfRule type="expression" dxfId="362" priority="168">
-      <formula>$C779=TODAY()</formula>
+      <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
@@ -28688,7 +28819,7 @@
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I780">
+  <conditionalFormatting sqref="K780">
     <cfRule type="expression" dxfId="360" priority="166">
       <formula>$C780=TODAY()</formula>
     </cfRule>
@@ -28698,9 +28829,9 @@
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K780">
+  <conditionalFormatting sqref="I781:I782">
     <cfRule type="expression" dxfId="358" priority="164">
-      <formula>$C780=TODAY()</formula>
+      <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
@@ -28708,7 +28839,7 @@
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I781:I782">
+  <conditionalFormatting sqref="G781:G782">
     <cfRule type="expression" dxfId="356" priority="162">
       <formula>$C781=TODAY()</formula>
     </cfRule>
@@ -28718,7 +28849,7 @@
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G781:G782">
+  <conditionalFormatting sqref="E781:E782">
     <cfRule type="expression" dxfId="354" priority="160">
       <formula>$C781=TODAY()</formula>
     </cfRule>
@@ -28728,12 +28859,12 @@
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E781:E782">
+  <conditionalFormatting sqref="E782">
     <cfRule type="expression" dxfId="352" priority="158">
-      <formula>$C781=TODAY()</formula>
+      <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E782">
+  <conditionalFormatting sqref="G782">
     <cfRule type="expression" dxfId="351" priority="157">
       <formula>$C782=TODAY()</formula>
     </cfRule>
@@ -28743,7 +28874,7 @@
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G782">
+  <conditionalFormatting sqref="I782">
     <cfRule type="expression" dxfId="349" priority="155">
       <formula>$C782=TODAY()</formula>
     </cfRule>
@@ -28753,7 +28884,7 @@
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I782">
+  <conditionalFormatting sqref="K782">
     <cfRule type="expression" dxfId="347" priority="153">
       <formula>$C782=TODAY()</formula>
     </cfRule>
@@ -28763,9 +28894,9 @@
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K782">
+  <conditionalFormatting sqref="I784">
     <cfRule type="expression" dxfId="345" priority="151">
-      <formula>$C782=TODAY()</formula>
+      <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
@@ -28773,7 +28904,7 @@
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I784">
+  <conditionalFormatting sqref="K784">
     <cfRule type="expression" dxfId="343" priority="149">
       <formula>$C784=TODAY()</formula>
     </cfRule>
@@ -28783,9 +28914,9 @@
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K784">
+  <conditionalFormatting sqref="E787">
     <cfRule type="expression" dxfId="341" priority="147">
-      <formula>$C784=TODAY()</formula>
+      <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
@@ -28793,7 +28924,7 @@
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E787">
+  <conditionalFormatting sqref="G787">
     <cfRule type="expression" dxfId="339" priority="145">
       <formula>$C787=TODAY()</formula>
     </cfRule>
@@ -28808,7 +28939,7 @@
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G787">
+  <conditionalFormatting sqref="I787:I788">
     <cfRule type="expression" dxfId="336" priority="142">
       <formula>$C787=TODAY()</formula>
     </cfRule>
@@ -28823,7 +28954,7 @@
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I787:I788">
+  <conditionalFormatting sqref="K787">
     <cfRule type="expression" dxfId="333" priority="139">
       <formula>$C787=TODAY()</formula>
     </cfRule>
@@ -28838,13 +28969,13 @@
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="330" priority="136">
-      <formula>$C787=TODAY()</formula>
+  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
+    <cfRule type="expression" dxfId="330" priority="134">
+      <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
-    <cfRule type="expression" dxfId="329" priority="133">
+  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
+    <cfRule type="expression" dxfId="329" priority="136">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28853,9 +28984,9 @@
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="327" priority="134">
-      <formula>$C789=TODAY()</formula>
+  <conditionalFormatting sqref="K790 I790 G790 E790">
+    <cfRule type="expression" dxfId="327" priority="133">
+      <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
@@ -28868,18 +28999,18 @@
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K790 I790 G790 E790">
+  <conditionalFormatting sqref="K790 I790 G790">
     <cfRule type="expression" dxfId="324" priority="130">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K790 I790 G790">
-    <cfRule type="expression" dxfId="323" priority="129">
-      <formula>$C790=TODAY()</formula>
+  <conditionalFormatting sqref="I792">
+    <cfRule type="expression" dxfId="323" priority="127">
+      <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="322" priority="126">
+    <cfRule type="expression" dxfId="322" priority="129">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28888,13 +29019,13 @@
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="320" priority="127">
+  <conditionalFormatting sqref="K792">
+    <cfRule type="expression" dxfId="320" priority="124">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="319" priority="123">
+    <cfRule type="expression" dxfId="319" priority="126">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28903,9 +29034,9 @@
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="317" priority="124">
-      <formula>$C792=TODAY()</formula>
+  <conditionalFormatting sqref="E795">
+    <cfRule type="expression" dxfId="317" priority="123">
+      <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
@@ -28913,7 +29044,7 @@
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E795">
+  <conditionalFormatting sqref="G795">
     <cfRule type="expression" dxfId="315" priority="121">
       <formula>$C795=TODAY()</formula>
     </cfRule>
@@ -28928,7 +29059,7 @@
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G795">
+  <conditionalFormatting sqref="I795:I796">
     <cfRule type="expression" dxfId="312" priority="118">
       <formula>$C795=TODAY()</formula>
     </cfRule>
@@ -28943,7 +29074,7 @@
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I795:I796">
+  <conditionalFormatting sqref="K795">
     <cfRule type="expression" dxfId="309" priority="115">
       <formula>$C795=TODAY()</formula>
     </cfRule>
@@ -28958,9 +29089,9 @@
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K795">
+  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
     <cfRule type="expression" dxfId="306" priority="112">
-      <formula>$C795=TODAY()</formula>
+      <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
@@ -28973,9 +29104,9 @@
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
+  <conditionalFormatting sqref="K798 I798 G798 E798">
     <cfRule type="expression" dxfId="303" priority="109">
-      <formula>$C797=TODAY()</formula>
+      <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
@@ -28998,14 +29129,14 @@
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798 E798">
+  <conditionalFormatting sqref="K798 I798 G798">
     <cfRule type="expression" dxfId="298" priority="104">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798">
+  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
     <cfRule type="expression" dxfId="297" priority="103">
-      <formula>$C798=TODAY()</formula>
+      <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
@@ -29018,14 +29149,14 @@
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
+  <conditionalFormatting sqref="I803 G803 K803:K805">
     <cfRule type="expression" dxfId="294" priority="100">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I803 G803 K803:K805">
+  <conditionalFormatting sqref="E805:E806">
     <cfRule type="expression" dxfId="293" priority="99">
-      <formula>$C803=TODAY()</formula>
+      <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
@@ -29038,9 +29169,9 @@
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E805:E806">
+  <conditionalFormatting sqref="E806">
     <cfRule type="expression" dxfId="290" priority="96">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
@@ -29063,9 +29194,9 @@
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
+  <conditionalFormatting sqref="G805:G806">
     <cfRule type="expression" dxfId="285" priority="91">
-      <formula>$C806=TODAY()</formula>
+      <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
@@ -29083,9 +29214,9 @@
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="281" priority="87">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
@@ -29108,9 +29239,9 @@
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="I805:I806">
     <cfRule type="expression" dxfId="276" priority="82">
-      <formula>$C806=TODAY()</formula>
+      <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
@@ -29128,9 +29259,9 @@
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+  <conditionalFormatting sqref="I806">
     <cfRule type="expression" dxfId="272" priority="78">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
@@ -29153,7 +29284,7 @@
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="267" priority="73">
       <formula>$C806=TODAY()</formula>
     </cfRule>
@@ -29198,9 +29329,9 @@
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+  <conditionalFormatting sqref="I808">
     <cfRule type="expression" dxfId="258" priority="64">
-      <formula>$C806=TODAY()</formula>
+      <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
@@ -29218,7 +29349,7 @@
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I808">
+  <conditionalFormatting sqref="K808">
     <cfRule type="expression" dxfId="254" priority="60">
       <formula>$C808=TODAY()</formula>
     </cfRule>
@@ -29238,9 +29369,9 @@
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K808">
+  <conditionalFormatting sqref="E811">
     <cfRule type="expression" dxfId="250" priority="56">
-      <formula>$C808=TODAY()</formula>
+      <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
@@ -29253,7 +29384,7 @@
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E811">
+  <conditionalFormatting sqref="G811">
     <cfRule type="expression" dxfId="247" priority="53">
       <formula>$C811=TODAY()</formula>
     </cfRule>
@@ -29273,7 +29404,7 @@
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+  <conditionalFormatting sqref="I811:I812">
     <cfRule type="expression" dxfId="243" priority="49">
       <formula>$C811=TODAY()</formula>
     </cfRule>
@@ -29293,7 +29424,7 @@
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="239" priority="45">
       <formula>$C811=TODAY()</formula>
     </cfRule>
@@ -29313,9 +29444,9 @@
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
+  <conditionalFormatting sqref="E813:E814">
     <cfRule type="expression" dxfId="235" priority="41">
-      <formula>$C811=TODAY()</formula>
+      <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
@@ -29328,9 +29459,9 @@
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E813:E814">
+  <conditionalFormatting sqref="E814">
     <cfRule type="expression" dxfId="232" priority="38">
-      <formula>$C813=TODAY()</formula>
+      <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
@@ -29353,9 +29484,9 @@
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
+  <conditionalFormatting sqref="G813:G814">
     <cfRule type="expression" dxfId="227" priority="33">
-      <formula>$C814=TODAY()</formula>
+      <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
@@ -29373,9 +29504,9 @@
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="223" priority="29">
-      <formula>$C813=TODAY()</formula>
+      <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
@@ -29398,9 +29529,9 @@
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
+  <conditionalFormatting sqref="I813:I814">
     <cfRule type="expression" dxfId="218" priority="24">
-      <formula>$C814=TODAY()</formula>
+      <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
@@ -29418,9 +29549,9 @@
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
+  <conditionalFormatting sqref="I814">
     <cfRule type="expression" dxfId="214" priority="20">
-      <formula>$C813=TODAY()</formula>
+      <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
@@ -29443,9 +29574,9 @@
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+  <conditionalFormatting sqref="K813:K814">
     <cfRule type="expression" dxfId="209" priority="15">
-      <formula>$C814=TODAY()</formula>
+      <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
@@ -29463,9 +29594,9 @@
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
+  <conditionalFormatting sqref="K814">
     <cfRule type="expression" dxfId="205" priority="11">
-      <formula>$C813=TODAY()</formula>
+      <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
@@ -29488,9 +29619,9 @@
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
+  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
     <cfRule type="expression" dxfId="200" priority="6">
-      <formula>$C814=TODAY()</formula>
+      <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
@@ -29503,19 +29634,19 @@
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
+  <conditionalFormatting sqref="G826 I826:I829 K826:K829">
     <cfRule type="expression" dxfId="197" priority="3">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G826 I826:I829 K826:K829">
+  <conditionalFormatting sqref="K829 I829 G829">
     <cfRule type="expression" dxfId="196" priority="2">
-      <formula>$C826=TODAY()</formula>
+      <formula>$C829=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K829 I829 G829">
+  <conditionalFormatting sqref="K834 I834 G834">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$C829=TODAY()</formula>
+      <formula>$C834=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
+++ b/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122D783-D101-471A-82A9-D7CF8CAF65C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66445EEA-A937-4736-B62F-7E99689C5E9F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3398" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="33">
   <si>
     <t>План поставок ПОКОМ</t>
   </si>
@@ -435,7 +435,77 @@
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Обычный 2 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="485">
+  <dxfs count="495">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4212,7 +4282,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMD838"/>
+  <dimension ref="A1:AMD839"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
@@ -28080,7 +28150,7 @@
         <v>830</v>
       </c>
       <c r="B834" s="7" t="str">
-        <f t="shared" ref="B834:B838" si="135">IF(C834&lt;&gt;"",TEXT(C834,"ДДД"),"")</f>
+        <f t="shared" ref="B834:B839" si="135">IF(C834&lt;&gt;"",TEXT(C834,"ДДД"),"")</f>
         <v>Вт</v>
       </c>
       <c r="C834" s="8">
@@ -28125,14 +28195,22 @@
       <c r="C835" s="8">
         <v>46036</v>
       </c>
-      <c r="D835" s="9"/>
-      <c r="E835" s="10"/>
+      <c r="D835" s="9">
+        <v>2200</v>
+      </c>
+      <c r="E835" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="F835" s="11"/>
       <c r="G835" s="12"/>
       <c r="H835" s="11"/>
       <c r="I835" s="12"/>
-      <c r="J835" s="11"/>
-      <c r="K835" s="12"/>
+      <c r="J835" s="11">
+        <v>7000</v>
+      </c>
+      <c r="K835" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="836" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A836" s="1">
@@ -28147,10 +28225,18 @@
       </c>
       <c r="D836" s="9"/>
       <c r="E836" s="10"/>
-      <c r="F836" s="11"/>
-      <c r="G836" s="12"/>
-      <c r="H836" s="11"/>
-      <c r="I836" s="12"/>
+      <c r="F836" s="11">
+        <v>2000</v>
+      </c>
+      <c r="G836" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H836" s="11">
+        <v>13700</v>
+      </c>
+      <c r="I836" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="J836" s="11"/>
       <c r="K836" s="12"/>
     </row>
@@ -28159,20 +28245,37 @@
         <v>833</v>
       </c>
       <c r="B837" s="7" t="str">
-        <f t="shared" si="135"/>
-        <v>Пт</v>
+        <f t="shared" ref="B837" si="136">IF(C837&lt;&gt;"",TEXT(C837,"ДДД"),"")</f>
+        <v>Чт</v>
       </c>
       <c r="C837" s="8">
-        <v>46038</v>
-      </c>
-      <c r="D837" s="9"/>
-      <c r="E837" s="10"/>
-      <c r="F837" s="11"/>
-      <c r="G837" s="12"/>
-      <c r="H837" s="11"/>
-      <c r="I837" s="12"/>
-      <c r="J837" s="11"/>
-      <c r="K837" s="12"/>
+        <v>46037</v>
+      </c>
+      <c r="D837" s="9">
+        <v>8900</v>
+      </c>
+      <c r="E837" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F837" s="11">
+        <f>3400+1500</f>
+        <v>4900</v>
+      </c>
+      <c r="G837" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H837" s="11">
+        <v>4400</v>
+      </c>
+      <c r="I837" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J837" s="11">
+        <v>6700</v>
+      </c>
+      <c r="K837" s="10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="838" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A838" s="1">
@@ -28180,10 +28283,10 @@
       </c>
       <c r="B838" s="7" t="str">
         <f t="shared" si="135"/>
-        <v>Сб</v>
+        <v>Пт</v>
       </c>
       <c r="C838" s="8">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="D838" s="9"/>
       <c r="E838" s="10"/>
@@ -28194,1459 +28297,1489 @@
       <c r="J838" s="11"/>
       <c r="K838" s="12"/>
     </row>
+    <row r="839" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A839" s="1">
+        <v>835</v>
+      </c>
+      <c r="B839" s="7" t="str">
+        <f t="shared" si="135"/>
+        <v>Сб</v>
+      </c>
+      <c r="C839" s="8">
+        <v>46039</v>
+      </c>
+      <c r="D839" s="9"/>
+      <c r="E839" s="10"/>
+      <c r="F839" s="11"/>
+      <c r="G839" s="12"/>
+      <c r="H839" s="11"/>
+      <c r="I839" s="12"/>
+      <c r="J839" s="11"/>
+      <c r="K839" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:E838">
-    <cfRule type="expression" dxfId="484" priority="709">
+  <conditionalFormatting sqref="B4:E839">
+    <cfRule type="expression" dxfId="494" priority="711">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:M683 B684:K838">
-    <cfRule type="expression" dxfId="483" priority="710">
+  <conditionalFormatting sqref="B4:M683 B684:K839">
+    <cfRule type="expression" dxfId="493" priority="712">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E678">
-    <cfRule type="expression" dxfId="482" priority="700">
+    <cfRule type="expression" dxfId="492" priority="702">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E693:E694">
-    <cfRule type="expression" dxfId="481" priority="687">
+    <cfRule type="expression" dxfId="491" priority="689">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E702">
-    <cfRule type="expression" dxfId="480" priority="674">
+    <cfRule type="expression" dxfId="490" priority="676">
       <formula>$C702=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E707">
-    <cfRule type="expression" dxfId="479" priority="670">
+    <cfRule type="expression" dxfId="489" priority="672">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709:E710">
-    <cfRule type="expression" dxfId="478" priority="662">
+    <cfRule type="expression" dxfId="488" priority="664">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E715">
-    <cfRule type="expression" dxfId="477" priority="658">
+    <cfRule type="expression" dxfId="487" priority="660">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E717:E718">
-    <cfRule type="expression" dxfId="476" priority="646">
+    <cfRule type="expression" dxfId="486" priority="648">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E723">
-    <cfRule type="expression" dxfId="475" priority="635">
+    <cfRule type="expression" dxfId="485" priority="637">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E725:E726">
-    <cfRule type="expression" dxfId="474" priority="612">
+    <cfRule type="expression" dxfId="484" priority="614">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E731">
-    <cfRule type="expression" dxfId="473" priority="600">
+    <cfRule type="expression" dxfId="483" priority="602">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E733:E734">
-    <cfRule type="expression" dxfId="472" priority="567">
+    <cfRule type="expression" dxfId="482" priority="569">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739">
-    <cfRule type="expression" dxfId="471" priority="535">
+    <cfRule type="expression" dxfId="481" priority="537">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E741:E742">
-    <cfRule type="expression" dxfId="470" priority="490">
+    <cfRule type="expression" dxfId="480" priority="492">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E747:E748">
-    <cfRule type="expression" dxfId="469" priority="427">
+    <cfRule type="expression" dxfId="479" priority="429">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E750">
-    <cfRule type="expression" dxfId="468" priority="411">
+    <cfRule type="expression" dxfId="478" priority="413">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="467" priority="385">
+    <cfRule type="expression" dxfId="477" priority="387">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E758">
-    <cfRule type="expression" dxfId="466" priority="337">
+    <cfRule type="expression" dxfId="476" priority="339">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E763">
-    <cfRule type="expression" dxfId="465" priority="310">
+    <cfRule type="expression" dxfId="475" priority="312">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E765:E766">
-    <cfRule type="expression" dxfId="464" priority="257">
+    <cfRule type="expression" dxfId="474" priority="259">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E771">
-    <cfRule type="expression" dxfId="463" priority="212">
+    <cfRule type="expression" dxfId="473" priority="214">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="462" priority="723">
+    <cfRule type="expression" dxfId="472" priority="725">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G661">
-    <cfRule type="expression" dxfId="461" priority="707">
+    <cfRule type="expression" dxfId="471" priority="709">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G670">
-    <cfRule type="expression" dxfId="460" priority="704">
+    <cfRule type="expression" dxfId="470" priority="706">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G678">
-    <cfRule type="expression" dxfId="459" priority="701">
+    <cfRule type="expression" dxfId="469" priority="703">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G686">
-    <cfRule type="expression" dxfId="458" priority="697">
+    <cfRule type="expression" dxfId="468" priority="699">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G691">
-    <cfRule type="expression" dxfId="457" priority="694">
+    <cfRule type="expression" dxfId="467" priority="696">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G693:G694">
-    <cfRule type="expression" dxfId="456" priority="686">
+    <cfRule type="expression" dxfId="466" priority="688">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G699">
-    <cfRule type="expression" dxfId="455" priority="683">
+    <cfRule type="expression" dxfId="465" priority="685">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701:G702">
-    <cfRule type="expression" dxfId="454" priority="675">
+    <cfRule type="expression" dxfId="464" priority="677">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G707">
-    <cfRule type="expression" dxfId="453" priority="671">
+    <cfRule type="expression" dxfId="463" priority="673">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G709:G710">
-    <cfRule type="expression" dxfId="452" priority="661">
+    <cfRule type="expression" dxfId="462" priority="663">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G715">
-    <cfRule type="expression" dxfId="451" priority="656">
+    <cfRule type="expression" dxfId="461" priority="658">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G717:G718">
-    <cfRule type="expression" dxfId="450" priority="643">
+    <cfRule type="expression" dxfId="460" priority="645">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G723">
-    <cfRule type="expression" dxfId="449" priority="632">
+    <cfRule type="expression" dxfId="459" priority="634">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G725:G726">
-    <cfRule type="expression" dxfId="448" priority="609">
+    <cfRule type="expression" dxfId="458" priority="611">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G731">
-    <cfRule type="expression" dxfId="447" priority="596">
+    <cfRule type="expression" dxfId="457" priority="598">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G733:G734">
-    <cfRule type="expression" dxfId="446" priority="561">
+    <cfRule type="expression" dxfId="456" priority="563">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739">
-    <cfRule type="expression" dxfId="445" priority="530">
+    <cfRule type="expression" dxfId="455" priority="532">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G741:G742">
-    <cfRule type="expression" dxfId="444" priority="484">
+    <cfRule type="expression" dxfId="454" priority="486">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G747">
-    <cfRule type="expression" dxfId="443" priority="447">
+    <cfRule type="expression" dxfId="453" priority="449">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="442" priority="404">
+    <cfRule type="expression" dxfId="452" priority="406">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="441" priority="379">
+    <cfRule type="expression" dxfId="451" priority="381">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G758">
-    <cfRule type="expression" dxfId="440" priority="330">
+    <cfRule type="expression" dxfId="450" priority="332">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763">
-    <cfRule type="expression" dxfId="439" priority="303">
+    <cfRule type="expression" dxfId="449" priority="305">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G765:G766">
-    <cfRule type="expression" dxfId="438" priority="244">
+    <cfRule type="expression" dxfId="448" priority="246">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G771">
-    <cfRule type="expression" dxfId="437" priority="205">
+    <cfRule type="expression" dxfId="447" priority="207">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H128:I129">
-    <cfRule type="expression" dxfId="436" priority="726">
+    <cfRule type="expression" dxfId="446" priority="728">
       <formula>$C128=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="expression" dxfId="435" priority="724">
+    <cfRule type="expression" dxfId="445" priority="726">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I661">
-    <cfRule type="expression" dxfId="434" priority="706">
+    <cfRule type="expression" dxfId="444" priority="708">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670">
-    <cfRule type="expression" dxfId="433" priority="703">
+    <cfRule type="expression" dxfId="443" priority="705">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I678">
-    <cfRule type="expression" dxfId="432" priority="699">
+    <cfRule type="expression" dxfId="442" priority="701">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I686">
-    <cfRule type="expression" dxfId="431" priority="696">
+    <cfRule type="expression" dxfId="441" priority="698">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I691">
-    <cfRule type="expression" dxfId="430" priority="693">
+    <cfRule type="expression" dxfId="440" priority="695">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I693:I694">
-    <cfRule type="expression" dxfId="429" priority="685">
+    <cfRule type="expression" dxfId="439" priority="687">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I699">
-    <cfRule type="expression" dxfId="428" priority="682">
+    <cfRule type="expression" dxfId="438" priority="684">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I701:I702">
-    <cfRule type="expression" dxfId="427" priority="676">
+    <cfRule type="expression" dxfId="437" priority="678">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I707">
-    <cfRule type="expression" dxfId="426" priority="673">
+    <cfRule type="expression" dxfId="436" priority="675">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I709:I710">
-    <cfRule type="expression" dxfId="425" priority="660">
+    <cfRule type="expression" dxfId="435" priority="662">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I715">
-    <cfRule type="expression" dxfId="424" priority="654">
+    <cfRule type="expression" dxfId="434" priority="656">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I717:I718">
-    <cfRule type="expression" dxfId="423" priority="640">
+    <cfRule type="expression" dxfId="433" priority="642">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I723:I726">
-    <cfRule type="expression" dxfId="422" priority="606">
+    <cfRule type="expression" dxfId="432" priority="608">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I731:I734">
-    <cfRule type="expression" dxfId="421" priority="555">
+    <cfRule type="expression" dxfId="431" priority="557">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I736">
-    <cfRule type="expression" dxfId="420" priority="544">
+    <cfRule type="expression" dxfId="430" priority="546">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I742">
-    <cfRule type="expression" dxfId="419" priority="478">
+    <cfRule type="expression" dxfId="429" priority="480">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I744">
-    <cfRule type="expression" dxfId="418" priority="462">
+    <cfRule type="expression" dxfId="428" priority="464">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I747:I748">
-    <cfRule type="expression" dxfId="417" priority="432">
+    <cfRule type="expression" dxfId="427" priority="434">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I750">
-    <cfRule type="expression" dxfId="416" priority="397">
+    <cfRule type="expression" dxfId="426" priority="399">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755:I756">
-    <cfRule type="expression" dxfId="415" priority="361">
+    <cfRule type="expression" dxfId="425" priority="363">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I758">
-    <cfRule type="expression" dxfId="414" priority="323">
+    <cfRule type="expression" dxfId="424" priority="325">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I763">
-    <cfRule type="expression" dxfId="413" priority="296">
+    <cfRule type="expression" dxfId="423" priority="298">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I765:I766">
-    <cfRule type="expression" dxfId="412" priority="231">
+    <cfRule type="expression" dxfId="422" priority="233">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I771:I772">
-    <cfRule type="expression" dxfId="411" priority="198">
+    <cfRule type="expression" dxfId="421" priority="200">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="410" priority="725">
+    <cfRule type="expression" dxfId="420" priority="727">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K661">
-    <cfRule type="expression" dxfId="409" priority="705">
+    <cfRule type="expression" dxfId="419" priority="707">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K670">
-    <cfRule type="expression" dxfId="408" priority="702">
+    <cfRule type="expression" dxfId="418" priority="704">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K678">
-    <cfRule type="expression" dxfId="407" priority="698">
+    <cfRule type="expression" dxfId="417" priority="700">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K686">
-    <cfRule type="expression" dxfId="406" priority="695">
+    <cfRule type="expression" dxfId="416" priority="697">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K691">
-    <cfRule type="expression" dxfId="405" priority="692">
+    <cfRule type="expression" dxfId="415" priority="694">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K693:K694">
-    <cfRule type="expression" dxfId="404" priority="684">
+    <cfRule type="expression" dxfId="414" priority="686">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K699">
-    <cfRule type="expression" dxfId="403" priority="681">
+    <cfRule type="expression" dxfId="413" priority="683">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701:K702">
-    <cfRule type="expression" dxfId="402" priority="677">
+    <cfRule type="expression" dxfId="412" priority="679">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K707">
-    <cfRule type="expression" dxfId="401" priority="672">
+    <cfRule type="expression" dxfId="411" priority="674">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K709:K710">
-    <cfRule type="expression" dxfId="400" priority="659">
+    <cfRule type="expression" dxfId="410" priority="661">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K715:K718">
-    <cfRule type="expression" dxfId="399" priority="637">
+    <cfRule type="expression" dxfId="409" priority="639">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K723">
-    <cfRule type="expression" dxfId="398" priority="626">
+    <cfRule type="expression" dxfId="408" priority="628">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K725:K726">
-    <cfRule type="expression" dxfId="397" priority="603">
+    <cfRule type="expression" dxfId="407" priority="605">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K731">
-    <cfRule type="expression" dxfId="396" priority="588">
+    <cfRule type="expression" dxfId="406" priority="590">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K733:K734">
-    <cfRule type="expression" dxfId="395" priority="549">
+    <cfRule type="expression" dxfId="405" priority="551">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K736">
-    <cfRule type="expression" dxfId="394" priority="539">
+    <cfRule type="expression" dxfId="404" priority="541">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K742">
-    <cfRule type="expression" dxfId="393" priority="467">
+    <cfRule type="expression" dxfId="403" priority="469">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K744">
-    <cfRule type="expression" dxfId="392" priority="457">
+    <cfRule type="expression" dxfId="402" priority="459">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K747">
-    <cfRule type="expression" dxfId="391" priority="437">
+    <cfRule type="expression" dxfId="401" priority="439">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K749:K750">
-    <cfRule type="expression" dxfId="390" priority="390">
+    <cfRule type="expression" dxfId="400" priority="392">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755:K756">
-    <cfRule type="expression" dxfId="389" priority="355">
+    <cfRule type="expression" dxfId="399" priority="357">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K758">
-    <cfRule type="expression" dxfId="388" priority="316">
+    <cfRule type="expression" dxfId="398" priority="318">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K763:K764">
-    <cfRule type="expression" dxfId="387" priority="289">
+    <cfRule type="expression" dxfId="397" priority="291">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766">
-    <cfRule type="expression" dxfId="386" priority="218">
+    <cfRule type="expression" dxfId="396" priority="220">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K771">
-    <cfRule type="expression" dxfId="385" priority="191">
+    <cfRule type="expression" dxfId="395" priority="193">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="384" priority="190">
+    <cfRule type="expression" dxfId="394" priority="192">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="383" priority="189">
+    <cfRule type="expression" dxfId="393" priority="191">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="382" priority="188">
+    <cfRule type="expression" dxfId="392" priority="190">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="381" priority="187">
+    <cfRule type="expression" dxfId="391" priority="189">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="380" priority="186">
+    <cfRule type="expression" dxfId="390" priority="188">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="379" priority="185">
+    <cfRule type="expression" dxfId="389" priority="187">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="378" priority="184">
+    <cfRule type="expression" dxfId="388" priority="186">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E774">
-    <cfRule type="expression" dxfId="377" priority="183">
+    <cfRule type="expression" dxfId="387" priority="185">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G774">
-    <cfRule type="expression" dxfId="376" priority="182">
+    <cfRule type="expression" dxfId="386" priority="184">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I774">
-    <cfRule type="expression" dxfId="375" priority="181">
+    <cfRule type="expression" dxfId="385" priority="183">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K774">
-    <cfRule type="expression" dxfId="374" priority="180">
+    <cfRule type="expression" dxfId="384" priority="182">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="373" priority="179">
+    <cfRule type="expression" dxfId="383" priority="181">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="372" priority="178">
+    <cfRule type="expression" dxfId="382" priority="180">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="371" priority="177">
+    <cfRule type="expression" dxfId="381" priority="179">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="370" priority="176">
+    <cfRule type="expression" dxfId="380" priority="178">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E779">
-    <cfRule type="expression" dxfId="369" priority="175">
+    <cfRule type="expression" dxfId="379" priority="177">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="368" priority="174">
+    <cfRule type="expression" dxfId="378" priority="176">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="367" priority="173">
+    <cfRule type="expression" dxfId="377" priority="175">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="366" priority="172">
+    <cfRule type="expression" dxfId="376" priority="174">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="365" priority="171">
+    <cfRule type="expression" dxfId="375" priority="173">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="364" priority="170">
+    <cfRule type="expression" dxfId="374" priority="172">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="363" priority="169">
+    <cfRule type="expression" dxfId="373" priority="171">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="362" priority="168">
+    <cfRule type="expression" dxfId="372" priority="170">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="361" priority="167">
+    <cfRule type="expression" dxfId="371" priority="169">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="360" priority="166">
+    <cfRule type="expression" dxfId="370" priority="168">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="359" priority="165">
+    <cfRule type="expression" dxfId="369" priority="167">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="358" priority="164">
+    <cfRule type="expression" dxfId="368" priority="166">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="357" priority="163">
+    <cfRule type="expression" dxfId="367" priority="165">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="356" priority="162">
+    <cfRule type="expression" dxfId="366" priority="164">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="355" priority="161">
+    <cfRule type="expression" dxfId="365" priority="163">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="354" priority="160">
+    <cfRule type="expression" dxfId="364" priority="162">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="353" priority="159">
+    <cfRule type="expression" dxfId="363" priority="161">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="352" priority="158">
+    <cfRule type="expression" dxfId="362" priority="160">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="351" priority="157">
+    <cfRule type="expression" dxfId="361" priority="159">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="350" priority="156">
+    <cfRule type="expression" dxfId="360" priority="158">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="349" priority="155">
+    <cfRule type="expression" dxfId="359" priority="157">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="348" priority="154">
+    <cfRule type="expression" dxfId="358" priority="156">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="347" priority="153">
+    <cfRule type="expression" dxfId="357" priority="155">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="346" priority="152">
+    <cfRule type="expression" dxfId="356" priority="154">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="345" priority="151">
+    <cfRule type="expression" dxfId="355" priority="153">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="344" priority="150">
+    <cfRule type="expression" dxfId="354" priority="152">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="343" priority="149">
+    <cfRule type="expression" dxfId="353" priority="151">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="342" priority="148">
+    <cfRule type="expression" dxfId="352" priority="150">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
-    <cfRule type="expression" dxfId="341" priority="147">
+    <cfRule type="expression" dxfId="351" priority="149">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
-    <cfRule type="expression" dxfId="340" priority="146">
+    <cfRule type="expression" dxfId="350" priority="148">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="339" priority="145">
+    <cfRule type="expression" dxfId="349" priority="147">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="338" priority="144">
+    <cfRule type="expression" dxfId="348" priority="146">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="337" priority="143">
+    <cfRule type="expression" dxfId="347" priority="145">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="336" priority="142">
+    <cfRule type="expression" dxfId="346" priority="144">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="335" priority="141">
+    <cfRule type="expression" dxfId="345" priority="143">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="334" priority="140">
+    <cfRule type="expression" dxfId="344" priority="142">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="333" priority="139">
+    <cfRule type="expression" dxfId="343" priority="141">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="332" priority="138">
+    <cfRule type="expression" dxfId="342" priority="140">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="331" priority="137">
+    <cfRule type="expression" dxfId="341" priority="139">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
-    <cfRule type="expression" dxfId="330" priority="134">
+    <cfRule type="expression" dxfId="340" priority="136">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="329" priority="136">
+    <cfRule type="expression" dxfId="339" priority="138">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="328" priority="135">
+    <cfRule type="expression" dxfId="338" priority="137">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="327" priority="133">
+    <cfRule type="expression" dxfId="337" priority="135">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="326" priority="132">
+    <cfRule type="expression" dxfId="336" priority="134">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="325" priority="131">
+    <cfRule type="expression" dxfId="335" priority="133">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790">
-    <cfRule type="expression" dxfId="324" priority="130">
+    <cfRule type="expression" dxfId="334" priority="132">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="323" priority="127">
+    <cfRule type="expression" dxfId="333" priority="129">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="322" priority="129">
+    <cfRule type="expression" dxfId="332" priority="131">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="321" priority="128">
+    <cfRule type="expression" dxfId="331" priority="130">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="320" priority="124">
+    <cfRule type="expression" dxfId="330" priority="126">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="319" priority="126">
+    <cfRule type="expression" dxfId="329" priority="128">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="318" priority="125">
+    <cfRule type="expression" dxfId="328" priority="127">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
-    <cfRule type="expression" dxfId="317" priority="123">
+    <cfRule type="expression" dxfId="327" priority="125">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
-    <cfRule type="expression" dxfId="316" priority="122">
+    <cfRule type="expression" dxfId="326" priority="124">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="315" priority="121">
+    <cfRule type="expression" dxfId="325" priority="123">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="314" priority="120">
+    <cfRule type="expression" dxfId="324" priority="122">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="313" priority="119">
+    <cfRule type="expression" dxfId="323" priority="121">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="312" priority="118">
+    <cfRule type="expression" dxfId="322" priority="120">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="311" priority="117">
+    <cfRule type="expression" dxfId="321" priority="119">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="310" priority="116">
+    <cfRule type="expression" dxfId="320" priority="118">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="309" priority="115">
+    <cfRule type="expression" dxfId="319" priority="117">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="308" priority="114">
+    <cfRule type="expression" dxfId="318" priority="116">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="307" priority="113">
+    <cfRule type="expression" dxfId="317" priority="115">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="306" priority="112">
+    <cfRule type="expression" dxfId="316" priority="114">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="305" priority="111">
+    <cfRule type="expression" dxfId="315" priority="113">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="304" priority="110">
+    <cfRule type="expression" dxfId="314" priority="112">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="303" priority="109">
+    <cfRule type="expression" dxfId="313" priority="111">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="302" priority="108">
+    <cfRule type="expression" dxfId="312" priority="110">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="301" priority="107">
+    <cfRule type="expression" dxfId="311" priority="109">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="300" priority="106">
+    <cfRule type="expression" dxfId="310" priority="108">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="299" priority="105">
+    <cfRule type="expression" dxfId="309" priority="107">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798">
-    <cfRule type="expression" dxfId="298" priority="104">
+    <cfRule type="expression" dxfId="308" priority="106">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="297" priority="103">
+    <cfRule type="expression" dxfId="307" priority="105">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="296" priority="102">
+    <cfRule type="expression" dxfId="306" priority="104">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="295" priority="101">
+    <cfRule type="expression" dxfId="305" priority="103">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 K803:K805">
-    <cfRule type="expression" dxfId="294" priority="100">
+    <cfRule type="expression" dxfId="304" priority="102">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="293" priority="99">
+    <cfRule type="expression" dxfId="303" priority="101">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="292" priority="98">
+    <cfRule type="expression" dxfId="302" priority="100">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="291" priority="97">
+    <cfRule type="expression" dxfId="301" priority="99">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="290" priority="96">
+    <cfRule type="expression" dxfId="300" priority="98">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="289" priority="95">
+    <cfRule type="expression" dxfId="299" priority="97">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="288" priority="94">
+    <cfRule type="expression" dxfId="298" priority="96">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="287" priority="93">
+    <cfRule type="expression" dxfId="297" priority="95">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="286" priority="92">
+    <cfRule type="expression" dxfId="296" priority="94">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="285" priority="91">
+    <cfRule type="expression" dxfId="295" priority="93">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="284" priority="90">
+    <cfRule type="expression" dxfId="294" priority="92">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="283" priority="89">
+    <cfRule type="expression" dxfId="293" priority="91">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="282" priority="88">
+    <cfRule type="expression" dxfId="292" priority="90">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="281" priority="87">
+    <cfRule type="expression" dxfId="291" priority="89">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="280" priority="86">
+    <cfRule type="expression" dxfId="290" priority="88">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="279" priority="85">
+    <cfRule type="expression" dxfId="289" priority="87">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="278" priority="84">
+    <cfRule type="expression" dxfId="288" priority="86">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="277" priority="83">
+    <cfRule type="expression" dxfId="287" priority="85">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="276" priority="82">
+    <cfRule type="expression" dxfId="286" priority="84">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="275" priority="81">
+    <cfRule type="expression" dxfId="285" priority="83">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="274" priority="80">
+    <cfRule type="expression" dxfId="284" priority="82">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="273" priority="79">
+    <cfRule type="expression" dxfId="283" priority="81">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="272" priority="78">
+    <cfRule type="expression" dxfId="282" priority="80">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="271" priority="77">
+    <cfRule type="expression" dxfId="281" priority="79">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="270" priority="76">
+    <cfRule type="expression" dxfId="280" priority="78">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="269" priority="75">
+    <cfRule type="expression" dxfId="279" priority="77">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="268" priority="74">
+    <cfRule type="expression" dxfId="278" priority="76">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="267" priority="73">
+    <cfRule type="expression" dxfId="277" priority="75">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="266" priority="72">
+    <cfRule type="expression" dxfId="276" priority="74">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="265" priority="71">
+    <cfRule type="expression" dxfId="275" priority="73">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="264" priority="70">
+    <cfRule type="expression" dxfId="274" priority="72">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="263" priority="69">
+    <cfRule type="expression" dxfId="273" priority="71">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="262" priority="68">
+    <cfRule type="expression" dxfId="272" priority="70">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="261" priority="67">
+    <cfRule type="expression" dxfId="271" priority="69">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="260" priority="66">
+    <cfRule type="expression" dxfId="270" priority="68">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="259" priority="65">
+    <cfRule type="expression" dxfId="269" priority="67">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="258" priority="64">
+    <cfRule type="expression" dxfId="268" priority="66">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="257" priority="63">
+    <cfRule type="expression" dxfId="267" priority="65">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="256" priority="62">
+    <cfRule type="expression" dxfId="266" priority="64">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="255" priority="61">
+    <cfRule type="expression" dxfId="265" priority="63">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="254" priority="60">
+    <cfRule type="expression" dxfId="264" priority="62">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="253" priority="59">
+    <cfRule type="expression" dxfId="263" priority="61">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="252" priority="58">
+    <cfRule type="expression" dxfId="262" priority="60">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="251" priority="57">
+    <cfRule type="expression" dxfId="261" priority="59">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="250" priority="56">
+    <cfRule type="expression" dxfId="260" priority="58">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="249" priority="55">
+    <cfRule type="expression" dxfId="259" priority="57">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="248" priority="54">
+    <cfRule type="expression" dxfId="258" priority="56">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="247" priority="53">
+    <cfRule type="expression" dxfId="257" priority="55">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="246" priority="52">
+    <cfRule type="expression" dxfId="256" priority="54">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="245" priority="51">
+    <cfRule type="expression" dxfId="255" priority="53">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="244" priority="50">
+    <cfRule type="expression" dxfId="254" priority="52">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="243" priority="49">
+    <cfRule type="expression" dxfId="253" priority="51">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="242" priority="48">
+    <cfRule type="expression" dxfId="252" priority="50">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="241" priority="47">
+    <cfRule type="expression" dxfId="251" priority="49">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="240" priority="46">
+    <cfRule type="expression" dxfId="250" priority="48">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="239" priority="45">
+    <cfRule type="expression" dxfId="249" priority="47">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="238" priority="44">
+    <cfRule type="expression" dxfId="248" priority="46">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="237" priority="43">
+    <cfRule type="expression" dxfId="247" priority="45">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="236" priority="42">
+    <cfRule type="expression" dxfId="246" priority="44">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="235" priority="41">
+    <cfRule type="expression" dxfId="245" priority="43">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="234" priority="40">
+    <cfRule type="expression" dxfId="244" priority="42">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="233" priority="39">
+    <cfRule type="expression" dxfId="243" priority="41">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="232" priority="38">
+    <cfRule type="expression" dxfId="242" priority="40">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="231" priority="37">
+    <cfRule type="expression" dxfId="241" priority="39">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="230" priority="36">
+    <cfRule type="expression" dxfId="240" priority="38">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="229" priority="35">
+    <cfRule type="expression" dxfId="239" priority="37">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="228" priority="34">
+    <cfRule type="expression" dxfId="238" priority="36">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="227" priority="33">
+    <cfRule type="expression" dxfId="237" priority="35">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="226" priority="32">
+    <cfRule type="expression" dxfId="236" priority="34">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="225" priority="31">
+    <cfRule type="expression" dxfId="235" priority="33">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="224" priority="30">
+    <cfRule type="expression" dxfId="234" priority="32">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="223" priority="29">
+    <cfRule type="expression" dxfId="233" priority="31">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="222" priority="28">
+    <cfRule type="expression" dxfId="232" priority="30">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="221" priority="27">
+    <cfRule type="expression" dxfId="231" priority="29">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="220" priority="26">
+    <cfRule type="expression" dxfId="230" priority="28">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="219" priority="25">
+    <cfRule type="expression" dxfId="229" priority="27">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="218" priority="24">
+    <cfRule type="expression" dxfId="228" priority="26">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="217" priority="23">
+    <cfRule type="expression" dxfId="227" priority="25">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="216" priority="22">
+    <cfRule type="expression" dxfId="226" priority="24">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="215" priority="21">
+    <cfRule type="expression" dxfId="225" priority="23">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="214" priority="20">
+    <cfRule type="expression" dxfId="224" priority="22">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="213" priority="19">
+    <cfRule type="expression" dxfId="223" priority="21">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="212" priority="18">
+    <cfRule type="expression" dxfId="222" priority="20">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="211" priority="17">
+    <cfRule type="expression" dxfId="221" priority="19">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="210" priority="16">
+    <cfRule type="expression" dxfId="220" priority="18">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="209" priority="15">
+    <cfRule type="expression" dxfId="219" priority="17">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="208" priority="14">
+    <cfRule type="expression" dxfId="218" priority="16">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="207" priority="13">
+    <cfRule type="expression" dxfId="217" priority="15">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="206" priority="12">
+    <cfRule type="expression" dxfId="216" priority="14">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="205" priority="11">
+    <cfRule type="expression" dxfId="215" priority="13">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="204" priority="10">
+    <cfRule type="expression" dxfId="214" priority="12">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="203" priority="9">
+    <cfRule type="expression" dxfId="213" priority="11">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="202" priority="8">
+    <cfRule type="expression" dxfId="212" priority="10">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="201" priority="7">
+    <cfRule type="expression" dxfId="211" priority="9">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="200" priority="6">
+    <cfRule type="expression" dxfId="210" priority="8">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="199" priority="5">
+    <cfRule type="expression" dxfId="209" priority="7">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="198" priority="4">
+    <cfRule type="expression" dxfId="208" priority="6">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="197" priority="3">
+    <cfRule type="expression" dxfId="207" priority="5">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K829 I829 G829">
-    <cfRule type="expression" dxfId="196" priority="2">
+    <cfRule type="expression" dxfId="206" priority="4">
       <formula>$C829=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K834 I834 G834">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="I834 G834 K834:K835">
+    <cfRule type="expression" dxfId="205" priority="3">
       <formula>$C834=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I836 G836">
+    <cfRule type="expression" dxfId="204" priority="2">
+      <formula>$C836=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K837 I837 G837">
+    <cfRule type="expression" dxfId="203" priority="1">
+      <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -29656,7 +29789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O848"/>
+  <dimension ref="A1:O857"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
@@ -50962,985 +51095,1260 @@
       <c r="J848" s="11"/>
       <c r="K848" s="12"/>
     </row>
+    <row r="849" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A849" s="1">
+        <v>848</v>
+      </c>
+      <c r="B849" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C849" s="8">
+        <v>46032</v>
+      </c>
+      <c r="D849" s="9"/>
+      <c r="E849" s="10"/>
+      <c r="F849" s="11"/>
+      <c r="G849" s="12"/>
+      <c r="H849" s="11"/>
+      <c r="I849" s="12"/>
+      <c r="J849" s="11"/>
+      <c r="K849" s="12"/>
+    </row>
+    <row r="850" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A850" s="1">
+        <v>849</v>
+      </c>
+      <c r="B850" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C850" s="8">
+        <v>46033</v>
+      </c>
+      <c r="D850" s="9"/>
+      <c r="E850" s="10"/>
+      <c r="F850" s="11"/>
+      <c r="G850" s="12"/>
+      <c r="H850" s="11"/>
+      <c r="I850" s="12"/>
+      <c r="J850" s="11"/>
+      <c r="K850" s="12"/>
+    </row>
+    <row r="851" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A851" s="1">
+        <v>850</v>
+      </c>
+      <c r="B851" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C851" s="8">
+        <v>46034</v>
+      </c>
+      <c r="D851" s="9"/>
+      <c r="E851" s="10"/>
+      <c r="F851" s="11"/>
+      <c r="G851" s="12"/>
+      <c r="H851" s="11"/>
+      <c r="I851" s="12"/>
+      <c r="J851" s="11"/>
+      <c r="K851" s="12"/>
+    </row>
+    <row r="852" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A852" s="1">
+        <v>851</v>
+      </c>
+      <c r="B852" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C852" s="8">
+        <v>46035</v>
+      </c>
+      <c r="D852" s="9"/>
+      <c r="E852" s="10"/>
+      <c r="F852" s="11"/>
+      <c r="G852" s="12"/>
+      <c r="H852" s="11"/>
+      <c r="I852" s="12"/>
+      <c r="J852" s="11"/>
+      <c r="K852" s="12"/>
+    </row>
+    <row r="853" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A853" s="1">
+        <v>852</v>
+      </c>
+      <c r="B853" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C853" s="8">
+        <v>46036</v>
+      </c>
+      <c r="D853" s="9">
+        <v>6100</v>
+      </c>
+      <c r="E853" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F853" s="11">
+        <v>3400</v>
+      </c>
+      <c r="G853" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H853" s="11">
+        <v>2800</v>
+      </c>
+      <c r="I853" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J853" s="11">
+        <v>5000</v>
+      </c>
+      <c r="K853" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="854" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A854" s="1">
+        <v>853</v>
+      </c>
+      <c r="B854" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C854" s="8">
+        <v>46037</v>
+      </c>
+      <c r="D854" s="9">
+        <v>4700</v>
+      </c>
+      <c r="E854" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F854" s="11">
+        <v>2700</v>
+      </c>
+      <c r="G854" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H854" s="11">
+        <v>2200</v>
+      </c>
+      <c r="I854" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J854" s="11">
+        <v>3900</v>
+      </c>
+      <c r="K854" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="855" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A855" s="1">
+        <v>854</v>
+      </c>
+      <c r="B855" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C855" s="8">
+        <v>46037</v>
+      </c>
+      <c r="D855" s="9">
+        <v>2700</v>
+      </c>
+      <c r="E855" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F855" s="11">
+        <v>2200</v>
+      </c>
+      <c r="G855" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H855" s="11">
+        <v>600</v>
+      </c>
+      <c r="I855" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J855" s="11">
+        <v>800</v>
+      </c>
+      <c r="K855" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="856" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A856" s="1">
+        <v>855</v>
+      </c>
+      <c r="B856" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C856" s="8">
+        <v>46037</v>
+      </c>
+      <c r="D856" s="9">
+        <v>500</v>
+      </c>
+      <c r="E856" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F856" s="11">
+        <v>100</v>
+      </c>
+      <c r="G856" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H856" s="11">
+        <v>10</v>
+      </c>
+      <c r="I856" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J856" s="11">
+        <v>100</v>
+      </c>
+      <c r="K856" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="857" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A857" s="1">
+        <v>856</v>
+      </c>
+      <c r="B857" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C857" s="8">
+        <v>46038</v>
+      </c>
+      <c r="D857" s="9"/>
+      <c r="E857" s="10"/>
+      <c r="F857" s="11"/>
+      <c r="G857" s="12"/>
+      <c r="H857" s="11"/>
+      <c r="I857" s="12"/>
+      <c r="J857" s="11"/>
+      <c r="K857" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="B4:E848">
-    <cfRule type="expression" dxfId="195" priority="373">
+  <conditionalFormatting sqref="B4:E857">
+    <cfRule type="expression" dxfId="202" priority="381">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K848">
-    <cfRule type="expression" dxfId="194" priority="374">
+  <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K857">
+    <cfRule type="expression" dxfId="201" priority="382">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G47 J44:K47">
-    <cfRule type="expression" dxfId="193" priority="383">
+    <cfRule type="expression" dxfId="200" priority="391">
       <formula>$B18=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E692">
-    <cfRule type="expression" dxfId="192" priority="367">
+    <cfRule type="expression" dxfId="199" priority="375">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E694">
-    <cfRule type="expression" dxfId="191" priority="365">
+    <cfRule type="expression" dxfId="198" priority="373">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E701">
-    <cfRule type="expression" dxfId="190" priority="355">
+    <cfRule type="expression" dxfId="197" priority="363">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E703">
-    <cfRule type="expression" dxfId="189" priority="350">
+    <cfRule type="expression" dxfId="196" priority="358">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E710">
-    <cfRule type="expression" dxfId="188" priority="340">
+    <cfRule type="expression" dxfId="195" priority="348">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E712:E714">
-    <cfRule type="expression" dxfId="187" priority="335">
+    <cfRule type="expression" dxfId="194" priority="343">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E719">
-    <cfRule type="expression" dxfId="186" priority="325">
+    <cfRule type="expression" dxfId="193" priority="333">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E721:E723">
-    <cfRule type="expression" dxfId="185" priority="320">
+    <cfRule type="expression" dxfId="192" priority="328">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E728">
-    <cfRule type="expression" dxfId="184" priority="313">
+    <cfRule type="expression" dxfId="191" priority="321">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E730:E732">
-    <cfRule type="expression" dxfId="183" priority="300">
+    <cfRule type="expression" dxfId="190" priority="308">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E737">
-    <cfRule type="expression" dxfId="182" priority="293">
+    <cfRule type="expression" dxfId="189" priority="301">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739:E741">
-    <cfRule type="expression" dxfId="181" priority="280">
+    <cfRule type="expression" dxfId="188" priority="288">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E746">
-    <cfRule type="expression" dxfId="180" priority="270">
+    <cfRule type="expression" dxfId="187" priority="278">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E748:E750">
-    <cfRule type="expression" dxfId="179" priority="248">
+    <cfRule type="expression" dxfId="186" priority="256">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="178" priority="241">
+    <cfRule type="expression" dxfId="185" priority="249">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E759">
-    <cfRule type="expression" dxfId="177" priority="214">
+    <cfRule type="expression" dxfId="184" priority="222">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E764">
-    <cfRule type="expression" dxfId="176" priority="210">
+    <cfRule type="expression" dxfId="183" priority="218">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E766:E768">
-    <cfRule type="expression" dxfId="175" priority="185">
+    <cfRule type="expression" dxfId="182" priority="193">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="174" priority="175">
+    <cfRule type="expression" dxfId="181" priority="183">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E775:E777">
-    <cfRule type="expression" dxfId="173" priority="163">
+    <cfRule type="expression" dxfId="180" priority="171">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="172" priority="141">
+    <cfRule type="expression" dxfId="179" priority="149">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E784:E786">
-    <cfRule type="expression" dxfId="171" priority="123">
+    <cfRule type="expression" dxfId="178" priority="131">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="170" priority="386">
+    <cfRule type="expression" dxfId="177" priority="394">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70">
-    <cfRule type="expression" dxfId="169" priority="395">
+    <cfRule type="expression" dxfId="176" priority="403">
       <formula>$C70=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G685">
-    <cfRule type="expression" dxfId="168" priority="371">
+    <cfRule type="expression" dxfId="175" priority="379">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G692">
-    <cfRule type="expression" dxfId="167" priority="368">
+    <cfRule type="expression" dxfId="174" priority="376">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G695">
-    <cfRule type="expression" dxfId="166" priority="358">
+    <cfRule type="expression" dxfId="173" priority="366">
       <formula>$C695=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701">
-    <cfRule type="expression" dxfId="165" priority="353">
+    <cfRule type="expression" dxfId="172" priority="361">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G704:G705">
-    <cfRule type="expression" dxfId="164" priority="342">
+    <cfRule type="expression" dxfId="171" priority="350">
       <formula>$C704=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G710">
-    <cfRule type="expression" dxfId="163" priority="338">
+    <cfRule type="expression" dxfId="170" priority="346">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G712:G714">
-    <cfRule type="expression" dxfId="162" priority="328">
+    <cfRule type="expression" dxfId="169" priority="336">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G719">
-    <cfRule type="expression" dxfId="161" priority="323">
+    <cfRule type="expression" dxfId="168" priority="331">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G721:G723">
-    <cfRule type="expression" dxfId="160" priority="318">
+    <cfRule type="expression" dxfId="167" priority="326">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G728">
-    <cfRule type="expression" dxfId="159" priority="311">
+    <cfRule type="expression" dxfId="166" priority="319">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G730:G732">
-    <cfRule type="expression" dxfId="158" priority="298">
+    <cfRule type="expression" dxfId="165" priority="306">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G737">
-    <cfRule type="expression" dxfId="157" priority="291">
+    <cfRule type="expression" dxfId="164" priority="299">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739:G741">
-    <cfRule type="expression" dxfId="156" priority="277">
+    <cfRule type="expression" dxfId="163" priority="285">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746">
-    <cfRule type="expression" dxfId="155" priority="268">
+    <cfRule type="expression" dxfId="162" priority="276">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="154" priority="245">
+    <cfRule type="expression" dxfId="161" priority="253">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="153" priority="239">
+    <cfRule type="expression" dxfId="160" priority="247">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G759">
-    <cfRule type="expression" dxfId="152" priority="211">
+    <cfRule type="expression" dxfId="159" priority="219">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G764">
-    <cfRule type="expression" dxfId="151" priority="208">
+    <cfRule type="expression" dxfId="158" priority="216">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G766:G768">
-    <cfRule type="expression" dxfId="150" priority="181">
+    <cfRule type="expression" dxfId="157" priority="189">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="149" priority="173">
+    <cfRule type="expression" dxfId="156" priority="181">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G775:G777">
-    <cfRule type="expression" dxfId="148" priority="156">
+    <cfRule type="expression" dxfId="155" priority="164">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="147" priority="139">
+    <cfRule type="expression" dxfId="154" priority="147">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G784:G786">
-    <cfRule type="expression" dxfId="146" priority="117">
+    <cfRule type="expression" dxfId="153" priority="125">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:I47">
-    <cfRule type="expression" dxfId="145" priority="408">
+    <cfRule type="expression" dxfId="152" priority="416">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="expression" dxfId="144" priority="412">
+    <cfRule type="expression" dxfId="151" priority="420">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I685">
-    <cfRule type="expression" dxfId="143" priority="370">
+    <cfRule type="expression" dxfId="150" priority="378">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I694:I695">
-    <cfRule type="expression" dxfId="142" priority="357">
+    <cfRule type="expression" dxfId="149" priority="365">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I703:I704">
-    <cfRule type="expression" dxfId="141" priority="344">
+    <cfRule type="expression" dxfId="148" priority="352">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I712:I714">
-    <cfRule type="expression" dxfId="140" priority="327">
+    <cfRule type="expression" dxfId="147" priority="335">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I721:I723">
-    <cfRule type="expression" dxfId="139" priority="316">
+    <cfRule type="expression" dxfId="146" priority="324">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I730:I732">
-    <cfRule type="expression" dxfId="138" priority="294">
+    <cfRule type="expression" dxfId="145" priority="302">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I741">
-    <cfRule type="expression" dxfId="137" priority="274">
+    <cfRule type="expression" dxfId="144" priority="282">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I748:I749">
-    <cfRule type="expression" dxfId="136" priority="253">
+    <cfRule type="expression" dxfId="143" priority="261">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755">
-    <cfRule type="expression" dxfId="135" priority="237">
+    <cfRule type="expression" dxfId="142" priority="245">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I757:I758">
-    <cfRule type="expression" dxfId="134" priority="220">
+    <cfRule type="expression" dxfId="141" priority="228">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I766:I768">
-    <cfRule type="expression" dxfId="133" priority="177">
+    <cfRule type="expression" dxfId="140" priority="185">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="132" priority="171">
+    <cfRule type="expression" dxfId="139" priority="179">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I775:I777">
-    <cfRule type="expression" dxfId="131" priority="149">
+    <cfRule type="expression" dxfId="138" priority="157">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="130" priority="137">
+    <cfRule type="expression" dxfId="137" priority="145">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784:I786">
-    <cfRule type="expression" dxfId="129" priority="111">
+    <cfRule type="expression" dxfId="136" priority="119">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="128" priority="387">
+    <cfRule type="expression" dxfId="135" priority="395">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K685">
-    <cfRule type="expression" dxfId="127" priority="369">
+    <cfRule type="expression" dxfId="134" priority="377">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K692">
-    <cfRule type="expression" dxfId="126" priority="366">
+    <cfRule type="expression" dxfId="133" priority="374">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K694:K695">
-    <cfRule type="expression" dxfId="125" priority="356">
+    <cfRule type="expression" dxfId="132" priority="364">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701">
-    <cfRule type="expression" dxfId="124" priority="351">
+    <cfRule type="expression" dxfId="131" priority="359">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K703:K705">
-    <cfRule type="expression" dxfId="123" priority="341">
+    <cfRule type="expression" dxfId="130" priority="349">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K710">
-    <cfRule type="expression" dxfId="122" priority="336">
+    <cfRule type="expression" dxfId="129" priority="344">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K712:K714">
-    <cfRule type="expression" dxfId="121" priority="326">
+    <cfRule type="expression" dxfId="128" priority="334">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K719">
-    <cfRule type="expression" dxfId="120" priority="321">
+    <cfRule type="expression" dxfId="127" priority="329">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K721:K723">
-    <cfRule type="expression" dxfId="119" priority="314">
+    <cfRule type="expression" dxfId="126" priority="322">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K728">
-    <cfRule type="expression" dxfId="118" priority="309">
+    <cfRule type="expression" dxfId="125" priority="317">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K730:K732">
-    <cfRule type="expression" dxfId="117" priority="296">
+    <cfRule type="expression" dxfId="124" priority="304">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K737">
-    <cfRule type="expression" dxfId="116" priority="289">
+    <cfRule type="expression" dxfId="123" priority="297">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K741">
-    <cfRule type="expression" dxfId="115" priority="271">
+    <cfRule type="expression" dxfId="122" priority="279">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K746">
-    <cfRule type="expression" dxfId="114" priority="266">
+    <cfRule type="expression" dxfId="121" priority="274">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K748:K750">
-    <cfRule type="expression" dxfId="113" priority="242">
+    <cfRule type="expression" dxfId="120" priority="250">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755">
-    <cfRule type="expression" dxfId="112" priority="235">
+    <cfRule type="expression" dxfId="119" priority="243">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K757:K758">
-    <cfRule type="expression" dxfId="111" priority="217">
+    <cfRule type="expression" dxfId="118" priority="225">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K764">
-    <cfRule type="expression" dxfId="110" priority="206">
+    <cfRule type="expression" dxfId="117" priority="214">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766:K767">
-    <cfRule type="expression" dxfId="109" priority="188">
+    <cfRule type="expression" dxfId="116" priority="196">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="108" priority="169">
+    <cfRule type="expression" dxfId="115" priority="177">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K775:K777">
-    <cfRule type="expression" dxfId="107" priority="142">
+    <cfRule type="expression" dxfId="114" priority="150">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="106" priority="135">
+    <cfRule type="expression" dxfId="113" priority="143">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784:K786">
-    <cfRule type="expression" dxfId="105" priority="105">
+    <cfRule type="expression" dxfId="112" priority="113">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E792:E793">
-    <cfRule type="expression" dxfId="104" priority="104">
+    <cfRule type="expression" dxfId="111" priority="112">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="103" priority="103">
+    <cfRule type="expression" dxfId="110" priority="111">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="102" priority="102">
+    <cfRule type="expression" dxfId="109" priority="110">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="101" priority="101">
+    <cfRule type="expression" dxfId="108" priority="109">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="100" priority="100">
+    <cfRule type="expression" dxfId="107" priority="108">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="99" priority="99">
+    <cfRule type="expression" dxfId="106" priority="107">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="98" priority="98">
+    <cfRule type="expression" dxfId="105" priority="106">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E794:E795">
-    <cfRule type="expression" dxfId="97" priority="97">
+    <cfRule type="expression" dxfId="104" priority="105">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="96" priority="96">
+    <cfRule type="expression" dxfId="103" priority="104">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="95" priority="95">
+    <cfRule type="expression" dxfId="102" priority="103">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="94" priority="94">
+    <cfRule type="expression" dxfId="101" priority="102">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="93" priority="93">
+    <cfRule type="expression" dxfId="100" priority="101">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="92" priority="92">
+    <cfRule type="expression" dxfId="99" priority="100">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="91" priority="91">
+    <cfRule type="expression" dxfId="98" priority="99">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E801:E802">
-    <cfRule type="expression" dxfId="90" priority="90">
+    <cfRule type="expression" dxfId="97" priority="98">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E803:E805">
-    <cfRule type="expression" dxfId="89" priority="89">
+    <cfRule type="expression" dxfId="96" priority="97">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G805">
-    <cfRule type="expression" dxfId="88" priority="88">
+    <cfRule type="expression" dxfId="95" priority="96">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G802">
-    <cfRule type="expression" dxfId="87" priority="87">
+    <cfRule type="expression" dxfId="94" priority="95">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G803:G805">
-    <cfRule type="expression" dxfId="86" priority="86">
+    <cfRule type="expression" dxfId="93" priority="94">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I805">
-    <cfRule type="expression" dxfId="85" priority="85">
+    <cfRule type="expression" dxfId="92" priority="93">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I802">
-    <cfRule type="expression" dxfId="84" priority="84">
+    <cfRule type="expression" dxfId="91" priority="92">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803:I805">
-    <cfRule type="expression" dxfId="83" priority="83">
+    <cfRule type="expression" dxfId="90" priority="91">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K805">
-    <cfRule type="expression" dxfId="82" priority="82">
+    <cfRule type="expression" dxfId="89" priority="90">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K802">
-    <cfRule type="expression" dxfId="81" priority="81">
+    <cfRule type="expression" dxfId="88" priority="89">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K803:K805">
-    <cfRule type="expression" dxfId="80" priority="80">
+    <cfRule type="expression" dxfId="87" priority="88">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E809:E810">
-    <cfRule type="expression" dxfId="79" priority="79">
+    <cfRule type="expression" dxfId="86" priority="87">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811:E812">
-    <cfRule type="expression" dxfId="78" priority="78">
+    <cfRule type="expression" dxfId="85" priority="86">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G812">
-    <cfRule type="expression" dxfId="77" priority="77">
+    <cfRule type="expression" dxfId="84" priority="85">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G810">
-    <cfRule type="expression" dxfId="76" priority="76">
+    <cfRule type="expression" dxfId="83" priority="84">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811:G812">
-    <cfRule type="expression" dxfId="75" priority="75">
+    <cfRule type="expression" dxfId="82" priority="83">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I812">
-    <cfRule type="expression" dxfId="74" priority="74">
+    <cfRule type="expression" dxfId="81" priority="82">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I810">
-    <cfRule type="expression" dxfId="73" priority="73">
+    <cfRule type="expression" dxfId="80" priority="81">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="72" priority="72">
+    <cfRule type="expression" dxfId="79" priority="80">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K812">
-    <cfRule type="expression" dxfId="71" priority="71">
+    <cfRule type="expression" dxfId="78" priority="79">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K810">
-    <cfRule type="expression" dxfId="70" priority="70">
+    <cfRule type="expression" dxfId="77" priority="78">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811:K812">
-    <cfRule type="expression" dxfId="69" priority="69">
+    <cfRule type="expression" dxfId="76" priority="77">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E818:E822 G818:G822 K818:K822 I818:I822">
-    <cfRule type="expression" dxfId="68" priority="68">
+    <cfRule type="expression" dxfId="75" priority="76">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K818:K822 G818:G822 I818:I822">
-    <cfRule type="expression" dxfId="67" priority="67">
+    <cfRule type="expression" dxfId="74" priority="75">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E820:E821">
-    <cfRule type="expression" dxfId="66" priority="66">
+    <cfRule type="expression" dxfId="73" priority="74">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="65" priority="65">
+    <cfRule type="expression" dxfId="72" priority="73">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="64" priority="64">
+    <cfRule type="expression" dxfId="71" priority="72">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="63" priority="63">
+    <cfRule type="expression" dxfId="70" priority="71">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="62" priority="62">
+    <cfRule type="expression" dxfId="69" priority="70">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K822 G822">
-    <cfRule type="expression" dxfId="61" priority="61">
+    <cfRule type="expression" dxfId="68" priority="69">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I822">
-    <cfRule type="expression" dxfId="60" priority="60">
+    <cfRule type="expression" dxfId="67" priority="68">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E828:E831">
-    <cfRule type="expression" dxfId="59" priority="59">
+    <cfRule type="expression" dxfId="66" priority="67">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="58" priority="58">
+    <cfRule type="expression" dxfId="65" priority="66">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="57" priority="57">
+    <cfRule type="expression" dxfId="64" priority="65">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="56" priority="56">
+    <cfRule type="expression" dxfId="63" priority="64">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="55" priority="55">
+    <cfRule type="expression" dxfId="62" priority="63">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="54" priority="54">
+    <cfRule type="expression" dxfId="61" priority="62">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="53" priority="53">
+    <cfRule type="expression" dxfId="60" priority="61">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="52" priority="52">
+    <cfRule type="expression" dxfId="59" priority="60">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="51" priority="51">
+    <cfRule type="expression" dxfId="58" priority="59">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="50" priority="50">
+    <cfRule type="expression" dxfId="57" priority="58">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="49" priority="49">
+    <cfRule type="expression" dxfId="56" priority="57">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="48" priority="48">
+    <cfRule type="expression" dxfId="55" priority="56">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="47" priority="47">
+    <cfRule type="expression" dxfId="54" priority="55">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="46" priority="46">
+    <cfRule type="expression" dxfId="53" priority="54">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837">
-    <cfRule type="expression" dxfId="45" priority="45">
+    <cfRule type="expression" dxfId="52" priority="53">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="44" priority="44">
+    <cfRule type="expression" dxfId="51" priority="52">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="43" priority="43">
+    <cfRule type="expression" dxfId="50" priority="51">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="42" priority="42">
+    <cfRule type="expression" dxfId="49" priority="50">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="41" priority="41">
+    <cfRule type="expression" dxfId="48" priority="49">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="40" priority="40">
+    <cfRule type="expression" dxfId="47" priority="48">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="39" priority="39">
+    <cfRule type="expression" dxfId="46" priority="47">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E845:E847">
-    <cfRule type="expression" dxfId="38" priority="38">
+    <cfRule type="expression" dxfId="45" priority="46">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="37" priority="37">
+    <cfRule type="expression" dxfId="44" priority="45">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="36" priority="36">
+    <cfRule type="expression" dxfId="43" priority="44">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="35" priority="35">
+    <cfRule type="expression" dxfId="42" priority="43">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="34" priority="34">
+    <cfRule type="expression" dxfId="41" priority="42">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="33" priority="33">
+    <cfRule type="expression" dxfId="40" priority="41">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="32" priority="32">
+    <cfRule type="expression" dxfId="39" priority="40">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="31" priority="31">
+    <cfRule type="expression" dxfId="38" priority="39">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="30" priority="30">
+    <cfRule type="expression" dxfId="37" priority="38">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="29" priority="29">
+    <cfRule type="expression" dxfId="36" priority="37">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="28" priority="28">
+    <cfRule type="expression" dxfId="35" priority="36">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="27" priority="27">
+    <cfRule type="expression" dxfId="34" priority="35">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="26" priority="26">
+    <cfRule type="expression" dxfId="33" priority="34">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="25" priority="25">
+    <cfRule type="expression" dxfId="32" priority="33">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="24" priority="24">
+    <cfRule type="expression" dxfId="31" priority="32">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="23" priority="23">
+    <cfRule type="expression" dxfId="30" priority="31">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="22" priority="22">
+    <cfRule type="expression" dxfId="29" priority="30">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="21" priority="21">
+    <cfRule type="expression" dxfId="28" priority="29">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="27" priority="28">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="26" priority="27">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="25" priority="26">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="17" priority="17">
+    <cfRule type="expression" dxfId="24" priority="25">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="16" priority="16">
+    <cfRule type="expression" dxfId="23" priority="24">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="15" priority="15">
+    <cfRule type="expression" dxfId="22" priority="23">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="21" priority="22">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="20" priority="21">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="19" priority="20">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="18" priority="19">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="17" priority="18">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="16" priority="17">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="15" priority="16">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E836">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="12" priority="13">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$C836=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K853 I853 G853 E853">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$C853=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K853 I853 G853">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>$C853=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K854 I854 G854 E854">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$C854=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K854 I854 G854">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$C854=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$C855=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$C855=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$C855=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
+++ b/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66445EEA-A937-4736-B62F-7E99689C5E9F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF55D53A-DE99-4D36-AA98-4F3FEF6881C7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3433" uniqueCount="33">
   <si>
     <t>План поставок ПОКОМ</t>
   </si>
@@ -435,7 +435,14 @@
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Обычный 2 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="495">
+  <dxfs count="496">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4282,7 +4289,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMD839"/>
+  <dimension ref="A1:AMD842"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
@@ -28312,517 +28319,590 @@
       <c r="E839" s="10"/>
       <c r="F839" s="11"/>
       <c r="G839" s="12"/>
-      <c r="H839" s="11"/>
-      <c r="I839" s="12"/>
-      <c r="J839" s="11"/>
-      <c r="K839" s="12"/>
+      <c r="H839" s="11">
+        <v>5600</v>
+      </c>
+      <c r="I839" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J839" s="11">
+        <v>4500</v>
+      </c>
+      <c r="K839" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="840" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A840" s="1">
+        <v>836</v>
+      </c>
+      <c r="B840" s="7" t="str">
+        <f t="shared" ref="B840:B842" si="137">IF(C840&lt;&gt;"",TEXT(C840,"ДДД"),"")</f>
+        <v>Вс</v>
+      </c>
+      <c r="C840" s="8">
+        <v>46040</v>
+      </c>
+      <c r="D840" s="9"/>
+      <c r="E840" s="10"/>
+      <c r="F840" s="11"/>
+      <c r="G840" s="12"/>
+      <c r="H840" s="11"/>
+      <c r="I840" s="12"/>
+      <c r="J840" s="11"/>
+      <c r="K840" s="12"/>
+    </row>
+    <row r="841" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A841" s="1">
+        <v>837</v>
+      </c>
+      <c r="B841" s="7" t="str">
+        <f t="shared" si="137"/>
+        <v>Пн</v>
+      </c>
+      <c r="C841" s="8">
+        <v>46041</v>
+      </c>
+      <c r="D841" s="9"/>
+      <c r="E841" s="10"/>
+      <c r="F841" s="11"/>
+      <c r="G841" s="12"/>
+      <c r="H841" s="11"/>
+      <c r="I841" s="12"/>
+      <c r="J841" s="11"/>
+      <c r="K841" s="12"/>
+    </row>
+    <row r="842" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A842" s="1">
+        <v>838</v>
+      </c>
+      <c r="B842" s="7" t="str">
+        <f t="shared" si="137"/>
+        <v>Вт</v>
+      </c>
+      <c r="C842" s="8">
+        <v>46042</v>
+      </c>
+      <c r="D842" s="9"/>
+      <c r="E842" s="10"/>
+      <c r="F842" s="11"/>
+      <c r="G842" s="12"/>
+      <c r="H842" s="11"/>
+      <c r="I842" s="12"/>
+      <c r="J842" s="11"/>
+      <c r="K842" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:E839">
-    <cfRule type="expression" dxfId="494" priority="711">
+  <conditionalFormatting sqref="B4:E842">
+    <cfRule type="expression" dxfId="495" priority="712">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:M683 B684:K839">
-    <cfRule type="expression" dxfId="493" priority="712">
+  <conditionalFormatting sqref="B4:M683 B684:K842">
+    <cfRule type="expression" dxfId="494" priority="713">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E678">
-    <cfRule type="expression" dxfId="492" priority="702">
+    <cfRule type="expression" dxfId="493" priority="703">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E693:E694">
-    <cfRule type="expression" dxfId="491" priority="689">
+    <cfRule type="expression" dxfId="492" priority="690">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E702">
-    <cfRule type="expression" dxfId="490" priority="676">
+    <cfRule type="expression" dxfId="491" priority="677">
       <formula>$C702=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E707">
-    <cfRule type="expression" dxfId="489" priority="672">
+    <cfRule type="expression" dxfId="490" priority="673">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709:E710">
-    <cfRule type="expression" dxfId="488" priority="664">
+    <cfRule type="expression" dxfId="489" priority="665">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E715">
-    <cfRule type="expression" dxfId="487" priority="660">
+    <cfRule type="expression" dxfId="488" priority="661">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E717:E718">
-    <cfRule type="expression" dxfId="486" priority="648">
+    <cfRule type="expression" dxfId="487" priority="649">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E723">
-    <cfRule type="expression" dxfId="485" priority="637">
+    <cfRule type="expression" dxfId="486" priority="638">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E725:E726">
-    <cfRule type="expression" dxfId="484" priority="614">
+    <cfRule type="expression" dxfId="485" priority="615">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E731">
-    <cfRule type="expression" dxfId="483" priority="602">
+    <cfRule type="expression" dxfId="484" priority="603">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E733:E734">
-    <cfRule type="expression" dxfId="482" priority="569">
+    <cfRule type="expression" dxfId="483" priority="570">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739">
-    <cfRule type="expression" dxfId="481" priority="537">
+    <cfRule type="expression" dxfId="482" priority="538">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E741:E742">
-    <cfRule type="expression" dxfId="480" priority="492">
+    <cfRule type="expression" dxfId="481" priority="493">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E747:E748">
-    <cfRule type="expression" dxfId="479" priority="429">
+    <cfRule type="expression" dxfId="480" priority="430">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E750">
-    <cfRule type="expression" dxfId="478" priority="413">
+    <cfRule type="expression" dxfId="479" priority="414">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="477" priority="387">
+    <cfRule type="expression" dxfId="478" priority="388">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E758">
-    <cfRule type="expression" dxfId="476" priority="339">
+    <cfRule type="expression" dxfId="477" priority="340">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E763">
-    <cfRule type="expression" dxfId="475" priority="312">
+    <cfRule type="expression" dxfId="476" priority="313">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E765:E766">
-    <cfRule type="expression" dxfId="474" priority="259">
+    <cfRule type="expression" dxfId="475" priority="260">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E771">
-    <cfRule type="expression" dxfId="473" priority="214">
+    <cfRule type="expression" dxfId="474" priority="215">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="472" priority="725">
+    <cfRule type="expression" dxfId="473" priority="726">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G661">
-    <cfRule type="expression" dxfId="471" priority="709">
+    <cfRule type="expression" dxfId="472" priority="710">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G670">
-    <cfRule type="expression" dxfId="470" priority="706">
+    <cfRule type="expression" dxfId="471" priority="707">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G678">
-    <cfRule type="expression" dxfId="469" priority="703">
+    <cfRule type="expression" dxfId="470" priority="704">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G686">
-    <cfRule type="expression" dxfId="468" priority="699">
+    <cfRule type="expression" dxfId="469" priority="700">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G691">
-    <cfRule type="expression" dxfId="467" priority="696">
+    <cfRule type="expression" dxfId="468" priority="697">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G693:G694">
-    <cfRule type="expression" dxfId="466" priority="688">
+    <cfRule type="expression" dxfId="467" priority="689">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G699">
-    <cfRule type="expression" dxfId="465" priority="685">
+    <cfRule type="expression" dxfId="466" priority="686">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701:G702">
-    <cfRule type="expression" dxfId="464" priority="677">
+    <cfRule type="expression" dxfId="465" priority="678">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G707">
-    <cfRule type="expression" dxfId="463" priority="673">
+    <cfRule type="expression" dxfId="464" priority="674">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G709:G710">
-    <cfRule type="expression" dxfId="462" priority="663">
+    <cfRule type="expression" dxfId="463" priority="664">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G715">
-    <cfRule type="expression" dxfId="461" priority="658">
+    <cfRule type="expression" dxfId="462" priority="659">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G717:G718">
-    <cfRule type="expression" dxfId="460" priority="645">
+    <cfRule type="expression" dxfId="461" priority="646">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G723">
-    <cfRule type="expression" dxfId="459" priority="634">
+    <cfRule type="expression" dxfId="460" priority="635">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G725:G726">
-    <cfRule type="expression" dxfId="458" priority="611">
+    <cfRule type="expression" dxfId="459" priority="612">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G731">
-    <cfRule type="expression" dxfId="457" priority="598">
+    <cfRule type="expression" dxfId="458" priority="599">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G733:G734">
-    <cfRule type="expression" dxfId="456" priority="563">
+    <cfRule type="expression" dxfId="457" priority="564">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739">
-    <cfRule type="expression" dxfId="455" priority="532">
+    <cfRule type="expression" dxfId="456" priority="533">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G741:G742">
-    <cfRule type="expression" dxfId="454" priority="486">
+    <cfRule type="expression" dxfId="455" priority="487">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G747">
-    <cfRule type="expression" dxfId="453" priority="449">
+    <cfRule type="expression" dxfId="454" priority="450">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="452" priority="406">
+    <cfRule type="expression" dxfId="453" priority="407">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="451" priority="381">
+    <cfRule type="expression" dxfId="452" priority="382">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G758">
-    <cfRule type="expression" dxfId="450" priority="332">
+    <cfRule type="expression" dxfId="451" priority="333">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763">
-    <cfRule type="expression" dxfId="449" priority="305">
+    <cfRule type="expression" dxfId="450" priority="306">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G765:G766">
-    <cfRule type="expression" dxfId="448" priority="246">
+    <cfRule type="expression" dxfId="449" priority="247">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G771">
-    <cfRule type="expression" dxfId="447" priority="207">
+    <cfRule type="expression" dxfId="448" priority="208">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H128:I129">
-    <cfRule type="expression" dxfId="446" priority="728">
+    <cfRule type="expression" dxfId="447" priority="729">
       <formula>$C128=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="expression" dxfId="445" priority="726">
+    <cfRule type="expression" dxfId="446" priority="727">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I661">
-    <cfRule type="expression" dxfId="444" priority="708">
+    <cfRule type="expression" dxfId="445" priority="709">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670">
-    <cfRule type="expression" dxfId="443" priority="705">
+    <cfRule type="expression" dxfId="444" priority="706">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I678">
-    <cfRule type="expression" dxfId="442" priority="701">
+    <cfRule type="expression" dxfId="443" priority="702">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I686">
-    <cfRule type="expression" dxfId="441" priority="698">
+    <cfRule type="expression" dxfId="442" priority="699">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I691">
-    <cfRule type="expression" dxfId="440" priority="695">
+    <cfRule type="expression" dxfId="441" priority="696">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I693:I694">
-    <cfRule type="expression" dxfId="439" priority="687">
+    <cfRule type="expression" dxfId="440" priority="688">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I699">
-    <cfRule type="expression" dxfId="438" priority="684">
+    <cfRule type="expression" dxfId="439" priority="685">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I701:I702">
-    <cfRule type="expression" dxfId="437" priority="678">
+    <cfRule type="expression" dxfId="438" priority="679">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I707">
-    <cfRule type="expression" dxfId="436" priority="675">
+    <cfRule type="expression" dxfId="437" priority="676">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I709:I710">
-    <cfRule type="expression" dxfId="435" priority="662">
+    <cfRule type="expression" dxfId="436" priority="663">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I715">
-    <cfRule type="expression" dxfId="434" priority="656">
+    <cfRule type="expression" dxfId="435" priority="657">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I717:I718">
-    <cfRule type="expression" dxfId="433" priority="642">
+    <cfRule type="expression" dxfId="434" priority="643">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I723:I726">
-    <cfRule type="expression" dxfId="432" priority="608">
+    <cfRule type="expression" dxfId="433" priority="609">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I731:I734">
-    <cfRule type="expression" dxfId="431" priority="557">
+    <cfRule type="expression" dxfId="432" priority="558">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I736">
-    <cfRule type="expression" dxfId="430" priority="546">
+    <cfRule type="expression" dxfId="431" priority="547">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I742">
-    <cfRule type="expression" dxfId="429" priority="480">
+    <cfRule type="expression" dxfId="430" priority="481">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I744">
-    <cfRule type="expression" dxfId="428" priority="464">
+    <cfRule type="expression" dxfId="429" priority="465">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I747:I748">
-    <cfRule type="expression" dxfId="427" priority="434">
+    <cfRule type="expression" dxfId="428" priority="435">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I750">
-    <cfRule type="expression" dxfId="426" priority="399">
+    <cfRule type="expression" dxfId="427" priority="400">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755:I756">
-    <cfRule type="expression" dxfId="425" priority="363">
+    <cfRule type="expression" dxfId="426" priority="364">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I758">
-    <cfRule type="expression" dxfId="424" priority="325">
+    <cfRule type="expression" dxfId="425" priority="326">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I763">
-    <cfRule type="expression" dxfId="423" priority="298">
+    <cfRule type="expression" dxfId="424" priority="299">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I765:I766">
-    <cfRule type="expression" dxfId="422" priority="233">
+    <cfRule type="expression" dxfId="423" priority="234">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I771:I772">
-    <cfRule type="expression" dxfId="421" priority="200">
+    <cfRule type="expression" dxfId="422" priority="201">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="420" priority="727">
+    <cfRule type="expression" dxfId="421" priority="728">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K661">
-    <cfRule type="expression" dxfId="419" priority="707">
+    <cfRule type="expression" dxfId="420" priority="708">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K670">
-    <cfRule type="expression" dxfId="418" priority="704">
+    <cfRule type="expression" dxfId="419" priority="705">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K678">
-    <cfRule type="expression" dxfId="417" priority="700">
+    <cfRule type="expression" dxfId="418" priority="701">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K686">
-    <cfRule type="expression" dxfId="416" priority="697">
+    <cfRule type="expression" dxfId="417" priority="698">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K691">
-    <cfRule type="expression" dxfId="415" priority="694">
+    <cfRule type="expression" dxfId="416" priority="695">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K693:K694">
-    <cfRule type="expression" dxfId="414" priority="686">
+    <cfRule type="expression" dxfId="415" priority="687">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K699">
-    <cfRule type="expression" dxfId="413" priority="683">
+    <cfRule type="expression" dxfId="414" priority="684">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701:K702">
-    <cfRule type="expression" dxfId="412" priority="679">
+    <cfRule type="expression" dxfId="413" priority="680">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K707">
-    <cfRule type="expression" dxfId="411" priority="674">
+    <cfRule type="expression" dxfId="412" priority="675">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K709:K710">
-    <cfRule type="expression" dxfId="410" priority="661">
+    <cfRule type="expression" dxfId="411" priority="662">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K715:K718">
-    <cfRule type="expression" dxfId="409" priority="639">
+    <cfRule type="expression" dxfId="410" priority="640">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K723">
-    <cfRule type="expression" dxfId="408" priority="628">
+    <cfRule type="expression" dxfId="409" priority="629">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K725:K726">
-    <cfRule type="expression" dxfId="407" priority="605">
+    <cfRule type="expression" dxfId="408" priority="606">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K731">
-    <cfRule type="expression" dxfId="406" priority="590">
+    <cfRule type="expression" dxfId="407" priority="591">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K733:K734">
-    <cfRule type="expression" dxfId="405" priority="551">
+    <cfRule type="expression" dxfId="406" priority="552">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K736">
-    <cfRule type="expression" dxfId="404" priority="541">
+    <cfRule type="expression" dxfId="405" priority="542">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K742">
-    <cfRule type="expression" dxfId="403" priority="469">
+    <cfRule type="expression" dxfId="404" priority="470">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K744">
-    <cfRule type="expression" dxfId="402" priority="459">
+    <cfRule type="expression" dxfId="403" priority="460">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K747">
-    <cfRule type="expression" dxfId="401" priority="439">
+    <cfRule type="expression" dxfId="402" priority="440">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K749:K750">
-    <cfRule type="expression" dxfId="400" priority="392">
+    <cfRule type="expression" dxfId="401" priority="393">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755:K756">
-    <cfRule type="expression" dxfId="399" priority="357">
+    <cfRule type="expression" dxfId="400" priority="358">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K758">
-    <cfRule type="expression" dxfId="398" priority="318">
+    <cfRule type="expression" dxfId="399" priority="319">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K763:K764">
-    <cfRule type="expression" dxfId="397" priority="291">
+    <cfRule type="expression" dxfId="398" priority="292">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766">
-    <cfRule type="expression" dxfId="396" priority="220">
+    <cfRule type="expression" dxfId="397" priority="221">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K771">
-    <cfRule type="expression" dxfId="395" priority="193">
+    <cfRule type="expression" dxfId="396" priority="194">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
+    <cfRule type="expression" dxfId="395" priority="193">
+      <formula>$C773=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G773">
     <cfRule type="expression" dxfId="394" priority="192">
       <formula>$C773=TODAY()</formula>
     </cfRule>
@@ -28832,7 +28912,7 @@
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G773">
+  <conditionalFormatting sqref="I773">
     <cfRule type="expression" dxfId="392" priority="190">
       <formula>$C773=TODAY()</formula>
     </cfRule>
@@ -28842,7 +28922,7 @@
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I773">
+  <conditionalFormatting sqref="K773">
     <cfRule type="expression" dxfId="390" priority="188">
       <formula>$C773=TODAY()</formula>
     </cfRule>
@@ -28852,29 +28932,29 @@
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K773">
+  <conditionalFormatting sqref="E774">
     <cfRule type="expression" dxfId="388" priority="186">
-      <formula>$C773=TODAY()</formula>
+      <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E774">
+  <conditionalFormatting sqref="G774">
     <cfRule type="expression" dxfId="387" priority="185">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G774">
+  <conditionalFormatting sqref="I774">
     <cfRule type="expression" dxfId="386" priority="184">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I774">
+  <conditionalFormatting sqref="K774">
     <cfRule type="expression" dxfId="385" priority="183">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K774">
+  <conditionalFormatting sqref="I776">
     <cfRule type="expression" dxfId="384" priority="182">
-      <formula>$C774=TODAY()</formula>
+      <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
@@ -28882,7 +28962,7 @@
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I776">
+  <conditionalFormatting sqref="K776">
     <cfRule type="expression" dxfId="382" priority="180">
       <formula>$C776=TODAY()</formula>
     </cfRule>
@@ -28892,12 +28972,12 @@
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K776">
+  <conditionalFormatting sqref="E779">
     <cfRule type="expression" dxfId="380" priority="178">
-      <formula>$C776=TODAY()</formula>
+      <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E779">
+  <conditionalFormatting sqref="G779">
     <cfRule type="expression" dxfId="379" priority="177">
       <formula>$C779=TODAY()</formula>
     </cfRule>
@@ -28907,7 +28987,7 @@
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G779">
+  <conditionalFormatting sqref="I779">
     <cfRule type="expression" dxfId="377" priority="175">
       <formula>$C779=TODAY()</formula>
     </cfRule>
@@ -28917,7 +28997,7 @@
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I779">
+  <conditionalFormatting sqref="K779">
     <cfRule type="expression" dxfId="375" priority="173">
       <formula>$C779=TODAY()</formula>
     </cfRule>
@@ -28927,9 +29007,9 @@
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K779">
+  <conditionalFormatting sqref="I780">
     <cfRule type="expression" dxfId="373" priority="171">
-      <formula>$C779=TODAY()</formula>
+      <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
@@ -28937,7 +29017,7 @@
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I780">
+  <conditionalFormatting sqref="K780">
     <cfRule type="expression" dxfId="371" priority="169">
       <formula>$C780=TODAY()</formula>
     </cfRule>
@@ -28947,9 +29027,9 @@
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K780">
+  <conditionalFormatting sqref="I781:I782">
     <cfRule type="expression" dxfId="369" priority="167">
-      <formula>$C780=TODAY()</formula>
+      <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
@@ -28957,7 +29037,7 @@
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I781:I782">
+  <conditionalFormatting sqref="G781:G782">
     <cfRule type="expression" dxfId="367" priority="165">
       <formula>$C781=TODAY()</formula>
     </cfRule>
@@ -28967,7 +29047,7 @@
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G781:G782">
+  <conditionalFormatting sqref="E781:E782">
     <cfRule type="expression" dxfId="365" priority="163">
       <formula>$C781=TODAY()</formula>
     </cfRule>
@@ -28977,12 +29057,12 @@
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E781:E782">
+  <conditionalFormatting sqref="E782">
     <cfRule type="expression" dxfId="363" priority="161">
-      <formula>$C781=TODAY()</formula>
+      <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E782">
+  <conditionalFormatting sqref="G782">
     <cfRule type="expression" dxfId="362" priority="160">
       <formula>$C782=TODAY()</formula>
     </cfRule>
@@ -28992,7 +29072,7 @@
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G782">
+  <conditionalFormatting sqref="I782">
     <cfRule type="expression" dxfId="360" priority="158">
       <formula>$C782=TODAY()</formula>
     </cfRule>
@@ -29002,7 +29082,7 @@
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I782">
+  <conditionalFormatting sqref="K782">
     <cfRule type="expression" dxfId="358" priority="156">
       <formula>$C782=TODAY()</formula>
     </cfRule>
@@ -29012,9 +29092,9 @@
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K782">
+  <conditionalFormatting sqref="I784">
     <cfRule type="expression" dxfId="356" priority="154">
-      <formula>$C782=TODAY()</formula>
+      <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
@@ -29022,7 +29102,7 @@
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I784">
+  <conditionalFormatting sqref="K784">
     <cfRule type="expression" dxfId="354" priority="152">
       <formula>$C784=TODAY()</formula>
     </cfRule>
@@ -29032,9 +29112,9 @@
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K784">
+  <conditionalFormatting sqref="E787">
     <cfRule type="expression" dxfId="352" priority="150">
-      <formula>$C784=TODAY()</formula>
+      <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
@@ -29042,7 +29122,7 @@
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E787">
+  <conditionalFormatting sqref="G787">
     <cfRule type="expression" dxfId="350" priority="148">
       <formula>$C787=TODAY()</formula>
     </cfRule>
@@ -29057,7 +29137,7 @@
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G787">
+  <conditionalFormatting sqref="I787:I788">
     <cfRule type="expression" dxfId="347" priority="145">
       <formula>$C787=TODAY()</formula>
     </cfRule>
@@ -29072,7 +29152,7 @@
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I787:I788">
+  <conditionalFormatting sqref="K787">
     <cfRule type="expression" dxfId="344" priority="142">
       <formula>$C787=TODAY()</formula>
     </cfRule>
@@ -29087,13 +29167,13 @@
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="341" priority="139">
-      <formula>$C787=TODAY()</formula>
+  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
+    <cfRule type="expression" dxfId="341" priority="137">
+      <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
-    <cfRule type="expression" dxfId="340" priority="136">
+  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
+    <cfRule type="expression" dxfId="340" priority="139">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29102,9 +29182,9 @@
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="338" priority="137">
-      <formula>$C789=TODAY()</formula>
+  <conditionalFormatting sqref="K790 I790 G790 E790">
+    <cfRule type="expression" dxfId="338" priority="136">
+      <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
@@ -29117,18 +29197,18 @@
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K790 I790 G790 E790">
+  <conditionalFormatting sqref="K790 I790 G790">
     <cfRule type="expression" dxfId="335" priority="133">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K790 I790 G790">
-    <cfRule type="expression" dxfId="334" priority="132">
-      <formula>$C790=TODAY()</formula>
+  <conditionalFormatting sqref="I792">
+    <cfRule type="expression" dxfId="334" priority="130">
+      <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="333" priority="129">
+    <cfRule type="expression" dxfId="333" priority="132">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29137,13 +29217,13 @@
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="331" priority="130">
+  <conditionalFormatting sqref="K792">
+    <cfRule type="expression" dxfId="331" priority="127">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="330" priority="126">
+    <cfRule type="expression" dxfId="330" priority="129">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29152,9 +29232,9 @@
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="328" priority="127">
-      <formula>$C792=TODAY()</formula>
+  <conditionalFormatting sqref="E795">
+    <cfRule type="expression" dxfId="328" priority="126">
+      <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
@@ -29162,7 +29242,7 @@
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E795">
+  <conditionalFormatting sqref="G795">
     <cfRule type="expression" dxfId="326" priority="124">
       <formula>$C795=TODAY()</formula>
     </cfRule>
@@ -29177,7 +29257,7 @@
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G795">
+  <conditionalFormatting sqref="I795:I796">
     <cfRule type="expression" dxfId="323" priority="121">
       <formula>$C795=TODAY()</formula>
     </cfRule>
@@ -29192,7 +29272,7 @@
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I795:I796">
+  <conditionalFormatting sqref="K795">
     <cfRule type="expression" dxfId="320" priority="118">
       <formula>$C795=TODAY()</formula>
     </cfRule>
@@ -29207,9 +29287,9 @@
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K795">
+  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
     <cfRule type="expression" dxfId="317" priority="115">
-      <formula>$C795=TODAY()</formula>
+      <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
@@ -29222,9 +29302,9 @@
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
+  <conditionalFormatting sqref="K798 I798 G798 E798">
     <cfRule type="expression" dxfId="314" priority="112">
-      <formula>$C797=TODAY()</formula>
+      <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
@@ -29247,14 +29327,14 @@
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798 E798">
+  <conditionalFormatting sqref="K798 I798 G798">
     <cfRule type="expression" dxfId="309" priority="107">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798">
+  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
     <cfRule type="expression" dxfId="308" priority="106">
-      <formula>$C798=TODAY()</formula>
+      <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
@@ -29267,14 +29347,14 @@
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
+  <conditionalFormatting sqref="I803 G803 K803:K805">
     <cfRule type="expression" dxfId="305" priority="103">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I803 G803 K803:K805">
+  <conditionalFormatting sqref="E805:E806">
     <cfRule type="expression" dxfId="304" priority="102">
-      <formula>$C803=TODAY()</formula>
+      <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
@@ -29287,9 +29367,9 @@
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E805:E806">
+  <conditionalFormatting sqref="E806">
     <cfRule type="expression" dxfId="301" priority="99">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
@@ -29312,9 +29392,9 @@
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
+  <conditionalFormatting sqref="G805:G806">
     <cfRule type="expression" dxfId="296" priority="94">
-      <formula>$C806=TODAY()</formula>
+      <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
@@ -29332,9 +29412,9 @@
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="292" priority="90">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
@@ -29357,9 +29437,9 @@
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="I805:I806">
     <cfRule type="expression" dxfId="287" priority="85">
-      <formula>$C806=TODAY()</formula>
+      <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
@@ -29377,9 +29457,9 @@
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+  <conditionalFormatting sqref="I806">
     <cfRule type="expression" dxfId="283" priority="81">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
@@ -29402,7 +29482,7 @@
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="278" priority="76">
       <formula>$C806=TODAY()</formula>
     </cfRule>
@@ -29447,9 +29527,9 @@
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+  <conditionalFormatting sqref="I808">
     <cfRule type="expression" dxfId="269" priority="67">
-      <formula>$C806=TODAY()</formula>
+      <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
@@ -29467,7 +29547,7 @@
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I808">
+  <conditionalFormatting sqref="K808">
     <cfRule type="expression" dxfId="265" priority="63">
       <formula>$C808=TODAY()</formula>
     </cfRule>
@@ -29487,9 +29567,9 @@
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K808">
+  <conditionalFormatting sqref="E811">
     <cfRule type="expression" dxfId="261" priority="59">
-      <formula>$C808=TODAY()</formula>
+      <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
@@ -29502,7 +29582,7 @@
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E811">
+  <conditionalFormatting sqref="G811">
     <cfRule type="expression" dxfId="258" priority="56">
       <formula>$C811=TODAY()</formula>
     </cfRule>
@@ -29522,7 +29602,7 @@
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+  <conditionalFormatting sqref="I811:I812">
     <cfRule type="expression" dxfId="254" priority="52">
       <formula>$C811=TODAY()</formula>
     </cfRule>
@@ -29542,7 +29622,7 @@
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="250" priority="48">
       <formula>$C811=TODAY()</formula>
     </cfRule>
@@ -29562,9 +29642,9 @@
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
+  <conditionalFormatting sqref="E813:E814">
     <cfRule type="expression" dxfId="246" priority="44">
-      <formula>$C811=TODAY()</formula>
+      <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
@@ -29577,9 +29657,9 @@
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E813:E814">
+  <conditionalFormatting sqref="E814">
     <cfRule type="expression" dxfId="243" priority="41">
-      <formula>$C813=TODAY()</formula>
+      <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
@@ -29602,9 +29682,9 @@
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
+  <conditionalFormatting sqref="G813:G814">
     <cfRule type="expression" dxfId="238" priority="36">
-      <formula>$C814=TODAY()</formula>
+      <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
@@ -29622,9 +29702,9 @@
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="234" priority="32">
-      <formula>$C813=TODAY()</formula>
+      <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
@@ -29647,9 +29727,9 @@
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
+  <conditionalFormatting sqref="I813:I814">
     <cfRule type="expression" dxfId="229" priority="27">
-      <formula>$C814=TODAY()</formula>
+      <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
@@ -29667,9 +29747,9 @@
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
+  <conditionalFormatting sqref="I814">
     <cfRule type="expression" dxfId="225" priority="23">
-      <formula>$C813=TODAY()</formula>
+      <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
@@ -29692,9 +29772,9 @@
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+  <conditionalFormatting sqref="K813:K814">
     <cfRule type="expression" dxfId="220" priority="18">
-      <formula>$C814=TODAY()</formula>
+      <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
@@ -29712,9 +29792,9 @@
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
+  <conditionalFormatting sqref="K814">
     <cfRule type="expression" dxfId="216" priority="14">
-      <formula>$C813=TODAY()</formula>
+      <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
@@ -29737,9 +29817,9 @@
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
+  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
     <cfRule type="expression" dxfId="211" priority="9">
-      <formula>$C814=TODAY()</formula>
+      <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
@@ -29752,34 +29832,34 @@
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
+  <conditionalFormatting sqref="G826 I826:I829 K826:K829">
     <cfRule type="expression" dxfId="208" priority="6">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G826 I826:I829 K826:K829">
+  <conditionalFormatting sqref="K829 I829 G829">
     <cfRule type="expression" dxfId="207" priority="5">
-      <formula>$C826=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K829 I829 G829">
-    <cfRule type="expression" dxfId="206" priority="4">
       <formula>$C829=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I834 G834 K834:K835">
-    <cfRule type="expression" dxfId="205" priority="3">
+    <cfRule type="expression" dxfId="206" priority="4">
       <formula>$C834=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836 G836">
-    <cfRule type="expression" dxfId="204" priority="2">
+    <cfRule type="expression" dxfId="205" priority="3">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837 I837 G837">
-    <cfRule type="expression" dxfId="203" priority="1">
+    <cfRule type="expression" dxfId="204" priority="2">
       <formula>$C837=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K839 I839">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$C839=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -51337,1017 +51417,1017 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="B4:E857">
-    <cfRule type="expression" dxfId="202" priority="381">
+    <cfRule type="expression" dxfId="203" priority="381">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K857">
-    <cfRule type="expression" dxfId="201" priority="382">
+    <cfRule type="expression" dxfId="202" priority="382">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G47 J44:K47">
-    <cfRule type="expression" dxfId="200" priority="391">
+    <cfRule type="expression" dxfId="201" priority="391">
       <formula>$B18=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E692">
-    <cfRule type="expression" dxfId="199" priority="375">
+    <cfRule type="expression" dxfId="200" priority="375">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E694">
-    <cfRule type="expression" dxfId="198" priority="373">
+    <cfRule type="expression" dxfId="199" priority="373">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E701">
-    <cfRule type="expression" dxfId="197" priority="363">
+    <cfRule type="expression" dxfId="198" priority="363">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E703">
-    <cfRule type="expression" dxfId="196" priority="358">
+    <cfRule type="expression" dxfId="197" priority="358">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E710">
-    <cfRule type="expression" dxfId="195" priority="348">
+    <cfRule type="expression" dxfId="196" priority="348">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E712:E714">
-    <cfRule type="expression" dxfId="194" priority="343">
+    <cfRule type="expression" dxfId="195" priority="343">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E719">
-    <cfRule type="expression" dxfId="193" priority="333">
+    <cfRule type="expression" dxfId="194" priority="333">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E721:E723">
-    <cfRule type="expression" dxfId="192" priority="328">
+    <cfRule type="expression" dxfId="193" priority="328">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E728">
-    <cfRule type="expression" dxfId="191" priority="321">
+    <cfRule type="expression" dxfId="192" priority="321">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E730:E732">
-    <cfRule type="expression" dxfId="190" priority="308">
+    <cfRule type="expression" dxfId="191" priority="308">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E737">
-    <cfRule type="expression" dxfId="189" priority="301">
+    <cfRule type="expression" dxfId="190" priority="301">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739:E741">
-    <cfRule type="expression" dxfId="188" priority="288">
+    <cfRule type="expression" dxfId="189" priority="288">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E746">
-    <cfRule type="expression" dxfId="187" priority="278">
+    <cfRule type="expression" dxfId="188" priority="278">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E748:E750">
-    <cfRule type="expression" dxfId="186" priority="256">
+    <cfRule type="expression" dxfId="187" priority="256">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="185" priority="249">
+    <cfRule type="expression" dxfId="186" priority="249">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E759">
-    <cfRule type="expression" dxfId="184" priority="222">
+    <cfRule type="expression" dxfId="185" priority="222">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E764">
-    <cfRule type="expression" dxfId="183" priority="218">
+    <cfRule type="expression" dxfId="184" priority="218">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E766:E768">
-    <cfRule type="expression" dxfId="182" priority="193">
+    <cfRule type="expression" dxfId="183" priority="193">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="181" priority="183">
+    <cfRule type="expression" dxfId="182" priority="183">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E775:E777">
-    <cfRule type="expression" dxfId="180" priority="171">
+    <cfRule type="expression" dxfId="181" priority="171">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="179" priority="149">
+    <cfRule type="expression" dxfId="180" priority="149">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E784:E786">
-    <cfRule type="expression" dxfId="178" priority="131">
+    <cfRule type="expression" dxfId="179" priority="131">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="177" priority="394">
+    <cfRule type="expression" dxfId="178" priority="394">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70">
-    <cfRule type="expression" dxfId="176" priority="403">
+    <cfRule type="expression" dxfId="177" priority="403">
       <formula>$C70=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G685">
-    <cfRule type="expression" dxfId="175" priority="379">
+    <cfRule type="expression" dxfId="176" priority="379">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G692">
-    <cfRule type="expression" dxfId="174" priority="376">
+    <cfRule type="expression" dxfId="175" priority="376">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G695">
-    <cfRule type="expression" dxfId="173" priority="366">
+    <cfRule type="expression" dxfId="174" priority="366">
       <formula>$C695=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701">
-    <cfRule type="expression" dxfId="172" priority="361">
+    <cfRule type="expression" dxfId="173" priority="361">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G704:G705">
-    <cfRule type="expression" dxfId="171" priority="350">
+    <cfRule type="expression" dxfId="172" priority="350">
       <formula>$C704=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G710">
-    <cfRule type="expression" dxfId="170" priority="346">
+    <cfRule type="expression" dxfId="171" priority="346">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G712:G714">
-    <cfRule type="expression" dxfId="169" priority="336">
+    <cfRule type="expression" dxfId="170" priority="336">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G719">
-    <cfRule type="expression" dxfId="168" priority="331">
+    <cfRule type="expression" dxfId="169" priority="331">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G721:G723">
-    <cfRule type="expression" dxfId="167" priority="326">
+    <cfRule type="expression" dxfId="168" priority="326">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G728">
-    <cfRule type="expression" dxfId="166" priority="319">
+    <cfRule type="expression" dxfId="167" priority="319">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G730:G732">
-    <cfRule type="expression" dxfId="165" priority="306">
+    <cfRule type="expression" dxfId="166" priority="306">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G737">
-    <cfRule type="expression" dxfId="164" priority="299">
+    <cfRule type="expression" dxfId="165" priority="299">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739:G741">
-    <cfRule type="expression" dxfId="163" priority="285">
+    <cfRule type="expression" dxfId="164" priority="285">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746">
-    <cfRule type="expression" dxfId="162" priority="276">
+    <cfRule type="expression" dxfId="163" priority="276">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="161" priority="253">
+    <cfRule type="expression" dxfId="162" priority="253">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="160" priority="247">
+    <cfRule type="expression" dxfId="161" priority="247">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G759">
-    <cfRule type="expression" dxfId="159" priority="219">
+    <cfRule type="expression" dxfId="160" priority="219">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G764">
-    <cfRule type="expression" dxfId="158" priority="216">
+    <cfRule type="expression" dxfId="159" priority="216">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G766:G768">
-    <cfRule type="expression" dxfId="157" priority="189">
+    <cfRule type="expression" dxfId="158" priority="189">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="156" priority="181">
+    <cfRule type="expression" dxfId="157" priority="181">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G775:G777">
-    <cfRule type="expression" dxfId="155" priority="164">
+    <cfRule type="expression" dxfId="156" priority="164">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="154" priority="147">
+    <cfRule type="expression" dxfId="155" priority="147">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G784:G786">
-    <cfRule type="expression" dxfId="153" priority="125">
+    <cfRule type="expression" dxfId="154" priority="125">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:I47">
-    <cfRule type="expression" dxfId="152" priority="416">
+    <cfRule type="expression" dxfId="153" priority="416">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="expression" dxfId="151" priority="420">
+    <cfRule type="expression" dxfId="152" priority="420">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I685">
-    <cfRule type="expression" dxfId="150" priority="378">
+    <cfRule type="expression" dxfId="151" priority="378">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I694:I695">
-    <cfRule type="expression" dxfId="149" priority="365">
+    <cfRule type="expression" dxfId="150" priority="365">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I703:I704">
-    <cfRule type="expression" dxfId="148" priority="352">
+    <cfRule type="expression" dxfId="149" priority="352">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I712:I714">
-    <cfRule type="expression" dxfId="147" priority="335">
+    <cfRule type="expression" dxfId="148" priority="335">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I721:I723">
-    <cfRule type="expression" dxfId="146" priority="324">
+    <cfRule type="expression" dxfId="147" priority="324">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I730:I732">
-    <cfRule type="expression" dxfId="145" priority="302">
+    <cfRule type="expression" dxfId="146" priority="302">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I741">
-    <cfRule type="expression" dxfId="144" priority="282">
+    <cfRule type="expression" dxfId="145" priority="282">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I748:I749">
-    <cfRule type="expression" dxfId="143" priority="261">
+    <cfRule type="expression" dxfId="144" priority="261">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755">
-    <cfRule type="expression" dxfId="142" priority="245">
+    <cfRule type="expression" dxfId="143" priority="245">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I757:I758">
-    <cfRule type="expression" dxfId="141" priority="228">
+    <cfRule type="expression" dxfId="142" priority="228">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I766:I768">
-    <cfRule type="expression" dxfId="140" priority="185">
+    <cfRule type="expression" dxfId="141" priority="185">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="139" priority="179">
+    <cfRule type="expression" dxfId="140" priority="179">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I775:I777">
-    <cfRule type="expression" dxfId="138" priority="157">
+    <cfRule type="expression" dxfId="139" priority="157">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="137" priority="145">
+    <cfRule type="expression" dxfId="138" priority="145">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784:I786">
-    <cfRule type="expression" dxfId="136" priority="119">
+    <cfRule type="expression" dxfId="137" priority="119">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="135" priority="395">
+    <cfRule type="expression" dxfId="136" priority="395">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K685">
-    <cfRule type="expression" dxfId="134" priority="377">
+    <cfRule type="expression" dxfId="135" priority="377">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K692">
-    <cfRule type="expression" dxfId="133" priority="374">
+    <cfRule type="expression" dxfId="134" priority="374">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K694:K695">
-    <cfRule type="expression" dxfId="132" priority="364">
+    <cfRule type="expression" dxfId="133" priority="364">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701">
-    <cfRule type="expression" dxfId="131" priority="359">
+    <cfRule type="expression" dxfId="132" priority="359">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K703:K705">
-    <cfRule type="expression" dxfId="130" priority="349">
+    <cfRule type="expression" dxfId="131" priority="349">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K710">
-    <cfRule type="expression" dxfId="129" priority="344">
+    <cfRule type="expression" dxfId="130" priority="344">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K712:K714">
-    <cfRule type="expression" dxfId="128" priority="334">
+    <cfRule type="expression" dxfId="129" priority="334">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K719">
-    <cfRule type="expression" dxfId="127" priority="329">
+    <cfRule type="expression" dxfId="128" priority="329">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K721:K723">
-    <cfRule type="expression" dxfId="126" priority="322">
+    <cfRule type="expression" dxfId="127" priority="322">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K728">
-    <cfRule type="expression" dxfId="125" priority="317">
+    <cfRule type="expression" dxfId="126" priority="317">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K730:K732">
-    <cfRule type="expression" dxfId="124" priority="304">
+    <cfRule type="expression" dxfId="125" priority="304">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K737">
-    <cfRule type="expression" dxfId="123" priority="297">
+    <cfRule type="expression" dxfId="124" priority="297">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K741">
-    <cfRule type="expression" dxfId="122" priority="279">
+    <cfRule type="expression" dxfId="123" priority="279">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K746">
-    <cfRule type="expression" dxfId="121" priority="274">
+    <cfRule type="expression" dxfId="122" priority="274">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K748:K750">
-    <cfRule type="expression" dxfId="120" priority="250">
+    <cfRule type="expression" dxfId="121" priority="250">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755">
-    <cfRule type="expression" dxfId="119" priority="243">
+    <cfRule type="expression" dxfId="120" priority="243">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K757:K758">
-    <cfRule type="expression" dxfId="118" priority="225">
+    <cfRule type="expression" dxfId="119" priority="225">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K764">
-    <cfRule type="expression" dxfId="117" priority="214">
+    <cfRule type="expression" dxfId="118" priority="214">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766:K767">
-    <cfRule type="expression" dxfId="116" priority="196">
+    <cfRule type="expression" dxfId="117" priority="196">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="115" priority="177">
+    <cfRule type="expression" dxfId="116" priority="177">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K775:K777">
-    <cfRule type="expression" dxfId="114" priority="150">
+    <cfRule type="expression" dxfId="115" priority="150">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="113" priority="143">
+    <cfRule type="expression" dxfId="114" priority="143">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784:K786">
-    <cfRule type="expression" dxfId="112" priority="113">
+    <cfRule type="expression" dxfId="113" priority="113">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E792:E793">
-    <cfRule type="expression" dxfId="111" priority="112">
+    <cfRule type="expression" dxfId="112" priority="112">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="110" priority="111">
+    <cfRule type="expression" dxfId="111" priority="111">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="109" priority="110">
+    <cfRule type="expression" dxfId="110" priority="110">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="108" priority="109">
+    <cfRule type="expression" dxfId="109" priority="109">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="107" priority="108">
+    <cfRule type="expression" dxfId="108" priority="108">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="106" priority="107">
+    <cfRule type="expression" dxfId="107" priority="107">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="105" priority="106">
+    <cfRule type="expression" dxfId="106" priority="106">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E794:E795">
-    <cfRule type="expression" dxfId="104" priority="105">
+    <cfRule type="expression" dxfId="105" priority="105">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="103" priority="104">
+    <cfRule type="expression" dxfId="104" priority="104">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="102" priority="103">
+    <cfRule type="expression" dxfId="103" priority="103">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="101" priority="102">
+    <cfRule type="expression" dxfId="102" priority="102">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="100" priority="101">
+    <cfRule type="expression" dxfId="101" priority="101">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="99" priority="100">
+    <cfRule type="expression" dxfId="100" priority="100">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="98" priority="99">
+    <cfRule type="expression" dxfId="99" priority="99">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E801:E802">
-    <cfRule type="expression" dxfId="97" priority="98">
+    <cfRule type="expression" dxfId="98" priority="98">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E803:E805">
-    <cfRule type="expression" dxfId="96" priority="97">
+    <cfRule type="expression" dxfId="97" priority="97">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G805">
-    <cfRule type="expression" dxfId="95" priority="96">
+    <cfRule type="expression" dxfId="96" priority="96">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G802">
-    <cfRule type="expression" dxfId="94" priority="95">
+    <cfRule type="expression" dxfId="95" priority="95">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G803:G805">
-    <cfRule type="expression" dxfId="93" priority="94">
+    <cfRule type="expression" dxfId="94" priority="94">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I805">
-    <cfRule type="expression" dxfId="92" priority="93">
+    <cfRule type="expression" dxfId="93" priority="93">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I802">
-    <cfRule type="expression" dxfId="91" priority="92">
+    <cfRule type="expression" dxfId="92" priority="92">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803:I805">
-    <cfRule type="expression" dxfId="90" priority="91">
+    <cfRule type="expression" dxfId="91" priority="91">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K805">
-    <cfRule type="expression" dxfId="89" priority="90">
+    <cfRule type="expression" dxfId="90" priority="90">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K802">
-    <cfRule type="expression" dxfId="88" priority="89">
+    <cfRule type="expression" dxfId="89" priority="89">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K803:K805">
-    <cfRule type="expression" dxfId="87" priority="88">
+    <cfRule type="expression" dxfId="88" priority="88">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E809:E810">
-    <cfRule type="expression" dxfId="86" priority="87">
+    <cfRule type="expression" dxfId="87" priority="87">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811:E812">
-    <cfRule type="expression" dxfId="85" priority="86">
+    <cfRule type="expression" dxfId="86" priority="86">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G812">
-    <cfRule type="expression" dxfId="84" priority="85">
+    <cfRule type="expression" dxfId="85" priority="85">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G810">
-    <cfRule type="expression" dxfId="83" priority="84">
+    <cfRule type="expression" dxfId="84" priority="84">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811:G812">
-    <cfRule type="expression" dxfId="82" priority="83">
+    <cfRule type="expression" dxfId="83" priority="83">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I812">
-    <cfRule type="expression" dxfId="81" priority="82">
+    <cfRule type="expression" dxfId="82" priority="82">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I810">
-    <cfRule type="expression" dxfId="80" priority="81">
+    <cfRule type="expression" dxfId="81" priority="81">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="79" priority="80">
+    <cfRule type="expression" dxfId="80" priority="80">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K812">
-    <cfRule type="expression" dxfId="78" priority="79">
+    <cfRule type="expression" dxfId="79" priority="79">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K810">
-    <cfRule type="expression" dxfId="77" priority="78">
+    <cfRule type="expression" dxfId="78" priority="78">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811:K812">
-    <cfRule type="expression" dxfId="76" priority="77">
+    <cfRule type="expression" dxfId="77" priority="77">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E818:E822 G818:G822 K818:K822 I818:I822">
-    <cfRule type="expression" dxfId="75" priority="76">
+    <cfRule type="expression" dxfId="76" priority="76">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K818:K822 G818:G822 I818:I822">
-    <cfRule type="expression" dxfId="74" priority="75">
+    <cfRule type="expression" dxfId="75" priority="75">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E820:E821">
-    <cfRule type="expression" dxfId="73" priority="74">
+    <cfRule type="expression" dxfId="74" priority="74">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="72" priority="73">
+    <cfRule type="expression" dxfId="73" priority="73">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="71" priority="72">
+    <cfRule type="expression" dxfId="72" priority="72">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="70" priority="71">
+    <cfRule type="expression" dxfId="71" priority="71">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="69" priority="70">
+    <cfRule type="expression" dxfId="70" priority="70">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K822 G822">
-    <cfRule type="expression" dxfId="68" priority="69">
+    <cfRule type="expression" dxfId="69" priority="69">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I822">
-    <cfRule type="expression" dxfId="67" priority="68">
+    <cfRule type="expression" dxfId="68" priority="68">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E828:E831">
-    <cfRule type="expression" dxfId="66" priority="67">
+    <cfRule type="expression" dxfId="67" priority="67">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="65" priority="66">
+    <cfRule type="expression" dxfId="66" priority="66">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="64" priority="65">
+    <cfRule type="expression" dxfId="65" priority="65">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="63" priority="64">
+    <cfRule type="expression" dxfId="64" priority="64">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="62" priority="63">
+    <cfRule type="expression" dxfId="63" priority="63">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="61" priority="62">
+    <cfRule type="expression" dxfId="62" priority="62">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="60" priority="61">
+    <cfRule type="expression" dxfId="61" priority="61">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="59" priority="60">
+    <cfRule type="expression" dxfId="60" priority="60">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="58" priority="59">
+    <cfRule type="expression" dxfId="59" priority="59">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="57" priority="58">
+    <cfRule type="expression" dxfId="58" priority="58">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="56" priority="57">
+    <cfRule type="expression" dxfId="57" priority="57">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="55" priority="56">
+    <cfRule type="expression" dxfId="56" priority="56">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="54" priority="55">
+    <cfRule type="expression" dxfId="55" priority="55">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="53" priority="54">
+    <cfRule type="expression" dxfId="54" priority="54">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837">
-    <cfRule type="expression" dxfId="52" priority="53">
+    <cfRule type="expression" dxfId="53" priority="53">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="51" priority="52">
+    <cfRule type="expression" dxfId="52" priority="52">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="50" priority="51">
+    <cfRule type="expression" dxfId="51" priority="51">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="49" priority="50">
+    <cfRule type="expression" dxfId="50" priority="50">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="48" priority="49">
+    <cfRule type="expression" dxfId="49" priority="49">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="47" priority="48">
+    <cfRule type="expression" dxfId="48" priority="48">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="46" priority="47">
+    <cfRule type="expression" dxfId="47" priority="47">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E845:E847">
-    <cfRule type="expression" dxfId="45" priority="46">
+    <cfRule type="expression" dxfId="46" priority="46">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="44" priority="45">
+    <cfRule type="expression" dxfId="45" priority="45">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="43" priority="44">
+    <cfRule type="expression" dxfId="44" priority="44">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="42" priority="43">
+    <cfRule type="expression" dxfId="43" priority="43">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="41" priority="42">
+    <cfRule type="expression" dxfId="42" priority="42">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="40" priority="41">
+    <cfRule type="expression" dxfId="41" priority="41">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="39" priority="40">
+    <cfRule type="expression" dxfId="40" priority="40">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="38" priority="39">
+    <cfRule type="expression" dxfId="39" priority="39">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="37" priority="38">
+    <cfRule type="expression" dxfId="38" priority="38">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="36" priority="37">
+    <cfRule type="expression" dxfId="37" priority="37">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="35" priority="36">
+    <cfRule type="expression" dxfId="36" priority="36">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="34" priority="35">
+    <cfRule type="expression" dxfId="35" priority="35">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="33" priority="34">
+    <cfRule type="expression" dxfId="34" priority="34">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="32" priority="33">
+    <cfRule type="expression" dxfId="33" priority="33">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="31" priority="32">
+    <cfRule type="expression" dxfId="32" priority="32">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="30" priority="31">
+    <cfRule type="expression" dxfId="31" priority="31">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="29" priority="30">
+    <cfRule type="expression" dxfId="30" priority="30">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="28" priority="29">
+    <cfRule type="expression" dxfId="29" priority="29">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="27" priority="28">
+    <cfRule type="expression" dxfId="28" priority="28">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="26" priority="27">
+    <cfRule type="expression" dxfId="27" priority="27">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="25" priority="26">
+    <cfRule type="expression" dxfId="26" priority="26">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="24" priority="25">
+    <cfRule type="expression" dxfId="25" priority="25">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="23" priority="24">
+    <cfRule type="expression" dxfId="24" priority="24">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="22" priority="23">
+    <cfRule type="expression" dxfId="23" priority="23">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="22" priority="22">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="20" priority="21">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="19" priority="20">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="18" priority="19">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="16" priority="16">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E836">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="15" priority="15">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="14" priority="14">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="12" priority="13">
+    <cfRule type="expression" dxfId="13" priority="13">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853 E853">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854 E854">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>

--- a/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
+++ b/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF55D53A-DE99-4D36-AA98-4F3FEF6881C7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3C2B28-785F-46AD-9CF0-28F9A3E8D9AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3433" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3464" uniqueCount="33">
   <si>
     <t>План поставок ПОКОМ</t>
   </si>
@@ -435,7 +435,63 @@
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Обычный 2 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="496">
+  <dxfs count="504">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4289,7 +4345,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMD842"/>
+  <dimension ref="A1:AMD846"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
@@ -28383,1483 +28439,1584 @@
       <c r="C842" s="8">
         <v>46042</v>
       </c>
-      <c r="D842" s="9"/>
-      <c r="E842" s="10"/>
-      <c r="F842" s="11"/>
-      <c r="G842" s="12"/>
-      <c r="H842" s="11"/>
-      <c r="I842" s="12"/>
-      <c r="J842" s="11"/>
-      <c r="K842" s="12"/>
+      <c r="D842" s="9">
+        <v>2100</v>
+      </c>
+      <c r="E842" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F842" s="11">
+        <v>1400</v>
+      </c>
+      <c r="G842" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H842" s="11">
+        <v>8300</v>
+      </c>
+      <c r="I842" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J842" s="11">
+        <v>4900</v>
+      </c>
+      <c r="K842" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="843" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A843" s="1">
+        <v>839</v>
+      </c>
+      <c r="B843" s="7" t="str">
+        <f t="shared" ref="B843:B846" si="138">IF(C843&lt;&gt;"",TEXT(C843,"ДДД"),"")</f>
+        <v>Ср</v>
+      </c>
+      <c r="C843" s="8">
+        <v>46043</v>
+      </c>
+      <c r="D843" s="9"/>
+      <c r="E843" s="10"/>
+      <c r="F843" s="11"/>
+      <c r="G843" s="12"/>
+      <c r="H843" s="11"/>
+      <c r="I843" s="12"/>
+      <c r="J843" s="11"/>
+      <c r="K843" s="12"/>
+    </row>
+    <row r="844" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A844" s="1">
+        <v>840</v>
+      </c>
+      <c r="B844" s="7" t="str">
+        <f t="shared" si="138"/>
+        <v>Чт</v>
+      </c>
+      <c r="C844" s="8">
+        <v>46044</v>
+      </c>
+      <c r="D844" s="9"/>
+      <c r="E844" s="10"/>
+      <c r="F844" s="11"/>
+      <c r="G844" s="12"/>
+      <c r="H844" s="11"/>
+      <c r="I844" s="12"/>
+      <c r="J844" s="11"/>
+      <c r="K844" s="12"/>
+    </row>
+    <row r="845" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A845" s="1">
+        <v>841</v>
+      </c>
+      <c r="B845" s="7" t="str">
+        <f t="shared" si="138"/>
+        <v>Пт</v>
+      </c>
+      <c r="C845" s="8">
+        <v>46045</v>
+      </c>
+      <c r="D845" s="9"/>
+      <c r="E845" s="10"/>
+      <c r="F845" s="11"/>
+      <c r="G845" s="12"/>
+      <c r="H845" s="11"/>
+      <c r="I845" s="12"/>
+      <c r="J845" s="11"/>
+      <c r="K845" s="12"/>
+    </row>
+    <row r="846" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A846" s="1">
+        <v>842</v>
+      </c>
+      <c r="B846" s="7" t="str">
+        <f t="shared" si="138"/>
+        <v>Сб</v>
+      </c>
+      <c r="C846" s="8">
+        <v>46046</v>
+      </c>
+      <c r="D846" s="9"/>
+      <c r="E846" s="10"/>
+      <c r="F846" s="11"/>
+      <c r="G846" s="12"/>
+      <c r="H846" s="11"/>
+      <c r="I846" s="12"/>
+      <c r="J846" s="11"/>
+      <c r="K846" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:E842">
-    <cfRule type="expression" dxfId="495" priority="712">
+  <conditionalFormatting sqref="B4:E846">
+    <cfRule type="expression" dxfId="503" priority="713">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:M683 B684:K842">
-    <cfRule type="expression" dxfId="494" priority="713">
+  <conditionalFormatting sqref="B4:M683 B684:K846">
+    <cfRule type="expression" dxfId="502" priority="714">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E678">
-    <cfRule type="expression" dxfId="493" priority="703">
+    <cfRule type="expression" dxfId="501" priority="704">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E693:E694">
-    <cfRule type="expression" dxfId="492" priority="690">
+    <cfRule type="expression" dxfId="500" priority="691">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E702">
-    <cfRule type="expression" dxfId="491" priority="677">
+    <cfRule type="expression" dxfId="499" priority="678">
       <formula>$C702=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E707">
-    <cfRule type="expression" dxfId="490" priority="673">
+    <cfRule type="expression" dxfId="498" priority="674">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709:E710">
-    <cfRule type="expression" dxfId="489" priority="665">
+    <cfRule type="expression" dxfId="497" priority="666">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E715">
-    <cfRule type="expression" dxfId="488" priority="661">
+    <cfRule type="expression" dxfId="496" priority="662">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E717:E718">
-    <cfRule type="expression" dxfId="487" priority="649">
+    <cfRule type="expression" dxfId="495" priority="650">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E723">
-    <cfRule type="expression" dxfId="486" priority="638">
+    <cfRule type="expression" dxfId="494" priority="639">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E725:E726">
-    <cfRule type="expression" dxfId="485" priority="615">
+    <cfRule type="expression" dxfId="493" priority="616">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E731">
-    <cfRule type="expression" dxfId="484" priority="603">
+    <cfRule type="expression" dxfId="492" priority="604">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E733:E734">
-    <cfRule type="expression" dxfId="483" priority="570">
+    <cfRule type="expression" dxfId="491" priority="571">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739">
-    <cfRule type="expression" dxfId="482" priority="538">
+    <cfRule type="expression" dxfId="490" priority="539">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E741:E742">
-    <cfRule type="expression" dxfId="481" priority="493">
+    <cfRule type="expression" dxfId="489" priority="494">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E747:E748">
-    <cfRule type="expression" dxfId="480" priority="430">
+    <cfRule type="expression" dxfId="488" priority="431">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E750">
-    <cfRule type="expression" dxfId="479" priority="414">
+    <cfRule type="expression" dxfId="487" priority="415">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="478" priority="388">
+    <cfRule type="expression" dxfId="486" priority="389">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E758">
-    <cfRule type="expression" dxfId="477" priority="340">
+    <cfRule type="expression" dxfId="485" priority="341">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E763">
-    <cfRule type="expression" dxfId="476" priority="313">
+    <cfRule type="expression" dxfId="484" priority="314">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E765:E766">
-    <cfRule type="expression" dxfId="475" priority="260">
+    <cfRule type="expression" dxfId="483" priority="261">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E771">
-    <cfRule type="expression" dxfId="474" priority="215">
+    <cfRule type="expression" dxfId="482" priority="216">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="473" priority="726">
+    <cfRule type="expression" dxfId="481" priority="727">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G661">
-    <cfRule type="expression" dxfId="472" priority="710">
+    <cfRule type="expression" dxfId="480" priority="711">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G670">
-    <cfRule type="expression" dxfId="471" priority="707">
+    <cfRule type="expression" dxfId="479" priority="708">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G678">
-    <cfRule type="expression" dxfId="470" priority="704">
+    <cfRule type="expression" dxfId="478" priority="705">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G686">
-    <cfRule type="expression" dxfId="469" priority="700">
+    <cfRule type="expression" dxfId="477" priority="701">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G691">
-    <cfRule type="expression" dxfId="468" priority="697">
+    <cfRule type="expression" dxfId="476" priority="698">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G693:G694">
-    <cfRule type="expression" dxfId="467" priority="689">
+    <cfRule type="expression" dxfId="475" priority="690">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G699">
-    <cfRule type="expression" dxfId="466" priority="686">
+    <cfRule type="expression" dxfId="474" priority="687">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701:G702">
-    <cfRule type="expression" dxfId="465" priority="678">
+    <cfRule type="expression" dxfId="473" priority="679">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G707">
-    <cfRule type="expression" dxfId="464" priority="674">
+    <cfRule type="expression" dxfId="472" priority="675">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G709:G710">
-    <cfRule type="expression" dxfId="463" priority="664">
+    <cfRule type="expression" dxfId="471" priority="665">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G715">
-    <cfRule type="expression" dxfId="462" priority="659">
+    <cfRule type="expression" dxfId="470" priority="660">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G717:G718">
-    <cfRule type="expression" dxfId="461" priority="646">
+    <cfRule type="expression" dxfId="469" priority="647">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G723">
-    <cfRule type="expression" dxfId="460" priority="635">
+    <cfRule type="expression" dxfId="468" priority="636">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G725:G726">
-    <cfRule type="expression" dxfId="459" priority="612">
+    <cfRule type="expression" dxfId="467" priority="613">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G731">
-    <cfRule type="expression" dxfId="458" priority="599">
+    <cfRule type="expression" dxfId="466" priority="600">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G733:G734">
-    <cfRule type="expression" dxfId="457" priority="564">
+    <cfRule type="expression" dxfId="465" priority="565">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739">
-    <cfRule type="expression" dxfId="456" priority="533">
+    <cfRule type="expression" dxfId="464" priority="534">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G741:G742">
-    <cfRule type="expression" dxfId="455" priority="487">
+    <cfRule type="expression" dxfId="463" priority="488">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G747">
-    <cfRule type="expression" dxfId="454" priority="450">
+    <cfRule type="expression" dxfId="462" priority="451">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="453" priority="407">
+    <cfRule type="expression" dxfId="461" priority="408">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="452" priority="382">
+    <cfRule type="expression" dxfId="460" priority="383">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G758">
-    <cfRule type="expression" dxfId="451" priority="333">
+    <cfRule type="expression" dxfId="459" priority="334">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763">
-    <cfRule type="expression" dxfId="450" priority="306">
+    <cfRule type="expression" dxfId="458" priority="307">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G765:G766">
-    <cfRule type="expression" dxfId="449" priority="247">
+    <cfRule type="expression" dxfId="457" priority="248">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G771">
-    <cfRule type="expression" dxfId="448" priority="208">
+    <cfRule type="expression" dxfId="456" priority="209">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H128:I129">
-    <cfRule type="expression" dxfId="447" priority="729">
+    <cfRule type="expression" dxfId="455" priority="730">
       <formula>$C128=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="expression" dxfId="446" priority="727">
+    <cfRule type="expression" dxfId="454" priority="728">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I661">
-    <cfRule type="expression" dxfId="445" priority="709">
+    <cfRule type="expression" dxfId="453" priority="710">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670">
-    <cfRule type="expression" dxfId="444" priority="706">
+    <cfRule type="expression" dxfId="452" priority="707">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I678">
-    <cfRule type="expression" dxfId="443" priority="702">
+    <cfRule type="expression" dxfId="451" priority="703">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I686">
-    <cfRule type="expression" dxfId="442" priority="699">
+    <cfRule type="expression" dxfId="450" priority="700">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I691">
-    <cfRule type="expression" dxfId="441" priority="696">
+    <cfRule type="expression" dxfId="449" priority="697">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I693:I694">
-    <cfRule type="expression" dxfId="440" priority="688">
+    <cfRule type="expression" dxfId="448" priority="689">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I699">
-    <cfRule type="expression" dxfId="439" priority="685">
+    <cfRule type="expression" dxfId="447" priority="686">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I701:I702">
-    <cfRule type="expression" dxfId="438" priority="679">
+    <cfRule type="expression" dxfId="446" priority="680">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I707">
-    <cfRule type="expression" dxfId="437" priority="676">
+    <cfRule type="expression" dxfId="445" priority="677">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I709:I710">
-    <cfRule type="expression" dxfId="436" priority="663">
+    <cfRule type="expression" dxfId="444" priority="664">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I715">
-    <cfRule type="expression" dxfId="435" priority="657">
+    <cfRule type="expression" dxfId="443" priority="658">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I717:I718">
-    <cfRule type="expression" dxfId="434" priority="643">
+    <cfRule type="expression" dxfId="442" priority="644">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I723:I726">
-    <cfRule type="expression" dxfId="433" priority="609">
+    <cfRule type="expression" dxfId="441" priority="610">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I731:I734">
-    <cfRule type="expression" dxfId="432" priority="558">
+    <cfRule type="expression" dxfId="440" priority="559">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I736">
-    <cfRule type="expression" dxfId="431" priority="547">
+    <cfRule type="expression" dxfId="439" priority="548">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I742">
-    <cfRule type="expression" dxfId="430" priority="481">
+    <cfRule type="expression" dxfId="438" priority="482">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I744">
-    <cfRule type="expression" dxfId="429" priority="465">
+    <cfRule type="expression" dxfId="437" priority="466">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I747:I748">
-    <cfRule type="expression" dxfId="428" priority="435">
+    <cfRule type="expression" dxfId="436" priority="436">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I750">
-    <cfRule type="expression" dxfId="427" priority="400">
+    <cfRule type="expression" dxfId="435" priority="401">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755:I756">
-    <cfRule type="expression" dxfId="426" priority="364">
+    <cfRule type="expression" dxfId="434" priority="365">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I758">
-    <cfRule type="expression" dxfId="425" priority="326">
+    <cfRule type="expression" dxfId="433" priority="327">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I763">
-    <cfRule type="expression" dxfId="424" priority="299">
+    <cfRule type="expression" dxfId="432" priority="300">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I765:I766">
-    <cfRule type="expression" dxfId="423" priority="234">
+    <cfRule type="expression" dxfId="431" priority="235">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I771:I772">
-    <cfRule type="expression" dxfId="422" priority="201">
+    <cfRule type="expression" dxfId="430" priority="202">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="421" priority="728">
+    <cfRule type="expression" dxfId="429" priority="729">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K661">
-    <cfRule type="expression" dxfId="420" priority="708">
+    <cfRule type="expression" dxfId="428" priority="709">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K670">
-    <cfRule type="expression" dxfId="419" priority="705">
+    <cfRule type="expression" dxfId="427" priority="706">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K678">
-    <cfRule type="expression" dxfId="418" priority="701">
+    <cfRule type="expression" dxfId="426" priority="702">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K686">
-    <cfRule type="expression" dxfId="417" priority="698">
+    <cfRule type="expression" dxfId="425" priority="699">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K691">
-    <cfRule type="expression" dxfId="416" priority="695">
+    <cfRule type="expression" dxfId="424" priority="696">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K693:K694">
-    <cfRule type="expression" dxfId="415" priority="687">
+    <cfRule type="expression" dxfId="423" priority="688">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K699">
-    <cfRule type="expression" dxfId="414" priority="684">
+    <cfRule type="expression" dxfId="422" priority="685">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701:K702">
-    <cfRule type="expression" dxfId="413" priority="680">
+    <cfRule type="expression" dxfId="421" priority="681">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K707">
-    <cfRule type="expression" dxfId="412" priority="675">
+    <cfRule type="expression" dxfId="420" priority="676">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K709:K710">
-    <cfRule type="expression" dxfId="411" priority="662">
+    <cfRule type="expression" dxfId="419" priority="663">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K715:K718">
-    <cfRule type="expression" dxfId="410" priority="640">
+    <cfRule type="expression" dxfId="418" priority="641">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K723">
-    <cfRule type="expression" dxfId="409" priority="629">
+    <cfRule type="expression" dxfId="417" priority="630">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K725:K726">
-    <cfRule type="expression" dxfId="408" priority="606">
+    <cfRule type="expression" dxfId="416" priority="607">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K731">
-    <cfRule type="expression" dxfId="407" priority="591">
+    <cfRule type="expression" dxfId="415" priority="592">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K733:K734">
-    <cfRule type="expression" dxfId="406" priority="552">
+    <cfRule type="expression" dxfId="414" priority="553">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K736">
-    <cfRule type="expression" dxfId="405" priority="542">
+    <cfRule type="expression" dxfId="413" priority="543">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K742">
-    <cfRule type="expression" dxfId="404" priority="470">
+    <cfRule type="expression" dxfId="412" priority="471">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K744">
-    <cfRule type="expression" dxfId="403" priority="460">
+    <cfRule type="expression" dxfId="411" priority="461">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K747">
-    <cfRule type="expression" dxfId="402" priority="440">
+    <cfRule type="expression" dxfId="410" priority="441">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K749:K750">
-    <cfRule type="expression" dxfId="401" priority="393">
+    <cfRule type="expression" dxfId="409" priority="394">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755:K756">
-    <cfRule type="expression" dxfId="400" priority="358">
+    <cfRule type="expression" dxfId="408" priority="359">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K758">
-    <cfRule type="expression" dxfId="399" priority="319">
+    <cfRule type="expression" dxfId="407" priority="320">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K763:K764">
-    <cfRule type="expression" dxfId="398" priority="292">
+    <cfRule type="expression" dxfId="406" priority="293">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766">
-    <cfRule type="expression" dxfId="397" priority="221">
+    <cfRule type="expression" dxfId="405" priority="222">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K771">
-    <cfRule type="expression" dxfId="396" priority="194">
+    <cfRule type="expression" dxfId="404" priority="195">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="395" priority="193">
+    <cfRule type="expression" dxfId="403" priority="194">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="394" priority="192">
+    <cfRule type="expression" dxfId="402" priority="193">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="393" priority="191">
+    <cfRule type="expression" dxfId="401" priority="192">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="392" priority="190">
+    <cfRule type="expression" dxfId="400" priority="191">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="391" priority="189">
+    <cfRule type="expression" dxfId="399" priority="190">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="390" priority="188">
+    <cfRule type="expression" dxfId="398" priority="189">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="389" priority="187">
+    <cfRule type="expression" dxfId="397" priority="188">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E774">
-    <cfRule type="expression" dxfId="388" priority="186">
+    <cfRule type="expression" dxfId="396" priority="187">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G774">
-    <cfRule type="expression" dxfId="387" priority="185">
+    <cfRule type="expression" dxfId="395" priority="186">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I774">
-    <cfRule type="expression" dxfId="386" priority="184">
+    <cfRule type="expression" dxfId="394" priority="185">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K774">
-    <cfRule type="expression" dxfId="385" priority="183">
+    <cfRule type="expression" dxfId="393" priority="184">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="384" priority="182">
+    <cfRule type="expression" dxfId="392" priority="183">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="383" priority="181">
+    <cfRule type="expression" dxfId="391" priority="182">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="382" priority="180">
+    <cfRule type="expression" dxfId="390" priority="181">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="381" priority="179">
+    <cfRule type="expression" dxfId="389" priority="180">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E779">
-    <cfRule type="expression" dxfId="380" priority="178">
+    <cfRule type="expression" dxfId="388" priority="179">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="379" priority="177">
+    <cfRule type="expression" dxfId="387" priority="178">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="378" priority="176">
+    <cfRule type="expression" dxfId="386" priority="177">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="377" priority="175">
+    <cfRule type="expression" dxfId="385" priority="176">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="376" priority="174">
+    <cfRule type="expression" dxfId="384" priority="175">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="375" priority="173">
+    <cfRule type="expression" dxfId="383" priority="174">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="374" priority="172">
+    <cfRule type="expression" dxfId="382" priority="173">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="373" priority="171">
+    <cfRule type="expression" dxfId="381" priority="172">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="372" priority="170">
+    <cfRule type="expression" dxfId="380" priority="171">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="371" priority="169">
+    <cfRule type="expression" dxfId="379" priority="170">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="370" priority="168">
+    <cfRule type="expression" dxfId="378" priority="169">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="369" priority="167">
+    <cfRule type="expression" dxfId="377" priority="168">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="368" priority="166">
+    <cfRule type="expression" dxfId="376" priority="167">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="367" priority="165">
+    <cfRule type="expression" dxfId="375" priority="166">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="366" priority="164">
+    <cfRule type="expression" dxfId="374" priority="165">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="365" priority="163">
+    <cfRule type="expression" dxfId="373" priority="164">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="364" priority="162">
+    <cfRule type="expression" dxfId="372" priority="163">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="363" priority="161">
+    <cfRule type="expression" dxfId="371" priority="162">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="362" priority="160">
+    <cfRule type="expression" dxfId="370" priority="161">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="361" priority="159">
+    <cfRule type="expression" dxfId="369" priority="160">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="360" priority="158">
+    <cfRule type="expression" dxfId="368" priority="159">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="359" priority="157">
+    <cfRule type="expression" dxfId="367" priority="158">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="358" priority="156">
+    <cfRule type="expression" dxfId="366" priority="157">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="357" priority="155">
+    <cfRule type="expression" dxfId="365" priority="156">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="356" priority="154">
+    <cfRule type="expression" dxfId="364" priority="155">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="355" priority="153">
+    <cfRule type="expression" dxfId="363" priority="154">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="354" priority="152">
+    <cfRule type="expression" dxfId="362" priority="153">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="353" priority="151">
+    <cfRule type="expression" dxfId="361" priority="152">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
-    <cfRule type="expression" dxfId="352" priority="150">
+    <cfRule type="expression" dxfId="360" priority="151">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
-    <cfRule type="expression" dxfId="351" priority="149">
+    <cfRule type="expression" dxfId="359" priority="150">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="350" priority="148">
+    <cfRule type="expression" dxfId="358" priority="149">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="349" priority="147">
+    <cfRule type="expression" dxfId="357" priority="148">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="348" priority="146">
+    <cfRule type="expression" dxfId="356" priority="147">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="347" priority="145">
+    <cfRule type="expression" dxfId="355" priority="146">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="346" priority="144">
+    <cfRule type="expression" dxfId="354" priority="145">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="345" priority="143">
+    <cfRule type="expression" dxfId="353" priority="144">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="344" priority="142">
+    <cfRule type="expression" dxfId="352" priority="143">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="343" priority="141">
+    <cfRule type="expression" dxfId="351" priority="142">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="342" priority="140">
+    <cfRule type="expression" dxfId="350" priority="141">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
-    <cfRule type="expression" dxfId="341" priority="137">
+    <cfRule type="expression" dxfId="349" priority="138">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="340" priority="139">
+    <cfRule type="expression" dxfId="348" priority="140">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="339" priority="138">
+    <cfRule type="expression" dxfId="347" priority="139">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="338" priority="136">
+    <cfRule type="expression" dxfId="346" priority="137">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="337" priority="135">
+    <cfRule type="expression" dxfId="345" priority="136">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="336" priority="134">
+    <cfRule type="expression" dxfId="344" priority="135">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790">
-    <cfRule type="expression" dxfId="335" priority="133">
+    <cfRule type="expression" dxfId="343" priority="134">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="334" priority="130">
+    <cfRule type="expression" dxfId="342" priority="131">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="333" priority="132">
+    <cfRule type="expression" dxfId="341" priority="133">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="332" priority="131">
+    <cfRule type="expression" dxfId="340" priority="132">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="331" priority="127">
+    <cfRule type="expression" dxfId="339" priority="128">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="330" priority="129">
+    <cfRule type="expression" dxfId="338" priority="130">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="329" priority="128">
+    <cfRule type="expression" dxfId="337" priority="129">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
-    <cfRule type="expression" dxfId="328" priority="126">
+    <cfRule type="expression" dxfId="336" priority="127">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
-    <cfRule type="expression" dxfId="327" priority="125">
+    <cfRule type="expression" dxfId="335" priority="126">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="326" priority="124">
+    <cfRule type="expression" dxfId="334" priority="125">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="325" priority="123">
+    <cfRule type="expression" dxfId="333" priority="124">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="324" priority="122">
+    <cfRule type="expression" dxfId="332" priority="123">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="323" priority="121">
+    <cfRule type="expression" dxfId="331" priority="122">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="322" priority="120">
+    <cfRule type="expression" dxfId="330" priority="121">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="321" priority="119">
+    <cfRule type="expression" dxfId="329" priority="120">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="320" priority="118">
+    <cfRule type="expression" dxfId="328" priority="119">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="319" priority="117">
+    <cfRule type="expression" dxfId="327" priority="118">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="318" priority="116">
+    <cfRule type="expression" dxfId="326" priority="117">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="317" priority="115">
+    <cfRule type="expression" dxfId="325" priority="116">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="316" priority="114">
+    <cfRule type="expression" dxfId="324" priority="115">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="315" priority="113">
+    <cfRule type="expression" dxfId="323" priority="114">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="314" priority="112">
+    <cfRule type="expression" dxfId="322" priority="113">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="313" priority="111">
+    <cfRule type="expression" dxfId="321" priority="112">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="312" priority="110">
+    <cfRule type="expression" dxfId="320" priority="111">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="311" priority="109">
+    <cfRule type="expression" dxfId="319" priority="110">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="310" priority="108">
+    <cfRule type="expression" dxfId="318" priority="109">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798">
-    <cfRule type="expression" dxfId="309" priority="107">
+    <cfRule type="expression" dxfId="317" priority="108">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="308" priority="106">
+    <cfRule type="expression" dxfId="316" priority="107">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="307" priority="105">
+    <cfRule type="expression" dxfId="315" priority="106">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="306" priority="104">
+    <cfRule type="expression" dxfId="314" priority="105">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 K803:K805">
-    <cfRule type="expression" dxfId="305" priority="103">
+    <cfRule type="expression" dxfId="313" priority="104">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="304" priority="102">
+    <cfRule type="expression" dxfId="312" priority="103">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="303" priority="101">
+    <cfRule type="expression" dxfId="311" priority="102">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="302" priority="100">
+    <cfRule type="expression" dxfId="310" priority="101">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="301" priority="99">
+    <cfRule type="expression" dxfId="309" priority="100">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="300" priority="98">
+    <cfRule type="expression" dxfId="308" priority="99">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="299" priority="97">
+    <cfRule type="expression" dxfId="307" priority="98">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="298" priority="96">
+    <cfRule type="expression" dxfId="306" priority="97">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="297" priority="95">
+    <cfRule type="expression" dxfId="305" priority="96">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="296" priority="94">
+    <cfRule type="expression" dxfId="304" priority="95">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="295" priority="93">
+    <cfRule type="expression" dxfId="303" priority="94">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="294" priority="92">
+    <cfRule type="expression" dxfId="302" priority="93">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="293" priority="91">
+    <cfRule type="expression" dxfId="301" priority="92">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="292" priority="90">
+    <cfRule type="expression" dxfId="300" priority="91">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="291" priority="89">
+    <cfRule type="expression" dxfId="299" priority="90">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="290" priority="88">
+    <cfRule type="expression" dxfId="298" priority="89">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="289" priority="87">
+    <cfRule type="expression" dxfId="297" priority="88">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="288" priority="86">
+    <cfRule type="expression" dxfId="296" priority="87">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="287" priority="85">
+    <cfRule type="expression" dxfId="295" priority="86">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="286" priority="84">
+    <cfRule type="expression" dxfId="294" priority="85">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="285" priority="83">
+    <cfRule type="expression" dxfId="293" priority="84">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="284" priority="82">
+    <cfRule type="expression" dxfId="292" priority="83">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="283" priority="81">
+    <cfRule type="expression" dxfId="291" priority="82">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="282" priority="80">
+    <cfRule type="expression" dxfId="290" priority="81">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="281" priority="79">
+    <cfRule type="expression" dxfId="289" priority="80">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="280" priority="78">
+    <cfRule type="expression" dxfId="288" priority="79">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="279" priority="77">
+    <cfRule type="expression" dxfId="287" priority="78">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="278" priority="76">
+    <cfRule type="expression" dxfId="286" priority="77">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="277" priority="75">
+    <cfRule type="expression" dxfId="285" priority="76">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="276" priority="74">
+    <cfRule type="expression" dxfId="284" priority="75">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="275" priority="73">
+    <cfRule type="expression" dxfId="283" priority="74">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="274" priority="72">
+    <cfRule type="expression" dxfId="282" priority="73">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="273" priority="71">
+    <cfRule type="expression" dxfId="281" priority="72">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="272" priority="70">
+    <cfRule type="expression" dxfId="280" priority="71">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="271" priority="69">
+    <cfRule type="expression" dxfId="279" priority="70">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="270" priority="68">
+    <cfRule type="expression" dxfId="278" priority="69">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="269" priority="67">
+    <cfRule type="expression" dxfId="277" priority="68">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="268" priority="66">
+    <cfRule type="expression" dxfId="276" priority="67">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="267" priority="65">
+    <cfRule type="expression" dxfId="275" priority="66">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="266" priority="64">
+    <cfRule type="expression" dxfId="274" priority="65">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="265" priority="63">
+    <cfRule type="expression" dxfId="273" priority="64">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="264" priority="62">
+    <cfRule type="expression" dxfId="272" priority="63">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="263" priority="61">
+    <cfRule type="expression" dxfId="271" priority="62">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="262" priority="60">
+    <cfRule type="expression" dxfId="270" priority="61">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="261" priority="59">
+    <cfRule type="expression" dxfId="269" priority="60">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="260" priority="58">
+    <cfRule type="expression" dxfId="268" priority="59">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="259" priority="57">
+    <cfRule type="expression" dxfId="267" priority="58">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="258" priority="56">
+    <cfRule type="expression" dxfId="266" priority="57">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="257" priority="55">
+    <cfRule type="expression" dxfId="265" priority="56">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="256" priority="54">
+    <cfRule type="expression" dxfId="264" priority="55">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="255" priority="53">
+    <cfRule type="expression" dxfId="263" priority="54">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="254" priority="52">
+    <cfRule type="expression" dxfId="262" priority="53">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="253" priority="51">
+    <cfRule type="expression" dxfId="261" priority="52">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="252" priority="50">
+    <cfRule type="expression" dxfId="260" priority="51">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="251" priority="49">
+    <cfRule type="expression" dxfId="259" priority="50">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="250" priority="48">
+    <cfRule type="expression" dxfId="258" priority="49">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="249" priority="47">
+    <cfRule type="expression" dxfId="257" priority="48">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="248" priority="46">
+    <cfRule type="expression" dxfId="256" priority="47">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="247" priority="45">
+    <cfRule type="expression" dxfId="255" priority="46">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="246" priority="44">
+    <cfRule type="expression" dxfId="254" priority="45">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="245" priority="43">
+    <cfRule type="expression" dxfId="253" priority="44">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="244" priority="42">
+    <cfRule type="expression" dxfId="252" priority="43">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="243" priority="41">
+    <cfRule type="expression" dxfId="251" priority="42">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="242" priority="40">
+    <cfRule type="expression" dxfId="250" priority="41">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="241" priority="39">
+    <cfRule type="expression" dxfId="249" priority="40">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="240" priority="38">
+    <cfRule type="expression" dxfId="248" priority="39">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="239" priority="37">
+    <cfRule type="expression" dxfId="247" priority="38">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="238" priority="36">
+    <cfRule type="expression" dxfId="246" priority="37">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="237" priority="35">
+    <cfRule type="expression" dxfId="245" priority="36">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="236" priority="34">
+    <cfRule type="expression" dxfId="244" priority="35">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="235" priority="33">
+    <cfRule type="expression" dxfId="243" priority="34">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="234" priority="32">
+    <cfRule type="expression" dxfId="242" priority="33">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="233" priority="31">
+    <cfRule type="expression" dxfId="241" priority="32">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="232" priority="30">
+    <cfRule type="expression" dxfId="240" priority="31">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="231" priority="29">
+    <cfRule type="expression" dxfId="239" priority="30">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="230" priority="28">
+    <cfRule type="expression" dxfId="238" priority="29">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="229" priority="27">
+    <cfRule type="expression" dxfId="237" priority="28">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="228" priority="26">
+    <cfRule type="expression" dxfId="236" priority="27">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="227" priority="25">
+    <cfRule type="expression" dxfId="235" priority="26">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="226" priority="24">
+    <cfRule type="expression" dxfId="234" priority="25">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="225" priority="23">
+    <cfRule type="expression" dxfId="233" priority="24">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="224" priority="22">
+    <cfRule type="expression" dxfId="232" priority="23">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="223" priority="21">
+    <cfRule type="expression" dxfId="231" priority="22">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="222" priority="20">
+    <cfRule type="expression" dxfId="230" priority="21">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="221" priority="19">
+    <cfRule type="expression" dxfId="229" priority="20">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="220" priority="18">
+    <cfRule type="expression" dxfId="228" priority="19">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="219" priority="17">
+    <cfRule type="expression" dxfId="227" priority="18">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="218" priority="16">
+    <cfRule type="expression" dxfId="226" priority="17">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="217" priority="15">
+    <cfRule type="expression" dxfId="225" priority="16">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="216" priority="14">
+    <cfRule type="expression" dxfId="224" priority="15">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="215" priority="13">
+    <cfRule type="expression" dxfId="223" priority="14">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="214" priority="12">
+    <cfRule type="expression" dxfId="222" priority="13">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="213" priority="11">
+    <cfRule type="expression" dxfId="221" priority="12">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="212" priority="10">
+    <cfRule type="expression" dxfId="220" priority="11">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="211" priority="9">
+    <cfRule type="expression" dxfId="219" priority="10">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="210" priority="8">
+    <cfRule type="expression" dxfId="218" priority="9">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="209" priority="7">
+    <cfRule type="expression" dxfId="217" priority="8">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="208" priority="6">
+    <cfRule type="expression" dxfId="216" priority="7">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K829 I829 G829">
-    <cfRule type="expression" dxfId="207" priority="5">
+    <cfRule type="expression" dxfId="215" priority="6">
       <formula>$C829=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I834 G834 K834:K835">
-    <cfRule type="expression" dxfId="206" priority="4">
+    <cfRule type="expression" dxfId="214" priority="5">
       <formula>$C834=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836 G836">
-    <cfRule type="expression" dxfId="205" priority="3">
+    <cfRule type="expression" dxfId="213" priority="4">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837 I837 G837">
-    <cfRule type="expression" dxfId="204" priority="2">
+    <cfRule type="expression" dxfId="212" priority="3">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K839 I839">
+    <cfRule type="expression" dxfId="211" priority="2">
+      <formula>$C839=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K842 I842 G842 E842">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$C839=TODAY()</formula>
+      <formula>$C842=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -29869,7 +30026,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O857"/>
+  <dimension ref="A1:O869"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
@@ -51410,1025 +51567,1348 @@
       <c r="J857" s="11"/>
       <c r="K857" s="12"/>
     </row>
+    <row r="858" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A858" s="1">
+        <v>857</v>
+      </c>
+      <c r="B858" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C858" s="8">
+        <v>46039</v>
+      </c>
+      <c r="D858" s="9"/>
+      <c r="E858" s="10"/>
+      <c r="F858" s="11"/>
+      <c r="G858" s="12"/>
+      <c r="H858" s="11"/>
+      <c r="I858" s="12"/>
+      <c r="J858" s="11"/>
+      <c r="K858" s="12"/>
+    </row>
+    <row r="859" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A859" s="1">
+        <v>858</v>
+      </c>
+      <c r="B859" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C859" s="8">
+        <v>46040</v>
+      </c>
+      <c r="D859" s="9"/>
+      <c r="E859" s="10"/>
+      <c r="F859" s="11"/>
+      <c r="G859" s="12"/>
+      <c r="H859" s="11"/>
+      <c r="I859" s="12"/>
+      <c r="J859" s="11"/>
+      <c r="K859" s="12"/>
+    </row>
+    <row r="860" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A860" s="1">
+        <v>859</v>
+      </c>
+      <c r="B860" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C860" s="8">
+        <v>46041</v>
+      </c>
+      <c r="D860" s="9"/>
+      <c r="E860" s="10"/>
+      <c r="F860" s="11"/>
+      <c r="G860" s="12"/>
+      <c r="H860" s="11"/>
+      <c r="I860" s="12"/>
+      <c r="J860" s="11"/>
+      <c r="K860" s="12"/>
+    </row>
+    <row r="861" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A861" s="1">
+        <v>860</v>
+      </c>
+      <c r="B861" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C861" s="8">
+        <v>46042</v>
+      </c>
+      <c r="D861" s="9"/>
+      <c r="E861" s="10"/>
+      <c r="F861" s="11"/>
+      <c r="G861" s="12"/>
+      <c r="H861" s="11"/>
+      <c r="I861" s="12"/>
+      <c r="J861" s="11"/>
+      <c r="K861" s="12"/>
+    </row>
+    <row r="862" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A862" s="1">
+        <v>861</v>
+      </c>
+      <c r="B862" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C862" s="8">
+        <v>46043</v>
+      </c>
+      <c r="D862" s="9">
+        <v>4600</v>
+      </c>
+      <c r="E862" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F862" s="11">
+        <v>3400</v>
+      </c>
+      <c r="G862" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H862" s="11">
+        <v>1700</v>
+      </c>
+      <c r="I862" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J862" s="11">
+        <v>5200</v>
+      </c>
+      <c r="K862" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="863" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A863" s="1">
+        <v>862</v>
+      </c>
+      <c r="B863" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C863" s="8">
+        <v>46044</v>
+      </c>
+      <c r="D863" s="9">
+        <v>4500</v>
+      </c>
+      <c r="E863" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F863" s="11">
+        <v>3400</v>
+      </c>
+      <c r="G863" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H863" s="11">
+        <v>1700</v>
+      </c>
+      <c r="I863" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J863" s="11">
+        <v>5100</v>
+      </c>
+      <c r="K863" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="864" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A864" s="1">
+        <v>863</v>
+      </c>
+      <c r="B864" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C864" s="8">
+        <v>46044</v>
+      </c>
+      <c r="D864" s="9">
+        <v>1800</v>
+      </c>
+      <c r="E864" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F864" s="11">
+        <v>300</v>
+      </c>
+      <c r="G864" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H864" s="11">
+        <v>100</v>
+      </c>
+      <c r="I864" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J864" s="11">
+        <v>200</v>
+      </c>
+      <c r="K864" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="865" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A865" s="1">
+        <v>864</v>
+      </c>
+      <c r="B865" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C865" s="8">
+        <v>46044</v>
+      </c>
+      <c r="D865" s="9">
+        <v>200</v>
+      </c>
+      <c r="E865" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F865" s="11">
+        <v>20</v>
+      </c>
+      <c r="G865" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H865" s="11">
+        <v>10</v>
+      </c>
+      <c r="I865" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J865" s="11"/>
+      <c r="K865" s="12"/>
+    </row>
+    <row r="866" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A866" s="1">
+        <v>865</v>
+      </c>
+      <c r="B866" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C866" s="8">
+        <v>46045</v>
+      </c>
+      <c r="D866" s="9"/>
+      <c r="E866" s="10"/>
+      <c r="F866" s="11"/>
+      <c r="G866" s="12"/>
+      <c r="H866" s="11"/>
+      <c r="I866" s="12"/>
+      <c r="J866" s="11"/>
+      <c r="K866" s="12"/>
+    </row>
+    <row r="867" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A867" s="1">
+        <v>866</v>
+      </c>
+      <c r="B867" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C867" s="8">
+        <v>46046</v>
+      </c>
+      <c r="D867" s="9"/>
+      <c r="E867" s="10"/>
+      <c r="F867" s="11"/>
+      <c r="G867" s="12"/>
+      <c r="H867" s="11"/>
+      <c r="I867" s="12"/>
+      <c r="J867" s="11"/>
+      <c r="K867" s="12"/>
+    </row>
+    <row r="868" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A868" s="1">
+        <v>867</v>
+      </c>
+      <c r="B868" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C868" s="8">
+        <v>46047</v>
+      </c>
+      <c r="D868" s="9"/>
+      <c r="E868" s="10"/>
+      <c r="F868" s="11"/>
+      <c r="G868" s="12"/>
+      <c r="H868" s="11"/>
+      <c r="I868" s="12"/>
+      <c r="J868" s="11"/>
+      <c r="K868" s="12"/>
+    </row>
+    <row r="869" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A869" s="1">
+        <v>868</v>
+      </c>
+      <c r="B869" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C869" s="8">
+        <v>46048</v>
+      </c>
+      <c r="D869" s="9"/>
+      <c r="E869" s="10"/>
+      <c r="F869" s="11"/>
+      <c r="G869" s="12"/>
+      <c r="H869" s="11"/>
+      <c r="I869" s="12"/>
+      <c r="J869" s="11"/>
+      <c r="K869" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="B4:E857">
-    <cfRule type="expression" dxfId="203" priority="381">
+  <conditionalFormatting sqref="B4:E869">
+    <cfRule type="expression" dxfId="210" priority="388">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K857">
-    <cfRule type="expression" dxfId="202" priority="382">
+  <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K869">
+    <cfRule type="expression" dxfId="209" priority="389">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G47 J44:K47">
-    <cfRule type="expression" dxfId="201" priority="391">
+    <cfRule type="expression" dxfId="208" priority="398">
       <formula>$B18=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E692">
-    <cfRule type="expression" dxfId="200" priority="375">
+    <cfRule type="expression" dxfId="207" priority="382">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E694">
-    <cfRule type="expression" dxfId="199" priority="373">
+    <cfRule type="expression" dxfId="206" priority="380">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E701">
-    <cfRule type="expression" dxfId="198" priority="363">
+    <cfRule type="expression" dxfId="205" priority="370">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E703">
-    <cfRule type="expression" dxfId="197" priority="358">
+    <cfRule type="expression" dxfId="204" priority="365">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E710">
-    <cfRule type="expression" dxfId="196" priority="348">
+    <cfRule type="expression" dxfId="203" priority="355">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E712:E714">
-    <cfRule type="expression" dxfId="195" priority="343">
+    <cfRule type="expression" dxfId="202" priority="350">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E719">
-    <cfRule type="expression" dxfId="194" priority="333">
+    <cfRule type="expression" dxfId="201" priority="340">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E721:E723">
-    <cfRule type="expression" dxfId="193" priority="328">
+    <cfRule type="expression" dxfId="200" priority="335">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E728">
-    <cfRule type="expression" dxfId="192" priority="321">
+    <cfRule type="expression" dxfId="199" priority="328">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E730:E732">
-    <cfRule type="expression" dxfId="191" priority="308">
+    <cfRule type="expression" dxfId="198" priority="315">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E737">
-    <cfRule type="expression" dxfId="190" priority="301">
+    <cfRule type="expression" dxfId="197" priority="308">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739:E741">
-    <cfRule type="expression" dxfId="189" priority="288">
+    <cfRule type="expression" dxfId="196" priority="295">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E746">
-    <cfRule type="expression" dxfId="188" priority="278">
+    <cfRule type="expression" dxfId="195" priority="285">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E748:E750">
-    <cfRule type="expression" dxfId="187" priority="256">
+    <cfRule type="expression" dxfId="194" priority="263">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="186" priority="249">
+    <cfRule type="expression" dxfId="193" priority="256">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E759">
-    <cfRule type="expression" dxfId="185" priority="222">
+    <cfRule type="expression" dxfId="192" priority="229">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E764">
-    <cfRule type="expression" dxfId="184" priority="218">
+    <cfRule type="expression" dxfId="191" priority="225">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E766:E768">
-    <cfRule type="expression" dxfId="183" priority="193">
+    <cfRule type="expression" dxfId="190" priority="200">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="182" priority="183">
+    <cfRule type="expression" dxfId="189" priority="190">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E775:E777">
-    <cfRule type="expression" dxfId="181" priority="171">
+    <cfRule type="expression" dxfId="188" priority="178">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="180" priority="149">
+    <cfRule type="expression" dxfId="187" priority="156">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E784:E786">
-    <cfRule type="expression" dxfId="179" priority="131">
+    <cfRule type="expression" dxfId="186" priority="138">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="178" priority="394">
+    <cfRule type="expression" dxfId="185" priority="401">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70">
-    <cfRule type="expression" dxfId="177" priority="403">
+    <cfRule type="expression" dxfId="184" priority="410">
       <formula>$C70=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G685">
-    <cfRule type="expression" dxfId="176" priority="379">
+    <cfRule type="expression" dxfId="183" priority="386">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G692">
-    <cfRule type="expression" dxfId="175" priority="376">
+    <cfRule type="expression" dxfId="182" priority="383">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G695">
-    <cfRule type="expression" dxfId="174" priority="366">
+    <cfRule type="expression" dxfId="181" priority="373">
       <formula>$C695=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701">
-    <cfRule type="expression" dxfId="173" priority="361">
+    <cfRule type="expression" dxfId="180" priority="368">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G704:G705">
-    <cfRule type="expression" dxfId="172" priority="350">
+    <cfRule type="expression" dxfId="179" priority="357">
       <formula>$C704=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G710">
-    <cfRule type="expression" dxfId="171" priority="346">
+    <cfRule type="expression" dxfId="178" priority="353">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G712:G714">
-    <cfRule type="expression" dxfId="170" priority="336">
+    <cfRule type="expression" dxfId="177" priority="343">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G719">
-    <cfRule type="expression" dxfId="169" priority="331">
+    <cfRule type="expression" dxfId="176" priority="338">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G721:G723">
-    <cfRule type="expression" dxfId="168" priority="326">
+    <cfRule type="expression" dxfId="175" priority="333">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G728">
-    <cfRule type="expression" dxfId="167" priority="319">
+    <cfRule type="expression" dxfId="174" priority="326">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G730:G732">
-    <cfRule type="expression" dxfId="166" priority="306">
+    <cfRule type="expression" dxfId="173" priority="313">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G737">
-    <cfRule type="expression" dxfId="165" priority="299">
+    <cfRule type="expression" dxfId="172" priority="306">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739:G741">
-    <cfRule type="expression" dxfId="164" priority="285">
+    <cfRule type="expression" dxfId="171" priority="292">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746">
-    <cfRule type="expression" dxfId="163" priority="276">
+    <cfRule type="expression" dxfId="170" priority="283">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="162" priority="253">
+    <cfRule type="expression" dxfId="169" priority="260">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="161" priority="247">
+    <cfRule type="expression" dxfId="168" priority="254">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G759">
-    <cfRule type="expression" dxfId="160" priority="219">
+    <cfRule type="expression" dxfId="167" priority="226">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G764">
-    <cfRule type="expression" dxfId="159" priority="216">
+    <cfRule type="expression" dxfId="166" priority="223">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G766:G768">
-    <cfRule type="expression" dxfId="158" priority="189">
+    <cfRule type="expression" dxfId="165" priority="196">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="157" priority="181">
+    <cfRule type="expression" dxfId="164" priority="188">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G775:G777">
-    <cfRule type="expression" dxfId="156" priority="164">
+    <cfRule type="expression" dxfId="163" priority="171">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="155" priority="147">
+    <cfRule type="expression" dxfId="162" priority="154">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G784:G786">
-    <cfRule type="expression" dxfId="154" priority="125">
+    <cfRule type="expression" dxfId="161" priority="132">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:I47">
-    <cfRule type="expression" dxfId="153" priority="416">
+    <cfRule type="expression" dxfId="160" priority="423">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="expression" dxfId="152" priority="420">
+    <cfRule type="expression" dxfId="159" priority="427">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I685">
-    <cfRule type="expression" dxfId="151" priority="378">
+    <cfRule type="expression" dxfId="158" priority="385">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I694:I695">
-    <cfRule type="expression" dxfId="150" priority="365">
+    <cfRule type="expression" dxfId="157" priority="372">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I703:I704">
-    <cfRule type="expression" dxfId="149" priority="352">
+    <cfRule type="expression" dxfId="156" priority="359">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I712:I714">
-    <cfRule type="expression" dxfId="148" priority="335">
+    <cfRule type="expression" dxfId="155" priority="342">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I721:I723">
-    <cfRule type="expression" dxfId="147" priority="324">
+    <cfRule type="expression" dxfId="154" priority="331">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I730:I732">
-    <cfRule type="expression" dxfId="146" priority="302">
+    <cfRule type="expression" dxfId="153" priority="309">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I741">
-    <cfRule type="expression" dxfId="145" priority="282">
+    <cfRule type="expression" dxfId="152" priority="289">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I748:I749">
-    <cfRule type="expression" dxfId="144" priority="261">
+    <cfRule type="expression" dxfId="151" priority="268">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755">
-    <cfRule type="expression" dxfId="143" priority="245">
+    <cfRule type="expression" dxfId="150" priority="252">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I757:I758">
-    <cfRule type="expression" dxfId="142" priority="228">
+    <cfRule type="expression" dxfId="149" priority="235">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I766:I768">
-    <cfRule type="expression" dxfId="141" priority="185">
+    <cfRule type="expression" dxfId="148" priority="192">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="140" priority="179">
+    <cfRule type="expression" dxfId="147" priority="186">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I775:I777">
-    <cfRule type="expression" dxfId="139" priority="157">
+    <cfRule type="expression" dxfId="146" priority="164">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="138" priority="145">
+    <cfRule type="expression" dxfId="145" priority="152">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784:I786">
-    <cfRule type="expression" dxfId="137" priority="119">
+    <cfRule type="expression" dxfId="144" priority="126">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="136" priority="395">
+    <cfRule type="expression" dxfId="143" priority="402">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K685">
-    <cfRule type="expression" dxfId="135" priority="377">
+    <cfRule type="expression" dxfId="142" priority="384">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K692">
-    <cfRule type="expression" dxfId="134" priority="374">
+    <cfRule type="expression" dxfId="141" priority="381">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K694:K695">
-    <cfRule type="expression" dxfId="133" priority="364">
+    <cfRule type="expression" dxfId="140" priority="371">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701">
-    <cfRule type="expression" dxfId="132" priority="359">
+    <cfRule type="expression" dxfId="139" priority="366">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K703:K705">
-    <cfRule type="expression" dxfId="131" priority="349">
+    <cfRule type="expression" dxfId="138" priority="356">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K710">
-    <cfRule type="expression" dxfId="130" priority="344">
+    <cfRule type="expression" dxfId="137" priority="351">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K712:K714">
-    <cfRule type="expression" dxfId="129" priority="334">
+    <cfRule type="expression" dxfId="136" priority="341">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K719">
-    <cfRule type="expression" dxfId="128" priority="329">
+    <cfRule type="expression" dxfId="135" priority="336">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K721:K723">
-    <cfRule type="expression" dxfId="127" priority="322">
+    <cfRule type="expression" dxfId="134" priority="329">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K728">
-    <cfRule type="expression" dxfId="126" priority="317">
+    <cfRule type="expression" dxfId="133" priority="324">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K730:K732">
-    <cfRule type="expression" dxfId="125" priority="304">
+    <cfRule type="expression" dxfId="132" priority="311">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K737">
-    <cfRule type="expression" dxfId="124" priority="297">
+    <cfRule type="expression" dxfId="131" priority="304">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K741">
-    <cfRule type="expression" dxfId="123" priority="279">
+    <cfRule type="expression" dxfId="130" priority="286">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K746">
-    <cfRule type="expression" dxfId="122" priority="274">
+    <cfRule type="expression" dxfId="129" priority="281">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K748:K750">
-    <cfRule type="expression" dxfId="121" priority="250">
+    <cfRule type="expression" dxfId="128" priority="257">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755">
-    <cfRule type="expression" dxfId="120" priority="243">
+    <cfRule type="expression" dxfId="127" priority="250">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K757:K758">
-    <cfRule type="expression" dxfId="119" priority="225">
+    <cfRule type="expression" dxfId="126" priority="232">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K764">
-    <cfRule type="expression" dxfId="118" priority="214">
+    <cfRule type="expression" dxfId="125" priority="221">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766:K767">
-    <cfRule type="expression" dxfId="117" priority="196">
+    <cfRule type="expression" dxfId="124" priority="203">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="116" priority="177">
+    <cfRule type="expression" dxfId="123" priority="184">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K775:K777">
-    <cfRule type="expression" dxfId="115" priority="150">
+    <cfRule type="expression" dxfId="122" priority="157">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="114" priority="143">
+    <cfRule type="expression" dxfId="121" priority="150">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784:K786">
-    <cfRule type="expression" dxfId="113" priority="113">
+    <cfRule type="expression" dxfId="120" priority="120">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E792:E793">
-    <cfRule type="expression" dxfId="112" priority="112">
+    <cfRule type="expression" dxfId="119" priority="119">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="111" priority="111">
+    <cfRule type="expression" dxfId="118" priority="118">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="110" priority="110">
+    <cfRule type="expression" dxfId="117" priority="117">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="109" priority="109">
+    <cfRule type="expression" dxfId="116" priority="116">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="108" priority="108">
+    <cfRule type="expression" dxfId="115" priority="115">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="107" priority="107">
+    <cfRule type="expression" dxfId="114" priority="114">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="106" priority="106">
+    <cfRule type="expression" dxfId="113" priority="113">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E794:E795">
-    <cfRule type="expression" dxfId="105" priority="105">
+    <cfRule type="expression" dxfId="112" priority="112">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="104" priority="104">
+    <cfRule type="expression" dxfId="111" priority="111">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="103" priority="103">
+    <cfRule type="expression" dxfId="110" priority="110">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="102" priority="102">
+    <cfRule type="expression" dxfId="109" priority="109">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="101" priority="101">
+    <cfRule type="expression" dxfId="108" priority="108">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="100" priority="100">
+    <cfRule type="expression" dxfId="107" priority="107">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="99" priority="99">
+    <cfRule type="expression" dxfId="106" priority="106">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E801:E802">
-    <cfRule type="expression" dxfId="98" priority="98">
+    <cfRule type="expression" dxfId="105" priority="105">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E803:E805">
-    <cfRule type="expression" dxfId="97" priority="97">
+    <cfRule type="expression" dxfId="104" priority="104">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G805">
+    <cfRule type="expression" dxfId="103" priority="103">
+      <formula>$C801=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G801:G802">
+    <cfRule type="expression" dxfId="102" priority="102">
+      <formula>$C801=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G803:G805">
+    <cfRule type="expression" dxfId="101" priority="101">
+      <formula>$C803=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I801:I805">
+    <cfRule type="expression" dxfId="100" priority="100">
+      <formula>$C801=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I801:I802">
+    <cfRule type="expression" dxfId="99" priority="99">
+      <formula>$C801=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I803:I805">
+    <cfRule type="expression" dxfId="98" priority="98">
+      <formula>$C803=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K801:K805">
+    <cfRule type="expression" dxfId="97" priority="97">
+      <formula>$C801=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K801:K802">
     <cfRule type="expression" dxfId="96" priority="96">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G801:G802">
+  <conditionalFormatting sqref="K803:K805">
     <cfRule type="expression" dxfId="95" priority="95">
-      <formula>$C801=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G803:G805">
-    <cfRule type="expression" dxfId="94" priority="94">
-      <formula>$C803=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I801:I805">
-    <cfRule type="expression" dxfId="93" priority="93">
-      <formula>$C801=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I801:I802">
-    <cfRule type="expression" dxfId="92" priority="92">
-      <formula>$C801=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I803:I805">
-    <cfRule type="expression" dxfId="91" priority="91">
-      <formula>$C803=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K801:K805">
-    <cfRule type="expression" dxfId="90" priority="90">
-      <formula>$C801=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K801:K802">
-    <cfRule type="expression" dxfId="89" priority="89">
-      <formula>$C801=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K803:K805">
-    <cfRule type="expression" dxfId="88" priority="88">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E809:E810">
-    <cfRule type="expression" dxfId="87" priority="87">
+    <cfRule type="expression" dxfId="94" priority="94">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811:E812">
-    <cfRule type="expression" dxfId="86" priority="86">
+    <cfRule type="expression" dxfId="93" priority="93">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G812">
+    <cfRule type="expression" dxfId="92" priority="92">
+      <formula>$C809=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G809:G810">
+    <cfRule type="expression" dxfId="91" priority="91">
+      <formula>$C809=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G811:G812">
+    <cfRule type="expression" dxfId="90" priority="90">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I809:I812">
+    <cfRule type="expression" dxfId="89" priority="89">
+      <formula>$C809=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I809:I810">
+    <cfRule type="expression" dxfId="88" priority="88">
+      <formula>$C809=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I811:I812">
+    <cfRule type="expression" dxfId="87" priority="87">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K809:K812">
+    <cfRule type="expression" dxfId="86" priority="86">
+      <formula>$C809=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K809:K810">
     <cfRule type="expression" dxfId="85" priority="85">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G809:G810">
+  <conditionalFormatting sqref="K811:K812">
     <cfRule type="expression" dxfId="84" priority="84">
-      <formula>$C809=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G811:G812">
-    <cfRule type="expression" dxfId="83" priority="83">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I809:I812">
-    <cfRule type="expression" dxfId="82" priority="82">
-      <formula>$C809=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I809:I810">
-    <cfRule type="expression" dxfId="81" priority="81">
-      <formula>$C809=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="80" priority="80">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K809:K812">
-    <cfRule type="expression" dxfId="79" priority="79">
-      <formula>$C809=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K809:K810">
-    <cfRule type="expression" dxfId="78" priority="78">
-      <formula>$C809=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K811:K812">
-    <cfRule type="expression" dxfId="77" priority="77">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E818:E822 G818:G822 K818:K822 I818:I822">
-    <cfRule type="expression" dxfId="76" priority="76">
+    <cfRule type="expression" dxfId="83" priority="83">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K818:K822 G818:G822 I818:I822">
-    <cfRule type="expression" dxfId="75" priority="75">
+    <cfRule type="expression" dxfId="82" priority="82">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E820:E821">
-    <cfRule type="expression" dxfId="74" priority="74">
+    <cfRule type="expression" dxfId="81" priority="81">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="73" priority="73">
+    <cfRule type="expression" dxfId="80" priority="80">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="72" priority="72">
+    <cfRule type="expression" dxfId="79" priority="79">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="71" priority="71">
+    <cfRule type="expression" dxfId="78" priority="78">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="70" priority="70">
+    <cfRule type="expression" dxfId="77" priority="77">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K822 G822">
-    <cfRule type="expression" dxfId="69" priority="69">
+    <cfRule type="expression" dxfId="76" priority="76">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I822">
-    <cfRule type="expression" dxfId="68" priority="68">
+    <cfRule type="expression" dxfId="75" priority="75">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E828:E831">
-    <cfRule type="expression" dxfId="67" priority="67">
+    <cfRule type="expression" dxfId="74" priority="74">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="66" priority="66">
+    <cfRule type="expression" dxfId="73" priority="73">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="65" priority="65">
+    <cfRule type="expression" dxfId="72" priority="72">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
+    <cfRule type="expression" dxfId="71" priority="71">
+      <formula>$C830=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E830:E831">
+    <cfRule type="expression" dxfId="70" priority="70">
+      <formula>$C830=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G830:G831">
+    <cfRule type="expression" dxfId="69" priority="69">
+      <formula>$C830=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G830:G831">
+    <cfRule type="expression" dxfId="68" priority="68">
+      <formula>$C830=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G830:G831">
+    <cfRule type="expression" dxfId="67" priority="67">
+      <formula>$C830=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I830:I831">
+    <cfRule type="expression" dxfId="66" priority="66">
+      <formula>$C830=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I830:I831">
+    <cfRule type="expression" dxfId="65" priority="65">
+      <formula>$C830=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I830:I831">
     <cfRule type="expression" dxfId="64" priority="64">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E830:E831">
+  <conditionalFormatting sqref="K830:K831">
     <cfRule type="expression" dxfId="63" priority="63">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G830:G831">
+  <conditionalFormatting sqref="K830:K831">
     <cfRule type="expression" dxfId="62" priority="62">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G830:G831">
+  <conditionalFormatting sqref="K830:K831">
     <cfRule type="expression" dxfId="61" priority="61">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G830:G831">
+  <conditionalFormatting sqref="E837">
     <cfRule type="expression" dxfId="60" priority="60">
-      <formula>$C830=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="59" priority="59">
-      <formula>$C830=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="58" priority="58">
-      <formula>$C830=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="57" priority="57">
-      <formula>$C830=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="56" priority="56">
-      <formula>$C830=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="55" priority="55">
-      <formula>$C830=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="54" priority="54">
-      <formula>$C830=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E837">
-    <cfRule type="expression" dxfId="53" priority="53">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="52" priority="52">
+    <cfRule type="expression" dxfId="59" priority="59">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="51" priority="51">
+    <cfRule type="expression" dxfId="58" priority="58">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="50" priority="50">
+    <cfRule type="expression" dxfId="57" priority="57">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="49" priority="49">
+    <cfRule type="expression" dxfId="56" priority="56">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="48" priority="48">
+    <cfRule type="expression" dxfId="55" priority="55">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="47" priority="47">
+    <cfRule type="expression" dxfId="54" priority="54">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E845:E847">
+    <cfRule type="expression" dxfId="53" priority="53">
+      <formula>$C845=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E846:E847">
+    <cfRule type="expression" dxfId="52" priority="52">
+      <formula>$C846=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E846:E847">
+    <cfRule type="expression" dxfId="51" priority="51">
+      <formula>$C846=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G845:G847">
+    <cfRule type="expression" dxfId="50" priority="50">
+      <formula>$C845=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G845:G847">
+    <cfRule type="expression" dxfId="49" priority="49">
+      <formula>$C845=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G846:G847">
+    <cfRule type="expression" dxfId="48" priority="48">
+      <formula>$C846=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G846:G847">
+    <cfRule type="expression" dxfId="47" priority="47">
+      <formula>$C846=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I845:I847">
     <cfRule type="expression" dxfId="46" priority="46">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E846:E847">
+  <conditionalFormatting sqref="I845:I847">
     <cfRule type="expression" dxfId="45" priority="45">
-      <formula>$C846=TODAY()</formula>
+      <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E846:E847">
+  <conditionalFormatting sqref="I846:I847">
     <cfRule type="expression" dxfId="44" priority="44">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G845:G847">
+  <conditionalFormatting sqref="I846:I847">
     <cfRule type="expression" dxfId="43" priority="43">
-      <formula>$C845=TODAY()</formula>
+      <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G845:G847">
+  <conditionalFormatting sqref="K845:K847">
     <cfRule type="expression" dxfId="42" priority="42">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G846:G847">
+  <conditionalFormatting sqref="K845:K847">
     <cfRule type="expression" dxfId="41" priority="41">
-      <formula>$C846=TODAY()</formula>
+      <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G846:G847">
+  <conditionalFormatting sqref="K846:K847">
     <cfRule type="expression" dxfId="40" priority="40">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I845:I847">
+  <conditionalFormatting sqref="K846:K847">
     <cfRule type="expression" dxfId="39" priority="39">
-      <formula>$C845=TODAY()</formula>
+      <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I845:I847">
+  <conditionalFormatting sqref="K845:K847">
     <cfRule type="expression" dxfId="38" priority="38">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I846:I847">
+  <conditionalFormatting sqref="K845:K847">
     <cfRule type="expression" dxfId="37" priority="37">
-      <formula>$C846=TODAY()</formula>
+      <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I846:I847">
+  <conditionalFormatting sqref="K846:K847">
     <cfRule type="expression" dxfId="36" priority="36">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K845:K847">
+  <conditionalFormatting sqref="K846:K847">
     <cfRule type="expression" dxfId="35" priority="35">
-      <formula>$C845=TODAY()</formula>
+      <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K845:K847">
+  <conditionalFormatting sqref="G846">
     <cfRule type="expression" dxfId="34" priority="34">
-      <formula>$C845=TODAY()</formula>
+      <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K846:K847">
+  <conditionalFormatting sqref="G846">
     <cfRule type="expression" dxfId="33" priority="33">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K846:K847">
+  <conditionalFormatting sqref="G846">
     <cfRule type="expression" dxfId="32" priority="32">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K845:K847">
+  <conditionalFormatting sqref="G846">
     <cfRule type="expression" dxfId="31" priority="31">
-      <formula>$C845=TODAY()</formula>
+      <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K845:K847">
+  <conditionalFormatting sqref="I846">
     <cfRule type="expression" dxfId="30" priority="30">
-      <formula>$C845=TODAY()</formula>
+      <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K846:K847">
+  <conditionalFormatting sqref="I846">
     <cfRule type="expression" dxfId="29" priority="29">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K846:K847">
+  <conditionalFormatting sqref="I846">
     <cfRule type="expression" dxfId="28" priority="28">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G846">
+  <conditionalFormatting sqref="I846">
     <cfRule type="expression" dxfId="27" priority="27">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G846">
+  <conditionalFormatting sqref="K846">
     <cfRule type="expression" dxfId="26" priority="26">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G846">
+  <conditionalFormatting sqref="K846">
     <cfRule type="expression" dxfId="25" priority="25">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G846">
+  <conditionalFormatting sqref="K846">
     <cfRule type="expression" dxfId="24" priority="24">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I846">
+  <conditionalFormatting sqref="K846">
     <cfRule type="expression" dxfId="23" priority="23">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I846">
+  <conditionalFormatting sqref="E836">
     <cfRule type="expression" dxfId="22" priority="22">
-      <formula>$C846=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="21" priority="21">
-      <formula>$C846=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="20" priority="20">
-      <formula>$C846=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="19" priority="19">
-      <formula>$C846=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="18" priority="18">
-      <formula>$C846=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="17" priority="17">
-      <formula>$C846=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="16" priority="16">
-      <formula>$C846=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E836">
-    <cfRule type="expression" dxfId="15" priority="15">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="16" priority="16">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853 E853">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="15" priority="15">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="14" priority="14">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854 E854">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="13" priority="13">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856">
+    <cfRule type="expression" dxfId="8" priority="8">
+      <formula>$C855=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K862 I862 G862 E862">
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>$C862=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K862 I862 G862">
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>$C862=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K863 I863 G863 E863">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>$C863=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>$C864=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$C864=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$C864=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K863:K865 I863:I865 G863:G865">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$C855=TODAY()</formula>
+      <formula>$C863=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
+++ b/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3C2B28-785F-46AD-9CF0-28F9A3E8D9AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979F2D7F-76AD-43D7-88DC-85924B833247}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3464" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3474" uniqueCount="33">
   <si>
     <t>План поставок ПОКОМ</t>
   </si>
@@ -435,7 +435,70 @@
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Обычный 2 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="504">
+  <dxfs count="513">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4345,7 +4408,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMD846"/>
+  <dimension ref="A1:AMD855"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
@@ -28469,7 +28532,7 @@
         <v>839</v>
       </c>
       <c r="B843" s="7" t="str">
-        <f t="shared" ref="B843:B846" si="138">IF(C843&lt;&gt;"",TEXT(C843,"ДДД"),"")</f>
+        <f t="shared" ref="B843:B847" si="138">IF(C843&lt;&gt;"",TEXT(C843,"ДДД"),"")</f>
         <v>Ср</v>
       </c>
       <c r="C843" s="8">
@@ -28479,10 +28542,18 @@
       <c r="E843" s="10"/>
       <c r="F843" s="11"/>
       <c r="G843" s="12"/>
-      <c r="H843" s="11"/>
-      <c r="I843" s="12"/>
-      <c r="J843" s="11"/>
-      <c r="K843" s="12"/>
+      <c r="H843" s="11">
+        <v>6400</v>
+      </c>
+      <c r="I843" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J843" s="11">
+        <v>7100</v>
+      </c>
+      <c r="K843" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="844" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A844" s="1">
@@ -28495,45 +28566,77 @@
       <c r="C844" s="8">
         <v>46044</v>
       </c>
-      <c r="D844" s="9"/>
-      <c r="E844" s="10"/>
-      <c r="F844" s="11"/>
-      <c r="G844" s="12"/>
-      <c r="H844" s="11"/>
-      <c r="I844" s="12"/>
-      <c r="J844" s="11"/>
-      <c r="K844" s="12"/>
+      <c r="D844" s="9">
+        <v>2900</v>
+      </c>
+      <c r="E844" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F844" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G844" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H844" s="11">
+        <v>5400</v>
+      </c>
+      <c r="I844" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J844" s="11">
+        <v>5900</v>
+      </c>
+      <c r="K844" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="845" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A845" s="1">
         <v>841</v>
       </c>
       <c r="B845" s="7" t="str">
-        <f t="shared" si="138"/>
-        <v>Пт</v>
+        <f t="shared" ref="B845" si="139">IF(C845&lt;&gt;"",TEXT(C845,"ДДД"),"")</f>
+        <v>Чт</v>
       </c>
       <c r="C845" s="8">
-        <v>46045</v>
-      </c>
-      <c r="D845" s="9"/>
-      <c r="E845" s="10"/>
-      <c r="F845" s="11"/>
-      <c r="G845" s="12"/>
-      <c r="H845" s="11"/>
-      <c r="I845" s="12"/>
-      <c r="J845" s="11"/>
-      <c r="K845" s="12"/>
+        <v>46044</v>
+      </c>
+      <c r="D845" s="9">
+        <v>6400</v>
+      </c>
+      <c r="E845" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F845" s="11">
+        <v>7800</v>
+      </c>
+      <c r="G845" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H845" s="11">
+        <v>5700</v>
+      </c>
+      <c r="I845" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J845" s="11">
+        <v>8000</v>
+      </c>
+      <c r="K845" s="10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="846" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A846" s="1">
         <v>842</v>
       </c>
       <c r="B846" s="7" t="str">
-        <f t="shared" si="138"/>
-        <v>Сб</v>
+        <f t="shared" ref="B846" si="140">IF(C846&lt;&gt;"",TEXT(C846,"ДДД"),"")</f>
+        <v>Пт</v>
       </c>
       <c r="C846" s="8">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="D846" s="9"/>
       <c r="E846" s="10"/>
@@ -28544,1479 +28647,1704 @@
       <c r="J846" s="11"/>
       <c r="K846" s="12"/>
     </row>
+    <row r="847" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A847" s="1">
+        <v>843</v>
+      </c>
+      <c r="B847" s="7" t="str">
+        <f t="shared" si="138"/>
+        <v>Сб</v>
+      </c>
+      <c r="C847" s="8">
+        <v>46046</v>
+      </c>
+      <c r="D847" s="9"/>
+      <c r="E847" s="10"/>
+      <c r="F847" s="11"/>
+      <c r="G847" s="12"/>
+      <c r="H847" s="11"/>
+      <c r="I847" s="12"/>
+      <c r="J847" s="11"/>
+      <c r="K847" s="12"/>
+    </row>
+    <row r="848" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A848" s="1">
+        <v>844</v>
+      </c>
+      <c r="B848" s="7" t="str">
+        <f t="shared" ref="B848:B855" si="141">IF(C848&lt;&gt;"",TEXT(C848,"ДДД"),"")</f>
+        <v>Вс</v>
+      </c>
+      <c r="C848" s="8">
+        <v>46047</v>
+      </c>
+      <c r="D848" s="9"/>
+      <c r="E848" s="10"/>
+      <c r="F848" s="11"/>
+      <c r="G848" s="12"/>
+      <c r="H848" s="11"/>
+      <c r="I848" s="12"/>
+      <c r="J848" s="11"/>
+      <c r="K848" s="12"/>
+    </row>
+    <row r="849" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A849" s="1">
+        <v>845</v>
+      </c>
+      <c r="B849" s="7" t="str">
+        <f t="shared" si="141"/>
+        <v>Пн</v>
+      </c>
+      <c r="C849" s="8">
+        <v>46048</v>
+      </c>
+      <c r="D849" s="9"/>
+      <c r="E849" s="10"/>
+      <c r="F849" s="11"/>
+      <c r="G849" s="12"/>
+      <c r="H849" s="11"/>
+      <c r="I849" s="12"/>
+      <c r="J849" s="11"/>
+      <c r="K849" s="12"/>
+    </row>
+    <row r="850" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A850" s="1">
+        <v>846</v>
+      </c>
+      <c r="B850" s="7" t="str">
+        <f t="shared" si="141"/>
+        <v>Вт</v>
+      </c>
+      <c r="C850" s="8">
+        <v>46049</v>
+      </c>
+      <c r="D850" s="9"/>
+      <c r="E850" s="10"/>
+      <c r="F850" s="11"/>
+      <c r="G850" s="12"/>
+      <c r="H850" s="11"/>
+      <c r="I850" s="12"/>
+      <c r="J850" s="11"/>
+      <c r="K850" s="12"/>
+    </row>
+    <row r="851" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A851" s="1">
+        <v>847</v>
+      </c>
+      <c r="B851" s="7" t="str">
+        <f t="shared" si="141"/>
+        <v>Ср</v>
+      </c>
+      <c r="C851" s="8">
+        <v>46050</v>
+      </c>
+      <c r="D851" s="9"/>
+      <c r="E851" s="10"/>
+      <c r="F851" s="11"/>
+      <c r="G851" s="12"/>
+      <c r="H851" s="11"/>
+      <c r="I851" s="12"/>
+      <c r="J851" s="11"/>
+      <c r="K851" s="12"/>
+    </row>
+    <row r="852" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A852" s="1">
+        <v>848</v>
+      </c>
+      <c r="B852" s="7" t="str">
+        <f t="shared" si="141"/>
+        <v>Чт</v>
+      </c>
+      <c r="C852" s="8">
+        <v>46051</v>
+      </c>
+      <c r="D852" s="9"/>
+      <c r="E852" s="10"/>
+      <c r="F852" s="11"/>
+      <c r="G852" s="12"/>
+      <c r="H852" s="11"/>
+      <c r="I852" s="12"/>
+      <c r="J852" s="11"/>
+      <c r="K852" s="12"/>
+    </row>
+    <row r="853" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A853" s="1">
+        <v>849</v>
+      </c>
+      <c r="B853" s="7" t="str">
+        <f t="shared" si="141"/>
+        <v>Пт</v>
+      </c>
+      <c r="C853" s="8">
+        <v>46052</v>
+      </c>
+      <c r="D853" s="9"/>
+      <c r="E853" s="10"/>
+      <c r="F853" s="11"/>
+      <c r="G853" s="12"/>
+      <c r="H853" s="11"/>
+      <c r="I853" s="12"/>
+      <c r="J853" s="11"/>
+      <c r="K853" s="12"/>
+    </row>
+    <row r="854" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A854" s="1">
+        <v>850</v>
+      </c>
+      <c r="B854" s="7" t="str">
+        <f t="shared" si="141"/>
+        <v>Сб</v>
+      </c>
+      <c r="C854" s="8">
+        <v>46053</v>
+      </c>
+      <c r="D854" s="9"/>
+      <c r="E854" s="10"/>
+      <c r="F854" s="11"/>
+      <c r="G854" s="12"/>
+      <c r="H854" s="11"/>
+      <c r="I854" s="12"/>
+      <c r="J854" s="11"/>
+      <c r="K854" s="12"/>
+    </row>
+    <row r="855" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A855" s="1">
+        <v>851</v>
+      </c>
+      <c r="B855" s="7" t="str">
+        <f t="shared" si="141"/>
+        <v>Вс</v>
+      </c>
+      <c r="C855" s="8">
+        <v>46054</v>
+      </c>
+      <c r="D855" s="9"/>
+      <c r="E855" s="10"/>
+      <c r="F855" s="11"/>
+      <c r="G855" s="12"/>
+      <c r="H855" s="11"/>
+      <c r="I855" s="12"/>
+      <c r="J855" s="11"/>
+      <c r="K855" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:E846">
-    <cfRule type="expression" dxfId="503" priority="713">
+  <conditionalFormatting sqref="B4:E855">
+    <cfRule type="expression" dxfId="512" priority="722">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:M683 B684:K846">
-    <cfRule type="expression" dxfId="502" priority="714">
+  <conditionalFormatting sqref="B4:M683 B684:K855">
+    <cfRule type="expression" dxfId="511" priority="723">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E678">
-    <cfRule type="expression" dxfId="501" priority="704">
+    <cfRule type="expression" dxfId="510" priority="713">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E693:E694">
-    <cfRule type="expression" dxfId="500" priority="691">
+    <cfRule type="expression" dxfId="509" priority="700">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E702">
-    <cfRule type="expression" dxfId="499" priority="678">
+    <cfRule type="expression" dxfId="508" priority="687">
       <formula>$C702=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E707">
-    <cfRule type="expression" dxfId="498" priority="674">
+    <cfRule type="expression" dxfId="507" priority="683">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709:E710">
-    <cfRule type="expression" dxfId="497" priority="666">
+    <cfRule type="expression" dxfId="506" priority="675">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E715">
-    <cfRule type="expression" dxfId="496" priority="662">
+    <cfRule type="expression" dxfId="505" priority="671">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E717:E718">
-    <cfRule type="expression" dxfId="495" priority="650">
+    <cfRule type="expression" dxfId="504" priority="659">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E723">
-    <cfRule type="expression" dxfId="494" priority="639">
+    <cfRule type="expression" dxfId="503" priority="648">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E725:E726">
-    <cfRule type="expression" dxfId="493" priority="616">
+    <cfRule type="expression" dxfId="502" priority="625">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E731">
-    <cfRule type="expression" dxfId="492" priority="604">
+    <cfRule type="expression" dxfId="501" priority="613">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E733:E734">
-    <cfRule type="expression" dxfId="491" priority="571">
+    <cfRule type="expression" dxfId="500" priority="580">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739">
-    <cfRule type="expression" dxfId="490" priority="539">
+    <cfRule type="expression" dxfId="499" priority="548">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E741:E742">
-    <cfRule type="expression" dxfId="489" priority="494">
+    <cfRule type="expression" dxfId="498" priority="503">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E747:E748">
-    <cfRule type="expression" dxfId="488" priority="431">
+    <cfRule type="expression" dxfId="497" priority="440">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E750">
-    <cfRule type="expression" dxfId="487" priority="415">
+    <cfRule type="expression" dxfId="496" priority="424">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="486" priority="389">
+    <cfRule type="expression" dxfId="495" priority="398">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E758">
-    <cfRule type="expression" dxfId="485" priority="341">
+    <cfRule type="expression" dxfId="494" priority="350">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E763">
-    <cfRule type="expression" dxfId="484" priority="314">
+    <cfRule type="expression" dxfId="493" priority="323">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E765:E766">
-    <cfRule type="expression" dxfId="483" priority="261">
+    <cfRule type="expression" dxfId="492" priority="270">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E771">
-    <cfRule type="expression" dxfId="482" priority="216">
+    <cfRule type="expression" dxfId="491" priority="225">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="481" priority="727">
+    <cfRule type="expression" dxfId="490" priority="736">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G661">
-    <cfRule type="expression" dxfId="480" priority="711">
+    <cfRule type="expression" dxfId="489" priority="720">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G670">
-    <cfRule type="expression" dxfId="479" priority="708">
+    <cfRule type="expression" dxfId="488" priority="717">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G678">
-    <cfRule type="expression" dxfId="478" priority="705">
+    <cfRule type="expression" dxfId="487" priority="714">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G686">
-    <cfRule type="expression" dxfId="477" priority="701">
+    <cfRule type="expression" dxfId="486" priority="710">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G691">
-    <cfRule type="expression" dxfId="476" priority="698">
+    <cfRule type="expression" dxfId="485" priority="707">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G693:G694">
-    <cfRule type="expression" dxfId="475" priority="690">
+    <cfRule type="expression" dxfId="484" priority="699">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G699">
-    <cfRule type="expression" dxfId="474" priority="687">
+    <cfRule type="expression" dxfId="483" priority="696">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701:G702">
-    <cfRule type="expression" dxfId="473" priority="679">
+    <cfRule type="expression" dxfId="482" priority="688">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G707">
-    <cfRule type="expression" dxfId="472" priority="675">
+    <cfRule type="expression" dxfId="481" priority="684">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G709:G710">
-    <cfRule type="expression" dxfId="471" priority="665">
+    <cfRule type="expression" dxfId="480" priority="674">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G715">
-    <cfRule type="expression" dxfId="470" priority="660">
+    <cfRule type="expression" dxfId="479" priority="669">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G717:G718">
-    <cfRule type="expression" dxfId="469" priority="647">
+    <cfRule type="expression" dxfId="478" priority="656">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G723">
-    <cfRule type="expression" dxfId="468" priority="636">
+    <cfRule type="expression" dxfId="477" priority="645">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G725:G726">
-    <cfRule type="expression" dxfId="467" priority="613">
+    <cfRule type="expression" dxfId="476" priority="622">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G731">
-    <cfRule type="expression" dxfId="466" priority="600">
+    <cfRule type="expression" dxfId="475" priority="609">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G733:G734">
-    <cfRule type="expression" dxfId="465" priority="565">
+    <cfRule type="expression" dxfId="474" priority="574">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739">
-    <cfRule type="expression" dxfId="464" priority="534">
+    <cfRule type="expression" dxfId="473" priority="543">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G741:G742">
-    <cfRule type="expression" dxfId="463" priority="488">
+    <cfRule type="expression" dxfId="472" priority="497">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G747">
-    <cfRule type="expression" dxfId="462" priority="451">
+    <cfRule type="expression" dxfId="471" priority="460">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="461" priority="408">
+    <cfRule type="expression" dxfId="470" priority="417">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="460" priority="383">
+    <cfRule type="expression" dxfId="469" priority="392">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G758">
-    <cfRule type="expression" dxfId="459" priority="334">
+    <cfRule type="expression" dxfId="468" priority="343">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763">
-    <cfRule type="expression" dxfId="458" priority="307">
+    <cfRule type="expression" dxfId="467" priority="316">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G765:G766">
-    <cfRule type="expression" dxfId="457" priority="248">
+    <cfRule type="expression" dxfId="466" priority="257">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G771">
-    <cfRule type="expression" dxfId="456" priority="209">
+    <cfRule type="expression" dxfId="465" priority="218">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H128:I129">
-    <cfRule type="expression" dxfId="455" priority="730">
+    <cfRule type="expression" dxfId="464" priority="739">
       <formula>$C128=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="expression" dxfId="454" priority="728">
+    <cfRule type="expression" dxfId="463" priority="737">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I661">
-    <cfRule type="expression" dxfId="453" priority="710">
+    <cfRule type="expression" dxfId="462" priority="719">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670">
-    <cfRule type="expression" dxfId="452" priority="707">
+    <cfRule type="expression" dxfId="461" priority="716">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I678">
-    <cfRule type="expression" dxfId="451" priority="703">
+    <cfRule type="expression" dxfId="460" priority="712">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I686">
-    <cfRule type="expression" dxfId="450" priority="700">
+    <cfRule type="expression" dxfId="459" priority="709">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I691">
-    <cfRule type="expression" dxfId="449" priority="697">
+    <cfRule type="expression" dxfId="458" priority="706">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I693:I694">
-    <cfRule type="expression" dxfId="448" priority="689">
+    <cfRule type="expression" dxfId="457" priority="698">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I699">
-    <cfRule type="expression" dxfId="447" priority="686">
+    <cfRule type="expression" dxfId="456" priority="695">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I701:I702">
-    <cfRule type="expression" dxfId="446" priority="680">
+    <cfRule type="expression" dxfId="455" priority="689">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I707">
-    <cfRule type="expression" dxfId="445" priority="677">
+    <cfRule type="expression" dxfId="454" priority="686">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I709:I710">
-    <cfRule type="expression" dxfId="444" priority="664">
+    <cfRule type="expression" dxfId="453" priority="673">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I715">
-    <cfRule type="expression" dxfId="443" priority="658">
+    <cfRule type="expression" dxfId="452" priority="667">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I717:I718">
-    <cfRule type="expression" dxfId="442" priority="644">
+    <cfRule type="expression" dxfId="451" priority="653">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I723:I726">
-    <cfRule type="expression" dxfId="441" priority="610">
+    <cfRule type="expression" dxfId="450" priority="619">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I731:I734">
-    <cfRule type="expression" dxfId="440" priority="559">
+    <cfRule type="expression" dxfId="449" priority="568">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I736">
-    <cfRule type="expression" dxfId="439" priority="548">
+    <cfRule type="expression" dxfId="448" priority="557">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I742">
-    <cfRule type="expression" dxfId="438" priority="482">
+    <cfRule type="expression" dxfId="447" priority="491">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I744">
-    <cfRule type="expression" dxfId="437" priority="466">
+    <cfRule type="expression" dxfId="446" priority="475">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I747:I748">
-    <cfRule type="expression" dxfId="436" priority="436">
+    <cfRule type="expression" dxfId="445" priority="445">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I750">
-    <cfRule type="expression" dxfId="435" priority="401">
+    <cfRule type="expression" dxfId="444" priority="410">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755:I756">
-    <cfRule type="expression" dxfId="434" priority="365">
+    <cfRule type="expression" dxfId="443" priority="374">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I758">
-    <cfRule type="expression" dxfId="433" priority="327">
+    <cfRule type="expression" dxfId="442" priority="336">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I763">
-    <cfRule type="expression" dxfId="432" priority="300">
+    <cfRule type="expression" dxfId="441" priority="309">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I765:I766">
-    <cfRule type="expression" dxfId="431" priority="235">
+    <cfRule type="expression" dxfId="440" priority="244">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I771:I772">
-    <cfRule type="expression" dxfId="430" priority="202">
+    <cfRule type="expression" dxfId="439" priority="211">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="429" priority="729">
+    <cfRule type="expression" dxfId="438" priority="738">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K661">
-    <cfRule type="expression" dxfId="428" priority="709">
+    <cfRule type="expression" dxfId="437" priority="718">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K670">
-    <cfRule type="expression" dxfId="427" priority="706">
+    <cfRule type="expression" dxfId="436" priority="715">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K678">
-    <cfRule type="expression" dxfId="426" priority="702">
+    <cfRule type="expression" dxfId="435" priority="711">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K686">
-    <cfRule type="expression" dxfId="425" priority="699">
+    <cfRule type="expression" dxfId="434" priority="708">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K691">
-    <cfRule type="expression" dxfId="424" priority="696">
+    <cfRule type="expression" dxfId="433" priority="705">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K693:K694">
-    <cfRule type="expression" dxfId="423" priority="688">
+    <cfRule type="expression" dxfId="432" priority="697">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K699">
-    <cfRule type="expression" dxfId="422" priority="685">
+    <cfRule type="expression" dxfId="431" priority="694">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701:K702">
-    <cfRule type="expression" dxfId="421" priority="681">
+    <cfRule type="expression" dxfId="430" priority="690">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K707">
-    <cfRule type="expression" dxfId="420" priority="676">
+    <cfRule type="expression" dxfId="429" priority="685">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K709:K710">
-    <cfRule type="expression" dxfId="419" priority="663">
+    <cfRule type="expression" dxfId="428" priority="672">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K715:K718">
-    <cfRule type="expression" dxfId="418" priority="641">
+    <cfRule type="expression" dxfId="427" priority="650">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K723">
-    <cfRule type="expression" dxfId="417" priority="630">
+    <cfRule type="expression" dxfId="426" priority="639">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K725:K726">
-    <cfRule type="expression" dxfId="416" priority="607">
+    <cfRule type="expression" dxfId="425" priority="616">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K731">
-    <cfRule type="expression" dxfId="415" priority="592">
+    <cfRule type="expression" dxfId="424" priority="601">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K733:K734">
-    <cfRule type="expression" dxfId="414" priority="553">
+    <cfRule type="expression" dxfId="423" priority="562">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K736">
-    <cfRule type="expression" dxfId="413" priority="543">
+    <cfRule type="expression" dxfId="422" priority="552">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K742">
-    <cfRule type="expression" dxfId="412" priority="471">
+    <cfRule type="expression" dxfId="421" priority="480">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K744">
-    <cfRule type="expression" dxfId="411" priority="461">
+    <cfRule type="expression" dxfId="420" priority="470">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K747">
-    <cfRule type="expression" dxfId="410" priority="441">
+    <cfRule type="expression" dxfId="419" priority="450">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K749:K750">
-    <cfRule type="expression" dxfId="409" priority="394">
+    <cfRule type="expression" dxfId="418" priority="403">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755:K756">
-    <cfRule type="expression" dxfId="408" priority="359">
+    <cfRule type="expression" dxfId="417" priority="368">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K758">
-    <cfRule type="expression" dxfId="407" priority="320">
+    <cfRule type="expression" dxfId="416" priority="329">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K763:K764">
-    <cfRule type="expression" dxfId="406" priority="293">
+    <cfRule type="expression" dxfId="415" priority="302">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766">
-    <cfRule type="expression" dxfId="405" priority="222">
+    <cfRule type="expression" dxfId="414" priority="231">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K771">
-    <cfRule type="expression" dxfId="404" priority="195">
+    <cfRule type="expression" dxfId="413" priority="204">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="403" priority="194">
+    <cfRule type="expression" dxfId="412" priority="203">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="402" priority="193">
+    <cfRule type="expression" dxfId="411" priority="202">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="401" priority="192">
+    <cfRule type="expression" dxfId="410" priority="201">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="400" priority="191">
+    <cfRule type="expression" dxfId="409" priority="200">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="399" priority="190">
+    <cfRule type="expression" dxfId="408" priority="199">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="398" priority="189">
+    <cfRule type="expression" dxfId="407" priority="198">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="397" priority="188">
+    <cfRule type="expression" dxfId="406" priority="197">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E774">
-    <cfRule type="expression" dxfId="396" priority="187">
+    <cfRule type="expression" dxfId="405" priority="196">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G774">
-    <cfRule type="expression" dxfId="395" priority="186">
+    <cfRule type="expression" dxfId="404" priority="195">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I774">
-    <cfRule type="expression" dxfId="394" priority="185">
+    <cfRule type="expression" dxfId="403" priority="194">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K774">
-    <cfRule type="expression" dxfId="393" priority="184">
+    <cfRule type="expression" dxfId="402" priority="193">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="392" priority="183">
+    <cfRule type="expression" dxfId="401" priority="192">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="391" priority="182">
+    <cfRule type="expression" dxfId="400" priority="191">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="390" priority="181">
+    <cfRule type="expression" dxfId="399" priority="190">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="389" priority="180">
+    <cfRule type="expression" dxfId="398" priority="189">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E779">
-    <cfRule type="expression" dxfId="388" priority="179">
+    <cfRule type="expression" dxfId="397" priority="188">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="387" priority="178">
+    <cfRule type="expression" dxfId="396" priority="187">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="386" priority="177">
+    <cfRule type="expression" dxfId="395" priority="186">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="385" priority="176">
+    <cfRule type="expression" dxfId="394" priority="185">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="384" priority="175">
+    <cfRule type="expression" dxfId="393" priority="184">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="383" priority="174">
+    <cfRule type="expression" dxfId="392" priority="183">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="382" priority="173">
+    <cfRule type="expression" dxfId="391" priority="182">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="381" priority="172">
+    <cfRule type="expression" dxfId="390" priority="181">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="380" priority="171">
+    <cfRule type="expression" dxfId="389" priority="180">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="379" priority="170">
+    <cfRule type="expression" dxfId="388" priority="179">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="378" priority="169">
+    <cfRule type="expression" dxfId="387" priority="178">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="377" priority="168">
+    <cfRule type="expression" dxfId="386" priority="177">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="376" priority="167">
+    <cfRule type="expression" dxfId="385" priority="176">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="375" priority="166">
+    <cfRule type="expression" dxfId="384" priority="175">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="374" priority="165">
+    <cfRule type="expression" dxfId="383" priority="174">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="373" priority="164">
+    <cfRule type="expression" dxfId="382" priority="173">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="372" priority="163">
+    <cfRule type="expression" dxfId="381" priority="172">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="371" priority="162">
+    <cfRule type="expression" dxfId="380" priority="171">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="370" priority="161">
+    <cfRule type="expression" dxfId="379" priority="170">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="369" priority="160">
+    <cfRule type="expression" dxfId="378" priority="169">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="368" priority="159">
+    <cfRule type="expression" dxfId="377" priority="168">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="367" priority="158">
+    <cfRule type="expression" dxfId="376" priority="167">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="366" priority="157">
+    <cfRule type="expression" dxfId="375" priority="166">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="365" priority="156">
+    <cfRule type="expression" dxfId="374" priority="165">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="364" priority="155">
+    <cfRule type="expression" dxfId="373" priority="164">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="363" priority="154">
+    <cfRule type="expression" dxfId="372" priority="163">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="362" priority="153">
+    <cfRule type="expression" dxfId="371" priority="162">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="361" priority="152">
+    <cfRule type="expression" dxfId="370" priority="161">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
+    <cfRule type="expression" dxfId="369" priority="160">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E787">
+    <cfRule type="expression" dxfId="368" priority="159">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G787">
+    <cfRule type="expression" dxfId="367" priority="158">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G787">
+    <cfRule type="expression" dxfId="366" priority="157">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G787">
+    <cfRule type="expression" dxfId="365" priority="156">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I787:I788">
+    <cfRule type="expression" dxfId="364" priority="155">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I787:I788">
+    <cfRule type="expression" dxfId="363" priority="154">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I787:I788">
+    <cfRule type="expression" dxfId="362" priority="153">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K787">
+    <cfRule type="expression" dxfId="361" priority="152">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K787">
     <cfRule type="expression" dxfId="360" priority="151">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E787">
+  <conditionalFormatting sqref="K787">
     <cfRule type="expression" dxfId="359" priority="150">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="358" priority="149">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="357" priority="148">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="356" priority="147">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="355" priority="146">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="354" priority="145">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="353" priority="144">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="352" priority="143">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="351" priority="142">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="350" priority="141">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
-    <cfRule type="expression" dxfId="349" priority="138">
+    <cfRule type="expression" dxfId="358" priority="147">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="348" priority="140">
+    <cfRule type="expression" dxfId="357" priority="149">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="347" priority="139">
+    <cfRule type="expression" dxfId="356" priority="148">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="346" priority="137">
+    <cfRule type="expression" dxfId="355" priority="146">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="345" priority="136">
+    <cfRule type="expression" dxfId="354" priority="145">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="344" priority="135">
+    <cfRule type="expression" dxfId="353" priority="144">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790">
-    <cfRule type="expression" dxfId="343" priority="134">
+    <cfRule type="expression" dxfId="352" priority="143">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="342" priority="131">
+    <cfRule type="expression" dxfId="351" priority="140">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="341" priority="133">
+    <cfRule type="expression" dxfId="350" priority="142">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="340" priority="132">
+    <cfRule type="expression" dxfId="349" priority="141">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="339" priority="128">
+    <cfRule type="expression" dxfId="348" priority="137">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="338" priority="130">
+    <cfRule type="expression" dxfId="347" priority="139">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="337" priority="129">
+    <cfRule type="expression" dxfId="346" priority="138">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
+    <cfRule type="expression" dxfId="345" priority="136">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E795">
+    <cfRule type="expression" dxfId="344" priority="135">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G795">
+    <cfRule type="expression" dxfId="343" priority="134">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G795">
+    <cfRule type="expression" dxfId="342" priority="133">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G795">
+    <cfRule type="expression" dxfId="341" priority="132">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I795:I796">
+    <cfRule type="expression" dxfId="340" priority="131">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I795:I796">
+    <cfRule type="expression" dxfId="339" priority="130">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I795:I796">
+    <cfRule type="expression" dxfId="338" priority="129">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K795">
+    <cfRule type="expression" dxfId="337" priority="128">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K795">
     <cfRule type="expression" dxfId="336" priority="127">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E795">
+  <conditionalFormatting sqref="K795">
     <cfRule type="expression" dxfId="335" priority="126">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G795">
+  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
     <cfRule type="expression" dxfId="334" priority="125">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="333" priority="124">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="332" priority="123">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="331" priority="122">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="330" priority="121">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="329" priority="120">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="328" priority="119">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="327" priority="118">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="326" priority="117">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="325" priority="116">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="324" priority="115">
+    <cfRule type="expression" dxfId="333" priority="124">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="323" priority="114">
+    <cfRule type="expression" dxfId="332" priority="123">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="322" priority="113">
+    <cfRule type="expression" dxfId="331" priority="122">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="321" priority="112">
+    <cfRule type="expression" dxfId="330" priority="121">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="320" priority="111">
+    <cfRule type="expression" dxfId="329" priority="120">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="319" priority="110">
+    <cfRule type="expression" dxfId="328" priority="119">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="318" priority="109">
+    <cfRule type="expression" dxfId="327" priority="118">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798">
-    <cfRule type="expression" dxfId="317" priority="108">
+    <cfRule type="expression" dxfId="326" priority="117">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="316" priority="107">
+    <cfRule type="expression" dxfId="325" priority="116">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="315" priority="106">
+    <cfRule type="expression" dxfId="324" priority="115">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="314" priority="105">
+    <cfRule type="expression" dxfId="323" priority="114">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 K803:K805">
-    <cfRule type="expression" dxfId="313" priority="104">
+    <cfRule type="expression" dxfId="322" priority="113">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
+    <cfRule type="expression" dxfId="321" priority="112">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E805:E806">
+    <cfRule type="expression" dxfId="320" priority="111">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E805:E806">
+    <cfRule type="expression" dxfId="319" priority="110">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
+    <cfRule type="expression" dxfId="318" priority="109">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
+    <cfRule type="expression" dxfId="317" priority="108">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
+    <cfRule type="expression" dxfId="316" priority="107">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
+    <cfRule type="expression" dxfId="315" priority="106">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
+    <cfRule type="expression" dxfId="314" priority="105">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G805:G806">
+    <cfRule type="expression" dxfId="313" priority="104">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G805:G806">
     <cfRule type="expression" dxfId="312" priority="103">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E805:E806">
+  <conditionalFormatting sqref="G805:G806">
     <cfRule type="expression" dxfId="311" priority="102">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E805:E806">
+  <conditionalFormatting sqref="G805:G806">
     <cfRule type="expression" dxfId="310" priority="101">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="309" priority="100">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="308" priority="99">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="307" priority="98">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="306" priority="97">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="305" priority="96">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
+  <conditionalFormatting sqref="I805:I806">
     <cfRule type="expression" dxfId="304" priority="95">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
+  <conditionalFormatting sqref="I805:I806">
     <cfRule type="expression" dxfId="303" priority="94">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
+  <conditionalFormatting sqref="I805:I806">
     <cfRule type="expression" dxfId="302" priority="93">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
+  <conditionalFormatting sqref="I805:I806">
     <cfRule type="expression" dxfId="301" priority="92">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="I806">
     <cfRule type="expression" dxfId="300" priority="91">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="I806">
     <cfRule type="expression" dxfId="299" priority="90">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="I806">
     <cfRule type="expression" dxfId="298" priority="89">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="I806">
     <cfRule type="expression" dxfId="297" priority="88">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="I806">
     <cfRule type="expression" dxfId="296" priority="87">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="295" priority="86">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="294" priority="85">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="293" priority="84">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="292" priority="83">
-      <formula>$C805=TODAY()</formula>
+      <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="291" priority="82">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="290" priority="81">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="289" priority="80">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="288" priority="79">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="287" priority="78">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+  <conditionalFormatting sqref="I808">
     <cfRule type="expression" dxfId="286" priority="77">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="285" priority="76">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="284" priority="75">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="283" priority="74">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="282" priority="73">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="281" priority="72">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="280" priority="71">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="279" priority="70">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="278" priority="69">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="277" priority="68">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="276" priority="67">
+    <cfRule type="expression" dxfId="285" priority="76">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="275" priority="66">
+    <cfRule type="expression" dxfId="284" priority="75">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="274" priority="65">
+    <cfRule type="expression" dxfId="283" priority="74">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="273" priority="64">
+    <cfRule type="expression" dxfId="282" priority="73">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="272" priority="63">
+    <cfRule type="expression" dxfId="281" priority="72">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="271" priority="62">
+    <cfRule type="expression" dxfId="280" priority="71">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="270" priority="61">
+    <cfRule type="expression" dxfId="279" priority="70">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
+    <cfRule type="expression" dxfId="278" priority="69">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E811">
+    <cfRule type="expression" dxfId="277" priority="68">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E811">
+    <cfRule type="expression" dxfId="276" priority="67">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G811">
+    <cfRule type="expression" dxfId="275" priority="66">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G811">
+    <cfRule type="expression" dxfId="274" priority="65">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G811">
+    <cfRule type="expression" dxfId="273" priority="64">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G811">
+    <cfRule type="expression" dxfId="272" priority="63">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I811:I812">
+    <cfRule type="expression" dxfId="271" priority="62">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I811:I812">
+    <cfRule type="expression" dxfId="270" priority="61">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I811:I812">
     <cfRule type="expression" dxfId="269" priority="60">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E811">
+  <conditionalFormatting sqref="I811:I812">
     <cfRule type="expression" dxfId="268" priority="59">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E811">
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="267" priority="58">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="266" priority="57">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="265" priority="56">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="264" priority="55">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+  <conditionalFormatting sqref="E813:E814">
     <cfRule type="expression" dxfId="263" priority="54">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="262" priority="53">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="261" priority="52">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="260" priority="51">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="259" priority="50">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="258" priority="49">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="257" priority="48">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="256" priority="47">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="255" priority="46">
-      <formula>$C811=TODAY()</formula>
+      <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
+    <cfRule type="expression" dxfId="262" priority="53">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E813:E814">
+    <cfRule type="expression" dxfId="261" priority="52">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
+    <cfRule type="expression" dxfId="260" priority="51">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
+    <cfRule type="expression" dxfId="259" priority="50">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
+    <cfRule type="expression" dxfId="258" priority="49">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
+    <cfRule type="expression" dxfId="257" priority="48">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
+    <cfRule type="expression" dxfId="256" priority="47">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G813:G814">
+    <cfRule type="expression" dxfId="255" priority="46">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G813:G814">
     <cfRule type="expression" dxfId="254" priority="45">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E813:E814">
+  <conditionalFormatting sqref="G813:G814">
     <cfRule type="expression" dxfId="253" priority="44">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E813:E814">
+  <conditionalFormatting sqref="G813:G814">
     <cfRule type="expression" dxfId="252" priority="43">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="251" priority="42">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="250" priority="41">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="249" priority="40">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="248" priority="39">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="247" priority="38">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
+  <conditionalFormatting sqref="I813:I814">
     <cfRule type="expression" dxfId="246" priority="37">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
+  <conditionalFormatting sqref="I813:I814">
     <cfRule type="expression" dxfId="245" priority="36">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
+  <conditionalFormatting sqref="I813:I814">
     <cfRule type="expression" dxfId="244" priority="35">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
+  <conditionalFormatting sqref="I813:I814">
     <cfRule type="expression" dxfId="243" priority="34">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
+  <conditionalFormatting sqref="I814">
     <cfRule type="expression" dxfId="242" priority="33">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
+  <conditionalFormatting sqref="I814">
     <cfRule type="expression" dxfId="241" priority="32">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
+  <conditionalFormatting sqref="I814">
     <cfRule type="expression" dxfId="240" priority="31">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
+  <conditionalFormatting sqref="I814">
     <cfRule type="expression" dxfId="239" priority="30">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
+  <conditionalFormatting sqref="I814">
     <cfRule type="expression" dxfId="238" priority="29">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
+  <conditionalFormatting sqref="K813:K814">
     <cfRule type="expression" dxfId="237" priority="28">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
+  <conditionalFormatting sqref="K813:K814">
     <cfRule type="expression" dxfId="236" priority="27">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
+  <conditionalFormatting sqref="K813:K814">
     <cfRule type="expression" dxfId="235" priority="26">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
+  <conditionalFormatting sqref="K813:K814">
     <cfRule type="expression" dxfId="234" priority="25">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+  <conditionalFormatting sqref="K814">
     <cfRule type="expression" dxfId="233" priority="24">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+  <conditionalFormatting sqref="K814">
     <cfRule type="expression" dxfId="232" priority="23">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+  <conditionalFormatting sqref="K814">
     <cfRule type="expression" dxfId="231" priority="22">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+  <conditionalFormatting sqref="K814">
     <cfRule type="expression" dxfId="230" priority="21">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+  <conditionalFormatting sqref="K814">
     <cfRule type="expression" dxfId="229" priority="20">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
+  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
     <cfRule type="expression" dxfId="228" priority="19">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="227" priority="18">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="226" priority="17">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="225" priority="16">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="224" priority="15">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="223" priority="14">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="222" priority="13">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="221" priority="12">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="220" priority="11">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="219" priority="10">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="218" priority="9">
+    <cfRule type="expression" dxfId="227" priority="18">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="217" priority="8">
+    <cfRule type="expression" dxfId="226" priority="17">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="216" priority="7">
+    <cfRule type="expression" dxfId="225" priority="16">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K829 I829 G829">
-    <cfRule type="expression" dxfId="215" priority="6">
+    <cfRule type="expression" dxfId="224" priority="15">
       <formula>$C829=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I834 G834 K834:K835">
-    <cfRule type="expression" dxfId="214" priority="5">
+    <cfRule type="expression" dxfId="223" priority="14">
       <formula>$C834=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836 G836">
-    <cfRule type="expression" dxfId="213" priority="4">
+    <cfRule type="expression" dxfId="222" priority="13">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837 I837 G837">
-    <cfRule type="expression" dxfId="212" priority="3">
+    <cfRule type="expression" dxfId="221" priority="12">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K839 I839">
-    <cfRule type="expression" dxfId="211" priority="2">
+    <cfRule type="expression" dxfId="220" priority="11">
       <formula>$C839=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K842 I842 G842 E842">
+    <cfRule type="expression" dxfId="219" priority="10">
+      <formula>$C842=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K845 I845 G845 E845">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>$C845=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K845 I845 G845">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$C845=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K844 I844 G844 E844">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>$C844=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K844 I844 G844">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$C844=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K843 I843">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$C843=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K843 I843">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$C843=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K844 I844 G844 E844">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$C844=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K844 I844 G844">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$C844=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K845 I845 G845 E845">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$C842=TODAY()</formula>
+      <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -51862,1052 +52190,1052 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="B4:E869">
-    <cfRule type="expression" dxfId="210" priority="388">
+    <cfRule type="expression" dxfId="218" priority="388">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K869">
-    <cfRule type="expression" dxfId="209" priority="389">
+    <cfRule type="expression" dxfId="217" priority="389">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G47 J44:K47">
-    <cfRule type="expression" dxfId="208" priority="398">
+    <cfRule type="expression" dxfId="216" priority="398">
       <formula>$B18=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E692">
-    <cfRule type="expression" dxfId="207" priority="382">
+    <cfRule type="expression" dxfId="215" priority="382">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E694">
-    <cfRule type="expression" dxfId="206" priority="380">
+    <cfRule type="expression" dxfId="214" priority="380">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E701">
-    <cfRule type="expression" dxfId="205" priority="370">
+    <cfRule type="expression" dxfId="213" priority="370">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E703">
-    <cfRule type="expression" dxfId="204" priority="365">
+    <cfRule type="expression" dxfId="212" priority="365">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E710">
-    <cfRule type="expression" dxfId="203" priority="355">
+    <cfRule type="expression" dxfId="211" priority="355">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E712:E714">
-    <cfRule type="expression" dxfId="202" priority="350">
+    <cfRule type="expression" dxfId="210" priority="350">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E719">
-    <cfRule type="expression" dxfId="201" priority="340">
+    <cfRule type="expression" dxfId="209" priority="340">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E721:E723">
-    <cfRule type="expression" dxfId="200" priority="335">
+    <cfRule type="expression" dxfId="208" priority="335">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E728">
-    <cfRule type="expression" dxfId="199" priority="328">
+    <cfRule type="expression" dxfId="207" priority="328">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E730:E732">
-    <cfRule type="expression" dxfId="198" priority="315">
+    <cfRule type="expression" dxfId="206" priority="315">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E737">
-    <cfRule type="expression" dxfId="197" priority="308">
+    <cfRule type="expression" dxfId="205" priority="308">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739:E741">
-    <cfRule type="expression" dxfId="196" priority="295">
+    <cfRule type="expression" dxfId="204" priority="295">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E746">
-    <cfRule type="expression" dxfId="195" priority="285">
+    <cfRule type="expression" dxfId="203" priority="285">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E748:E750">
-    <cfRule type="expression" dxfId="194" priority="263">
+    <cfRule type="expression" dxfId="202" priority="263">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="193" priority="256">
+    <cfRule type="expression" dxfId="201" priority="256">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E759">
-    <cfRule type="expression" dxfId="192" priority="229">
+    <cfRule type="expression" dxfId="200" priority="229">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E764">
-    <cfRule type="expression" dxfId="191" priority="225">
+    <cfRule type="expression" dxfId="199" priority="225">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E766:E768">
-    <cfRule type="expression" dxfId="190" priority="200">
+    <cfRule type="expression" dxfId="198" priority="200">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="189" priority="190">
+    <cfRule type="expression" dxfId="197" priority="190">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E775:E777">
-    <cfRule type="expression" dxfId="188" priority="178">
+    <cfRule type="expression" dxfId="196" priority="178">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="187" priority="156">
+    <cfRule type="expression" dxfId="195" priority="156">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E784:E786">
-    <cfRule type="expression" dxfId="186" priority="138">
+    <cfRule type="expression" dxfId="194" priority="138">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="185" priority="401">
+    <cfRule type="expression" dxfId="193" priority="401">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70">
-    <cfRule type="expression" dxfId="184" priority="410">
+    <cfRule type="expression" dxfId="192" priority="410">
       <formula>$C70=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G685">
-    <cfRule type="expression" dxfId="183" priority="386">
+    <cfRule type="expression" dxfId="191" priority="386">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G692">
-    <cfRule type="expression" dxfId="182" priority="383">
+    <cfRule type="expression" dxfId="190" priority="383">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G695">
-    <cfRule type="expression" dxfId="181" priority="373">
+    <cfRule type="expression" dxfId="189" priority="373">
       <formula>$C695=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701">
-    <cfRule type="expression" dxfId="180" priority="368">
+    <cfRule type="expression" dxfId="188" priority="368">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G704:G705">
-    <cfRule type="expression" dxfId="179" priority="357">
+    <cfRule type="expression" dxfId="187" priority="357">
       <formula>$C704=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G710">
-    <cfRule type="expression" dxfId="178" priority="353">
+    <cfRule type="expression" dxfId="186" priority="353">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G712:G714">
-    <cfRule type="expression" dxfId="177" priority="343">
+    <cfRule type="expression" dxfId="185" priority="343">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G719">
-    <cfRule type="expression" dxfId="176" priority="338">
+    <cfRule type="expression" dxfId="184" priority="338">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G721:G723">
-    <cfRule type="expression" dxfId="175" priority="333">
+    <cfRule type="expression" dxfId="183" priority="333">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G728">
-    <cfRule type="expression" dxfId="174" priority="326">
+    <cfRule type="expression" dxfId="182" priority="326">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G730:G732">
-    <cfRule type="expression" dxfId="173" priority="313">
+    <cfRule type="expression" dxfId="181" priority="313">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G737">
-    <cfRule type="expression" dxfId="172" priority="306">
+    <cfRule type="expression" dxfId="180" priority="306">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739:G741">
-    <cfRule type="expression" dxfId="171" priority="292">
+    <cfRule type="expression" dxfId="179" priority="292">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746">
-    <cfRule type="expression" dxfId="170" priority="283">
+    <cfRule type="expression" dxfId="178" priority="283">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="169" priority="260">
+    <cfRule type="expression" dxfId="177" priority="260">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="168" priority="254">
+    <cfRule type="expression" dxfId="176" priority="254">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G759">
-    <cfRule type="expression" dxfId="167" priority="226">
+    <cfRule type="expression" dxfId="175" priority="226">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G764">
-    <cfRule type="expression" dxfId="166" priority="223">
+    <cfRule type="expression" dxfId="174" priority="223">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G766:G768">
-    <cfRule type="expression" dxfId="165" priority="196">
+    <cfRule type="expression" dxfId="173" priority="196">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="164" priority="188">
+    <cfRule type="expression" dxfId="172" priority="188">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G775:G777">
-    <cfRule type="expression" dxfId="163" priority="171">
+    <cfRule type="expression" dxfId="171" priority="171">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="162" priority="154">
+    <cfRule type="expression" dxfId="170" priority="154">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G784:G786">
-    <cfRule type="expression" dxfId="161" priority="132">
+    <cfRule type="expression" dxfId="169" priority="132">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:I47">
-    <cfRule type="expression" dxfId="160" priority="423">
+    <cfRule type="expression" dxfId="168" priority="423">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="expression" dxfId="159" priority="427">
+    <cfRule type="expression" dxfId="167" priority="427">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I685">
-    <cfRule type="expression" dxfId="158" priority="385">
+    <cfRule type="expression" dxfId="166" priority="385">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I694:I695">
-    <cfRule type="expression" dxfId="157" priority="372">
+    <cfRule type="expression" dxfId="165" priority="372">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I703:I704">
-    <cfRule type="expression" dxfId="156" priority="359">
+    <cfRule type="expression" dxfId="164" priority="359">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I712:I714">
-    <cfRule type="expression" dxfId="155" priority="342">
+    <cfRule type="expression" dxfId="163" priority="342">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I721:I723">
-    <cfRule type="expression" dxfId="154" priority="331">
+    <cfRule type="expression" dxfId="162" priority="331">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I730:I732">
-    <cfRule type="expression" dxfId="153" priority="309">
+    <cfRule type="expression" dxfId="161" priority="309">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I741">
-    <cfRule type="expression" dxfId="152" priority="289">
+    <cfRule type="expression" dxfId="160" priority="289">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I748:I749">
-    <cfRule type="expression" dxfId="151" priority="268">
+    <cfRule type="expression" dxfId="159" priority="268">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755">
-    <cfRule type="expression" dxfId="150" priority="252">
+    <cfRule type="expression" dxfId="158" priority="252">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I757:I758">
-    <cfRule type="expression" dxfId="149" priority="235">
+    <cfRule type="expression" dxfId="157" priority="235">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I766:I768">
-    <cfRule type="expression" dxfId="148" priority="192">
+    <cfRule type="expression" dxfId="156" priority="192">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="147" priority="186">
+    <cfRule type="expression" dxfId="155" priority="186">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I775:I777">
-    <cfRule type="expression" dxfId="146" priority="164">
+    <cfRule type="expression" dxfId="154" priority="164">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="145" priority="152">
+    <cfRule type="expression" dxfId="153" priority="152">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784:I786">
-    <cfRule type="expression" dxfId="144" priority="126">
+    <cfRule type="expression" dxfId="152" priority="126">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="143" priority="402">
+    <cfRule type="expression" dxfId="151" priority="402">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K685">
-    <cfRule type="expression" dxfId="142" priority="384">
+    <cfRule type="expression" dxfId="150" priority="384">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K692">
-    <cfRule type="expression" dxfId="141" priority="381">
+    <cfRule type="expression" dxfId="149" priority="381">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K694:K695">
-    <cfRule type="expression" dxfId="140" priority="371">
+    <cfRule type="expression" dxfId="148" priority="371">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701">
-    <cfRule type="expression" dxfId="139" priority="366">
+    <cfRule type="expression" dxfId="147" priority="366">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K703:K705">
-    <cfRule type="expression" dxfId="138" priority="356">
+    <cfRule type="expression" dxfId="146" priority="356">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K710">
-    <cfRule type="expression" dxfId="137" priority="351">
+    <cfRule type="expression" dxfId="145" priority="351">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K712:K714">
-    <cfRule type="expression" dxfId="136" priority="341">
+    <cfRule type="expression" dxfId="144" priority="341">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K719">
-    <cfRule type="expression" dxfId="135" priority="336">
+    <cfRule type="expression" dxfId="143" priority="336">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K721:K723">
-    <cfRule type="expression" dxfId="134" priority="329">
+    <cfRule type="expression" dxfId="142" priority="329">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K728">
-    <cfRule type="expression" dxfId="133" priority="324">
+    <cfRule type="expression" dxfId="141" priority="324">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K730:K732">
-    <cfRule type="expression" dxfId="132" priority="311">
+    <cfRule type="expression" dxfId="140" priority="311">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K737">
-    <cfRule type="expression" dxfId="131" priority="304">
+    <cfRule type="expression" dxfId="139" priority="304">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K741">
-    <cfRule type="expression" dxfId="130" priority="286">
+    <cfRule type="expression" dxfId="138" priority="286">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K746">
-    <cfRule type="expression" dxfId="129" priority="281">
+    <cfRule type="expression" dxfId="137" priority="281">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K748:K750">
-    <cfRule type="expression" dxfId="128" priority="257">
+    <cfRule type="expression" dxfId="136" priority="257">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755">
-    <cfRule type="expression" dxfId="127" priority="250">
+    <cfRule type="expression" dxfId="135" priority="250">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K757:K758">
-    <cfRule type="expression" dxfId="126" priority="232">
+    <cfRule type="expression" dxfId="134" priority="232">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K764">
-    <cfRule type="expression" dxfId="125" priority="221">
+    <cfRule type="expression" dxfId="133" priority="221">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766:K767">
-    <cfRule type="expression" dxfId="124" priority="203">
+    <cfRule type="expression" dxfId="132" priority="203">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="123" priority="184">
+    <cfRule type="expression" dxfId="131" priority="184">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K775:K777">
-    <cfRule type="expression" dxfId="122" priority="157">
+    <cfRule type="expression" dxfId="130" priority="157">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="121" priority="150">
+    <cfRule type="expression" dxfId="129" priority="150">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784:K786">
-    <cfRule type="expression" dxfId="120" priority="120">
+    <cfRule type="expression" dxfId="128" priority="120">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E792:E793">
-    <cfRule type="expression" dxfId="119" priority="119">
+    <cfRule type="expression" dxfId="127" priority="119">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="118" priority="118">
+    <cfRule type="expression" dxfId="126" priority="118">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="117" priority="117">
+    <cfRule type="expression" dxfId="125" priority="117">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="116" priority="116">
+    <cfRule type="expression" dxfId="124" priority="116">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="115" priority="115">
+    <cfRule type="expression" dxfId="123" priority="115">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="114" priority="114">
+    <cfRule type="expression" dxfId="122" priority="114">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="113" priority="113">
+    <cfRule type="expression" dxfId="121" priority="113">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E794:E795">
-    <cfRule type="expression" dxfId="112" priority="112">
+    <cfRule type="expression" dxfId="120" priority="112">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="111" priority="111">
+    <cfRule type="expression" dxfId="119" priority="111">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="110" priority="110">
+    <cfRule type="expression" dxfId="118" priority="110">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="109" priority="109">
+    <cfRule type="expression" dxfId="117" priority="109">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="108" priority="108">
+    <cfRule type="expression" dxfId="116" priority="108">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="107" priority="107">
+    <cfRule type="expression" dxfId="115" priority="107">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="106" priority="106">
+    <cfRule type="expression" dxfId="114" priority="106">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E801:E802">
-    <cfRule type="expression" dxfId="105" priority="105">
+    <cfRule type="expression" dxfId="113" priority="105">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E803:E805">
-    <cfRule type="expression" dxfId="104" priority="104">
+    <cfRule type="expression" dxfId="112" priority="104">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G805">
-    <cfRule type="expression" dxfId="103" priority="103">
+    <cfRule type="expression" dxfId="111" priority="103">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G802">
-    <cfRule type="expression" dxfId="102" priority="102">
+    <cfRule type="expression" dxfId="110" priority="102">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G803:G805">
-    <cfRule type="expression" dxfId="101" priority="101">
+    <cfRule type="expression" dxfId="109" priority="101">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I805">
-    <cfRule type="expression" dxfId="100" priority="100">
+    <cfRule type="expression" dxfId="108" priority="100">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I802">
-    <cfRule type="expression" dxfId="99" priority="99">
+    <cfRule type="expression" dxfId="107" priority="99">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803:I805">
-    <cfRule type="expression" dxfId="98" priority="98">
+    <cfRule type="expression" dxfId="106" priority="98">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K805">
-    <cfRule type="expression" dxfId="97" priority="97">
+    <cfRule type="expression" dxfId="105" priority="97">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K802">
-    <cfRule type="expression" dxfId="96" priority="96">
+    <cfRule type="expression" dxfId="104" priority="96">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K803:K805">
-    <cfRule type="expression" dxfId="95" priority="95">
+    <cfRule type="expression" dxfId="103" priority="95">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E809:E810">
-    <cfRule type="expression" dxfId="94" priority="94">
+    <cfRule type="expression" dxfId="102" priority="94">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811:E812">
-    <cfRule type="expression" dxfId="93" priority="93">
+    <cfRule type="expression" dxfId="101" priority="93">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G812">
-    <cfRule type="expression" dxfId="92" priority="92">
+    <cfRule type="expression" dxfId="100" priority="92">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G810">
-    <cfRule type="expression" dxfId="91" priority="91">
+    <cfRule type="expression" dxfId="99" priority="91">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811:G812">
-    <cfRule type="expression" dxfId="90" priority="90">
+    <cfRule type="expression" dxfId="98" priority="90">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I812">
-    <cfRule type="expression" dxfId="89" priority="89">
+    <cfRule type="expression" dxfId="97" priority="89">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I810">
-    <cfRule type="expression" dxfId="88" priority="88">
+    <cfRule type="expression" dxfId="96" priority="88">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="87" priority="87">
+    <cfRule type="expression" dxfId="95" priority="87">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K812">
-    <cfRule type="expression" dxfId="86" priority="86">
+    <cfRule type="expression" dxfId="94" priority="86">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K810">
-    <cfRule type="expression" dxfId="85" priority="85">
+    <cfRule type="expression" dxfId="93" priority="85">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811:K812">
-    <cfRule type="expression" dxfId="84" priority="84">
+    <cfRule type="expression" dxfId="92" priority="84">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E818:E822 G818:G822 K818:K822 I818:I822">
-    <cfRule type="expression" dxfId="83" priority="83">
+    <cfRule type="expression" dxfId="91" priority="83">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K818:K822 G818:G822 I818:I822">
-    <cfRule type="expression" dxfId="82" priority="82">
+    <cfRule type="expression" dxfId="90" priority="82">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E820:E821">
-    <cfRule type="expression" dxfId="81" priority="81">
+    <cfRule type="expression" dxfId="89" priority="81">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="80" priority="80">
+    <cfRule type="expression" dxfId="88" priority="80">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="79" priority="79">
+    <cfRule type="expression" dxfId="87" priority="79">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="78" priority="78">
+    <cfRule type="expression" dxfId="86" priority="78">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="77" priority="77">
+    <cfRule type="expression" dxfId="85" priority="77">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K822 G822">
-    <cfRule type="expression" dxfId="76" priority="76">
+    <cfRule type="expression" dxfId="84" priority="76">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I822">
-    <cfRule type="expression" dxfId="75" priority="75">
+    <cfRule type="expression" dxfId="83" priority="75">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E828:E831">
-    <cfRule type="expression" dxfId="74" priority="74">
+    <cfRule type="expression" dxfId="82" priority="74">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="73" priority="73">
+    <cfRule type="expression" dxfId="81" priority="73">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="72" priority="72">
+    <cfRule type="expression" dxfId="80" priority="72">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="71" priority="71">
+    <cfRule type="expression" dxfId="79" priority="71">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="70" priority="70">
+    <cfRule type="expression" dxfId="78" priority="70">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="69" priority="69">
+    <cfRule type="expression" dxfId="77" priority="69">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="68" priority="68">
+    <cfRule type="expression" dxfId="76" priority="68">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="67" priority="67">
+    <cfRule type="expression" dxfId="75" priority="67">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="66" priority="66">
+    <cfRule type="expression" dxfId="74" priority="66">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="65" priority="65">
+    <cfRule type="expression" dxfId="73" priority="65">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="64" priority="64">
+    <cfRule type="expression" dxfId="72" priority="64">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="63" priority="63">
+    <cfRule type="expression" dxfId="71" priority="63">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="62" priority="62">
+    <cfRule type="expression" dxfId="70" priority="62">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="61" priority="61">
+    <cfRule type="expression" dxfId="69" priority="61">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837">
-    <cfRule type="expression" dxfId="60" priority="60">
+    <cfRule type="expression" dxfId="68" priority="60">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="59" priority="59">
+    <cfRule type="expression" dxfId="67" priority="59">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="58" priority="58">
+    <cfRule type="expression" dxfId="66" priority="58">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="57" priority="57">
+    <cfRule type="expression" dxfId="65" priority="57">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="56" priority="56">
+    <cfRule type="expression" dxfId="64" priority="56">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="55" priority="55">
+    <cfRule type="expression" dxfId="63" priority="55">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="54" priority="54">
+    <cfRule type="expression" dxfId="62" priority="54">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E845:E847">
-    <cfRule type="expression" dxfId="53" priority="53">
+    <cfRule type="expression" dxfId="61" priority="53">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="52" priority="52">
+    <cfRule type="expression" dxfId="60" priority="52">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="51" priority="51">
+    <cfRule type="expression" dxfId="59" priority="51">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="50" priority="50">
+    <cfRule type="expression" dxfId="58" priority="50">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="49" priority="49">
+    <cfRule type="expression" dxfId="57" priority="49">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="48" priority="48">
+    <cfRule type="expression" dxfId="56" priority="48">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="47" priority="47">
+    <cfRule type="expression" dxfId="55" priority="47">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="46" priority="46">
+    <cfRule type="expression" dxfId="54" priority="46">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="45" priority="45">
+    <cfRule type="expression" dxfId="53" priority="45">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="44" priority="44">
+    <cfRule type="expression" dxfId="52" priority="44">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="43" priority="43">
+    <cfRule type="expression" dxfId="51" priority="43">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="42" priority="42">
+    <cfRule type="expression" dxfId="50" priority="42">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="41" priority="41">
+    <cfRule type="expression" dxfId="49" priority="41">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="40" priority="40">
+    <cfRule type="expression" dxfId="48" priority="40">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="39" priority="39">
+    <cfRule type="expression" dxfId="47" priority="39">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="38" priority="38">
+    <cfRule type="expression" dxfId="46" priority="38">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="37" priority="37">
+    <cfRule type="expression" dxfId="45" priority="37">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="36" priority="36">
+    <cfRule type="expression" dxfId="44" priority="36">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="35" priority="35">
+    <cfRule type="expression" dxfId="43" priority="35">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="34" priority="34">
+    <cfRule type="expression" dxfId="42" priority="34">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="33" priority="33">
+    <cfRule type="expression" dxfId="41" priority="33">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="32" priority="32">
+    <cfRule type="expression" dxfId="40" priority="32">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="31" priority="31">
+    <cfRule type="expression" dxfId="39" priority="31">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="30" priority="30">
+    <cfRule type="expression" dxfId="38" priority="30">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="29" priority="29">
+    <cfRule type="expression" dxfId="37" priority="29">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="28" priority="28">
+    <cfRule type="expression" dxfId="36" priority="28">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="27" priority="27">
+    <cfRule type="expression" dxfId="35" priority="27">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="26" priority="26">
+    <cfRule type="expression" dxfId="34" priority="26">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="25" priority="25">
+    <cfRule type="expression" dxfId="33" priority="25">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="24" priority="24">
+    <cfRule type="expression" dxfId="32" priority="24">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="23" priority="23">
+    <cfRule type="expression" dxfId="31" priority="23">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E836">
-    <cfRule type="expression" dxfId="22" priority="22">
+    <cfRule type="expression" dxfId="30" priority="22">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="21" priority="21">
+    <cfRule type="expression" dxfId="29" priority="21">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="28" priority="20">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="27" priority="19">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="26" priority="18">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="17" priority="17">
+    <cfRule type="expression" dxfId="25" priority="17">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="16" priority="16">
+    <cfRule type="expression" dxfId="24" priority="16">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853 E853">
-    <cfRule type="expression" dxfId="15" priority="15">
+    <cfRule type="expression" dxfId="23" priority="15">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853">
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="22" priority="14">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854 E854">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="21" priority="13">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="20" priority="12">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="19" priority="11">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="18" priority="10">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="17" priority="9">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K862 I862 G862 E862">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="15" priority="7">
       <formula>$C862=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K862 I862 G862">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="14" priority="6">
       <formula>$C862=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K863 I863 G863 E863">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>$C863=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K863:K865 I863:I865 G863:G865">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$C863=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>

--- a/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
+++ b/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979F2D7F-76AD-43D7-88DC-85924B833247}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7395786-D5A4-4442-8F85-F4F724485014}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3474" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3503" uniqueCount="33">
   <si>
     <t>План поставок ПОКОМ</t>
   </si>
@@ -435,7 +435,182 @@
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Обычный 2 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="513">
+  <dxfs count="538">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -28718,14 +28893,30 @@
       <c r="C850" s="8">
         <v>46049</v>
       </c>
-      <c r="D850" s="9"/>
-      <c r="E850" s="10"/>
-      <c r="F850" s="11"/>
-      <c r="G850" s="12"/>
-      <c r="H850" s="11"/>
-      <c r="I850" s="12"/>
-      <c r="J850" s="11"/>
-      <c r="K850" s="12"/>
+      <c r="D850" s="9">
+        <v>11500</v>
+      </c>
+      <c r="E850" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F850" s="11">
+        <v>7000</v>
+      </c>
+      <c r="G850" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H850" s="11">
+        <v>14000</v>
+      </c>
+      <c r="I850" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J850" s="11">
+        <v>10900</v>
+      </c>
+      <c r="K850" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="851" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A851" s="1">
@@ -28833,1518 +29024,1528 @@
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E855">
-    <cfRule type="expression" dxfId="512" priority="722">
+    <cfRule type="expression" dxfId="537" priority="724">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:M683 B684:K855">
-    <cfRule type="expression" dxfId="511" priority="723">
+    <cfRule type="expression" dxfId="536" priority="725">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E678">
-    <cfRule type="expression" dxfId="510" priority="713">
+    <cfRule type="expression" dxfId="535" priority="715">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E693:E694">
-    <cfRule type="expression" dxfId="509" priority="700">
+    <cfRule type="expression" dxfId="534" priority="702">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E702">
-    <cfRule type="expression" dxfId="508" priority="687">
+    <cfRule type="expression" dxfId="533" priority="689">
       <formula>$C702=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E707">
-    <cfRule type="expression" dxfId="507" priority="683">
+    <cfRule type="expression" dxfId="532" priority="685">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709:E710">
-    <cfRule type="expression" dxfId="506" priority="675">
+    <cfRule type="expression" dxfId="531" priority="677">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E715">
-    <cfRule type="expression" dxfId="505" priority="671">
+    <cfRule type="expression" dxfId="530" priority="673">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E717:E718">
-    <cfRule type="expression" dxfId="504" priority="659">
+    <cfRule type="expression" dxfId="529" priority="661">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E723">
-    <cfRule type="expression" dxfId="503" priority="648">
+    <cfRule type="expression" dxfId="528" priority="650">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E725:E726">
-    <cfRule type="expression" dxfId="502" priority="625">
+    <cfRule type="expression" dxfId="527" priority="627">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E731">
-    <cfRule type="expression" dxfId="501" priority="613">
+    <cfRule type="expression" dxfId="526" priority="615">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E733:E734">
-    <cfRule type="expression" dxfId="500" priority="580">
+    <cfRule type="expression" dxfId="525" priority="582">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739">
-    <cfRule type="expression" dxfId="499" priority="548">
+    <cfRule type="expression" dxfId="524" priority="550">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E741:E742">
-    <cfRule type="expression" dxfId="498" priority="503">
+    <cfRule type="expression" dxfId="523" priority="505">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E747:E748">
-    <cfRule type="expression" dxfId="497" priority="440">
+    <cfRule type="expression" dxfId="522" priority="442">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E750">
-    <cfRule type="expression" dxfId="496" priority="424">
+    <cfRule type="expression" dxfId="521" priority="426">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="495" priority="398">
+    <cfRule type="expression" dxfId="520" priority="400">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E758">
-    <cfRule type="expression" dxfId="494" priority="350">
+    <cfRule type="expression" dxfId="519" priority="352">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E763">
-    <cfRule type="expression" dxfId="493" priority="323">
+    <cfRule type="expression" dxfId="518" priority="325">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E765:E766">
-    <cfRule type="expression" dxfId="492" priority="270">
+    <cfRule type="expression" dxfId="517" priority="272">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E771">
-    <cfRule type="expression" dxfId="491" priority="225">
+    <cfRule type="expression" dxfId="516" priority="227">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="490" priority="736">
+    <cfRule type="expression" dxfId="515" priority="738">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G661">
-    <cfRule type="expression" dxfId="489" priority="720">
+    <cfRule type="expression" dxfId="514" priority="722">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G670">
-    <cfRule type="expression" dxfId="488" priority="717">
+    <cfRule type="expression" dxfId="513" priority="719">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G678">
-    <cfRule type="expression" dxfId="487" priority="714">
+    <cfRule type="expression" dxfId="512" priority="716">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G686">
-    <cfRule type="expression" dxfId="486" priority="710">
+    <cfRule type="expression" dxfId="511" priority="712">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G691">
-    <cfRule type="expression" dxfId="485" priority="707">
+    <cfRule type="expression" dxfId="510" priority="709">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G693:G694">
-    <cfRule type="expression" dxfId="484" priority="699">
+    <cfRule type="expression" dxfId="509" priority="701">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G699">
-    <cfRule type="expression" dxfId="483" priority="696">
+    <cfRule type="expression" dxfId="508" priority="698">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701:G702">
-    <cfRule type="expression" dxfId="482" priority="688">
+    <cfRule type="expression" dxfId="507" priority="690">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G707">
-    <cfRule type="expression" dxfId="481" priority="684">
+    <cfRule type="expression" dxfId="506" priority="686">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G709:G710">
-    <cfRule type="expression" dxfId="480" priority="674">
+    <cfRule type="expression" dxfId="505" priority="676">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G715">
-    <cfRule type="expression" dxfId="479" priority="669">
+    <cfRule type="expression" dxfId="504" priority="671">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G717:G718">
-    <cfRule type="expression" dxfId="478" priority="656">
+    <cfRule type="expression" dxfId="503" priority="658">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G723">
-    <cfRule type="expression" dxfId="477" priority="645">
+    <cfRule type="expression" dxfId="502" priority="647">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G725:G726">
-    <cfRule type="expression" dxfId="476" priority="622">
+    <cfRule type="expression" dxfId="501" priority="624">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G731">
-    <cfRule type="expression" dxfId="475" priority="609">
+    <cfRule type="expression" dxfId="500" priority="611">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G733:G734">
-    <cfRule type="expression" dxfId="474" priority="574">
+    <cfRule type="expression" dxfId="499" priority="576">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739">
-    <cfRule type="expression" dxfId="473" priority="543">
+    <cfRule type="expression" dxfId="498" priority="545">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G741:G742">
-    <cfRule type="expression" dxfId="472" priority="497">
+    <cfRule type="expression" dxfId="497" priority="499">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G747">
-    <cfRule type="expression" dxfId="471" priority="460">
+    <cfRule type="expression" dxfId="496" priority="462">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="470" priority="417">
+    <cfRule type="expression" dxfId="495" priority="419">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="469" priority="392">
+    <cfRule type="expression" dxfId="494" priority="394">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G758">
-    <cfRule type="expression" dxfId="468" priority="343">
+    <cfRule type="expression" dxfId="493" priority="345">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763">
-    <cfRule type="expression" dxfId="467" priority="316">
+    <cfRule type="expression" dxfId="492" priority="318">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G765:G766">
-    <cfRule type="expression" dxfId="466" priority="257">
+    <cfRule type="expression" dxfId="491" priority="259">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G771">
-    <cfRule type="expression" dxfId="465" priority="218">
+    <cfRule type="expression" dxfId="490" priority="220">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H128:I129">
-    <cfRule type="expression" dxfId="464" priority="739">
+    <cfRule type="expression" dxfId="489" priority="741">
       <formula>$C128=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="expression" dxfId="463" priority="737">
+    <cfRule type="expression" dxfId="488" priority="739">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I661">
-    <cfRule type="expression" dxfId="462" priority="719">
+    <cfRule type="expression" dxfId="487" priority="721">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670">
-    <cfRule type="expression" dxfId="461" priority="716">
+    <cfRule type="expression" dxfId="486" priority="718">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I678">
-    <cfRule type="expression" dxfId="460" priority="712">
+    <cfRule type="expression" dxfId="485" priority="714">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I686">
-    <cfRule type="expression" dxfId="459" priority="709">
+    <cfRule type="expression" dxfId="484" priority="711">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I691">
-    <cfRule type="expression" dxfId="458" priority="706">
+    <cfRule type="expression" dxfId="483" priority="708">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I693:I694">
-    <cfRule type="expression" dxfId="457" priority="698">
+    <cfRule type="expression" dxfId="482" priority="700">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I699">
-    <cfRule type="expression" dxfId="456" priority="695">
+    <cfRule type="expression" dxfId="481" priority="697">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I701:I702">
-    <cfRule type="expression" dxfId="455" priority="689">
+    <cfRule type="expression" dxfId="480" priority="691">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I707">
-    <cfRule type="expression" dxfId="454" priority="686">
+    <cfRule type="expression" dxfId="479" priority="688">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I709:I710">
-    <cfRule type="expression" dxfId="453" priority="673">
+    <cfRule type="expression" dxfId="478" priority="675">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I715">
-    <cfRule type="expression" dxfId="452" priority="667">
+    <cfRule type="expression" dxfId="477" priority="669">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I717:I718">
-    <cfRule type="expression" dxfId="451" priority="653">
+    <cfRule type="expression" dxfId="476" priority="655">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I723:I726">
-    <cfRule type="expression" dxfId="450" priority="619">
+    <cfRule type="expression" dxfId="475" priority="621">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I731:I734">
-    <cfRule type="expression" dxfId="449" priority="568">
+    <cfRule type="expression" dxfId="474" priority="570">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I736">
-    <cfRule type="expression" dxfId="448" priority="557">
+    <cfRule type="expression" dxfId="473" priority="559">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I742">
-    <cfRule type="expression" dxfId="447" priority="491">
+    <cfRule type="expression" dxfId="472" priority="493">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I744">
-    <cfRule type="expression" dxfId="446" priority="475">
+    <cfRule type="expression" dxfId="471" priority="477">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I747:I748">
-    <cfRule type="expression" dxfId="445" priority="445">
+    <cfRule type="expression" dxfId="470" priority="447">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I750">
-    <cfRule type="expression" dxfId="444" priority="410">
+    <cfRule type="expression" dxfId="469" priority="412">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755:I756">
-    <cfRule type="expression" dxfId="443" priority="374">
+    <cfRule type="expression" dxfId="468" priority="376">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I758">
-    <cfRule type="expression" dxfId="442" priority="336">
+    <cfRule type="expression" dxfId="467" priority="338">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I763">
-    <cfRule type="expression" dxfId="441" priority="309">
+    <cfRule type="expression" dxfId="466" priority="311">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I765:I766">
-    <cfRule type="expression" dxfId="440" priority="244">
+    <cfRule type="expression" dxfId="465" priority="246">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I771:I772">
-    <cfRule type="expression" dxfId="439" priority="211">
+    <cfRule type="expression" dxfId="464" priority="213">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="438" priority="738">
+    <cfRule type="expression" dxfId="463" priority="740">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K661">
-    <cfRule type="expression" dxfId="437" priority="718">
+    <cfRule type="expression" dxfId="462" priority="720">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K670">
-    <cfRule type="expression" dxfId="436" priority="715">
+    <cfRule type="expression" dxfId="461" priority="717">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K678">
-    <cfRule type="expression" dxfId="435" priority="711">
+    <cfRule type="expression" dxfId="460" priority="713">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K686">
-    <cfRule type="expression" dxfId="434" priority="708">
+    <cfRule type="expression" dxfId="459" priority="710">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K691">
-    <cfRule type="expression" dxfId="433" priority="705">
+    <cfRule type="expression" dxfId="458" priority="707">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K693:K694">
-    <cfRule type="expression" dxfId="432" priority="697">
+    <cfRule type="expression" dxfId="457" priority="699">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K699">
-    <cfRule type="expression" dxfId="431" priority="694">
+    <cfRule type="expression" dxfId="456" priority="696">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701:K702">
-    <cfRule type="expression" dxfId="430" priority="690">
+    <cfRule type="expression" dxfId="455" priority="692">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K707">
-    <cfRule type="expression" dxfId="429" priority="685">
+    <cfRule type="expression" dxfId="454" priority="687">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K709:K710">
-    <cfRule type="expression" dxfId="428" priority="672">
+    <cfRule type="expression" dxfId="453" priority="674">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K715:K718">
-    <cfRule type="expression" dxfId="427" priority="650">
+    <cfRule type="expression" dxfId="452" priority="652">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K723">
-    <cfRule type="expression" dxfId="426" priority="639">
+    <cfRule type="expression" dxfId="451" priority="641">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K725:K726">
-    <cfRule type="expression" dxfId="425" priority="616">
+    <cfRule type="expression" dxfId="450" priority="618">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K731">
-    <cfRule type="expression" dxfId="424" priority="601">
+    <cfRule type="expression" dxfId="449" priority="603">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K733:K734">
-    <cfRule type="expression" dxfId="423" priority="562">
+    <cfRule type="expression" dxfId="448" priority="564">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K736">
-    <cfRule type="expression" dxfId="422" priority="552">
+    <cfRule type="expression" dxfId="447" priority="554">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K742">
-    <cfRule type="expression" dxfId="421" priority="480">
+    <cfRule type="expression" dxfId="446" priority="482">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K744">
-    <cfRule type="expression" dxfId="420" priority="470">
+    <cfRule type="expression" dxfId="445" priority="472">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K747">
-    <cfRule type="expression" dxfId="419" priority="450">
+    <cfRule type="expression" dxfId="444" priority="452">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K749:K750">
-    <cfRule type="expression" dxfId="418" priority="403">
+    <cfRule type="expression" dxfId="443" priority="405">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755:K756">
-    <cfRule type="expression" dxfId="417" priority="368">
+    <cfRule type="expression" dxfId="442" priority="370">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K758">
-    <cfRule type="expression" dxfId="416" priority="329">
+    <cfRule type="expression" dxfId="441" priority="331">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K763:K764">
-    <cfRule type="expression" dxfId="415" priority="302">
+    <cfRule type="expression" dxfId="440" priority="304">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766">
-    <cfRule type="expression" dxfId="414" priority="231">
+    <cfRule type="expression" dxfId="439" priority="233">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K771">
-    <cfRule type="expression" dxfId="413" priority="204">
+    <cfRule type="expression" dxfId="438" priority="206">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="412" priority="203">
+    <cfRule type="expression" dxfId="437" priority="205">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="411" priority="202">
+    <cfRule type="expression" dxfId="436" priority="204">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="410" priority="201">
+    <cfRule type="expression" dxfId="435" priority="203">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="409" priority="200">
+    <cfRule type="expression" dxfId="434" priority="202">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="408" priority="199">
+    <cfRule type="expression" dxfId="433" priority="201">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="407" priority="198">
+    <cfRule type="expression" dxfId="432" priority="200">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="406" priority="197">
+    <cfRule type="expression" dxfId="431" priority="199">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E774">
-    <cfRule type="expression" dxfId="405" priority="196">
+    <cfRule type="expression" dxfId="430" priority="198">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G774">
-    <cfRule type="expression" dxfId="404" priority="195">
+    <cfRule type="expression" dxfId="429" priority="197">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I774">
-    <cfRule type="expression" dxfId="403" priority="194">
+    <cfRule type="expression" dxfId="428" priority="196">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K774">
-    <cfRule type="expression" dxfId="402" priority="193">
+    <cfRule type="expression" dxfId="427" priority="195">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="401" priority="192">
+    <cfRule type="expression" dxfId="426" priority="194">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="400" priority="191">
+    <cfRule type="expression" dxfId="425" priority="193">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="399" priority="190">
+    <cfRule type="expression" dxfId="424" priority="192">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="398" priority="189">
+    <cfRule type="expression" dxfId="423" priority="191">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E779">
-    <cfRule type="expression" dxfId="397" priority="188">
+    <cfRule type="expression" dxfId="422" priority="190">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="396" priority="187">
+    <cfRule type="expression" dxfId="421" priority="189">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="395" priority="186">
+    <cfRule type="expression" dxfId="420" priority="188">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="394" priority="185">
+    <cfRule type="expression" dxfId="419" priority="187">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="393" priority="184">
+    <cfRule type="expression" dxfId="418" priority="186">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="392" priority="183">
+    <cfRule type="expression" dxfId="417" priority="185">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="391" priority="182">
+    <cfRule type="expression" dxfId="416" priority="184">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="390" priority="181">
+    <cfRule type="expression" dxfId="415" priority="183">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="389" priority="180">
+    <cfRule type="expression" dxfId="414" priority="182">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="388" priority="179">
+    <cfRule type="expression" dxfId="413" priority="181">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="387" priority="178">
+    <cfRule type="expression" dxfId="412" priority="180">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="386" priority="177">
+    <cfRule type="expression" dxfId="411" priority="179">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="385" priority="176">
+    <cfRule type="expression" dxfId="410" priority="178">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="384" priority="175">
+    <cfRule type="expression" dxfId="409" priority="177">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="383" priority="174">
+    <cfRule type="expression" dxfId="408" priority="176">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="382" priority="173">
+    <cfRule type="expression" dxfId="407" priority="175">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="381" priority="172">
+    <cfRule type="expression" dxfId="406" priority="174">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="380" priority="171">
+    <cfRule type="expression" dxfId="405" priority="173">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="379" priority="170">
+    <cfRule type="expression" dxfId="404" priority="172">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="378" priority="169">
+    <cfRule type="expression" dxfId="403" priority="171">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="377" priority="168">
+    <cfRule type="expression" dxfId="402" priority="170">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="376" priority="167">
+    <cfRule type="expression" dxfId="401" priority="169">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="375" priority="166">
+    <cfRule type="expression" dxfId="400" priority="168">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="374" priority="165">
+    <cfRule type="expression" dxfId="399" priority="167">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="373" priority="164">
+    <cfRule type="expression" dxfId="398" priority="166">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="372" priority="163">
+    <cfRule type="expression" dxfId="397" priority="165">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="371" priority="162">
+    <cfRule type="expression" dxfId="396" priority="164">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="370" priority="161">
+    <cfRule type="expression" dxfId="395" priority="163">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
-    <cfRule type="expression" dxfId="369" priority="160">
+    <cfRule type="expression" dxfId="394" priority="162">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
-    <cfRule type="expression" dxfId="368" priority="159">
+    <cfRule type="expression" dxfId="393" priority="161">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="367" priority="158">
+    <cfRule type="expression" dxfId="392" priority="160">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="366" priority="157">
+    <cfRule type="expression" dxfId="391" priority="159">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="365" priority="156">
+    <cfRule type="expression" dxfId="390" priority="158">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="364" priority="155">
+    <cfRule type="expression" dxfId="389" priority="157">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="363" priority="154">
+    <cfRule type="expression" dxfId="388" priority="156">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="362" priority="153">
+    <cfRule type="expression" dxfId="387" priority="155">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="361" priority="152">
+    <cfRule type="expression" dxfId="386" priority="154">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="360" priority="151">
+    <cfRule type="expression" dxfId="385" priority="153">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="359" priority="150">
+    <cfRule type="expression" dxfId="384" priority="152">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
-    <cfRule type="expression" dxfId="358" priority="147">
+    <cfRule type="expression" dxfId="383" priority="149">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="357" priority="149">
+    <cfRule type="expression" dxfId="382" priority="151">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="356" priority="148">
+    <cfRule type="expression" dxfId="381" priority="150">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="355" priority="146">
+    <cfRule type="expression" dxfId="380" priority="148">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="354" priority="145">
+    <cfRule type="expression" dxfId="379" priority="147">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="353" priority="144">
+    <cfRule type="expression" dxfId="378" priority="146">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790">
-    <cfRule type="expression" dxfId="352" priority="143">
+    <cfRule type="expression" dxfId="377" priority="145">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="351" priority="140">
+    <cfRule type="expression" dxfId="376" priority="142">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="350" priority="142">
+    <cfRule type="expression" dxfId="375" priority="144">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="349" priority="141">
+    <cfRule type="expression" dxfId="374" priority="143">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="348" priority="137">
+    <cfRule type="expression" dxfId="373" priority="139">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="347" priority="139">
+    <cfRule type="expression" dxfId="372" priority="141">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="346" priority="138">
+    <cfRule type="expression" dxfId="371" priority="140">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
-    <cfRule type="expression" dxfId="345" priority="136">
+    <cfRule type="expression" dxfId="370" priority="138">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
-    <cfRule type="expression" dxfId="344" priority="135">
+    <cfRule type="expression" dxfId="369" priority="137">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="343" priority="134">
+    <cfRule type="expression" dxfId="368" priority="136">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="342" priority="133">
+    <cfRule type="expression" dxfId="367" priority="135">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="341" priority="132">
+    <cfRule type="expression" dxfId="366" priority="134">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="340" priority="131">
+    <cfRule type="expression" dxfId="365" priority="133">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="339" priority="130">
+    <cfRule type="expression" dxfId="364" priority="132">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="338" priority="129">
+    <cfRule type="expression" dxfId="363" priority="131">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="337" priority="128">
+    <cfRule type="expression" dxfId="362" priority="130">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="336" priority="127">
+    <cfRule type="expression" dxfId="361" priority="129">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="335" priority="126">
+    <cfRule type="expression" dxfId="360" priority="128">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="334" priority="125">
+    <cfRule type="expression" dxfId="359" priority="127">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="333" priority="124">
+    <cfRule type="expression" dxfId="358" priority="126">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="332" priority="123">
+    <cfRule type="expression" dxfId="357" priority="125">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="331" priority="122">
+    <cfRule type="expression" dxfId="356" priority="124">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="330" priority="121">
+    <cfRule type="expression" dxfId="355" priority="123">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="329" priority="120">
+    <cfRule type="expression" dxfId="354" priority="122">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="328" priority="119">
+    <cfRule type="expression" dxfId="353" priority="121">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="327" priority="118">
+    <cfRule type="expression" dxfId="352" priority="120">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798">
-    <cfRule type="expression" dxfId="326" priority="117">
+    <cfRule type="expression" dxfId="351" priority="119">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="325" priority="116">
+    <cfRule type="expression" dxfId="350" priority="118">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="324" priority="115">
+    <cfRule type="expression" dxfId="349" priority="117">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="323" priority="114">
+    <cfRule type="expression" dxfId="348" priority="116">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 K803:K805">
-    <cfRule type="expression" dxfId="322" priority="113">
+    <cfRule type="expression" dxfId="347" priority="115">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="321" priority="112">
+    <cfRule type="expression" dxfId="346" priority="114">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="320" priority="111">
+    <cfRule type="expression" dxfId="345" priority="113">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="319" priority="110">
+    <cfRule type="expression" dxfId="344" priority="112">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="318" priority="109">
+    <cfRule type="expression" dxfId="343" priority="111">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="317" priority="108">
+    <cfRule type="expression" dxfId="342" priority="110">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="316" priority="107">
+    <cfRule type="expression" dxfId="341" priority="109">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="315" priority="106">
+    <cfRule type="expression" dxfId="340" priority="108">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="314" priority="105">
+    <cfRule type="expression" dxfId="339" priority="107">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="313" priority="104">
+    <cfRule type="expression" dxfId="338" priority="106">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="312" priority="103">
+    <cfRule type="expression" dxfId="337" priority="105">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="311" priority="102">
+    <cfRule type="expression" dxfId="336" priority="104">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="310" priority="101">
+    <cfRule type="expression" dxfId="335" priority="103">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="309" priority="100">
+    <cfRule type="expression" dxfId="334" priority="102">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="308" priority="99">
+    <cfRule type="expression" dxfId="333" priority="101">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="307" priority="98">
+    <cfRule type="expression" dxfId="332" priority="100">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="306" priority="97">
+    <cfRule type="expression" dxfId="331" priority="99">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="305" priority="96">
+    <cfRule type="expression" dxfId="330" priority="98">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="304" priority="95">
+    <cfRule type="expression" dxfId="329" priority="97">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="303" priority="94">
+    <cfRule type="expression" dxfId="328" priority="96">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="302" priority="93">
+    <cfRule type="expression" dxfId="327" priority="95">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="301" priority="92">
+    <cfRule type="expression" dxfId="326" priority="94">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="300" priority="91">
+    <cfRule type="expression" dxfId="325" priority="93">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="299" priority="90">
+    <cfRule type="expression" dxfId="324" priority="92">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="298" priority="89">
+    <cfRule type="expression" dxfId="323" priority="91">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="297" priority="88">
+    <cfRule type="expression" dxfId="322" priority="90">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="296" priority="87">
+    <cfRule type="expression" dxfId="321" priority="89">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="295" priority="86">
+    <cfRule type="expression" dxfId="320" priority="88">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="294" priority="85">
+    <cfRule type="expression" dxfId="319" priority="87">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="293" priority="84">
+    <cfRule type="expression" dxfId="318" priority="86">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="292" priority="83">
+    <cfRule type="expression" dxfId="317" priority="85">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="291" priority="82">
+    <cfRule type="expression" dxfId="316" priority="84">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="290" priority="81">
+    <cfRule type="expression" dxfId="315" priority="83">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="289" priority="80">
+    <cfRule type="expression" dxfId="314" priority="82">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="288" priority="79">
+    <cfRule type="expression" dxfId="313" priority="81">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="287" priority="78">
+    <cfRule type="expression" dxfId="312" priority="80">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="286" priority="77">
+    <cfRule type="expression" dxfId="311" priority="79">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="285" priority="76">
+    <cfRule type="expression" dxfId="310" priority="78">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="284" priority="75">
+    <cfRule type="expression" dxfId="309" priority="77">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="283" priority="74">
+    <cfRule type="expression" dxfId="308" priority="76">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="282" priority="73">
+    <cfRule type="expression" dxfId="307" priority="75">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="281" priority="72">
+    <cfRule type="expression" dxfId="306" priority="74">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="280" priority="71">
+    <cfRule type="expression" dxfId="305" priority="73">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="279" priority="70">
+    <cfRule type="expression" dxfId="304" priority="72">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="278" priority="69">
+    <cfRule type="expression" dxfId="303" priority="71">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="277" priority="68">
+    <cfRule type="expression" dxfId="302" priority="70">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="276" priority="67">
+    <cfRule type="expression" dxfId="301" priority="69">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="275" priority="66">
+    <cfRule type="expression" dxfId="300" priority="68">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="274" priority="65">
+    <cfRule type="expression" dxfId="299" priority="67">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="273" priority="64">
+    <cfRule type="expression" dxfId="298" priority="66">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="272" priority="63">
+    <cfRule type="expression" dxfId="297" priority="65">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="271" priority="62">
+    <cfRule type="expression" dxfId="296" priority="64">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="270" priority="61">
+    <cfRule type="expression" dxfId="295" priority="63">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="269" priority="60">
+    <cfRule type="expression" dxfId="294" priority="62">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="268" priority="59">
+    <cfRule type="expression" dxfId="293" priority="61">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="267" priority="58">
+    <cfRule type="expression" dxfId="292" priority="60">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="266" priority="57">
+    <cfRule type="expression" dxfId="291" priority="59">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="265" priority="56">
+    <cfRule type="expression" dxfId="290" priority="58">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="264" priority="55">
+    <cfRule type="expression" dxfId="289" priority="57">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="263" priority="54">
+    <cfRule type="expression" dxfId="288" priority="56">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="262" priority="53">
+    <cfRule type="expression" dxfId="287" priority="55">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="261" priority="52">
+    <cfRule type="expression" dxfId="286" priority="54">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="260" priority="51">
+    <cfRule type="expression" dxfId="285" priority="53">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="259" priority="50">
+    <cfRule type="expression" dxfId="284" priority="52">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="258" priority="49">
+    <cfRule type="expression" dxfId="283" priority="51">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="257" priority="48">
+    <cfRule type="expression" dxfId="282" priority="50">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="256" priority="47">
+    <cfRule type="expression" dxfId="281" priority="49">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="255" priority="46">
+    <cfRule type="expression" dxfId="280" priority="48">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="254" priority="45">
+    <cfRule type="expression" dxfId="279" priority="47">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="253" priority="44">
+    <cfRule type="expression" dxfId="278" priority="46">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="252" priority="43">
+    <cfRule type="expression" dxfId="277" priority="45">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="251" priority="42">
+    <cfRule type="expression" dxfId="276" priority="44">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="250" priority="41">
+    <cfRule type="expression" dxfId="275" priority="43">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="249" priority="40">
+    <cfRule type="expression" dxfId="274" priority="42">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="248" priority="39">
+    <cfRule type="expression" dxfId="273" priority="41">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="247" priority="38">
+    <cfRule type="expression" dxfId="272" priority="40">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="246" priority="37">
+    <cfRule type="expression" dxfId="271" priority="39">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="245" priority="36">
+    <cfRule type="expression" dxfId="270" priority="38">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="244" priority="35">
+    <cfRule type="expression" dxfId="269" priority="37">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="243" priority="34">
+    <cfRule type="expression" dxfId="268" priority="36">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="242" priority="33">
+    <cfRule type="expression" dxfId="267" priority="35">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="241" priority="32">
+    <cfRule type="expression" dxfId="266" priority="34">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="240" priority="31">
+    <cfRule type="expression" dxfId="265" priority="33">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="239" priority="30">
+    <cfRule type="expression" dxfId="264" priority="32">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="238" priority="29">
+    <cfRule type="expression" dxfId="263" priority="31">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="237" priority="28">
+    <cfRule type="expression" dxfId="262" priority="30">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="236" priority="27">
+    <cfRule type="expression" dxfId="261" priority="29">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="235" priority="26">
+    <cfRule type="expression" dxfId="260" priority="28">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="234" priority="25">
+    <cfRule type="expression" dxfId="259" priority="27">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="233" priority="24">
+    <cfRule type="expression" dxfId="258" priority="26">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="232" priority="23">
+    <cfRule type="expression" dxfId="257" priority="25">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="231" priority="22">
+    <cfRule type="expression" dxfId="256" priority="24">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="230" priority="21">
+    <cfRule type="expression" dxfId="255" priority="23">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="229" priority="20">
+    <cfRule type="expression" dxfId="254" priority="22">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="228" priority="19">
+    <cfRule type="expression" dxfId="253" priority="21">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="227" priority="18">
+    <cfRule type="expression" dxfId="252" priority="20">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="226" priority="17">
+    <cfRule type="expression" dxfId="251" priority="19">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="225" priority="16">
+    <cfRule type="expression" dxfId="250" priority="18">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K829 I829 G829">
-    <cfRule type="expression" dxfId="224" priority="15">
+    <cfRule type="expression" dxfId="249" priority="17">
       <formula>$C829=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I834 G834 K834:K835">
-    <cfRule type="expression" dxfId="223" priority="14">
+    <cfRule type="expression" dxfId="248" priority="16">
       <formula>$C834=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836 G836">
-    <cfRule type="expression" dxfId="222" priority="13">
+    <cfRule type="expression" dxfId="247" priority="15">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837 I837 G837">
-    <cfRule type="expression" dxfId="221" priority="12">
+    <cfRule type="expression" dxfId="246" priority="14">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K839 I839">
-    <cfRule type="expression" dxfId="220" priority="11">
+    <cfRule type="expression" dxfId="245" priority="13">
       <formula>$C839=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K842 I842 G842 E842">
-    <cfRule type="expression" dxfId="219" priority="10">
+    <cfRule type="expression" dxfId="244" priority="12">
       <formula>$C842=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845 I845 G845 E845">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="243" priority="11">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845 I845 G845">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="242" priority="10">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K844 I844 G844 E844">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="241" priority="9">
       <formula>$C844=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K844 I844 G844">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="240" priority="8">
       <formula>$C844=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K843 I843">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="239" priority="7">
       <formula>$C843=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K843 I843">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="238" priority="6">
       <formula>$C843=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K844 I844 G844 E844">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="237" priority="5">
       <formula>$C844=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K844 I844 G844">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="236" priority="4">
       <formula>$C844=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845 I845 G845 E845">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="235" priority="3">
       <formula>$C845=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K850 I850 G850 E850">
+    <cfRule type="expression" dxfId="234" priority="2">
+      <formula>$C850=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K850 I850 G850">
+    <cfRule type="expression" dxfId="233" priority="1">
+      <formula>$C850=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -30354,7 +30555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O869"/>
+  <dimension ref="A1:O879"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
@@ -52183,1060 +52384,1425 @@
       <c r="J869" s="11"/>
       <c r="K869" s="12"/>
     </row>
+    <row r="870" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A870" s="1">
+        <v>869</v>
+      </c>
+      <c r="B870" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C870" s="8">
+        <v>46049</v>
+      </c>
+      <c r="D870" s="9"/>
+      <c r="E870" s="10"/>
+      <c r="F870" s="11"/>
+      <c r="G870" s="12"/>
+      <c r="H870" s="11"/>
+      <c r="I870" s="12"/>
+      <c r="J870" s="11"/>
+      <c r="K870" s="12"/>
+    </row>
+    <row r="871" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A871" s="1">
+        <v>870</v>
+      </c>
+      <c r="B871" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C871" s="8">
+        <v>46050</v>
+      </c>
+      <c r="D871" s="9">
+        <v>2900</v>
+      </c>
+      <c r="E871" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F871" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G871" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H871" s="11">
+        <v>2300</v>
+      </c>
+      <c r="I871" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J871" s="11">
+        <v>3600</v>
+      </c>
+      <c r="K871" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="872" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A872" s="1">
+        <v>871</v>
+      </c>
+      <c r="B872" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C872" s="8">
+        <v>46051</v>
+      </c>
+      <c r="D872" s="9">
+        <v>3900</v>
+      </c>
+      <c r="E872" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F872" s="11">
+        <v>4800</v>
+      </c>
+      <c r="G872" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H872" s="11">
+        <v>3100</v>
+      </c>
+      <c r="I872" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J872" s="11">
+        <v>4800</v>
+      </c>
+      <c r="K872" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="873" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A873" s="1">
+        <v>872</v>
+      </c>
+      <c r="B873" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C873" s="8">
+        <v>46051</v>
+      </c>
+      <c r="D873" s="9">
+        <v>2000</v>
+      </c>
+      <c r="E873" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F873" s="11">
+        <v>1500</v>
+      </c>
+      <c r="G873" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H873" s="11">
+        <v>300</v>
+      </c>
+      <c r="I873" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J873" s="11">
+        <v>300</v>
+      </c>
+      <c r="K873" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="874" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A874" s="1">
+        <v>873</v>
+      </c>
+      <c r="B874" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C874" s="8">
+        <v>46051</v>
+      </c>
+      <c r="D874" s="9">
+        <v>400</v>
+      </c>
+      <c r="E874" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F874" s="11">
+        <v>400</v>
+      </c>
+      <c r="G874" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H874" s="11"/>
+      <c r="I874" s="12"/>
+      <c r="J874" s="11">
+        <v>100</v>
+      </c>
+      <c r="K874" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="875" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A875" s="1">
+        <v>874</v>
+      </c>
+      <c r="B875" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C875" s="8">
+        <v>46052</v>
+      </c>
+      <c r="D875" s="9"/>
+      <c r="E875" s="10"/>
+      <c r="F875" s="11"/>
+      <c r="G875" s="12"/>
+      <c r="H875" s="11"/>
+      <c r="I875" s="12"/>
+      <c r="J875" s="11"/>
+      <c r="K875" s="12"/>
+    </row>
+    <row r="876" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A876" s="1">
+        <v>875</v>
+      </c>
+      <c r="B876" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C876" s="8">
+        <v>46053</v>
+      </c>
+      <c r="D876" s="9"/>
+      <c r="E876" s="10"/>
+      <c r="F876" s="11"/>
+      <c r="G876" s="12"/>
+      <c r="H876" s="11"/>
+      <c r="I876" s="12"/>
+      <c r="J876" s="11"/>
+      <c r="K876" s="12"/>
+    </row>
+    <row r="877" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A877" s="1">
+        <v>876</v>
+      </c>
+      <c r="B877" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C877" s="8">
+        <v>46054</v>
+      </c>
+      <c r="D877" s="9"/>
+      <c r="E877" s="10"/>
+      <c r="F877" s="11"/>
+      <c r="G877" s="12"/>
+      <c r="H877" s="11"/>
+      <c r="I877" s="12"/>
+      <c r="J877" s="11"/>
+      <c r="K877" s="12"/>
+    </row>
+    <row r="878" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A878" s="1">
+        <v>877</v>
+      </c>
+      <c r="B878" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C878" s="8">
+        <v>46055</v>
+      </c>
+      <c r="D878" s="9"/>
+      <c r="E878" s="10"/>
+      <c r="F878" s="11"/>
+      <c r="G878" s="12"/>
+      <c r="H878" s="11"/>
+      <c r="I878" s="12"/>
+      <c r="J878" s="11"/>
+      <c r="K878" s="12"/>
+    </row>
+    <row r="879" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A879" s="1">
+        <v>878</v>
+      </c>
+      <c r="B879" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C879" s="8">
+        <v>46056</v>
+      </c>
+      <c r="D879" s="9"/>
+      <c r="E879" s="10"/>
+      <c r="F879" s="11"/>
+      <c r="G879" s="12"/>
+      <c r="H879" s="11"/>
+      <c r="I879" s="12"/>
+      <c r="J879" s="11"/>
+      <c r="K879" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="B4:E869">
-    <cfRule type="expression" dxfId="218" priority="388">
+  <conditionalFormatting sqref="B4:E879">
+    <cfRule type="expression" dxfId="232" priority="411">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K869">
-    <cfRule type="expression" dxfId="217" priority="389">
+  <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K879">
+    <cfRule type="expression" dxfId="231" priority="412">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G47 J44:K47">
-    <cfRule type="expression" dxfId="216" priority="398">
+    <cfRule type="expression" dxfId="230" priority="421">
       <formula>$B18=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E692">
-    <cfRule type="expression" dxfId="215" priority="382">
+    <cfRule type="expression" dxfId="229" priority="405">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E694">
-    <cfRule type="expression" dxfId="214" priority="380">
+    <cfRule type="expression" dxfId="228" priority="403">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E701">
-    <cfRule type="expression" dxfId="213" priority="370">
+    <cfRule type="expression" dxfId="227" priority="393">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E703">
-    <cfRule type="expression" dxfId="212" priority="365">
+    <cfRule type="expression" dxfId="226" priority="388">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E710">
-    <cfRule type="expression" dxfId="211" priority="355">
+    <cfRule type="expression" dxfId="225" priority="378">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E712:E714">
-    <cfRule type="expression" dxfId="210" priority="350">
+    <cfRule type="expression" dxfId="224" priority="373">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E719">
-    <cfRule type="expression" dxfId="209" priority="340">
+    <cfRule type="expression" dxfId="223" priority="363">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E721:E723">
-    <cfRule type="expression" dxfId="208" priority="335">
+    <cfRule type="expression" dxfId="222" priority="358">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E728">
-    <cfRule type="expression" dxfId="207" priority="328">
+    <cfRule type="expression" dxfId="221" priority="351">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E730:E732">
-    <cfRule type="expression" dxfId="206" priority="315">
+    <cfRule type="expression" dxfId="220" priority="338">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E737">
-    <cfRule type="expression" dxfId="205" priority="308">
+    <cfRule type="expression" dxfId="219" priority="331">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739:E741">
-    <cfRule type="expression" dxfId="204" priority="295">
+    <cfRule type="expression" dxfId="218" priority="318">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E746">
-    <cfRule type="expression" dxfId="203" priority="285">
+    <cfRule type="expression" dxfId="217" priority="308">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E748:E750">
-    <cfRule type="expression" dxfId="202" priority="263">
+    <cfRule type="expression" dxfId="216" priority="286">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="201" priority="256">
+    <cfRule type="expression" dxfId="215" priority="279">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E759">
-    <cfRule type="expression" dxfId="200" priority="229">
+    <cfRule type="expression" dxfId="214" priority="252">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E764">
-    <cfRule type="expression" dxfId="199" priority="225">
+    <cfRule type="expression" dxfId="213" priority="248">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E766:E768">
-    <cfRule type="expression" dxfId="198" priority="200">
+    <cfRule type="expression" dxfId="212" priority="223">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="197" priority="190">
+    <cfRule type="expression" dxfId="211" priority="213">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E775:E777">
-    <cfRule type="expression" dxfId="196" priority="178">
+    <cfRule type="expression" dxfId="210" priority="201">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="195" priority="156">
+    <cfRule type="expression" dxfId="209" priority="179">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E784:E786">
-    <cfRule type="expression" dxfId="194" priority="138">
+    <cfRule type="expression" dxfId="208" priority="161">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="193" priority="401">
+    <cfRule type="expression" dxfId="207" priority="424">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70">
-    <cfRule type="expression" dxfId="192" priority="410">
+    <cfRule type="expression" dxfId="206" priority="433">
       <formula>$C70=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G685">
-    <cfRule type="expression" dxfId="191" priority="386">
+    <cfRule type="expression" dxfId="205" priority="409">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G692">
-    <cfRule type="expression" dxfId="190" priority="383">
+    <cfRule type="expression" dxfId="204" priority="406">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G695">
-    <cfRule type="expression" dxfId="189" priority="373">
+    <cfRule type="expression" dxfId="203" priority="396">
       <formula>$C695=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701">
-    <cfRule type="expression" dxfId="188" priority="368">
+    <cfRule type="expression" dxfId="202" priority="391">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G704:G705">
-    <cfRule type="expression" dxfId="187" priority="357">
+    <cfRule type="expression" dxfId="201" priority="380">
       <formula>$C704=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G710">
-    <cfRule type="expression" dxfId="186" priority="353">
+    <cfRule type="expression" dxfId="200" priority="376">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G712:G714">
-    <cfRule type="expression" dxfId="185" priority="343">
+    <cfRule type="expression" dxfId="199" priority="366">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G719">
-    <cfRule type="expression" dxfId="184" priority="338">
+    <cfRule type="expression" dxfId="198" priority="361">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G721:G723">
-    <cfRule type="expression" dxfId="183" priority="333">
+    <cfRule type="expression" dxfId="197" priority="356">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G728">
-    <cfRule type="expression" dxfId="182" priority="326">
+    <cfRule type="expression" dxfId="196" priority="349">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G730:G732">
-    <cfRule type="expression" dxfId="181" priority="313">
+    <cfRule type="expression" dxfId="195" priority="336">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G737">
-    <cfRule type="expression" dxfId="180" priority="306">
+    <cfRule type="expression" dxfId="194" priority="329">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739:G741">
-    <cfRule type="expression" dxfId="179" priority="292">
+    <cfRule type="expression" dxfId="193" priority="315">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746">
-    <cfRule type="expression" dxfId="178" priority="283">
+    <cfRule type="expression" dxfId="192" priority="306">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="177" priority="260">
+    <cfRule type="expression" dxfId="191" priority="283">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="176" priority="254">
+    <cfRule type="expression" dxfId="190" priority="277">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G759">
-    <cfRule type="expression" dxfId="175" priority="226">
+    <cfRule type="expression" dxfId="189" priority="249">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G764">
-    <cfRule type="expression" dxfId="174" priority="223">
+    <cfRule type="expression" dxfId="188" priority="246">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G766:G768">
-    <cfRule type="expression" dxfId="173" priority="196">
+    <cfRule type="expression" dxfId="187" priority="219">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="172" priority="188">
+    <cfRule type="expression" dxfId="186" priority="211">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G775:G777">
-    <cfRule type="expression" dxfId="171" priority="171">
+    <cfRule type="expression" dxfId="185" priority="194">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="170" priority="154">
+    <cfRule type="expression" dxfId="184" priority="177">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G784:G786">
-    <cfRule type="expression" dxfId="169" priority="132">
+    <cfRule type="expression" dxfId="183" priority="155">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:I47">
-    <cfRule type="expression" dxfId="168" priority="423">
+    <cfRule type="expression" dxfId="182" priority="446">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="expression" dxfId="167" priority="427">
+    <cfRule type="expression" dxfId="181" priority="450">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I685">
-    <cfRule type="expression" dxfId="166" priority="385">
+    <cfRule type="expression" dxfId="180" priority="408">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I694:I695">
-    <cfRule type="expression" dxfId="165" priority="372">
+    <cfRule type="expression" dxfId="179" priority="395">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I703:I704">
-    <cfRule type="expression" dxfId="164" priority="359">
+    <cfRule type="expression" dxfId="178" priority="382">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I712:I714">
-    <cfRule type="expression" dxfId="163" priority="342">
+    <cfRule type="expression" dxfId="177" priority="365">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I721:I723">
-    <cfRule type="expression" dxfId="162" priority="331">
+    <cfRule type="expression" dxfId="176" priority="354">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I730:I732">
-    <cfRule type="expression" dxfId="161" priority="309">
+    <cfRule type="expression" dxfId="175" priority="332">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I741">
-    <cfRule type="expression" dxfId="160" priority="289">
+    <cfRule type="expression" dxfId="174" priority="312">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I748:I749">
-    <cfRule type="expression" dxfId="159" priority="268">
+    <cfRule type="expression" dxfId="173" priority="291">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755">
-    <cfRule type="expression" dxfId="158" priority="252">
+    <cfRule type="expression" dxfId="172" priority="275">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I757:I758">
-    <cfRule type="expression" dxfId="157" priority="235">
+    <cfRule type="expression" dxfId="171" priority="258">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I766:I768">
-    <cfRule type="expression" dxfId="156" priority="192">
+    <cfRule type="expression" dxfId="170" priority="215">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="155" priority="186">
+    <cfRule type="expression" dxfId="169" priority="209">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I775:I777">
-    <cfRule type="expression" dxfId="154" priority="164">
+    <cfRule type="expression" dxfId="168" priority="187">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="153" priority="152">
+    <cfRule type="expression" dxfId="167" priority="175">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784:I786">
-    <cfRule type="expression" dxfId="152" priority="126">
+    <cfRule type="expression" dxfId="166" priority="149">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="151" priority="402">
+    <cfRule type="expression" dxfId="165" priority="425">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K685">
-    <cfRule type="expression" dxfId="150" priority="384">
+    <cfRule type="expression" dxfId="164" priority="407">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K692">
-    <cfRule type="expression" dxfId="149" priority="381">
+    <cfRule type="expression" dxfId="163" priority="404">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K694:K695">
-    <cfRule type="expression" dxfId="148" priority="371">
+    <cfRule type="expression" dxfId="162" priority="394">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701">
-    <cfRule type="expression" dxfId="147" priority="366">
+    <cfRule type="expression" dxfId="161" priority="389">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K703:K705">
-    <cfRule type="expression" dxfId="146" priority="356">
+    <cfRule type="expression" dxfId="160" priority="379">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K710">
-    <cfRule type="expression" dxfId="145" priority="351">
+    <cfRule type="expression" dxfId="159" priority="374">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K712:K714">
-    <cfRule type="expression" dxfId="144" priority="341">
+    <cfRule type="expression" dxfId="158" priority="364">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K719">
-    <cfRule type="expression" dxfId="143" priority="336">
+    <cfRule type="expression" dxfId="157" priority="359">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K721:K723">
-    <cfRule type="expression" dxfId="142" priority="329">
+    <cfRule type="expression" dxfId="156" priority="352">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K728">
-    <cfRule type="expression" dxfId="141" priority="324">
+    <cfRule type="expression" dxfId="155" priority="347">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K730:K732">
-    <cfRule type="expression" dxfId="140" priority="311">
+    <cfRule type="expression" dxfId="154" priority="334">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K737">
-    <cfRule type="expression" dxfId="139" priority="304">
+    <cfRule type="expression" dxfId="153" priority="327">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K741">
-    <cfRule type="expression" dxfId="138" priority="286">
+    <cfRule type="expression" dxfId="152" priority="309">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K746">
-    <cfRule type="expression" dxfId="137" priority="281">
+    <cfRule type="expression" dxfId="151" priority="304">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K748:K750">
-    <cfRule type="expression" dxfId="136" priority="257">
+    <cfRule type="expression" dxfId="150" priority="280">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755">
-    <cfRule type="expression" dxfId="135" priority="250">
+    <cfRule type="expression" dxfId="149" priority="273">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K757:K758">
-    <cfRule type="expression" dxfId="134" priority="232">
+    <cfRule type="expression" dxfId="148" priority="255">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K764">
-    <cfRule type="expression" dxfId="133" priority="221">
+    <cfRule type="expression" dxfId="147" priority="244">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766:K767">
-    <cfRule type="expression" dxfId="132" priority="203">
+    <cfRule type="expression" dxfId="146" priority="226">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="131" priority="184">
+    <cfRule type="expression" dxfId="145" priority="207">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K775:K777">
-    <cfRule type="expression" dxfId="130" priority="157">
+    <cfRule type="expression" dxfId="144" priority="180">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="129" priority="150">
+    <cfRule type="expression" dxfId="143" priority="173">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784:K786">
-    <cfRule type="expression" dxfId="128" priority="120">
+    <cfRule type="expression" dxfId="142" priority="143">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E792:E793">
-    <cfRule type="expression" dxfId="127" priority="119">
+    <cfRule type="expression" dxfId="141" priority="142">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="126" priority="118">
+    <cfRule type="expression" dxfId="140" priority="141">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="125" priority="117">
+    <cfRule type="expression" dxfId="139" priority="140">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="124" priority="116">
+    <cfRule type="expression" dxfId="138" priority="139">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="123" priority="115">
+    <cfRule type="expression" dxfId="137" priority="138">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="122" priority="114">
+    <cfRule type="expression" dxfId="136" priority="137">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="121" priority="113">
+    <cfRule type="expression" dxfId="135" priority="136">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E794:E795">
-    <cfRule type="expression" dxfId="120" priority="112">
+    <cfRule type="expression" dxfId="134" priority="135">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="119" priority="111">
+    <cfRule type="expression" dxfId="133" priority="134">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="118" priority="110">
+    <cfRule type="expression" dxfId="132" priority="133">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="117" priority="109">
+    <cfRule type="expression" dxfId="131" priority="132">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="116" priority="108">
+    <cfRule type="expression" dxfId="130" priority="131">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="115" priority="107">
+    <cfRule type="expression" dxfId="129" priority="130">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="114" priority="106">
+    <cfRule type="expression" dxfId="128" priority="129">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E801:E802">
-    <cfRule type="expression" dxfId="113" priority="105">
+    <cfRule type="expression" dxfId="127" priority="128">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E803:E805">
-    <cfRule type="expression" dxfId="112" priority="104">
+    <cfRule type="expression" dxfId="126" priority="127">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G805">
-    <cfRule type="expression" dxfId="111" priority="103">
+    <cfRule type="expression" dxfId="125" priority="126">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G802">
-    <cfRule type="expression" dxfId="110" priority="102">
+    <cfRule type="expression" dxfId="124" priority="125">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G803:G805">
-    <cfRule type="expression" dxfId="109" priority="101">
+    <cfRule type="expression" dxfId="123" priority="124">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I805">
-    <cfRule type="expression" dxfId="108" priority="100">
+    <cfRule type="expression" dxfId="122" priority="123">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I802">
-    <cfRule type="expression" dxfId="107" priority="99">
+    <cfRule type="expression" dxfId="121" priority="122">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803:I805">
-    <cfRule type="expression" dxfId="106" priority="98">
+    <cfRule type="expression" dxfId="120" priority="121">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K805">
-    <cfRule type="expression" dxfId="105" priority="97">
+    <cfRule type="expression" dxfId="119" priority="120">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K802">
-    <cfRule type="expression" dxfId="104" priority="96">
+    <cfRule type="expression" dxfId="118" priority="119">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K803:K805">
-    <cfRule type="expression" dxfId="103" priority="95">
+    <cfRule type="expression" dxfId="117" priority="118">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E809:E810">
-    <cfRule type="expression" dxfId="102" priority="94">
+    <cfRule type="expression" dxfId="116" priority="117">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811:E812">
-    <cfRule type="expression" dxfId="101" priority="93">
+    <cfRule type="expression" dxfId="115" priority="116">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G812">
-    <cfRule type="expression" dxfId="100" priority="92">
+    <cfRule type="expression" dxfId="114" priority="115">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G810">
-    <cfRule type="expression" dxfId="99" priority="91">
+    <cfRule type="expression" dxfId="113" priority="114">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811:G812">
-    <cfRule type="expression" dxfId="98" priority="90">
+    <cfRule type="expression" dxfId="112" priority="113">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I812">
-    <cfRule type="expression" dxfId="97" priority="89">
+    <cfRule type="expression" dxfId="111" priority="112">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I810">
-    <cfRule type="expression" dxfId="96" priority="88">
+    <cfRule type="expression" dxfId="110" priority="111">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="95" priority="87">
+    <cfRule type="expression" dxfId="109" priority="110">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K812">
-    <cfRule type="expression" dxfId="94" priority="86">
+    <cfRule type="expression" dxfId="108" priority="109">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K810">
-    <cfRule type="expression" dxfId="93" priority="85">
+    <cfRule type="expression" dxfId="107" priority="108">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811:K812">
-    <cfRule type="expression" dxfId="92" priority="84">
+    <cfRule type="expression" dxfId="106" priority="107">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E818:E822 G818:G822 K818:K822 I818:I822">
-    <cfRule type="expression" dxfId="91" priority="83">
+    <cfRule type="expression" dxfId="105" priority="106">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K818:K822 G818:G822 I818:I822">
-    <cfRule type="expression" dxfId="90" priority="82">
+    <cfRule type="expression" dxfId="104" priority="105">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E820:E821">
-    <cfRule type="expression" dxfId="89" priority="81">
+    <cfRule type="expression" dxfId="103" priority="104">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="88" priority="80">
+    <cfRule type="expression" dxfId="102" priority="103">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="87" priority="79">
+    <cfRule type="expression" dxfId="101" priority="102">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="86" priority="78">
+    <cfRule type="expression" dxfId="100" priority="101">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="85" priority="77">
+    <cfRule type="expression" dxfId="99" priority="100">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K822 G822">
-    <cfRule type="expression" dxfId="84" priority="76">
+    <cfRule type="expression" dxfId="98" priority="99">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I822">
-    <cfRule type="expression" dxfId="83" priority="75">
+    <cfRule type="expression" dxfId="97" priority="98">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E828:E831">
-    <cfRule type="expression" dxfId="82" priority="74">
+    <cfRule type="expression" dxfId="96" priority="97">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="81" priority="73">
+    <cfRule type="expression" dxfId="95" priority="96">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="80" priority="72">
+    <cfRule type="expression" dxfId="94" priority="95">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="79" priority="71">
+    <cfRule type="expression" dxfId="93" priority="94">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="78" priority="70">
+    <cfRule type="expression" dxfId="92" priority="93">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="77" priority="69">
+    <cfRule type="expression" dxfId="91" priority="92">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="76" priority="68">
+    <cfRule type="expression" dxfId="90" priority="91">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="75" priority="67">
+    <cfRule type="expression" dxfId="89" priority="90">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="74" priority="66">
+    <cfRule type="expression" dxfId="88" priority="89">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="73" priority="65">
+    <cfRule type="expression" dxfId="87" priority="88">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="72" priority="64">
+    <cfRule type="expression" dxfId="86" priority="87">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="71" priority="63">
+    <cfRule type="expression" dxfId="85" priority="86">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="70" priority="62">
+    <cfRule type="expression" dxfId="84" priority="85">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="69" priority="61">
+    <cfRule type="expression" dxfId="83" priority="84">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837">
-    <cfRule type="expression" dxfId="68" priority="60">
+    <cfRule type="expression" dxfId="82" priority="83">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="67" priority="59">
+    <cfRule type="expression" dxfId="81" priority="82">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="66" priority="58">
+    <cfRule type="expression" dxfId="80" priority="81">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="65" priority="57">
+    <cfRule type="expression" dxfId="79" priority="80">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="64" priority="56">
+    <cfRule type="expression" dxfId="78" priority="79">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="63" priority="55">
+    <cfRule type="expression" dxfId="77" priority="78">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="62" priority="54">
+    <cfRule type="expression" dxfId="76" priority="77">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E845:E847">
-    <cfRule type="expression" dxfId="61" priority="53">
+    <cfRule type="expression" dxfId="75" priority="76">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="60" priority="52">
+    <cfRule type="expression" dxfId="74" priority="75">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="59" priority="51">
+    <cfRule type="expression" dxfId="73" priority="74">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="58" priority="50">
+    <cfRule type="expression" dxfId="72" priority="73">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="57" priority="49">
+    <cfRule type="expression" dxfId="71" priority="72">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="56" priority="48">
+    <cfRule type="expression" dxfId="70" priority="71">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="55" priority="47">
+    <cfRule type="expression" dxfId="69" priority="70">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="54" priority="46">
+    <cfRule type="expression" dxfId="68" priority="69">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="53" priority="45">
+    <cfRule type="expression" dxfId="67" priority="68">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="52" priority="44">
+    <cfRule type="expression" dxfId="66" priority="67">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="51" priority="43">
+    <cfRule type="expression" dxfId="65" priority="66">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="50" priority="42">
+    <cfRule type="expression" dxfId="64" priority="65">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="49" priority="41">
+    <cfRule type="expression" dxfId="63" priority="64">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="48" priority="40">
+    <cfRule type="expression" dxfId="62" priority="63">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="47" priority="39">
+    <cfRule type="expression" dxfId="61" priority="62">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="46" priority="38">
+    <cfRule type="expression" dxfId="60" priority="61">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="45" priority="37">
+    <cfRule type="expression" dxfId="59" priority="60">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="44" priority="36">
+    <cfRule type="expression" dxfId="58" priority="59">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="43" priority="35">
+    <cfRule type="expression" dxfId="57" priority="58">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="42" priority="34">
+    <cfRule type="expression" dxfId="56" priority="57">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="41" priority="33">
+    <cfRule type="expression" dxfId="55" priority="56">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="40" priority="32">
+    <cfRule type="expression" dxfId="54" priority="55">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="39" priority="31">
+    <cfRule type="expression" dxfId="53" priority="54">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="38" priority="30">
+    <cfRule type="expression" dxfId="52" priority="53">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="37" priority="29">
+    <cfRule type="expression" dxfId="51" priority="52">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="36" priority="28">
+    <cfRule type="expression" dxfId="50" priority="51">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="35" priority="27">
+    <cfRule type="expression" dxfId="49" priority="50">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="34" priority="26">
+    <cfRule type="expression" dxfId="48" priority="49">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="33" priority="25">
+    <cfRule type="expression" dxfId="47" priority="48">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="32" priority="24">
+    <cfRule type="expression" dxfId="46" priority="47">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="31" priority="23">
+    <cfRule type="expression" dxfId="45" priority="46">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E836">
-    <cfRule type="expression" dxfId="30" priority="22">
+    <cfRule type="expression" dxfId="44" priority="45">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="29" priority="21">
+    <cfRule type="expression" dxfId="43" priority="44">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="28" priority="20">
+    <cfRule type="expression" dxfId="42" priority="43">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="27" priority="19">
+    <cfRule type="expression" dxfId="41" priority="42">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="26" priority="18">
+    <cfRule type="expression" dxfId="40" priority="41">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="25" priority="17">
+    <cfRule type="expression" dxfId="39" priority="40">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="24" priority="16">
+    <cfRule type="expression" dxfId="38" priority="39">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853 E853">
-    <cfRule type="expression" dxfId="23" priority="15">
+    <cfRule type="expression" dxfId="37" priority="38">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853">
-    <cfRule type="expression" dxfId="22" priority="14">
+    <cfRule type="expression" dxfId="36" priority="37">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854 E854">
-    <cfRule type="expression" dxfId="21" priority="13">
+    <cfRule type="expression" dxfId="35" priority="36">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854">
-    <cfRule type="expression" dxfId="20" priority="12">
+    <cfRule type="expression" dxfId="34" priority="35">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="19" priority="11">
+    <cfRule type="expression" dxfId="33" priority="34">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="18" priority="10">
+    <cfRule type="expression" dxfId="32" priority="33">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="17" priority="9">
+    <cfRule type="expression" dxfId="31" priority="32">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="30" priority="31">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K862 I862 G862 E862">
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="29" priority="30">
       <formula>$C862=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K862 I862 G862">
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="28" priority="29">
       <formula>$C862=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K863 I863 G863 E863">
-    <cfRule type="expression" dxfId="13" priority="5">
+    <cfRule type="expression" dxfId="27" priority="28">
       <formula>$C863=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="26" priority="27">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="25" priority="26">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="24" priority="25">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K863:K865 I863:I865 G863:G865">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="23" priority="24">
       <formula>$C863=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E871">
+    <cfRule type="expression" dxfId="22" priority="23">
+      <formula>$C871=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E872">
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>$C872=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E873:E874">
+    <cfRule type="expression" dxfId="20" priority="21">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E873:E874">
+    <cfRule type="expression" dxfId="19" priority="20">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E873:E874">
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G871:G874">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>$C871=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G871">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>$C871=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G872">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>$C872=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G873:G874">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G873:G874">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G873:G874">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I871:I874">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>$C871=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I871">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>$C871=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I872">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>$C872=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I873:I874">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I873:I874">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I873:I874">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K871:K874">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$C871=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K871">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$C871=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K872">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$C872=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K873:K874">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K873:K874">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K873:K874">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
+++ b/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7395786-D5A4-4442-8F85-F4F724485014}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCA5AAB-E86F-4EA7-9535-D9D2001755A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3503" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="33">
   <si>
     <t>План поставок ПОКОМ</t>
   </si>
@@ -435,7 +435,98 @@
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Обычный 2 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="538">
+  <dxfs count="551">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4583,7 +4674,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMD855"/>
+  <dimension ref="A1:AMD856"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
@@ -28847,7 +28938,7 @@
         <v>844</v>
       </c>
       <c r="B848" s="7" t="str">
-        <f t="shared" ref="B848:B855" si="141">IF(C848&lt;&gt;"",TEXT(C848,"ДДД"),"")</f>
+        <f t="shared" ref="B848:B856" si="141">IF(C848&lt;&gt;"",TEXT(C848,"ДДД"),"")</f>
         <v>Вс</v>
       </c>
       <c r="C848" s="8">
@@ -28932,11 +29023,15 @@
       <c r="D851" s="9"/>
       <c r="E851" s="10"/>
       <c r="F851" s="11"/>
-      <c r="G851" s="12"/>
+      <c r="G851" s="10"/>
       <c r="H851" s="11"/>
       <c r="I851" s="12"/>
-      <c r="J851" s="11"/>
-      <c r="K851" s="12"/>
+      <c r="J851" s="11">
+        <v>10500</v>
+      </c>
+      <c r="K851" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="852" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A852" s="1">
@@ -28949,34 +29044,68 @@
       <c r="C852" s="8">
         <v>46051</v>
       </c>
-      <c r="D852" s="9"/>
-      <c r="E852" s="10"/>
-      <c r="F852" s="11"/>
-      <c r="G852" s="12"/>
-      <c r="H852" s="11"/>
-      <c r="I852" s="12"/>
-      <c r="J852" s="11"/>
-      <c r="K852" s="12"/>
+      <c r="D852" s="9">
+        <f>2300+3500</f>
+        <v>5800</v>
+      </c>
+      <c r="E852" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F852" s="11">
+        <v>1600</v>
+      </c>
+      <c r="G852" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H852" s="11">
+        <f>2900+7800</f>
+        <v>10700</v>
+      </c>
+      <c r="I852" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J852" s="11">
+        <v>5800</v>
+      </c>
+      <c r="K852" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="853" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A853" s="1">
         <v>849</v>
       </c>
       <c r="B853" s="7" t="str">
-        <f t="shared" si="141"/>
-        <v>Пт</v>
+        <f t="shared" ref="B853" si="142">IF(C853&lt;&gt;"",TEXT(C853,"ДДД"),"")</f>
+        <v>Чт</v>
       </c>
       <c r="C853" s="8">
-        <v>46052</v>
-      </c>
-      <c r="D853" s="9"/>
-      <c r="E853" s="10"/>
-      <c r="F853" s="11"/>
-      <c r="G853" s="12"/>
-      <c r="H853" s="11"/>
-      <c r="I853" s="12"/>
-      <c r="J853" s="11"/>
-      <c r="K853" s="12"/>
+        <v>46051</v>
+      </c>
+      <c r="D853" s="9">
+        <v>6000</v>
+      </c>
+      <c r="E853" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F853" s="11">
+        <v>5300</v>
+      </c>
+      <c r="G853" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H853" s="11">
+        <v>6400</v>
+      </c>
+      <c r="I853" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J853" s="11">
+        <v>11100</v>
+      </c>
+      <c r="K853" s="10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="854" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A854" s="1">
@@ -28984,10 +29113,10 @@
       </c>
       <c r="B854" s="7" t="str">
         <f t="shared" si="141"/>
-        <v>Сб</v>
+        <v>Пт</v>
       </c>
       <c r="C854" s="8">
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="D854" s="9"/>
       <c r="E854" s="10"/>
@@ -29004,10 +29133,10 @@
       </c>
       <c r="B855" s="7" t="str">
         <f t="shared" si="141"/>
-        <v>Вс</v>
+        <v>Сб</v>
       </c>
       <c r="C855" s="8">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="D855" s="9"/>
       <c r="E855" s="10"/>
@@ -29018,1534 +29147,1619 @@
       <c r="J855" s="11"/>
       <c r="K855" s="12"/>
     </row>
+    <row r="856" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A856" s="1">
+        <v>852</v>
+      </c>
+      <c r="B856" s="7" t="str">
+        <f t="shared" si="141"/>
+        <v>Вс</v>
+      </c>
+      <c r="C856" s="8">
+        <v>46054</v>
+      </c>
+      <c r="D856" s="9"/>
+      <c r="E856" s="10"/>
+      <c r="F856" s="11"/>
+      <c r="G856" s="12"/>
+      <c r="H856" s="11"/>
+      <c r="I856" s="12"/>
+      <c r="J856" s="11"/>
+      <c r="K856" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:E855">
-    <cfRule type="expression" dxfId="537" priority="724">
+  <conditionalFormatting sqref="B4:E856">
+    <cfRule type="expression" dxfId="550" priority="737">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:M683 B684:K855">
-    <cfRule type="expression" dxfId="536" priority="725">
+  <conditionalFormatting sqref="B4:M683 B684:K856">
+    <cfRule type="expression" dxfId="549" priority="738">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E678">
-    <cfRule type="expression" dxfId="535" priority="715">
+    <cfRule type="expression" dxfId="548" priority="728">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E693:E694">
-    <cfRule type="expression" dxfId="534" priority="702">
+    <cfRule type="expression" dxfId="547" priority="715">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E702">
-    <cfRule type="expression" dxfId="533" priority="689">
+    <cfRule type="expression" dxfId="546" priority="702">
       <formula>$C702=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E707">
-    <cfRule type="expression" dxfId="532" priority="685">
+    <cfRule type="expression" dxfId="545" priority="698">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709:E710">
-    <cfRule type="expression" dxfId="531" priority="677">
+    <cfRule type="expression" dxfId="544" priority="690">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E715">
-    <cfRule type="expression" dxfId="530" priority="673">
+    <cfRule type="expression" dxfId="543" priority="686">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E717:E718">
-    <cfRule type="expression" dxfId="529" priority="661">
+    <cfRule type="expression" dxfId="542" priority="674">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E723">
-    <cfRule type="expression" dxfId="528" priority="650">
+    <cfRule type="expression" dxfId="541" priority="663">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E725:E726">
-    <cfRule type="expression" dxfId="527" priority="627">
+    <cfRule type="expression" dxfId="540" priority="640">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E731">
-    <cfRule type="expression" dxfId="526" priority="615">
+    <cfRule type="expression" dxfId="539" priority="628">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E733:E734">
-    <cfRule type="expression" dxfId="525" priority="582">
+    <cfRule type="expression" dxfId="538" priority="595">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739">
-    <cfRule type="expression" dxfId="524" priority="550">
+    <cfRule type="expression" dxfId="537" priority="563">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E741:E742">
-    <cfRule type="expression" dxfId="523" priority="505">
+    <cfRule type="expression" dxfId="536" priority="518">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E747:E748">
-    <cfRule type="expression" dxfId="522" priority="442">
+    <cfRule type="expression" dxfId="535" priority="455">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E750">
-    <cfRule type="expression" dxfId="521" priority="426">
+    <cfRule type="expression" dxfId="534" priority="439">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="520" priority="400">
+    <cfRule type="expression" dxfId="533" priority="413">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E758">
-    <cfRule type="expression" dxfId="519" priority="352">
+    <cfRule type="expression" dxfId="532" priority="365">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E763">
-    <cfRule type="expression" dxfId="518" priority="325">
+    <cfRule type="expression" dxfId="531" priority="338">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E765:E766">
-    <cfRule type="expression" dxfId="517" priority="272">
+    <cfRule type="expression" dxfId="530" priority="285">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E771">
-    <cfRule type="expression" dxfId="516" priority="227">
+    <cfRule type="expression" dxfId="529" priority="240">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="515" priority="738">
+    <cfRule type="expression" dxfId="528" priority="751">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G661">
-    <cfRule type="expression" dxfId="514" priority="722">
+    <cfRule type="expression" dxfId="527" priority="735">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G670">
-    <cfRule type="expression" dxfId="513" priority="719">
+    <cfRule type="expression" dxfId="526" priority="732">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G678">
-    <cfRule type="expression" dxfId="512" priority="716">
+    <cfRule type="expression" dxfId="525" priority="729">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G686">
-    <cfRule type="expression" dxfId="511" priority="712">
+    <cfRule type="expression" dxfId="524" priority="725">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G691">
-    <cfRule type="expression" dxfId="510" priority="709">
+    <cfRule type="expression" dxfId="523" priority="722">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G693:G694">
-    <cfRule type="expression" dxfId="509" priority="701">
+    <cfRule type="expression" dxfId="522" priority="714">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G699">
-    <cfRule type="expression" dxfId="508" priority="698">
+    <cfRule type="expression" dxfId="521" priority="711">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701:G702">
-    <cfRule type="expression" dxfId="507" priority="690">
+    <cfRule type="expression" dxfId="520" priority="703">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G707">
-    <cfRule type="expression" dxfId="506" priority="686">
+    <cfRule type="expression" dxfId="519" priority="699">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G709:G710">
-    <cfRule type="expression" dxfId="505" priority="676">
+    <cfRule type="expression" dxfId="518" priority="689">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G715">
-    <cfRule type="expression" dxfId="504" priority="671">
+    <cfRule type="expression" dxfId="517" priority="684">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G717:G718">
-    <cfRule type="expression" dxfId="503" priority="658">
+    <cfRule type="expression" dxfId="516" priority="671">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G723">
-    <cfRule type="expression" dxfId="502" priority="647">
+    <cfRule type="expression" dxfId="515" priority="660">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G725:G726">
-    <cfRule type="expression" dxfId="501" priority="624">
+    <cfRule type="expression" dxfId="514" priority="637">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G731">
-    <cfRule type="expression" dxfId="500" priority="611">
+    <cfRule type="expression" dxfId="513" priority="624">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G733:G734">
-    <cfRule type="expression" dxfId="499" priority="576">
+    <cfRule type="expression" dxfId="512" priority="589">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739">
-    <cfRule type="expression" dxfId="498" priority="545">
+    <cfRule type="expression" dxfId="511" priority="558">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G741:G742">
-    <cfRule type="expression" dxfId="497" priority="499">
+    <cfRule type="expression" dxfId="510" priority="512">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G747">
-    <cfRule type="expression" dxfId="496" priority="462">
+    <cfRule type="expression" dxfId="509" priority="475">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="495" priority="419">
+    <cfRule type="expression" dxfId="508" priority="432">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="494" priority="394">
+    <cfRule type="expression" dxfId="507" priority="407">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G758">
-    <cfRule type="expression" dxfId="493" priority="345">
+    <cfRule type="expression" dxfId="506" priority="358">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763">
-    <cfRule type="expression" dxfId="492" priority="318">
+    <cfRule type="expression" dxfId="505" priority="331">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G765:G766">
-    <cfRule type="expression" dxfId="491" priority="259">
+    <cfRule type="expression" dxfId="504" priority="272">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G771">
-    <cfRule type="expression" dxfId="490" priority="220">
+    <cfRule type="expression" dxfId="503" priority="233">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H128:I129">
-    <cfRule type="expression" dxfId="489" priority="741">
+    <cfRule type="expression" dxfId="502" priority="754">
       <formula>$C128=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="expression" dxfId="488" priority="739">
+    <cfRule type="expression" dxfId="501" priority="752">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I661">
-    <cfRule type="expression" dxfId="487" priority="721">
+    <cfRule type="expression" dxfId="500" priority="734">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670">
-    <cfRule type="expression" dxfId="486" priority="718">
+    <cfRule type="expression" dxfId="499" priority="731">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I678">
-    <cfRule type="expression" dxfId="485" priority="714">
+    <cfRule type="expression" dxfId="498" priority="727">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I686">
-    <cfRule type="expression" dxfId="484" priority="711">
+    <cfRule type="expression" dxfId="497" priority="724">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I691">
-    <cfRule type="expression" dxfId="483" priority="708">
+    <cfRule type="expression" dxfId="496" priority="721">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I693:I694">
-    <cfRule type="expression" dxfId="482" priority="700">
+    <cfRule type="expression" dxfId="495" priority="713">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I699">
-    <cfRule type="expression" dxfId="481" priority="697">
+    <cfRule type="expression" dxfId="494" priority="710">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I701:I702">
-    <cfRule type="expression" dxfId="480" priority="691">
+    <cfRule type="expression" dxfId="493" priority="704">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I707">
-    <cfRule type="expression" dxfId="479" priority="688">
+    <cfRule type="expression" dxfId="492" priority="701">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I709:I710">
-    <cfRule type="expression" dxfId="478" priority="675">
+    <cfRule type="expression" dxfId="491" priority="688">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I715">
-    <cfRule type="expression" dxfId="477" priority="669">
+    <cfRule type="expression" dxfId="490" priority="682">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I717:I718">
-    <cfRule type="expression" dxfId="476" priority="655">
+    <cfRule type="expression" dxfId="489" priority="668">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I723:I726">
-    <cfRule type="expression" dxfId="475" priority="621">
+    <cfRule type="expression" dxfId="488" priority="634">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I731:I734">
-    <cfRule type="expression" dxfId="474" priority="570">
+    <cfRule type="expression" dxfId="487" priority="583">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I736">
-    <cfRule type="expression" dxfId="473" priority="559">
+    <cfRule type="expression" dxfId="486" priority="572">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I742">
-    <cfRule type="expression" dxfId="472" priority="493">
+    <cfRule type="expression" dxfId="485" priority="506">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I744">
-    <cfRule type="expression" dxfId="471" priority="477">
+    <cfRule type="expression" dxfId="484" priority="490">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I747:I748">
-    <cfRule type="expression" dxfId="470" priority="447">
+    <cfRule type="expression" dxfId="483" priority="460">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I750">
-    <cfRule type="expression" dxfId="469" priority="412">
+    <cfRule type="expression" dxfId="482" priority="425">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755:I756">
-    <cfRule type="expression" dxfId="468" priority="376">
+    <cfRule type="expression" dxfId="481" priority="389">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I758">
-    <cfRule type="expression" dxfId="467" priority="338">
+    <cfRule type="expression" dxfId="480" priority="351">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I763">
-    <cfRule type="expression" dxfId="466" priority="311">
+    <cfRule type="expression" dxfId="479" priority="324">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I765:I766">
-    <cfRule type="expression" dxfId="465" priority="246">
+    <cfRule type="expression" dxfId="478" priority="259">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I771:I772">
-    <cfRule type="expression" dxfId="464" priority="213">
+    <cfRule type="expression" dxfId="477" priority="226">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="463" priority="740">
+    <cfRule type="expression" dxfId="476" priority="753">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K661">
-    <cfRule type="expression" dxfId="462" priority="720">
+    <cfRule type="expression" dxfId="475" priority="733">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K670">
-    <cfRule type="expression" dxfId="461" priority="717">
+    <cfRule type="expression" dxfId="474" priority="730">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K678">
-    <cfRule type="expression" dxfId="460" priority="713">
+    <cfRule type="expression" dxfId="473" priority="726">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K686">
-    <cfRule type="expression" dxfId="459" priority="710">
+    <cfRule type="expression" dxfId="472" priority="723">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K691">
-    <cfRule type="expression" dxfId="458" priority="707">
+    <cfRule type="expression" dxfId="471" priority="720">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K693:K694">
-    <cfRule type="expression" dxfId="457" priority="699">
+    <cfRule type="expression" dxfId="470" priority="712">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K699">
-    <cfRule type="expression" dxfId="456" priority="696">
+    <cfRule type="expression" dxfId="469" priority="709">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701:K702">
-    <cfRule type="expression" dxfId="455" priority="692">
+    <cfRule type="expression" dxfId="468" priority="705">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K707">
-    <cfRule type="expression" dxfId="454" priority="687">
+    <cfRule type="expression" dxfId="467" priority="700">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K709:K710">
-    <cfRule type="expression" dxfId="453" priority="674">
+    <cfRule type="expression" dxfId="466" priority="687">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K715:K718">
-    <cfRule type="expression" dxfId="452" priority="652">
+    <cfRule type="expression" dxfId="465" priority="665">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K723">
-    <cfRule type="expression" dxfId="451" priority="641">
+    <cfRule type="expression" dxfId="464" priority="654">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K725:K726">
-    <cfRule type="expression" dxfId="450" priority="618">
+    <cfRule type="expression" dxfId="463" priority="631">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K731">
-    <cfRule type="expression" dxfId="449" priority="603">
+    <cfRule type="expression" dxfId="462" priority="616">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K733:K734">
-    <cfRule type="expression" dxfId="448" priority="564">
+    <cfRule type="expression" dxfId="461" priority="577">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K736">
-    <cfRule type="expression" dxfId="447" priority="554">
+    <cfRule type="expression" dxfId="460" priority="567">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K742">
-    <cfRule type="expression" dxfId="446" priority="482">
+    <cfRule type="expression" dxfId="459" priority="495">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K744">
-    <cfRule type="expression" dxfId="445" priority="472">
+    <cfRule type="expression" dxfId="458" priority="485">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K747">
-    <cfRule type="expression" dxfId="444" priority="452">
+    <cfRule type="expression" dxfId="457" priority="465">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K749:K750">
-    <cfRule type="expression" dxfId="443" priority="405">
+    <cfRule type="expression" dxfId="456" priority="418">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755:K756">
-    <cfRule type="expression" dxfId="442" priority="370">
+    <cfRule type="expression" dxfId="455" priority="383">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K758">
-    <cfRule type="expression" dxfId="441" priority="331">
+    <cfRule type="expression" dxfId="454" priority="344">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K763:K764">
-    <cfRule type="expression" dxfId="440" priority="304">
+    <cfRule type="expression" dxfId="453" priority="317">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766">
-    <cfRule type="expression" dxfId="439" priority="233">
+    <cfRule type="expression" dxfId="452" priority="246">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K771">
+    <cfRule type="expression" dxfId="451" priority="219">
+      <formula>$C771=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E773">
+    <cfRule type="expression" dxfId="450" priority="218">
+      <formula>$C773=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G773">
+    <cfRule type="expression" dxfId="449" priority="217">
+      <formula>$C773=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G773">
+    <cfRule type="expression" dxfId="448" priority="216">
+      <formula>$C773=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I773">
+    <cfRule type="expression" dxfId="447" priority="215">
+      <formula>$C773=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I773">
+    <cfRule type="expression" dxfId="446" priority="214">
+      <formula>$C773=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K773">
+    <cfRule type="expression" dxfId="445" priority="213">
+      <formula>$C773=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K773">
+    <cfRule type="expression" dxfId="444" priority="212">
+      <formula>$C773=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E774">
+    <cfRule type="expression" dxfId="443" priority="211">
+      <formula>$C774=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G774">
+    <cfRule type="expression" dxfId="442" priority="210">
+      <formula>$C774=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I774">
+    <cfRule type="expression" dxfId="441" priority="209">
+      <formula>$C774=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K774">
+    <cfRule type="expression" dxfId="440" priority="208">
+      <formula>$C774=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I776">
+    <cfRule type="expression" dxfId="439" priority="207">
+      <formula>$C776=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I776">
     <cfRule type="expression" dxfId="438" priority="206">
-      <formula>$C771=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E773">
+      <formula>$C776=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K776">
     <cfRule type="expression" dxfId="437" priority="205">
-      <formula>$C773=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G773">
+      <formula>$C776=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K776">
     <cfRule type="expression" dxfId="436" priority="204">
-      <formula>$C773=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G773">
+      <formula>$C776=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E779">
     <cfRule type="expression" dxfId="435" priority="203">
-      <formula>$C773=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I773">
+      <formula>$C779=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G779">
     <cfRule type="expression" dxfId="434" priority="202">
-      <formula>$C773=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I773">
+      <formula>$C779=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G779">
     <cfRule type="expression" dxfId="433" priority="201">
-      <formula>$C773=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K773">
+      <formula>$C779=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I779">
     <cfRule type="expression" dxfId="432" priority="200">
-      <formula>$C773=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K773">
+      <formula>$C779=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I779">
     <cfRule type="expression" dxfId="431" priority="199">
-      <formula>$C773=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E774">
+      <formula>$C779=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K779">
     <cfRule type="expression" dxfId="430" priority="198">
-      <formula>$C774=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G774">
+      <formula>$C779=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K779">
     <cfRule type="expression" dxfId="429" priority="197">
-      <formula>$C774=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I774">
+      <formula>$C779=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I780">
     <cfRule type="expression" dxfId="428" priority="196">
-      <formula>$C774=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K774">
+      <formula>$C780=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I780">
     <cfRule type="expression" dxfId="427" priority="195">
-      <formula>$C774=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I776">
+      <formula>$C780=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K780">
     <cfRule type="expression" dxfId="426" priority="194">
-      <formula>$C776=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I776">
+      <formula>$C780=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K780">
     <cfRule type="expression" dxfId="425" priority="193">
-      <formula>$C776=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K776">
+      <formula>$C780=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I781:I782">
     <cfRule type="expression" dxfId="424" priority="192">
-      <formula>$C776=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K776">
+      <formula>$C781=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I781:I782">
     <cfRule type="expression" dxfId="423" priority="191">
-      <formula>$C776=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E779">
+      <formula>$C781=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G781:G782">
     <cfRule type="expression" dxfId="422" priority="190">
-      <formula>$C779=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G779">
+      <formula>$C781=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G781:G782">
     <cfRule type="expression" dxfId="421" priority="189">
-      <formula>$C779=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G779">
+      <formula>$C781=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E781:E782">
     <cfRule type="expression" dxfId="420" priority="188">
-      <formula>$C779=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I779">
+      <formula>$C781=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E781:E782">
     <cfRule type="expression" dxfId="419" priority="187">
-      <formula>$C779=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I779">
+      <formula>$C781=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E782">
     <cfRule type="expression" dxfId="418" priority="186">
-      <formula>$C779=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K779">
+      <formula>$C782=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G782">
     <cfRule type="expression" dxfId="417" priority="185">
-      <formula>$C779=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K779">
+      <formula>$C782=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G782">
     <cfRule type="expression" dxfId="416" priority="184">
-      <formula>$C779=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I780">
+      <formula>$C782=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I782">
     <cfRule type="expression" dxfId="415" priority="183">
-      <formula>$C780=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I780">
+      <formula>$C782=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I782">
     <cfRule type="expression" dxfId="414" priority="182">
-      <formula>$C780=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K780">
+      <formula>$C782=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K782">
     <cfRule type="expression" dxfId="413" priority="181">
-      <formula>$C780=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K780">
+      <formula>$C782=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K782">
     <cfRule type="expression" dxfId="412" priority="180">
-      <formula>$C780=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I781:I782">
+      <formula>$C782=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I784">
     <cfRule type="expression" dxfId="411" priority="179">
-      <formula>$C781=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I781:I782">
+      <formula>$C784=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I784">
     <cfRule type="expression" dxfId="410" priority="178">
-      <formula>$C781=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G781:G782">
+      <formula>$C784=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K784">
     <cfRule type="expression" dxfId="409" priority="177">
-      <formula>$C781=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G781:G782">
+      <formula>$C784=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K784">
     <cfRule type="expression" dxfId="408" priority="176">
-      <formula>$C781=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E781:E782">
+      <formula>$C784=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E787">
     <cfRule type="expression" dxfId="407" priority="175">
-      <formula>$C781=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E781:E782">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E787">
     <cfRule type="expression" dxfId="406" priority="174">
-      <formula>$C781=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E782">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G787">
     <cfRule type="expression" dxfId="405" priority="173">
-      <formula>$C782=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G782">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G787">
     <cfRule type="expression" dxfId="404" priority="172">
-      <formula>$C782=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G782">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G787">
     <cfRule type="expression" dxfId="403" priority="171">
-      <formula>$C782=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I782">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I787:I788">
     <cfRule type="expression" dxfId="402" priority="170">
-      <formula>$C782=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I782">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I787:I788">
     <cfRule type="expression" dxfId="401" priority="169">
-      <formula>$C782=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K782">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I787:I788">
     <cfRule type="expression" dxfId="400" priority="168">
-      <formula>$C782=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K782">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K787">
     <cfRule type="expression" dxfId="399" priority="167">
-      <formula>$C782=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I784">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K787">
     <cfRule type="expression" dxfId="398" priority="166">
-      <formula>$C784=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I784">
+      <formula>$C787=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K787">
     <cfRule type="expression" dxfId="397" priority="165">
-      <formula>$C784=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="396" priority="164">
-      <formula>$C784=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="395" priority="163">
-      <formula>$C784=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E787">
-    <cfRule type="expression" dxfId="394" priority="162">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E787">
+  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
+    <cfRule type="expression" dxfId="396" priority="162">
+      <formula>$C789=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
+    <cfRule type="expression" dxfId="395" priority="164">
+      <formula>$C789=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
+    <cfRule type="expression" dxfId="394" priority="163">
+      <formula>$C789=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K790 I790 G790 E790">
     <cfRule type="expression" dxfId="393" priority="161">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G787">
+      <formula>$C790=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K790 I790 G790 E790">
     <cfRule type="expression" dxfId="392" priority="160">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G787">
+      <formula>$C790=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K790 I790 G790 E790">
     <cfRule type="expression" dxfId="391" priority="159">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G787">
+      <formula>$C790=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K790 I790 G790">
     <cfRule type="expression" dxfId="390" priority="158">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="389" priority="157">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="388" priority="156">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="387" priority="155">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="386" priority="154">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="385" priority="153">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="384" priority="152">
-      <formula>$C787=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
-    <cfRule type="expression" dxfId="383" priority="149">
-      <formula>$C789=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="382" priority="151">
-      <formula>$C789=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="381" priority="150">
-      <formula>$C789=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K790 I790 G790 E790">
+      <formula>$C790=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I792">
+    <cfRule type="expression" dxfId="389" priority="155">
+      <formula>$C792=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I792">
+    <cfRule type="expression" dxfId="388" priority="157">
+      <formula>$C792=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I792">
+    <cfRule type="expression" dxfId="387" priority="156">
+      <formula>$C792=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K792">
+    <cfRule type="expression" dxfId="386" priority="152">
+      <formula>$C792=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K792">
+    <cfRule type="expression" dxfId="385" priority="154">
+      <formula>$C792=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K792">
+    <cfRule type="expression" dxfId="384" priority="153">
+      <formula>$C792=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E795">
+    <cfRule type="expression" dxfId="383" priority="151">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E795">
+    <cfRule type="expression" dxfId="382" priority="150">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G795">
+    <cfRule type="expression" dxfId="381" priority="149">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G795">
     <cfRule type="expression" dxfId="380" priority="148">
-      <formula>$C790=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K790 I790 G790 E790">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G795">
     <cfRule type="expression" dxfId="379" priority="147">
-      <formula>$C790=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K790 I790 G790 E790">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I795:I796">
     <cfRule type="expression" dxfId="378" priority="146">
-      <formula>$C790=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K790 I790 G790">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I795:I796">
     <cfRule type="expression" dxfId="377" priority="145">
-      <formula>$C790=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="376" priority="142">
-      <formula>$C792=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="375" priority="144">
-      <formula>$C792=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="374" priority="143">
-      <formula>$C792=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="373" priority="139">
-      <formula>$C792=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="372" priority="141">
-      <formula>$C792=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="371" priority="140">
-      <formula>$C792=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E795">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I795:I796">
+    <cfRule type="expression" dxfId="376" priority="144">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K795">
+    <cfRule type="expression" dxfId="375" priority="143">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K795">
+    <cfRule type="expression" dxfId="374" priority="142">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K795">
+    <cfRule type="expression" dxfId="373" priority="141">
+      <formula>$C795=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
+    <cfRule type="expression" dxfId="372" priority="140">
+      <formula>$C797=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
+    <cfRule type="expression" dxfId="371" priority="139">
+      <formula>$C797=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
     <cfRule type="expression" dxfId="370" priority="138">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E795">
+      <formula>$C797=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K798 I798 G798 E798">
     <cfRule type="expression" dxfId="369" priority="137">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G795">
+      <formula>$C798=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K798 I798 G798 E798">
     <cfRule type="expression" dxfId="368" priority="136">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G795">
+      <formula>$C798=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K798 I798 G798 E798">
     <cfRule type="expression" dxfId="367" priority="135">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G795">
+      <formula>$C798=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K798 I798 G798 E798">
     <cfRule type="expression" dxfId="366" priority="134">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I795:I796">
+      <formula>$C798=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K798 I798 G798 E798">
     <cfRule type="expression" dxfId="365" priority="133">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I795:I796">
+      <formula>$C798=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K798 I798 G798">
     <cfRule type="expression" dxfId="364" priority="132">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I795:I796">
+      <formula>$C798=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
     <cfRule type="expression" dxfId="363" priority="131">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K795">
+      <formula>$C803=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
     <cfRule type="expression" dxfId="362" priority="130">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K795">
+      <formula>$C803=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
     <cfRule type="expression" dxfId="361" priority="129">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K795">
+      <formula>$C803=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I803 G803 K803:K805">
     <cfRule type="expression" dxfId="360" priority="128">
-      <formula>$C795=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
+      <formula>$C803=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E805:E806">
     <cfRule type="expression" dxfId="359" priority="127">
-      <formula>$C797=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E805:E806">
     <cfRule type="expression" dxfId="358" priority="126">
-      <formula>$C797=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E805:E806">
     <cfRule type="expression" dxfId="357" priority="125">
-      <formula>$C797=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798 E798">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
     <cfRule type="expression" dxfId="356" priority="124">
-      <formula>$C798=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798 E798">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
     <cfRule type="expression" dxfId="355" priority="123">
-      <formula>$C798=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798 E798">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
     <cfRule type="expression" dxfId="354" priority="122">
-      <formula>$C798=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798 E798">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
     <cfRule type="expression" dxfId="353" priority="121">
-      <formula>$C798=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798 E798">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E806">
     <cfRule type="expression" dxfId="352" priority="120">
-      <formula>$C798=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K798 I798 G798">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G805:G806">
     <cfRule type="expression" dxfId="351" priority="119">
-      <formula>$C798=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G805:G806">
     <cfRule type="expression" dxfId="350" priority="118">
-      <formula>$C803=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G805:G806">
     <cfRule type="expression" dxfId="349" priority="117">
-      <formula>$C803=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I803 G803 E803 K803:K805">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G805:G806">
     <cfRule type="expression" dxfId="348" priority="116">
-      <formula>$C803=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I803 G803 K803:K805">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="347" priority="115">
-      <formula>$C803=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E805:E806">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="346" priority="114">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E805:E806">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="345" priority="113">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E805:E806">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="344" priority="112">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G806">
     <cfRule type="expression" dxfId="343" priority="111">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
+  <conditionalFormatting sqref="I805:I806">
     <cfRule type="expression" dxfId="342" priority="110">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I805:I806">
+    <cfRule type="expression" dxfId="341" priority="109">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I805:I806">
+    <cfRule type="expression" dxfId="340" priority="108">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I805:I806">
+    <cfRule type="expression" dxfId="339" priority="107">
+      <formula>$C805=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I806">
+    <cfRule type="expression" dxfId="338" priority="106">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="341" priority="109">
+  <conditionalFormatting sqref="I806">
+    <cfRule type="expression" dxfId="337" priority="105">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="340" priority="108">
+  <conditionalFormatting sqref="I806">
+    <cfRule type="expression" dxfId="336" priority="104">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="339" priority="107">
+  <conditionalFormatting sqref="I806">
+    <cfRule type="expression" dxfId="335" priority="103">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="338" priority="106">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="337" priority="105">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="336" priority="104">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="335" priority="103">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="I806">
     <cfRule type="expression" dxfId="334" priority="102">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="333" priority="101">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="332" priority="100">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="331" priority="99">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="330" priority="98">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="329" priority="97">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="328" priority="96">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="327" priority="95">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I805:I806">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="326" priority="94">
-      <formula>$C805=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+      <formula>$C806=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K806">
     <cfRule type="expression" dxfId="325" priority="93">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+  <conditionalFormatting sqref="I808">
     <cfRule type="expression" dxfId="324" priority="92">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+      <formula>$C808=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I808">
     <cfRule type="expression" dxfId="323" priority="91">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+      <formula>$C808=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I808">
     <cfRule type="expression" dxfId="322" priority="90">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I806">
+      <formula>$C808=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I808">
     <cfRule type="expression" dxfId="321" priority="89">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+      <formula>$C808=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K808">
     <cfRule type="expression" dxfId="320" priority="88">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+      <formula>$C808=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K808">
     <cfRule type="expression" dxfId="319" priority="87">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+      <formula>$C808=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K808">
     <cfRule type="expression" dxfId="318" priority="86">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+      <formula>$C808=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K808">
     <cfRule type="expression" dxfId="317" priority="85">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+      <formula>$C808=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E811">
     <cfRule type="expression" dxfId="316" priority="84">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E811">
     <cfRule type="expression" dxfId="315" priority="83">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E811">
     <cfRule type="expression" dxfId="314" priority="82">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G811">
     <cfRule type="expression" dxfId="313" priority="81">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K806">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G811">
     <cfRule type="expression" dxfId="312" priority="80">
-      <formula>$C806=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I808">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G811">
     <cfRule type="expression" dxfId="311" priority="79">
-      <formula>$C808=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I808">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G811">
     <cfRule type="expression" dxfId="310" priority="78">
-      <formula>$C808=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I808">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I811:I812">
     <cfRule type="expression" dxfId="309" priority="77">
-      <formula>$C808=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I808">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I811:I812">
     <cfRule type="expression" dxfId="308" priority="76">
-      <formula>$C808=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K808">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I811:I812">
     <cfRule type="expression" dxfId="307" priority="75">
-      <formula>$C808=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K808">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I811:I812">
     <cfRule type="expression" dxfId="306" priority="74">
-      <formula>$C808=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K808">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="305" priority="73">
-      <formula>$C808=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K808">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="304" priority="72">
-      <formula>$C808=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E811">
+      <formula>$C811=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="303" priority="71">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E811">
+  <conditionalFormatting sqref="K811">
     <cfRule type="expression" dxfId="302" priority="70">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E811">
+  <conditionalFormatting sqref="E813:E814">
     <cfRule type="expression" dxfId="301" priority="69">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E813:E814">
     <cfRule type="expression" dxfId="300" priority="68">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E813:E814">
     <cfRule type="expression" dxfId="299" priority="67">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
     <cfRule type="expression" dxfId="298" priority="66">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G811">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
     <cfRule type="expression" dxfId="297" priority="65">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
     <cfRule type="expression" dxfId="296" priority="64">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
     <cfRule type="expression" dxfId="295" priority="63">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E814">
     <cfRule type="expression" dxfId="294" priority="62">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I811:I812">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G813:G814">
     <cfRule type="expression" dxfId="293" priority="61">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G813:G814">
     <cfRule type="expression" dxfId="292" priority="60">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G813:G814">
     <cfRule type="expression" dxfId="291" priority="59">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G813:G814">
     <cfRule type="expression" dxfId="290" priority="58">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K811">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="289" priority="57">
-      <formula>$C811=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E813:E814">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="288" priority="56">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E813:E814">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="287" priority="55">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E813:E814">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="286" priority="54">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
+      <formula>$C814=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G814">
     <cfRule type="expression" dxfId="285" priority="53">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
+  <conditionalFormatting sqref="I813:I814">
     <cfRule type="expression" dxfId="284" priority="52">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I813:I814">
+    <cfRule type="expression" dxfId="283" priority="51">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I813:I814">
+    <cfRule type="expression" dxfId="282" priority="50">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I813:I814">
+    <cfRule type="expression" dxfId="281" priority="49">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I814">
+    <cfRule type="expression" dxfId="280" priority="48">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="283" priority="51">
+  <conditionalFormatting sqref="I814">
+    <cfRule type="expression" dxfId="279" priority="47">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="282" priority="50">
+  <conditionalFormatting sqref="I814">
+    <cfRule type="expression" dxfId="278" priority="46">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="281" priority="49">
+  <conditionalFormatting sqref="I814">
+    <cfRule type="expression" dxfId="277" priority="45">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="280" priority="48">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="279" priority="47">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="278" priority="46">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="277" priority="45">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
+  <conditionalFormatting sqref="I814">
     <cfRule type="expression" dxfId="276" priority="44">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
+  <conditionalFormatting sqref="K813:K814">
     <cfRule type="expression" dxfId="275" priority="43">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K813:K814">
+    <cfRule type="expression" dxfId="274" priority="42">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K813:K814">
+    <cfRule type="expression" dxfId="273" priority="41">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K813:K814">
+    <cfRule type="expression" dxfId="272" priority="40">
+      <formula>$C813=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K814">
+    <cfRule type="expression" dxfId="271" priority="39">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="274" priority="42">
+  <conditionalFormatting sqref="K814">
+    <cfRule type="expression" dxfId="270" priority="38">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="273" priority="41">
+  <conditionalFormatting sqref="K814">
+    <cfRule type="expression" dxfId="269" priority="37">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="272" priority="40">
+  <conditionalFormatting sqref="K814">
+    <cfRule type="expression" dxfId="268" priority="36">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="271" priority="39">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="270" priority="38">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="269" priority="37">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="268" priority="36">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+  <conditionalFormatting sqref="K814">
     <cfRule type="expression" dxfId="267" priority="35">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
     <cfRule type="expression" dxfId="266" priority="34">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+      <formula>$C826=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
     <cfRule type="expression" dxfId="265" priority="33">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+      <formula>$C826=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
     <cfRule type="expression" dxfId="264" priority="32">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I814">
+      <formula>$C826=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G826 I826:I829 K826:K829">
     <cfRule type="expression" dxfId="263" priority="31">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
+      <formula>$C826=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K829 I829 G829">
     <cfRule type="expression" dxfId="262" priority="30">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
+      <formula>$C829=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I834 G834 K834:K835">
     <cfRule type="expression" dxfId="261" priority="29">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
+      <formula>$C834=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I836 G836">
     <cfRule type="expression" dxfId="260" priority="28">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K813:K814">
+      <formula>$C836=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K837 I837 G837">
     <cfRule type="expression" dxfId="259" priority="27">
-      <formula>$C813=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
+      <formula>$C837=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K839 I839">
     <cfRule type="expression" dxfId="258" priority="26">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
+      <formula>$C839=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K842 I842 G842 E842">
     <cfRule type="expression" dxfId="257" priority="25">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
+      <formula>$C842=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K845 I845 G845 E845">
     <cfRule type="expression" dxfId="256" priority="24">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
+      <formula>$C845=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K845 I845 G845">
     <cfRule type="expression" dxfId="255" priority="23">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K814">
+      <formula>$C845=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K844 I844 G844 E844">
     <cfRule type="expression" dxfId="254" priority="22">
-      <formula>$C814=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
+      <formula>$C844=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K844 I844 G844">
     <cfRule type="expression" dxfId="253" priority="21">
-      <formula>$C826=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
+      <formula>$C844=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K843 I843">
     <cfRule type="expression" dxfId="252" priority="20">
-      <formula>$C826=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
+      <formula>$C843=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K843 I843">
     <cfRule type="expression" dxfId="251" priority="19">
-      <formula>$C826=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G826 I826:I829 K826:K829">
+      <formula>$C843=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K844 I844 G844 E844">
     <cfRule type="expression" dxfId="250" priority="18">
-      <formula>$C826=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K829 I829 G829">
+      <formula>$C844=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K844 I844 G844">
     <cfRule type="expression" dxfId="249" priority="17">
-      <formula>$C829=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I834 G834 K834:K835">
+      <formula>$C844=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K845 I845 G845 E845">
     <cfRule type="expression" dxfId="248" priority="16">
-      <formula>$C834=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I836 G836">
+      <formula>$C845=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I850 G850 E850 K850:K851">
     <cfRule type="expression" dxfId="247" priority="15">
-      <formula>$C836=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K837 I837 G837">
+      <formula>$C850=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I850 G850 K850:K851">
     <cfRule type="expression" dxfId="246" priority="14">
-      <formula>$C837=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K839 I839">
+      <formula>$C850=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E851">
     <cfRule type="expression" dxfId="245" priority="13">
-      <formula>$C839=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K842 I842 G842 E842">
+      <formula>$C851=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G851">
     <cfRule type="expression" dxfId="244" priority="12">
-      <formula>$C842=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K845 I845 G845 E845">
+      <formula>$C851=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G851">
     <cfRule type="expression" dxfId="243" priority="11">
-      <formula>$C845=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K845 I845 G845">
+      <formula>$C851=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E852:E853">
     <cfRule type="expression" dxfId="242" priority="10">
-      <formula>$C845=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K844 I844 G844 E844">
+      <formula>$C852=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G852:G853">
     <cfRule type="expression" dxfId="241" priority="9">
-      <formula>$C844=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K844 I844 G844">
+      <formula>$C852=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G852:G853">
     <cfRule type="expression" dxfId="240" priority="8">
-      <formula>$C844=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K843 I843">
+      <formula>$C852=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I852:I853">
     <cfRule type="expression" dxfId="239" priority="7">
-      <formula>$C843=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K843 I843">
+      <formula>$C852=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I852:I853">
     <cfRule type="expression" dxfId="238" priority="6">
-      <formula>$C843=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K844 I844 G844 E844">
+      <formula>$C852=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K852:K853">
     <cfRule type="expression" dxfId="237" priority="5">
-      <formula>$C844=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K844 I844 G844">
+      <formula>$C852=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K852:K853">
     <cfRule type="expression" dxfId="236" priority="4">
-      <formula>$C844=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K845 I845 G845 E845">
-    <cfRule type="expression" dxfId="235" priority="3">
-      <formula>$C845=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K850 I850 G850 E850">
-    <cfRule type="expression" dxfId="234" priority="2">
-      <formula>$C850=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K850 I850 G850">
-    <cfRule type="expression" dxfId="233" priority="1">
-      <formula>$C850=TODAY()</formula>
+      <formula>$C852=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K853 I853 G853 E853">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$C853=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K853 I853 G853 E853">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$C853=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K853 I853 G853">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -52641,1167 +52855,1167 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="B4:E879">
-    <cfRule type="expression" dxfId="232" priority="411">
+    <cfRule type="expression" dxfId="235" priority="411">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K879">
-    <cfRule type="expression" dxfId="231" priority="412">
+    <cfRule type="expression" dxfId="234" priority="412">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G47 J44:K47">
-    <cfRule type="expression" dxfId="230" priority="421">
+    <cfRule type="expression" dxfId="233" priority="421">
       <formula>$B18=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E692">
-    <cfRule type="expression" dxfId="229" priority="405">
+    <cfRule type="expression" dxfId="232" priority="405">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E694">
-    <cfRule type="expression" dxfId="228" priority="403">
+    <cfRule type="expression" dxfId="231" priority="403">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E701">
-    <cfRule type="expression" dxfId="227" priority="393">
+    <cfRule type="expression" dxfId="230" priority="393">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E703">
-    <cfRule type="expression" dxfId="226" priority="388">
+    <cfRule type="expression" dxfId="229" priority="388">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E710">
-    <cfRule type="expression" dxfId="225" priority="378">
+    <cfRule type="expression" dxfId="228" priority="378">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E712:E714">
-    <cfRule type="expression" dxfId="224" priority="373">
+    <cfRule type="expression" dxfId="227" priority="373">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E719">
-    <cfRule type="expression" dxfId="223" priority="363">
+    <cfRule type="expression" dxfId="226" priority="363">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E721:E723">
-    <cfRule type="expression" dxfId="222" priority="358">
+    <cfRule type="expression" dxfId="225" priority="358">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E728">
-    <cfRule type="expression" dxfId="221" priority="351">
+    <cfRule type="expression" dxfId="224" priority="351">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E730:E732">
-    <cfRule type="expression" dxfId="220" priority="338">
+    <cfRule type="expression" dxfId="223" priority="338">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E737">
-    <cfRule type="expression" dxfId="219" priority="331">
+    <cfRule type="expression" dxfId="222" priority="331">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739:E741">
-    <cfRule type="expression" dxfId="218" priority="318">
+    <cfRule type="expression" dxfId="221" priority="318">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E746">
-    <cfRule type="expression" dxfId="217" priority="308">
+    <cfRule type="expression" dxfId="220" priority="308">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E748:E750">
-    <cfRule type="expression" dxfId="216" priority="286">
+    <cfRule type="expression" dxfId="219" priority="286">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="215" priority="279">
+    <cfRule type="expression" dxfId="218" priority="279">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E759">
-    <cfRule type="expression" dxfId="214" priority="252">
+    <cfRule type="expression" dxfId="217" priority="252">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E764">
-    <cfRule type="expression" dxfId="213" priority="248">
+    <cfRule type="expression" dxfId="216" priority="248">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E766:E768">
-    <cfRule type="expression" dxfId="212" priority="223">
+    <cfRule type="expression" dxfId="215" priority="223">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="211" priority="213">
+    <cfRule type="expression" dxfId="214" priority="213">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E775:E777">
-    <cfRule type="expression" dxfId="210" priority="201">
+    <cfRule type="expression" dxfId="213" priority="201">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="209" priority="179">
+    <cfRule type="expression" dxfId="212" priority="179">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E784:E786">
-    <cfRule type="expression" dxfId="208" priority="161">
+    <cfRule type="expression" dxfId="211" priority="161">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="207" priority="424">
+    <cfRule type="expression" dxfId="210" priority="424">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70">
-    <cfRule type="expression" dxfId="206" priority="433">
+    <cfRule type="expression" dxfId="209" priority="433">
       <formula>$C70=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G685">
-    <cfRule type="expression" dxfId="205" priority="409">
+    <cfRule type="expression" dxfId="208" priority="409">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G692">
-    <cfRule type="expression" dxfId="204" priority="406">
+    <cfRule type="expression" dxfId="207" priority="406">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G695">
-    <cfRule type="expression" dxfId="203" priority="396">
+    <cfRule type="expression" dxfId="206" priority="396">
       <formula>$C695=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701">
-    <cfRule type="expression" dxfId="202" priority="391">
+    <cfRule type="expression" dxfId="205" priority="391">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G704:G705">
-    <cfRule type="expression" dxfId="201" priority="380">
+    <cfRule type="expression" dxfId="204" priority="380">
       <formula>$C704=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G710">
-    <cfRule type="expression" dxfId="200" priority="376">
+    <cfRule type="expression" dxfId="203" priority="376">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G712:G714">
-    <cfRule type="expression" dxfId="199" priority="366">
+    <cfRule type="expression" dxfId="202" priority="366">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G719">
-    <cfRule type="expression" dxfId="198" priority="361">
+    <cfRule type="expression" dxfId="201" priority="361">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G721:G723">
-    <cfRule type="expression" dxfId="197" priority="356">
+    <cfRule type="expression" dxfId="200" priority="356">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G728">
-    <cfRule type="expression" dxfId="196" priority="349">
+    <cfRule type="expression" dxfId="199" priority="349">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G730:G732">
-    <cfRule type="expression" dxfId="195" priority="336">
+    <cfRule type="expression" dxfId="198" priority="336">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G737">
-    <cfRule type="expression" dxfId="194" priority="329">
+    <cfRule type="expression" dxfId="197" priority="329">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739:G741">
-    <cfRule type="expression" dxfId="193" priority="315">
+    <cfRule type="expression" dxfId="196" priority="315">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746">
-    <cfRule type="expression" dxfId="192" priority="306">
+    <cfRule type="expression" dxfId="195" priority="306">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="191" priority="283">
+    <cfRule type="expression" dxfId="194" priority="283">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="190" priority="277">
+    <cfRule type="expression" dxfId="193" priority="277">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G759">
-    <cfRule type="expression" dxfId="189" priority="249">
+    <cfRule type="expression" dxfId="192" priority="249">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G764">
-    <cfRule type="expression" dxfId="188" priority="246">
+    <cfRule type="expression" dxfId="191" priority="246">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G766:G768">
-    <cfRule type="expression" dxfId="187" priority="219">
+    <cfRule type="expression" dxfId="190" priority="219">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="186" priority="211">
+    <cfRule type="expression" dxfId="189" priority="211">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G775:G777">
-    <cfRule type="expression" dxfId="185" priority="194">
+    <cfRule type="expression" dxfId="188" priority="194">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="184" priority="177">
+    <cfRule type="expression" dxfId="187" priority="177">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G784:G786">
-    <cfRule type="expression" dxfId="183" priority="155">
+    <cfRule type="expression" dxfId="186" priority="155">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:I47">
-    <cfRule type="expression" dxfId="182" priority="446">
+    <cfRule type="expression" dxfId="185" priority="446">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="expression" dxfId="181" priority="450">
+    <cfRule type="expression" dxfId="184" priority="450">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I685">
-    <cfRule type="expression" dxfId="180" priority="408">
+    <cfRule type="expression" dxfId="183" priority="408">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I694:I695">
-    <cfRule type="expression" dxfId="179" priority="395">
+    <cfRule type="expression" dxfId="182" priority="395">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I703:I704">
-    <cfRule type="expression" dxfId="178" priority="382">
+    <cfRule type="expression" dxfId="181" priority="382">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I712:I714">
-    <cfRule type="expression" dxfId="177" priority="365">
+    <cfRule type="expression" dxfId="180" priority="365">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I721:I723">
-    <cfRule type="expression" dxfId="176" priority="354">
+    <cfRule type="expression" dxfId="179" priority="354">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I730:I732">
-    <cfRule type="expression" dxfId="175" priority="332">
+    <cfRule type="expression" dxfId="178" priority="332">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I741">
-    <cfRule type="expression" dxfId="174" priority="312">
+    <cfRule type="expression" dxfId="177" priority="312">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I748:I749">
-    <cfRule type="expression" dxfId="173" priority="291">
+    <cfRule type="expression" dxfId="176" priority="291">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755">
-    <cfRule type="expression" dxfId="172" priority="275">
+    <cfRule type="expression" dxfId="175" priority="275">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I757:I758">
-    <cfRule type="expression" dxfId="171" priority="258">
+    <cfRule type="expression" dxfId="174" priority="258">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I766:I768">
-    <cfRule type="expression" dxfId="170" priority="215">
+    <cfRule type="expression" dxfId="173" priority="215">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="169" priority="209">
+    <cfRule type="expression" dxfId="172" priority="209">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I775:I777">
-    <cfRule type="expression" dxfId="168" priority="187">
+    <cfRule type="expression" dxfId="171" priority="187">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="167" priority="175">
+    <cfRule type="expression" dxfId="170" priority="175">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784:I786">
-    <cfRule type="expression" dxfId="166" priority="149">
+    <cfRule type="expression" dxfId="169" priority="149">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="165" priority="425">
+    <cfRule type="expression" dxfId="168" priority="425">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K685">
-    <cfRule type="expression" dxfId="164" priority="407">
+    <cfRule type="expression" dxfId="167" priority="407">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K692">
-    <cfRule type="expression" dxfId="163" priority="404">
+    <cfRule type="expression" dxfId="166" priority="404">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K694:K695">
-    <cfRule type="expression" dxfId="162" priority="394">
+    <cfRule type="expression" dxfId="165" priority="394">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701">
-    <cfRule type="expression" dxfId="161" priority="389">
+    <cfRule type="expression" dxfId="164" priority="389">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K703:K705">
-    <cfRule type="expression" dxfId="160" priority="379">
+    <cfRule type="expression" dxfId="163" priority="379">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K710">
-    <cfRule type="expression" dxfId="159" priority="374">
+    <cfRule type="expression" dxfId="162" priority="374">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K712:K714">
-    <cfRule type="expression" dxfId="158" priority="364">
+    <cfRule type="expression" dxfId="161" priority="364">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K719">
-    <cfRule type="expression" dxfId="157" priority="359">
+    <cfRule type="expression" dxfId="160" priority="359">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K721:K723">
-    <cfRule type="expression" dxfId="156" priority="352">
+    <cfRule type="expression" dxfId="159" priority="352">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K728">
-    <cfRule type="expression" dxfId="155" priority="347">
+    <cfRule type="expression" dxfId="158" priority="347">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K730:K732">
-    <cfRule type="expression" dxfId="154" priority="334">
+    <cfRule type="expression" dxfId="157" priority="334">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K737">
-    <cfRule type="expression" dxfId="153" priority="327">
+    <cfRule type="expression" dxfId="156" priority="327">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K741">
-    <cfRule type="expression" dxfId="152" priority="309">
+    <cfRule type="expression" dxfId="155" priority="309">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K746">
-    <cfRule type="expression" dxfId="151" priority="304">
+    <cfRule type="expression" dxfId="154" priority="304">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K748:K750">
-    <cfRule type="expression" dxfId="150" priority="280">
+    <cfRule type="expression" dxfId="153" priority="280">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755">
-    <cfRule type="expression" dxfId="149" priority="273">
+    <cfRule type="expression" dxfId="152" priority="273">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K757:K758">
-    <cfRule type="expression" dxfId="148" priority="255">
+    <cfRule type="expression" dxfId="151" priority="255">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K764">
-    <cfRule type="expression" dxfId="147" priority="244">
+    <cfRule type="expression" dxfId="150" priority="244">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766:K767">
-    <cfRule type="expression" dxfId="146" priority="226">
+    <cfRule type="expression" dxfId="149" priority="226">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="145" priority="207">
+    <cfRule type="expression" dxfId="148" priority="207">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K775:K777">
-    <cfRule type="expression" dxfId="144" priority="180">
+    <cfRule type="expression" dxfId="147" priority="180">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="143" priority="173">
+    <cfRule type="expression" dxfId="146" priority="173">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784:K786">
-    <cfRule type="expression" dxfId="142" priority="143">
+    <cfRule type="expression" dxfId="145" priority="143">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E792:E793">
-    <cfRule type="expression" dxfId="141" priority="142">
+    <cfRule type="expression" dxfId="144" priority="142">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="140" priority="141">
+    <cfRule type="expression" dxfId="143" priority="141">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="139" priority="140">
+    <cfRule type="expression" dxfId="142" priority="140">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="138" priority="139">
+    <cfRule type="expression" dxfId="141" priority="139">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="137" priority="138">
+    <cfRule type="expression" dxfId="140" priority="138">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="136" priority="137">
+    <cfRule type="expression" dxfId="139" priority="137">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="135" priority="136">
+    <cfRule type="expression" dxfId="138" priority="136">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E794:E795">
-    <cfRule type="expression" dxfId="134" priority="135">
+    <cfRule type="expression" dxfId="137" priority="135">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="133" priority="134">
+    <cfRule type="expression" dxfId="136" priority="134">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="132" priority="133">
+    <cfRule type="expression" dxfId="135" priority="133">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="131" priority="132">
+    <cfRule type="expression" dxfId="134" priority="132">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="130" priority="131">
+    <cfRule type="expression" dxfId="133" priority="131">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="129" priority="130">
+    <cfRule type="expression" dxfId="132" priority="130">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="128" priority="129">
+    <cfRule type="expression" dxfId="131" priority="129">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E801:E802">
-    <cfRule type="expression" dxfId="127" priority="128">
+    <cfRule type="expression" dxfId="130" priority="128">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E803:E805">
-    <cfRule type="expression" dxfId="126" priority="127">
+    <cfRule type="expression" dxfId="129" priority="127">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G805">
-    <cfRule type="expression" dxfId="125" priority="126">
+    <cfRule type="expression" dxfId="128" priority="126">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G802">
-    <cfRule type="expression" dxfId="124" priority="125">
+    <cfRule type="expression" dxfId="127" priority="125">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G803:G805">
-    <cfRule type="expression" dxfId="123" priority="124">
+    <cfRule type="expression" dxfId="126" priority="124">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I805">
-    <cfRule type="expression" dxfId="122" priority="123">
+    <cfRule type="expression" dxfId="125" priority="123">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I802">
-    <cfRule type="expression" dxfId="121" priority="122">
+    <cfRule type="expression" dxfId="124" priority="122">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803:I805">
-    <cfRule type="expression" dxfId="120" priority="121">
+    <cfRule type="expression" dxfId="123" priority="121">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K805">
-    <cfRule type="expression" dxfId="119" priority="120">
+    <cfRule type="expression" dxfId="122" priority="120">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K802">
-    <cfRule type="expression" dxfId="118" priority="119">
+    <cfRule type="expression" dxfId="121" priority="119">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K803:K805">
-    <cfRule type="expression" dxfId="117" priority="118">
+    <cfRule type="expression" dxfId="120" priority="118">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E809:E810">
-    <cfRule type="expression" dxfId="116" priority="117">
+    <cfRule type="expression" dxfId="119" priority="117">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811:E812">
-    <cfRule type="expression" dxfId="115" priority="116">
+    <cfRule type="expression" dxfId="118" priority="116">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G812">
-    <cfRule type="expression" dxfId="114" priority="115">
+    <cfRule type="expression" dxfId="117" priority="115">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G810">
-    <cfRule type="expression" dxfId="113" priority="114">
+    <cfRule type="expression" dxfId="116" priority="114">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811:G812">
-    <cfRule type="expression" dxfId="112" priority="113">
+    <cfRule type="expression" dxfId="115" priority="113">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I812">
-    <cfRule type="expression" dxfId="111" priority="112">
+    <cfRule type="expression" dxfId="114" priority="112">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I810">
-    <cfRule type="expression" dxfId="110" priority="111">
+    <cfRule type="expression" dxfId="113" priority="111">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="109" priority="110">
+    <cfRule type="expression" dxfId="112" priority="110">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K812">
-    <cfRule type="expression" dxfId="108" priority="109">
+    <cfRule type="expression" dxfId="111" priority="109">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K810">
-    <cfRule type="expression" dxfId="107" priority="108">
+    <cfRule type="expression" dxfId="110" priority="108">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811:K812">
-    <cfRule type="expression" dxfId="106" priority="107">
+    <cfRule type="expression" dxfId="109" priority="107">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E818:E822 G818:G822 K818:K822 I818:I822">
-    <cfRule type="expression" dxfId="105" priority="106">
+    <cfRule type="expression" dxfId="108" priority="106">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K818:K822 G818:G822 I818:I822">
-    <cfRule type="expression" dxfId="104" priority="105">
+    <cfRule type="expression" dxfId="107" priority="105">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E820:E821">
-    <cfRule type="expression" dxfId="103" priority="104">
+    <cfRule type="expression" dxfId="106" priority="104">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="102" priority="103">
+    <cfRule type="expression" dxfId="105" priority="103">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="101" priority="102">
+    <cfRule type="expression" dxfId="104" priority="102">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="100" priority="101">
+    <cfRule type="expression" dxfId="103" priority="101">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="99" priority="100">
+    <cfRule type="expression" dxfId="102" priority="100">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K822 G822">
-    <cfRule type="expression" dxfId="98" priority="99">
+    <cfRule type="expression" dxfId="101" priority="99">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I822">
-    <cfRule type="expression" dxfId="97" priority="98">
+    <cfRule type="expression" dxfId="100" priority="98">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E828:E831">
-    <cfRule type="expression" dxfId="96" priority="97">
+    <cfRule type="expression" dxfId="99" priority="97">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="95" priority="96">
+    <cfRule type="expression" dxfId="98" priority="96">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="94" priority="95">
+    <cfRule type="expression" dxfId="97" priority="95">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="93" priority="94">
+    <cfRule type="expression" dxfId="96" priority="94">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="92" priority="93">
+    <cfRule type="expression" dxfId="95" priority="93">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="91" priority="92">
+    <cfRule type="expression" dxfId="94" priority="92">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="90" priority="91">
+    <cfRule type="expression" dxfId="93" priority="91">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="89" priority="90">
+    <cfRule type="expression" dxfId="92" priority="90">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="88" priority="89">
+    <cfRule type="expression" dxfId="91" priority="89">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="87" priority="88">
+    <cfRule type="expression" dxfId="90" priority="88">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="86" priority="87">
+    <cfRule type="expression" dxfId="89" priority="87">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="85" priority="86">
+    <cfRule type="expression" dxfId="88" priority="86">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="84" priority="85">
+    <cfRule type="expression" dxfId="87" priority="85">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="83" priority="84">
+    <cfRule type="expression" dxfId="86" priority="84">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837">
-    <cfRule type="expression" dxfId="82" priority="83">
+    <cfRule type="expression" dxfId="85" priority="83">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="81" priority="82">
+    <cfRule type="expression" dxfId="84" priority="82">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="80" priority="81">
+    <cfRule type="expression" dxfId="83" priority="81">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="79" priority="80">
+    <cfRule type="expression" dxfId="82" priority="80">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="78" priority="79">
+    <cfRule type="expression" dxfId="81" priority="79">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="77" priority="78">
+    <cfRule type="expression" dxfId="80" priority="78">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="76" priority="77">
+    <cfRule type="expression" dxfId="79" priority="77">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E845:E847">
-    <cfRule type="expression" dxfId="75" priority="76">
+    <cfRule type="expression" dxfId="78" priority="76">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="74" priority="75">
+    <cfRule type="expression" dxfId="77" priority="75">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="73" priority="74">
+    <cfRule type="expression" dxfId="76" priority="74">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="72" priority="73">
+    <cfRule type="expression" dxfId="75" priority="73">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="71" priority="72">
+    <cfRule type="expression" dxfId="74" priority="72">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="70" priority="71">
+    <cfRule type="expression" dxfId="73" priority="71">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="69" priority="70">
+    <cfRule type="expression" dxfId="72" priority="70">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="68" priority="69">
+    <cfRule type="expression" dxfId="71" priority="69">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="67" priority="68">
+    <cfRule type="expression" dxfId="70" priority="68">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="66" priority="67">
+    <cfRule type="expression" dxfId="69" priority="67">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="65" priority="66">
+    <cfRule type="expression" dxfId="68" priority="66">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="64" priority="65">
+    <cfRule type="expression" dxfId="67" priority="65">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="63" priority="64">
+    <cfRule type="expression" dxfId="66" priority="64">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="62" priority="63">
+    <cfRule type="expression" dxfId="65" priority="63">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="61" priority="62">
+    <cfRule type="expression" dxfId="64" priority="62">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="60" priority="61">
+    <cfRule type="expression" dxfId="63" priority="61">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="59" priority="60">
+    <cfRule type="expression" dxfId="62" priority="60">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="58" priority="59">
+    <cfRule type="expression" dxfId="61" priority="59">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="57" priority="58">
+    <cfRule type="expression" dxfId="60" priority="58">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="56" priority="57">
+    <cfRule type="expression" dxfId="59" priority="57">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="55" priority="56">
+    <cfRule type="expression" dxfId="58" priority="56">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="54" priority="55">
+    <cfRule type="expression" dxfId="57" priority="55">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="53" priority="54">
+    <cfRule type="expression" dxfId="56" priority="54">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="52" priority="53">
+    <cfRule type="expression" dxfId="55" priority="53">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="51" priority="52">
+    <cfRule type="expression" dxfId="54" priority="52">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="50" priority="51">
+    <cfRule type="expression" dxfId="53" priority="51">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="49" priority="50">
+    <cfRule type="expression" dxfId="52" priority="50">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="48" priority="49">
+    <cfRule type="expression" dxfId="51" priority="49">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="47" priority="48">
+    <cfRule type="expression" dxfId="50" priority="48">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="46" priority="47">
+    <cfRule type="expression" dxfId="49" priority="47">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="45" priority="46">
+    <cfRule type="expression" dxfId="48" priority="46">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E836">
-    <cfRule type="expression" dxfId="44" priority="45">
+    <cfRule type="expression" dxfId="47" priority="45">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="43" priority="44">
+    <cfRule type="expression" dxfId="46" priority="44">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="42" priority="43">
+    <cfRule type="expression" dxfId="45" priority="43">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="41" priority="42">
+    <cfRule type="expression" dxfId="44" priority="42">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="40" priority="41">
+    <cfRule type="expression" dxfId="43" priority="41">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="39" priority="40">
+    <cfRule type="expression" dxfId="42" priority="40">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="38" priority="39">
+    <cfRule type="expression" dxfId="41" priority="39">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853 E853">
-    <cfRule type="expression" dxfId="37" priority="38">
+    <cfRule type="expression" dxfId="40" priority="38">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853">
-    <cfRule type="expression" dxfId="36" priority="37">
+    <cfRule type="expression" dxfId="39" priority="37">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854 E854">
-    <cfRule type="expression" dxfId="35" priority="36">
+    <cfRule type="expression" dxfId="38" priority="36">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854">
-    <cfRule type="expression" dxfId="34" priority="35">
+    <cfRule type="expression" dxfId="37" priority="35">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="33" priority="34">
+    <cfRule type="expression" dxfId="36" priority="34">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="32" priority="33">
+    <cfRule type="expression" dxfId="35" priority="33">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="31" priority="32">
+    <cfRule type="expression" dxfId="34" priority="32">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856">
-    <cfRule type="expression" dxfId="30" priority="31">
+    <cfRule type="expression" dxfId="33" priority="31">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K862 I862 G862 E862">
-    <cfRule type="expression" dxfId="29" priority="30">
+    <cfRule type="expression" dxfId="32" priority="30">
       <formula>$C862=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K862 I862 G862">
-    <cfRule type="expression" dxfId="28" priority="29">
+    <cfRule type="expression" dxfId="31" priority="29">
       <formula>$C862=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K863 I863 G863 E863">
-    <cfRule type="expression" dxfId="27" priority="28">
+    <cfRule type="expression" dxfId="30" priority="28">
       <formula>$C863=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="26" priority="27">
+    <cfRule type="expression" dxfId="29" priority="27">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="25" priority="26">
+    <cfRule type="expression" dxfId="28" priority="26">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="24" priority="25">
+    <cfRule type="expression" dxfId="27" priority="25">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K863:K865 I863:I865 G863:G865">
-    <cfRule type="expression" dxfId="23" priority="24">
+    <cfRule type="expression" dxfId="26" priority="24">
       <formula>$C863=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E871">
-    <cfRule type="expression" dxfId="22" priority="23">
+    <cfRule type="expression" dxfId="25" priority="23">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E872">
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="24" priority="22">
       <formula>$C872=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E873:E874">
-    <cfRule type="expression" dxfId="20" priority="21">
+    <cfRule type="expression" dxfId="23" priority="21">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E873:E874">
-    <cfRule type="expression" dxfId="19" priority="20">
+    <cfRule type="expression" dxfId="22" priority="20">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E873:E874">
-    <cfRule type="expression" dxfId="18" priority="19">
+    <cfRule type="expression" dxfId="21" priority="19">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G871:G874">
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="20" priority="18">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G871">
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="19" priority="17">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G872">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="18" priority="16">
       <formula>$C872=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G873:G874">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="17" priority="15">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G873:G874">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="16" priority="14">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G873:G874">
-    <cfRule type="expression" dxfId="12" priority="13">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I871:I874">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="14" priority="12">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I871">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I872">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="12" priority="10">
       <formula>$C872=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I873:I874">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I873:I874">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="10" priority="8">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I873:I874">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K871:K874">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K871">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K872">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$C872=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K873:K874">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K873:K874">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K873:K874">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>

--- a/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
+++ b/графики/план поставок ПОКОМ, Останкино филиалы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCA5AAB-E86F-4EA7-9535-D9D2001755A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F681916-1316-4CAB-808C-BB717FCD34AC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3543" uniqueCount="33">
   <si>
     <t>План поставок ПОКОМ</t>
   </si>
@@ -435,7 +435,63 @@
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Обычный 2 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="551">
+  <dxfs count="559">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4674,7 +4730,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMD856"/>
+  <dimension ref="A1:AMD867"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" customWidth="1"/>
@@ -29167,1599 +29223,1847 @@
       <c r="J856" s="11"/>
       <c r="K856" s="12"/>
     </row>
+    <row r="857" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A857" s="1">
+        <v>853</v>
+      </c>
+      <c r="B857" s="7" t="str">
+        <f t="shared" ref="B857:B867" si="143">IF(C857&lt;&gt;"",TEXT(C857,"ДДД"),"")</f>
+        <v>Пн</v>
+      </c>
+      <c r="C857" s="8">
+        <v>46055</v>
+      </c>
+      <c r="D857" s="9"/>
+      <c r="E857" s="10"/>
+      <c r="F857" s="11"/>
+      <c r="G857" s="12"/>
+      <c r="H857" s="11"/>
+      <c r="I857" s="12"/>
+      <c r="J857" s="11"/>
+      <c r="K857" s="12"/>
+    </row>
+    <row r="858" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A858" s="1">
+        <v>854</v>
+      </c>
+      <c r="B858" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Вт</v>
+      </c>
+      <c r="C858" s="8">
+        <v>46056</v>
+      </c>
+      <c r="D858" s="9">
+        <v>5100</v>
+      </c>
+      <c r="E858" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F858" s="11">
+        <v>11100</v>
+      </c>
+      <c r="G858" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H858" s="11">
+        <f>12500+8000+7400</f>
+        <v>27900</v>
+      </c>
+      <c r="I858" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J858" s="11">
+        <f>6500+9500+7700</f>
+        <v>23700</v>
+      </c>
+      <c r="K858" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="859" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A859" s="1">
+        <v>855</v>
+      </c>
+      <c r="B859" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Ср</v>
+      </c>
+      <c r="C859" s="8">
+        <v>46057</v>
+      </c>
+      <c r="D859" s="9"/>
+      <c r="E859" s="10"/>
+      <c r="F859" s="11"/>
+      <c r="G859" s="12"/>
+      <c r="H859" s="11"/>
+      <c r="I859" s="12"/>
+      <c r="J859" s="11"/>
+      <c r="K859" s="12"/>
+    </row>
+    <row r="860" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A860" s="1">
+        <v>856</v>
+      </c>
+      <c r="B860" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Чт</v>
+      </c>
+      <c r="C860" s="8">
+        <v>46058</v>
+      </c>
+      <c r="D860" s="9"/>
+      <c r="E860" s="10"/>
+      <c r="F860" s="11"/>
+      <c r="G860" s="12"/>
+      <c r="H860" s="11"/>
+      <c r="I860" s="12"/>
+      <c r="J860" s="11"/>
+      <c r="K860" s="12"/>
+    </row>
+    <row r="861" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A861" s="1">
+        <v>857</v>
+      </c>
+      <c r="B861" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Пт</v>
+      </c>
+      <c r="C861" s="8">
+        <v>46059</v>
+      </c>
+      <c r="D861" s="9"/>
+      <c r="E861" s="10"/>
+      <c r="F861" s="11"/>
+      <c r="G861" s="12"/>
+      <c r="H861" s="11"/>
+      <c r="I861" s="12"/>
+      <c r="J861" s="11"/>
+      <c r="K861" s="12"/>
+    </row>
+    <row r="862" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A862" s="1">
+        <v>858</v>
+      </c>
+      <c r="B862" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Сб</v>
+      </c>
+      <c r="C862" s="8">
+        <v>46060</v>
+      </c>
+      <c r="D862" s="9"/>
+      <c r="E862" s="10"/>
+      <c r="F862" s="11"/>
+      <c r="G862" s="12"/>
+      <c r="H862" s="11"/>
+      <c r="I862" s="12"/>
+      <c r="J862" s="11"/>
+      <c r="K862" s="12"/>
+    </row>
+    <row r="863" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A863" s="1">
+        <v>859</v>
+      </c>
+      <c r="B863" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Вс</v>
+      </c>
+      <c r="C863" s="8">
+        <v>46061</v>
+      </c>
+      <c r="D863" s="9"/>
+      <c r="E863" s="10"/>
+      <c r="F863" s="11"/>
+      <c r="G863" s="12"/>
+      <c r="H863" s="11"/>
+      <c r="I863" s="12"/>
+      <c r="J863" s="11"/>
+      <c r="K863" s="12"/>
+    </row>
+    <row r="864" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A864" s="1">
+        <v>860</v>
+      </c>
+      <c r="B864" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Пн</v>
+      </c>
+      <c r="C864" s="8">
+        <v>46062</v>
+      </c>
+      <c r="D864" s="9"/>
+      <c r="E864" s="10"/>
+      <c r="F864" s="11"/>
+      <c r="G864" s="12"/>
+      <c r="H864" s="11"/>
+      <c r="I864" s="12"/>
+      <c r="J864" s="11"/>
+      <c r="K864" s="12"/>
+    </row>
+    <row r="865" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A865" s="1">
+        <v>861</v>
+      </c>
+      <c r="B865" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Вт</v>
+      </c>
+      <c r="C865" s="8">
+        <v>46063</v>
+      </c>
+      <c r="D865" s="9"/>
+      <c r="E865" s="10"/>
+      <c r="F865" s="11"/>
+      <c r="G865" s="12"/>
+      <c r="H865" s="11"/>
+      <c r="I865" s="12"/>
+      <c r="J865" s="11"/>
+      <c r="K865" s="12"/>
+    </row>
+    <row r="866" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A866" s="1">
+        <v>862</v>
+      </c>
+      <c r="B866" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Ср</v>
+      </c>
+      <c r="C866" s="8">
+        <v>46064</v>
+      </c>
+      <c r="D866" s="9"/>
+      <c r="E866" s="10"/>
+      <c r="F866" s="11"/>
+      <c r="G866" s="12"/>
+      <c r="H866" s="11"/>
+      <c r="I866" s="12"/>
+      <c r="J866" s="11"/>
+      <c r="K866" s="12"/>
+    </row>
+    <row r="867" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A867" s="1">
+        <v>863</v>
+      </c>
+      <c r="B867" s="7" t="str">
+        <f t="shared" si="143"/>
+        <v>Чт</v>
+      </c>
+      <c r="C867" s="8">
+        <v>46065</v>
+      </c>
+      <c r="D867" s="9"/>
+      <c r="E867" s="10"/>
+      <c r="F867" s="11"/>
+      <c r="G867" s="12"/>
+      <c r="H867" s="11"/>
+      <c r="I867" s="12"/>
+      <c r="J867" s="11"/>
+      <c r="K867" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:E856">
-    <cfRule type="expression" dxfId="550" priority="737">
+  <conditionalFormatting sqref="B4:E867">
+    <cfRule type="expression" dxfId="558" priority="739">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:M683 B684:K856">
-    <cfRule type="expression" dxfId="549" priority="738">
+  <conditionalFormatting sqref="B4:M683 B684:K867">
+    <cfRule type="expression" dxfId="557" priority="740">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E678">
-    <cfRule type="expression" dxfId="548" priority="728">
+    <cfRule type="expression" dxfId="556" priority="730">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E693:E694">
-    <cfRule type="expression" dxfId="547" priority="715">
+    <cfRule type="expression" dxfId="555" priority="717">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E702">
-    <cfRule type="expression" dxfId="546" priority="702">
+    <cfRule type="expression" dxfId="554" priority="704">
       <formula>$C702=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E707">
-    <cfRule type="expression" dxfId="545" priority="698">
+    <cfRule type="expression" dxfId="553" priority="700">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709:E710">
-    <cfRule type="expression" dxfId="544" priority="690">
+    <cfRule type="expression" dxfId="552" priority="692">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E715">
-    <cfRule type="expression" dxfId="543" priority="686">
+    <cfRule type="expression" dxfId="551" priority="688">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E717:E718">
-    <cfRule type="expression" dxfId="542" priority="674">
+    <cfRule type="expression" dxfId="550" priority="676">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E723">
-    <cfRule type="expression" dxfId="541" priority="663">
+    <cfRule type="expression" dxfId="549" priority="665">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E725:E726">
-    <cfRule type="expression" dxfId="540" priority="640">
+    <cfRule type="expression" dxfId="548" priority="642">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E731">
-    <cfRule type="expression" dxfId="539" priority="628">
+    <cfRule type="expression" dxfId="547" priority="630">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E733:E734">
-    <cfRule type="expression" dxfId="538" priority="595">
+    <cfRule type="expression" dxfId="546" priority="597">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739">
-    <cfRule type="expression" dxfId="537" priority="563">
+    <cfRule type="expression" dxfId="545" priority="565">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E741:E742">
-    <cfRule type="expression" dxfId="536" priority="518">
+    <cfRule type="expression" dxfId="544" priority="520">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E747:E748">
-    <cfRule type="expression" dxfId="535" priority="455">
+    <cfRule type="expression" dxfId="543" priority="457">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E750">
-    <cfRule type="expression" dxfId="534" priority="439">
+    <cfRule type="expression" dxfId="542" priority="441">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="533" priority="413">
+    <cfRule type="expression" dxfId="541" priority="415">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E758">
-    <cfRule type="expression" dxfId="532" priority="365">
+    <cfRule type="expression" dxfId="540" priority="367">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E763">
-    <cfRule type="expression" dxfId="531" priority="338">
+    <cfRule type="expression" dxfId="539" priority="340">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E765:E766">
-    <cfRule type="expression" dxfId="530" priority="285">
+    <cfRule type="expression" dxfId="538" priority="287">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E771">
-    <cfRule type="expression" dxfId="529" priority="240">
+    <cfRule type="expression" dxfId="537" priority="242">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="528" priority="751">
+    <cfRule type="expression" dxfId="536" priority="753">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G661">
-    <cfRule type="expression" dxfId="527" priority="735">
+    <cfRule type="expression" dxfId="535" priority="737">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G670">
-    <cfRule type="expression" dxfId="526" priority="732">
+    <cfRule type="expression" dxfId="534" priority="734">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G678">
-    <cfRule type="expression" dxfId="525" priority="729">
+    <cfRule type="expression" dxfId="533" priority="731">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G686">
-    <cfRule type="expression" dxfId="524" priority="725">
+    <cfRule type="expression" dxfId="532" priority="727">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G691">
-    <cfRule type="expression" dxfId="523" priority="722">
+    <cfRule type="expression" dxfId="531" priority="724">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G693:G694">
-    <cfRule type="expression" dxfId="522" priority="714">
+    <cfRule type="expression" dxfId="530" priority="716">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G699">
-    <cfRule type="expression" dxfId="521" priority="711">
+    <cfRule type="expression" dxfId="529" priority="713">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701:G702">
-    <cfRule type="expression" dxfId="520" priority="703">
+    <cfRule type="expression" dxfId="528" priority="705">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G707">
-    <cfRule type="expression" dxfId="519" priority="699">
+    <cfRule type="expression" dxfId="527" priority="701">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G709:G710">
-    <cfRule type="expression" dxfId="518" priority="689">
+    <cfRule type="expression" dxfId="526" priority="691">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G715">
-    <cfRule type="expression" dxfId="517" priority="684">
+    <cfRule type="expression" dxfId="525" priority="686">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G717:G718">
-    <cfRule type="expression" dxfId="516" priority="671">
+    <cfRule type="expression" dxfId="524" priority="673">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G723">
-    <cfRule type="expression" dxfId="515" priority="660">
+    <cfRule type="expression" dxfId="523" priority="662">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G725:G726">
-    <cfRule type="expression" dxfId="514" priority="637">
+    <cfRule type="expression" dxfId="522" priority="639">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G731">
-    <cfRule type="expression" dxfId="513" priority="624">
+    <cfRule type="expression" dxfId="521" priority="626">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G733:G734">
-    <cfRule type="expression" dxfId="512" priority="589">
+    <cfRule type="expression" dxfId="520" priority="591">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739">
-    <cfRule type="expression" dxfId="511" priority="558">
+    <cfRule type="expression" dxfId="519" priority="560">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G741:G742">
-    <cfRule type="expression" dxfId="510" priority="512">
+    <cfRule type="expression" dxfId="518" priority="514">
       <formula>$C741=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G747">
-    <cfRule type="expression" dxfId="509" priority="475">
+    <cfRule type="expression" dxfId="517" priority="477">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="508" priority="432">
+    <cfRule type="expression" dxfId="516" priority="434">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="507" priority="407">
+    <cfRule type="expression" dxfId="515" priority="409">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G758">
-    <cfRule type="expression" dxfId="506" priority="358">
+    <cfRule type="expression" dxfId="514" priority="360">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G763">
-    <cfRule type="expression" dxfId="505" priority="331">
+    <cfRule type="expression" dxfId="513" priority="333">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G765:G766">
-    <cfRule type="expression" dxfId="504" priority="272">
+    <cfRule type="expression" dxfId="512" priority="274">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G771">
-    <cfRule type="expression" dxfId="503" priority="233">
+    <cfRule type="expression" dxfId="511" priority="235">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H128:I129">
-    <cfRule type="expression" dxfId="502" priority="754">
+    <cfRule type="expression" dxfId="510" priority="756">
       <formula>$C128=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="expression" dxfId="501" priority="752">
+    <cfRule type="expression" dxfId="509" priority="754">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I661">
-    <cfRule type="expression" dxfId="500" priority="734">
+    <cfRule type="expression" dxfId="508" priority="736">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670">
-    <cfRule type="expression" dxfId="499" priority="731">
+    <cfRule type="expression" dxfId="507" priority="733">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I678">
-    <cfRule type="expression" dxfId="498" priority="727">
+    <cfRule type="expression" dxfId="506" priority="729">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I686">
-    <cfRule type="expression" dxfId="497" priority="724">
+    <cfRule type="expression" dxfId="505" priority="726">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I691">
-    <cfRule type="expression" dxfId="496" priority="721">
+    <cfRule type="expression" dxfId="504" priority="723">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I693:I694">
-    <cfRule type="expression" dxfId="495" priority="713">
+    <cfRule type="expression" dxfId="503" priority="715">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I699">
-    <cfRule type="expression" dxfId="494" priority="710">
+    <cfRule type="expression" dxfId="502" priority="712">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I701:I702">
-    <cfRule type="expression" dxfId="493" priority="704">
+    <cfRule type="expression" dxfId="501" priority="706">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I707">
-    <cfRule type="expression" dxfId="492" priority="701">
+    <cfRule type="expression" dxfId="500" priority="703">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I709:I710">
-    <cfRule type="expression" dxfId="491" priority="688">
+    <cfRule type="expression" dxfId="499" priority="690">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I715">
-    <cfRule type="expression" dxfId="490" priority="682">
+    <cfRule type="expression" dxfId="498" priority="684">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I717:I718">
-    <cfRule type="expression" dxfId="489" priority="668">
+    <cfRule type="expression" dxfId="497" priority="670">
       <formula>$C717=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I723:I726">
-    <cfRule type="expression" dxfId="488" priority="634">
+    <cfRule type="expression" dxfId="496" priority="636">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I731:I734">
-    <cfRule type="expression" dxfId="487" priority="583">
+    <cfRule type="expression" dxfId="495" priority="585">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I736">
-    <cfRule type="expression" dxfId="486" priority="572">
+    <cfRule type="expression" dxfId="494" priority="574">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I742">
-    <cfRule type="expression" dxfId="485" priority="506">
+    <cfRule type="expression" dxfId="493" priority="508">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I744">
-    <cfRule type="expression" dxfId="484" priority="490">
+    <cfRule type="expression" dxfId="492" priority="492">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I747:I748">
-    <cfRule type="expression" dxfId="483" priority="460">
+    <cfRule type="expression" dxfId="491" priority="462">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I750">
-    <cfRule type="expression" dxfId="482" priority="425">
+    <cfRule type="expression" dxfId="490" priority="427">
       <formula>$C750=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755:I756">
-    <cfRule type="expression" dxfId="481" priority="389">
+    <cfRule type="expression" dxfId="489" priority="391">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I758">
-    <cfRule type="expression" dxfId="480" priority="351">
+    <cfRule type="expression" dxfId="488" priority="353">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I763">
-    <cfRule type="expression" dxfId="479" priority="324">
+    <cfRule type="expression" dxfId="487" priority="326">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I765:I766">
-    <cfRule type="expression" dxfId="478" priority="259">
+    <cfRule type="expression" dxfId="486" priority="261">
       <formula>$C765=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I771:I772">
-    <cfRule type="expression" dxfId="477" priority="226">
+    <cfRule type="expression" dxfId="485" priority="228">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="expression" dxfId="476" priority="753">
+    <cfRule type="expression" dxfId="484" priority="755">
       <formula>$C34=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K661">
-    <cfRule type="expression" dxfId="475" priority="733">
+    <cfRule type="expression" dxfId="483" priority="735">
       <formula>$C661=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K670">
-    <cfRule type="expression" dxfId="474" priority="730">
+    <cfRule type="expression" dxfId="482" priority="732">
       <formula>$C670=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K678">
-    <cfRule type="expression" dxfId="473" priority="726">
+    <cfRule type="expression" dxfId="481" priority="728">
       <formula>$C678=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K686">
-    <cfRule type="expression" dxfId="472" priority="723">
+    <cfRule type="expression" dxfId="480" priority="725">
       <formula>$C686=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K691">
-    <cfRule type="expression" dxfId="471" priority="720">
+    <cfRule type="expression" dxfId="479" priority="722">
       <formula>$C691=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K693:K694">
-    <cfRule type="expression" dxfId="470" priority="712">
+    <cfRule type="expression" dxfId="478" priority="714">
       <formula>$C693=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K699">
-    <cfRule type="expression" dxfId="469" priority="709">
+    <cfRule type="expression" dxfId="477" priority="711">
       <formula>$C699=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701:K702">
-    <cfRule type="expression" dxfId="468" priority="705">
+    <cfRule type="expression" dxfId="476" priority="707">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K707">
-    <cfRule type="expression" dxfId="467" priority="700">
+    <cfRule type="expression" dxfId="475" priority="702">
       <formula>$C707=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K709:K710">
-    <cfRule type="expression" dxfId="466" priority="687">
+    <cfRule type="expression" dxfId="474" priority="689">
       <formula>$C709=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K715:K718">
-    <cfRule type="expression" dxfId="465" priority="665">
+    <cfRule type="expression" dxfId="473" priority="667">
       <formula>$C715=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K723">
-    <cfRule type="expression" dxfId="464" priority="654">
+    <cfRule type="expression" dxfId="472" priority="656">
       <formula>$C723=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K725:K726">
-    <cfRule type="expression" dxfId="463" priority="631">
+    <cfRule type="expression" dxfId="471" priority="633">
       <formula>$C725=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K731">
-    <cfRule type="expression" dxfId="462" priority="616">
+    <cfRule type="expression" dxfId="470" priority="618">
       <formula>$C731=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K733:K734">
-    <cfRule type="expression" dxfId="461" priority="577">
+    <cfRule type="expression" dxfId="469" priority="579">
       <formula>$C733=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K736">
-    <cfRule type="expression" dxfId="460" priority="567">
+    <cfRule type="expression" dxfId="468" priority="569">
       <formula>$C736=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K742">
-    <cfRule type="expression" dxfId="459" priority="495">
+    <cfRule type="expression" dxfId="467" priority="497">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K744">
-    <cfRule type="expression" dxfId="458" priority="485">
+    <cfRule type="expression" dxfId="466" priority="487">
       <formula>$C744=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K747">
-    <cfRule type="expression" dxfId="457" priority="465">
+    <cfRule type="expression" dxfId="465" priority="467">
       <formula>$C747=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K749:K750">
-    <cfRule type="expression" dxfId="456" priority="418">
+    <cfRule type="expression" dxfId="464" priority="420">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755:K756">
-    <cfRule type="expression" dxfId="455" priority="383">
+    <cfRule type="expression" dxfId="463" priority="385">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K758">
-    <cfRule type="expression" dxfId="454" priority="344">
+    <cfRule type="expression" dxfId="462" priority="346">
       <formula>$C758=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K763:K764">
-    <cfRule type="expression" dxfId="453" priority="317">
+    <cfRule type="expression" dxfId="461" priority="319">
       <formula>$C763=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766">
-    <cfRule type="expression" dxfId="452" priority="246">
+    <cfRule type="expression" dxfId="460" priority="248">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K771">
-    <cfRule type="expression" dxfId="451" priority="219">
+    <cfRule type="expression" dxfId="459" priority="221">
       <formula>$C771=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="450" priority="218">
+    <cfRule type="expression" dxfId="458" priority="220">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="449" priority="217">
+    <cfRule type="expression" dxfId="457" priority="219">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="448" priority="216">
+    <cfRule type="expression" dxfId="456" priority="218">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="447" priority="215">
+    <cfRule type="expression" dxfId="455" priority="217">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="446" priority="214">
+    <cfRule type="expression" dxfId="454" priority="216">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="445" priority="213">
+    <cfRule type="expression" dxfId="453" priority="215">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="444" priority="212">
+    <cfRule type="expression" dxfId="452" priority="214">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E774">
-    <cfRule type="expression" dxfId="443" priority="211">
+    <cfRule type="expression" dxfId="451" priority="213">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G774">
-    <cfRule type="expression" dxfId="442" priority="210">
+    <cfRule type="expression" dxfId="450" priority="212">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I774">
-    <cfRule type="expression" dxfId="441" priority="209">
+    <cfRule type="expression" dxfId="449" priority="211">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K774">
-    <cfRule type="expression" dxfId="440" priority="208">
+    <cfRule type="expression" dxfId="448" priority="210">
       <formula>$C774=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="439" priority="207">
+    <cfRule type="expression" dxfId="447" priority="209">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I776">
-    <cfRule type="expression" dxfId="438" priority="206">
+    <cfRule type="expression" dxfId="446" priority="208">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="437" priority="205">
+    <cfRule type="expression" dxfId="445" priority="207">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K776">
-    <cfRule type="expression" dxfId="436" priority="204">
+    <cfRule type="expression" dxfId="444" priority="206">
       <formula>$C776=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E779">
-    <cfRule type="expression" dxfId="435" priority="203">
+    <cfRule type="expression" dxfId="443" priority="205">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="434" priority="202">
+    <cfRule type="expression" dxfId="442" priority="204">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G779">
-    <cfRule type="expression" dxfId="433" priority="201">
+    <cfRule type="expression" dxfId="441" priority="203">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="432" priority="200">
+    <cfRule type="expression" dxfId="440" priority="202">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I779">
-    <cfRule type="expression" dxfId="431" priority="199">
+    <cfRule type="expression" dxfId="439" priority="201">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="430" priority="198">
+    <cfRule type="expression" dxfId="438" priority="200">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K779">
-    <cfRule type="expression" dxfId="429" priority="197">
+    <cfRule type="expression" dxfId="437" priority="199">
       <formula>$C779=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="428" priority="196">
+    <cfRule type="expression" dxfId="436" priority="198">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I780">
-    <cfRule type="expression" dxfId="427" priority="195">
+    <cfRule type="expression" dxfId="435" priority="197">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="426" priority="194">
+    <cfRule type="expression" dxfId="434" priority="196">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K780">
-    <cfRule type="expression" dxfId="425" priority="193">
+    <cfRule type="expression" dxfId="433" priority="195">
       <formula>$C780=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="424" priority="192">
+    <cfRule type="expression" dxfId="432" priority="194">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I781:I782">
-    <cfRule type="expression" dxfId="423" priority="191">
+    <cfRule type="expression" dxfId="431" priority="193">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="422" priority="190">
+    <cfRule type="expression" dxfId="430" priority="192">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G781:G782">
-    <cfRule type="expression" dxfId="421" priority="189">
+    <cfRule type="expression" dxfId="429" priority="191">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="420" priority="188">
+    <cfRule type="expression" dxfId="428" priority="190">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E781:E782">
-    <cfRule type="expression" dxfId="419" priority="187">
+    <cfRule type="expression" dxfId="427" priority="189">
       <formula>$C781=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="418" priority="186">
+    <cfRule type="expression" dxfId="426" priority="188">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="417" priority="185">
+    <cfRule type="expression" dxfId="425" priority="187">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="416" priority="184">
+    <cfRule type="expression" dxfId="424" priority="186">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="415" priority="183">
+    <cfRule type="expression" dxfId="423" priority="185">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="414" priority="182">
+    <cfRule type="expression" dxfId="422" priority="184">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="413" priority="181">
+    <cfRule type="expression" dxfId="421" priority="183">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="412" priority="180">
+    <cfRule type="expression" dxfId="420" priority="182">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="411" priority="179">
+    <cfRule type="expression" dxfId="419" priority="181">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784">
-    <cfRule type="expression" dxfId="410" priority="178">
+    <cfRule type="expression" dxfId="418" priority="180">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="409" priority="177">
+    <cfRule type="expression" dxfId="417" priority="179">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784">
-    <cfRule type="expression" dxfId="408" priority="176">
+    <cfRule type="expression" dxfId="416" priority="178">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
-    <cfRule type="expression" dxfId="407" priority="175">
+    <cfRule type="expression" dxfId="415" priority="177">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E787">
-    <cfRule type="expression" dxfId="406" priority="174">
+    <cfRule type="expression" dxfId="414" priority="176">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="405" priority="173">
+    <cfRule type="expression" dxfId="413" priority="175">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="404" priority="172">
+    <cfRule type="expression" dxfId="412" priority="174">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G787">
-    <cfRule type="expression" dxfId="403" priority="171">
+    <cfRule type="expression" dxfId="411" priority="173">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="402" priority="170">
+    <cfRule type="expression" dxfId="410" priority="172">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="401" priority="169">
+    <cfRule type="expression" dxfId="409" priority="171">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I787:I788">
-    <cfRule type="expression" dxfId="400" priority="168">
+    <cfRule type="expression" dxfId="408" priority="170">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="399" priority="167">
+    <cfRule type="expression" dxfId="407" priority="169">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="398" priority="166">
+    <cfRule type="expression" dxfId="406" priority="168">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K787">
-    <cfRule type="expression" dxfId="397" priority="165">
+    <cfRule type="expression" dxfId="405" priority="167">
       <formula>$C787=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790">
-    <cfRule type="expression" dxfId="396" priority="162">
+    <cfRule type="expression" dxfId="404" priority="164">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="395" priority="164">
+    <cfRule type="expression" dxfId="403" priority="166">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K789:K790 I789:I790 G789:G790 E789:E790">
-    <cfRule type="expression" dxfId="394" priority="163">
+    <cfRule type="expression" dxfId="402" priority="165">
       <formula>$C789=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="393" priority="161">
+    <cfRule type="expression" dxfId="401" priority="163">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="392" priority="160">
+    <cfRule type="expression" dxfId="400" priority="162">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790 E790">
-    <cfRule type="expression" dxfId="391" priority="159">
+    <cfRule type="expression" dxfId="399" priority="161">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K790 I790 G790">
-    <cfRule type="expression" dxfId="390" priority="158">
+    <cfRule type="expression" dxfId="398" priority="160">
       <formula>$C790=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="389" priority="155">
+    <cfRule type="expression" dxfId="397" priority="157">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="388" priority="157">
+    <cfRule type="expression" dxfId="396" priority="159">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792">
-    <cfRule type="expression" dxfId="387" priority="156">
+    <cfRule type="expression" dxfId="395" priority="158">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="386" priority="152">
+    <cfRule type="expression" dxfId="394" priority="154">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="385" priority="154">
+    <cfRule type="expression" dxfId="393" priority="156">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792">
-    <cfRule type="expression" dxfId="384" priority="153">
+    <cfRule type="expression" dxfId="392" priority="155">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
-    <cfRule type="expression" dxfId="383" priority="151">
+    <cfRule type="expression" dxfId="391" priority="153">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E795">
-    <cfRule type="expression" dxfId="382" priority="150">
+    <cfRule type="expression" dxfId="390" priority="152">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="381" priority="149">
+    <cfRule type="expression" dxfId="389" priority="151">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="380" priority="148">
+    <cfRule type="expression" dxfId="388" priority="150">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G795">
-    <cfRule type="expression" dxfId="379" priority="147">
+    <cfRule type="expression" dxfId="387" priority="149">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="378" priority="146">
+    <cfRule type="expression" dxfId="386" priority="148">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="377" priority="145">
+    <cfRule type="expression" dxfId="385" priority="147">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I795:I796">
-    <cfRule type="expression" dxfId="376" priority="144">
+    <cfRule type="expression" dxfId="384" priority="146">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="375" priority="143">
+    <cfRule type="expression" dxfId="383" priority="145">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="374" priority="142">
+    <cfRule type="expression" dxfId="382" priority="144">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K795">
-    <cfRule type="expression" dxfId="373" priority="141">
+    <cfRule type="expression" dxfId="381" priority="143">
       <formula>$C795=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="372" priority="140">
+    <cfRule type="expression" dxfId="380" priority="142">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="371" priority="139">
+    <cfRule type="expression" dxfId="379" priority="141">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E797:E798 G797:G798 K797:K798">
-    <cfRule type="expression" dxfId="370" priority="138">
+    <cfRule type="expression" dxfId="378" priority="140">
       <formula>$C797=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="369" priority="137">
+    <cfRule type="expression" dxfId="377" priority="139">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="368" priority="136">
+    <cfRule type="expression" dxfId="376" priority="138">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="367" priority="135">
+    <cfRule type="expression" dxfId="375" priority="137">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="366" priority="134">
+    <cfRule type="expression" dxfId="374" priority="136">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798 E798">
-    <cfRule type="expression" dxfId="365" priority="133">
+    <cfRule type="expression" dxfId="373" priority="135">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K798 I798 G798">
-    <cfRule type="expression" dxfId="364" priority="132">
+    <cfRule type="expression" dxfId="372" priority="134">
       <formula>$C798=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="363" priority="131">
+    <cfRule type="expression" dxfId="371" priority="133">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="362" priority="130">
+    <cfRule type="expression" dxfId="370" priority="132">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 E803 K803:K805">
-    <cfRule type="expression" dxfId="361" priority="129">
+    <cfRule type="expression" dxfId="369" priority="131">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803 G803 K803:K805">
-    <cfRule type="expression" dxfId="360" priority="128">
+    <cfRule type="expression" dxfId="368" priority="130">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="359" priority="127">
+    <cfRule type="expression" dxfId="367" priority="129">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="358" priority="126">
+    <cfRule type="expression" dxfId="366" priority="128">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E805:E806">
-    <cfRule type="expression" dxfId="357" priority="125">
+    <cfRule type="expression" dxfId="365" priority="127">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="356" priority="124">
+    <cfRule type="expression" dxfId="364" priority="126">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="355" priority="123">
+    <cfRule type="expression" dxfId="363" priority="125">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="354" priority="122">
+    <cfRule type="expression" dxfId="362" priority="124">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="353" priority="121">
+    <cfRule type="expression" dxfId="361" priority="123">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E806">
-    <cfRule type="expression" dxfId="352" priority="120">
+    <cfRule type="expression" dxfId="360" priority="122">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="351" priority="119">
+    <cfRule type="expression" dxfId="359" priority="121">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="350" priority="118">
+    <cfRule type="expression" dxfId="358" priority="120">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="349" priority="117">
+    <cfRule type="expression" dxfId="357" priority="119">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G805:G806">
-    <cfRule type="expression" dxfId="348" priority="116">
+    <cfRule type="expression" dxfId="356" priority="118">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="347" priority="115">
+    <cfRule type="expression" dxfId="355" priority="117">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="346" priority="114">
+    <cfRule type="expression" dxfId="354" priority="116">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="345" priority="113">
+    <cfRule type="expression" dxfId="353" priority="115">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="344" priority="112">
+    <cfRule type="expression" dxfId="352" priority="114">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G806">
-    <cfRule type="expression" dxfId="343" priority="111">
+    <cfRule type="expression" dxfId="351" priority="113">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="342" priority="110">
+    <cfRule type="expression" dxfId="350" priority="112">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="341" priority="109">
+    <cfRule type="expression" dxfId="349" priority="111">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="340" priority="108">
+    <cfRule type="expression" dxfId="348" priority="110">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I805:I806">
-    <cfRule type="expression" dxfId="339" priority="107">
+    <cfRule type="expression" dxfId="347" priority="109">
       <formula>$C805=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="338" priority="106">
+    <cfRule type="expression" dxfId="346" priority="108">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="337" priority="105">
+    <cfRule type="expression" dxfId="345" priority="107">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="336" priority="104">
+    <cfRule type="expression" dxfId="344" priority="106">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="335" priority="103">
+    <cfRule type="expression" dxfId="343" priority="105">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I806">
-    <cfRule type="expression" dxfId="334" priority="102">
+    <cfRule type="expression" dxfId="342" priority="104">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="333" priority="101">
+    <cfRule type="expression" dxfId="341" priority="103">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="332" priority="100">
+    <cfRule type="expression" dxfId="340" priority="102">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="331" priority="99">
+    <cfRule type="expression" dxfId="339" priority="101">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="330" priority="98">
+    <cfRule type="expression" dxfId="338" priority="100">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="329" priority="97">
+    <cfRule type="expression" dxfId="337" priority="99">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="328" priority="96">
+    <cfRule type="expression" dxfId="336" priority="98">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="327" priority="95">
+    <cfRule type="expression" dxfId="335" priority="97">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="326" priority="94">
+    <cfRule type="expression" dxfId="334" priority="96">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K806">
-    <cfRule type="expression" dxfId="325" priority="93">
+    <cfRule type="expression" dxfId="333" priority="95">
       <formula>$C806=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="324" priority="92">
+    <cfRule type="expression" dxfId="332" priority="94">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="323" priority="91">
+    <cfRule type="expression" dxfId="331" priority="93">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="322" priority="90">
+    <cfRule type="expression" dxfId="330" priority="92">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I808">
-    <cfRule type="expression" dxfId="321" priority="89">
+    <cfRule type="expression" dxfId="329" priority="91">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="320" priority="88">
+    <cfRule type="expression" dxfId="328" priority="90">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="319" priority="87">
+    <cfRule type="expression" dxfId="327" priority="89">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="318" priority="86">
+    <cfRule type="expression" dxfId="326" priority="88">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K808">
-    <cfRule type="expression" dxfId="317" priority="85">
+    <cfRule type="expression" dxfId="325" priority="87">
       <formula>$C808=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="316" priority="84">
+    <cfRule type="expression" dxfId="324" priority="86">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="315" priority="83">
+    <cfRule type="expression" dxfId="323" priority="85">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811">
-    <cfRule type="expression" dxfId="314" priority="82">
+    <cfRule type="expression" dxfId="322" priority="84">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="313" priority="81">
+    <cfRule type="expression" dxfId="321" priority="83">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="312" priority="80">
+    <cfRule type="expression" dxfId="320" priority="82">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="311" priority="79">
+    <cfRule type="expression" dxfId="319" priority="81">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811">
-    <cfRule type="expression" dxfId="310" priority="78">
+    <cfRule type="expression" dxfId="318" priority="80">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="309" priority="77">
+    <cfRule type="expression" dxfId="317" priority="79">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="308" priority="76">
+    <cfRule type="expression" dxfId="316" priority="78">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="307" priority="75">
+    <cfRule type="expression" dxfId="315" priority="77">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="306" priority="74">
+    <cfRule type="expression" dxfId="314" priority="76">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="305" priority="73">
+    <cfRule type="expression" dxfId="313" priority="75">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="304" priority="72">
+    <cfRule type="expression" dxfId="312" priority="74">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="303" priority="71">
+    <cfRule type="expression" dxfId="311" priority="73">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811">
-    <cfRule type="expression" dxfId="302" priority="70">
+    <cfRule type="expression" dxfId="310" priority="72">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="301" priority="69">
+    <cfRule type="expression" dxfId="309" priority="71">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="300" priority="68">
+    <cfRule type="expression" dxfId="308" priority="70">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E813:E814">
-    <cfRule type="expression" dxfId="299" priority="67">
+    <cfRule type="expression" dxfId="307" priority="69">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="298" priority="66">
+    <cfRule type="expression" dxfId="306" priority="68">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="297" priority="65">
+    <cfRule type="expression" dxfId="305" priority="67">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="296" priority="64">
+    <cfRule type="expression" dxfId="304" priority="66">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="295" priority="63">
+    <cfRule type="expression" dxfId="303" priority="65">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E814">
-    <cfRule type="expression" dxfId="294" priority="62">
+    <cfRule type="expression" dxfId="302" priority="64">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="293" priority="61">
+    <cfRule type="expression" dxfId="301" priority="63">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="292" priority="60">
+    <cfRule type="expression" dxfId="300" priority="62">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="291" priority="59">
+    <cfRule type="expression" dxfId="299" priority="61">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G813:G814">
-    <cfRule type="expression" dxfId="290" priority="58">
+    <cfRule type="expression" dxfId="298" priority="60">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="289" priority="57">
+    <cfRule type="expression" dxfId="297" priority="59">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="288" priority="56">
+    <cfRule type="expression" dxfId="296" priority="58">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="287" priority="55">
+    <cfRule type="expression" dxfId="295" priority="57">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="286" priority="54">
+    <cfRule type="expression" dxfId="294" priority="56">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G814">
-    <cfRule type="expression" dxfId="285" priority="53">
+    <cfRule type="expression" dxfId="293" priority="55">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="284" priority="52">
+    <cfRule type="expression" dxfId="292" priority="54">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="283" priority="51">
+    <cfRule type="expression" dxfId="291" priority="53">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="282" priority="50">
+    <cfRule type="expression" dxfId="290" priority="52">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I813:I814">
-    <cfRule type="expression" dxfId="281" priority="49">
+    <cfRule type="expression" dxfId="289" priority="51">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="280" priority="48">
+    <cfRule type="expression" dxfId="288" priority="50">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="279" priority="47">
+    <cfRule type="expression" dxfId="287" priority="49">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="278" priority="46">
+    <cfRule type="expression" dxfId="286" priority="48">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="277" priority="45">
+    <cfRule type="expression" dxfId="285" priority="47">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I814">
-    <cfRule type="expression" dxfId="276" priority="44">
+    <cfRule type="expression" dxfId="284" priority="46">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="275" priority="43">
+    <cfRule type="expression" dxfId="283" priority="45">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="274" priority="42">
+    <cfRule type="expression" dxfId="282" priority="44">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="273" priority="41">
+    <cfRule type="expression" dxfId="281" priority="43">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K813:K814">
-    <cfRule type="expression" dxfId="272" priority="40">
+    <cfRule type="expression" dxfId="280" priority="42">
       <formula>$C813=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="271" priority="39">
+    <cfRule type="expression" dxfId="279" priority="41">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="270" priority="38">
+    <cfRule type="expression" dxfId="278" priority="40">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="269" priority="37">
+    <cfRule type="expression" dxfId="277" priority="39">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="268" priority="36">
+    <cfRule type="expression" dxfId="276" priority="38">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K814">
-    <cfRule type="expression" dxfId="267" priority="35">
+    <cfRule type="expression" dxfId="275" priority="37">
       <formula>$C814=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="266" priority="34">
+    <cfRule type="expression" dxfId="274" priority="36">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="265" priority="33">
+    <cfRule type="expression" dxfId="273" priority="35">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 E826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="264" priority="32">
+    <cfRule type="expression" dxfId="272" priority="34">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G826 I826:I829 K826:K829">
-    <cfRule type="expression" dxfId="263" priority="31">
+    <cfRule type="expression" dxfId="271" priority="33">
       <formula>$C826=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K829 I829 G829">
-    <cfRule type="expression" dxfId="262" priority="30">
+    <cfRule type="expression" dxfId="270" priority="32">
       <formula>$C829=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I834 G834 K834:K835">
-    <cfRule type="expression" dxfId="261" priority="29">
+    <cfRule type="expression" dxfId="269" priority="31">
       <formula>$C834=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836 G836">
-    <cfRule type="expression" dxfId="260" priority="28">
+    <cfRule type="expression" dxfId="268" priority="30">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837 I837 G837">
-    <cfRule type="expression" dxfId="259" priority="27">
+    <cfRule type="expression" dxfId="267" priority="29">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K839 I839">
-    <cfRule type="expression" dxfId="258" priority="26">
+    <cfRule type="expression" dxfId="266" priority="28">
       <formula>$C839=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K842 I842 G842 E842">
-    <cfRule type="expression" dxfId="257" priority="25">
+    <cfRule type="expression" dxfId="265" priority="27">
       <formula>$C842=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845 I845 G845 E845">
-    <cfRule type="expression" dxfId="256" priority="24">
+    <cfRule type="expression" dxfId="264" priority="26">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845 I845 G845">
-    <cfRule type="expression" dxfId="255" priority="23">
+    <cfRule type="expression" dxfId="263" priority="25">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K844 I844 G844 E844">
-    <cfRule type="expression" dxfId="254" priority="22">
+    <cfRule type="expression" dxfId="262" priority="24">
       <formula>$C844=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K844 I844 G844">
-    <cfRule type="expression" dxfId="253" priority="21">
+    <cfRule type="expression" dxfId="261" priority="23">
       <formula>$C844=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K843 I843">
-    <cfRule type="expression" dxfId="252" priority="20">
+    <cfRule type="expression" dxfId="260" priority="22">
       <formula>$C843=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K843 I843">
-    <cfRule type="expression" dxfId="251" priority="19">
+    <cfRule type="expression" dxfId="259" priority="21">
       <formula>$C843=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K844 I844 G844 E844">
-    <cfRule type="expression" dxfId="250" priority="18">
+    <cfRule type="expression" dxfId="258" priority="20">
       <formula>$C844=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K844 I844 G844">
-    <cfRule type="expression" dxfId="249" priority="17">
+    <cfRule type="expression" dxfId="257" priority="19">
       <formula>$C844=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845 I845 G845 E845">
-    <cfRule type="expression" dxfId="248" priority="16">
+    <cfRule type="expression" dxfId="256" priority="18">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I850 G850 E850 K850:K851">
-    <cfRule type="expression" dxfId="247" priority="15">
+    <cfRule type="expression" dxfId="255" priority="17">
       <formula>$C850=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I850 G850 K850:K851">
-    <cfRule type="expression" dxfId="246" priority="14">
+    <cfRule type="expression" dxfId="254" priority="16">
       <formula>$C850=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E851">
-    <cfRule type="expression" dxfId="245" priority="13">
+    <cfRule type="expression" dxfId="253" priority="15">
       <formula>$C851=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G851">
-    <cfRule type="expression" dxfId="244" priority="12">
+    <cfRule type="expression" dxfId="252" priority="14">
       <formula>$C851=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G851">
-    <cfRule type="expression" dxfId="243" priority="11">
+    <cfRule type="expression" dxfId="251" priority="13">
       <formula>$C851=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E852:E853">
-    <cfRule type="expression" dxfId="242" priority="10">
+    <cfRule type="expression" dxfId="250" priority="12">
       <formula>$C852=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G852:G853">
-    <cfRule type="expression" dxfId="241" priority="9">
+    <cfRule type="expression" dxfId="249" priority="11">
       <formula>$C852=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G852:G853">
-    <cfRule type="expression" dxfId="240" priority="8">
+    <cfRule type="expression" dxfId="248" priority="10">
       <formula>$C852=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I852:I853">
-    <cfRule type="expression" dxfId="239" priority="7">
+    <cfRule type="expression" dxfId="247" priority="9">
       <formula>$C852=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I852:I853">
-    <cfRule type="expression" dxfId="238" priority="6">
+    <cfRule type="expression" dxfId="246" priority="8">
       <formula>$C852=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K852:K853">
-    <cfRule type="expression" dxfId="237" priority="5">
+    <cfRule type="expression" dxfId="245" priority="7">
       <formula>$C852=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K852:K853">
-    <cfRule type="expression" dxfId="236" priority="4">
+    <cfRule type="expression" dxfId="244" priority="6">
       <formula>$C852=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853 E853">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="243" priority="5">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853 E853">
+    <cfRule type="expression" dxfId="242" priority="4">
+      <formula>$C853=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K853 I853 G853">
+    <cfRule type="expression" dxfId="241" priority="3">
+      <formula>$C853=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K858 I858 G858 E858">
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$C853=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K853 I853 G853">
+      <formula>$C858=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K858 I858 G858">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$C853=TODAY()</formula>
+      <formula>$C858=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -30769,7 +31073,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O879"/>
+  <dimension ref="A1:O890"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
@@ -52848,1175 +53152,1478 @@
       <c r="J879" s="11"/>
       <c r="K879" s="12"/>
     </row>
+    <row r="880" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A880" s="1">
+        <v>879</v>
+      </c>
+      <c r="B880" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C880" s="8">
+        <v>46057</v>
+      </c>
+      <c r="D880" s="9">
+        <v>4000</v>
+      </c>
+      <c r="E880" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F880" s="11">
+        <v>2600</v>
+      </c>
+      <c r="G880" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H880" s="11">
+        <v>2500</v>
+      </c>
+      <c r="I880" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J880" s="11">
+        <v>5300</v>
+      </c>
+      <c r="K880" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="881" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A881" s="1">
+        <v>880</v>
+      </c>
+      <c r="B881" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C881" s="8">
+        <v>46058</v>
+      </c>
+      <c r="D881" s="9">
+        <v>4300</v>
+      </c>
+      <c r="E881" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F881" s="11">
+        <v>2900</v>
+      </c>
+      <c r="G881" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H881" s="11">
+        <v>2800</v>
+      </c>
+      <c r="I881" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J881" s="11">
+        <v>5800</v>
+      </c>
+      <c r="K881" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="882" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A882" s="1">
+        <v>881</v>
+      </c>
+      <c r="B882" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C882" s="8">
+        <v>46058</v>
+      </c>
+      <c r="D882" s="9">
+        <v>1100</v>
+      </c>
+      <c r="E882" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F882" s="11">
+        <v>900</v>
+      </c>
+      <c r="G882" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H882" s="11">
+        <v>400</v>
+      </c>
+      <c r="I882" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J882" s="11">
+        <v>600</v>
+      </c>
+      <c r="K882" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="883" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A883" s="1">
+        <v>882</v>
+      </c>
+      <c r="B883" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C883" s="8">
+        <v>46058</v>
+      </c>
+      <c r="D883" s="9">
+        <v>200</v>
+      </c>
+      <c r="E883" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F883" s="11">
+        <v>40</v>
+      </c>
+      <c r="G883" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H883" s="11">
+        <v>20</v>
+      </c>
+      <c r="I883" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J883" s="11">
+        <v>100</v>
+      </c>
+      <c r="K883" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="884" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A884" s="1">
+        <v>883</v>
+      </c>
+      <c r="B884" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C884" s="8">
+        <v>46059</v>
+      </c>
+      <c r="D884" s="9"/>
+      <c r="E884" s="10"/>
+      <c r="F884" s="11"/>
+      <c r="G884" s="12"/>
+      <c r="H884" s="11"/>
+      <c r="I884" s="12"/>
+      <c r="J884" s="11"/>
+      <c r="K884" s="12"/>
+    </row>
+    <row r="885" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A885" s="1">
+        <v>884</v>
+      </c>
+      <c r="B885" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C885" s="8">
+        <v>46060</v>
+      </c>
+      <c r="D885" s="9"/>
+      <c r="E885" s="10"/>
+      <c r="F885" s="11"/>
+      <c r="G885" s="12"/>
+      <c r="H885" s="11"/>
+      <c r="I885" s="12"/>
+      <c r="J885" s="11"/>
+      <c r="K885" s="12"/>
+    </row>
+    <row r="886" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A886" s="1">
+        <v>885</v>
+      </c>
+      <c r="B886" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C886" s="8">
+        <v>46061</v>
+      </c>
+      <c r="D886" s="9"/>
+      <c r="E886" s="10"/>
+      <c r="F886" s="11"/>
+      <c r="G886" s="12"/>
+      <c r="H886" s="11"/>
+      <c r="I886" s="12"/>
+      <c r="J886" s="11"/>
+      <c r="K886" s="12"/>
+    </row>
+    <row r="887" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A887" s="1">
+        <v>886</v>
+      </c>
+      <c r="B887" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C887" s="8">
+        <v>46062</v>
+      </c>
+      <c r="D887" s="9"/>
+      <c r="E887" s="10"/>
+      <c r="F887" s="11"/>
+      <c r="G887" s="12"/>
+      <c r="H887" s="11"/>
+      <c r="I887" s="12"/>
+      <c r="J887" s="11"/>
+      <c r="K887" s="12"/>
+    </row>
+    <row r="888" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A888" s="1">
+        <v>887</v>
+      </c>
+      <c r="B888" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C888" s="8">
+        <v>46063</v>
+      </c>
+      <c r="D888" s="9"/>
+      <c r="E888" s="10"/>
+      <c r="F888" s="11"/>
+      <c r="G888" s="12"/>
+      <c r="H888" s="11"/>
+      <c r="I888" s="12"/>
+      <c r="J888" s="11"/>
+      <c r="K888" s="12"/>
+    </row>
+    <row r="889" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A889" s="1">
+        <v>888</v>
+      </c>
+      <c r="B889" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C889" s="8">
+        <v>46064</v>
+      </c>
+      <c r="D889" s="9"/>
+      <c r="E889" s="10"/>
+      <c r="F889" s="11"/>
+      <c r="G889" s="12"/>
+      <c r="H889" s="11"/>
+      <c r="I889" s="12"/>
+      <c r="J889" s="11"/>
+      <c r="K889" s="12"/>
+    </row>
+    <row r="890" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A890" s="1">
+        <v>889</v>
+      </c>
+      <c r="B890" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C890" s="8">
+        <v>46065</v>
+      </c>
+      <c r="D890" s="9"/>
+      <c r="E890" s="10"/>
+      <c r="F890" s="11"/>
+      <c r="G890" s="12"/>
+      <c r="H890" s="11"/>
+      <c r="I890" s="12"/>
+      <c r="J890" s="11"/>
+      <c r="K890" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="B4:E879">
-    <cfRule type="expression" dxfId="235" priority="411">
+  <conditionalFormatting sqref="B4:E890">
+    <cfRule type="expression" dxfId="240" priority="417">
       <formula>$C4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K879">
-    <cfRule type="expression" dxfId="234" priority="412">
+  <conditionalFormatting sqref="C4:G17 J4:M43 B4:B373 C18:C373 D48:K739 B374:C739 B740:K890">
+    <cfRule type="expression" dxfId="239" priority="418">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G47 J44:K47">
-    <cfRule type="expression" dxfId="233" priority="421">
+    <cfRule type="expression" dxfId="238" priority="427">
       <formula>$B18=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E692">
-    <cfRule type="expression" dxfId="232" priority="405">
+    <cfRule type="expression" dxfId="237" priority="411">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E694">
-    <cfRule type="expression" dxfId="231" priority="403">
+    <cfRule type="expression" dxfId="236" priority="409">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E701">
-    <cfRule type="expression" dxfId="230" priority="393">
+    <cfRule type="expression" dxfId="235" priority="399">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E703">
-    <cfRule type="expression" dxfId="229" priority="388">
+    <cfRule type="expression" dxfId="234" priority="394">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E710">
-    <cfRule type="expression" dxfId="228" priority="378">
+    <cfRule type="expression" dxfId="233" priority="384">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E712:E714">
-    <cfRule type="expression" dxfId="227" priority="373">
+    <cfRule type="expression" dxfId="232" priority="379">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E719">
-    <cfRule type="expression" dxfId="226" priority="363">
+    <cfRule type="expression" dxfId="231" priority="369">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E721:E723">
-    <cfRule type="expression" dxfId="225" priority="358">
+    <cfRule type="expression" dxfId="230" priority="364">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E728">
-    <cfRule type="expression" dxfId="224" priority="351">
+    <cfRule type="expression" dxfId="229" priority="357">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E730:E732">
-    <cfRule type="expression" dxfId="223" priority="338">
+    <cfRule type="expression" dxfId="228" priority="344">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E737">
-    <cfRule type="expression" dxfId="222" priority="331">
+    <cfRule type="expression" dxfId="227" priority="337">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E739:E741">
-    <cfRule type="expression" dxfId="221" priority="318">
+    <cfRule type="expression" dxfId="226" priority="324">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E746">
-    <cfRule type="expression" dxfId="220" priority="308">
+    <cfRule type="expression" dxfId="225" priority="314">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E748:E750">
-    <cfRule type="expression" dxfId="219" priority="286">
+    <cfRule type="expression" dxfId="224" priority="292">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E755">
-    <cfRule type="expression" dxfId="218" priority="279">
+    <cfRule type="expression" dxfId="223" priority="285">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E757:E759">
-    <cfRule type="expression" dxfId="217" priority="252">
+    <cfRule type="expression" dxfId="222" priority="258">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E764">
-    <cfRule type="expression" dxfId="216" priority="248">
+    <cfRule type="expression" dxfId="221" priority="254">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E766:E768">
-    <cfRule type="expression" dxfId="215" priority="223">
+    <cfRule type="expression" dxfId="220" priority="229">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E773">
-    <cfRule type="expression" dxfId="214" priority="213">
+    <cfRule type="expression" dxfId="219" priority="219">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E775:E777">
-    <cfRule type="expression" dxfId="213" priority="201">
+    <cfRule type="expression" dxfId="218" priority="207">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E782">
-    <cfRule type="expression" dxfId="212" priority="179">
+    <cfRule type="expression" dxfId="217" priority="185">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E784:E786">
-    <cfRule type="expression" dxfId="211" priority="161">
+    <cfRule type="expression" dxfId="216" priority="167">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="210" priority="424">
+    <cfRule type="expression" dxfId="215" priority="430">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70">
-    <cfRule type="expression" dxfId="209" priority="433">
+    <cfRule type="expression" dxfId="214" priority="439">
       <formula>$C70=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G685">
-    <cfRule type="expression" dxfId="208" priority="409">
+    <cfRule type="expression" dxfId="213" priority="415">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G692">
-    <cfRule type="expression" dxfId="207" priority="406">
+    <cfRule type="expression" dxfId="212" priority="412">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G695">
-    <cfRule type="expression" dxfId="206" priority="396">
+    <cfRule type="expression" dxfId="211" priority="402">
       <formula>$C695=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G701">
-    <cfRule type="expression" dxfId="205" priority="391">
+    <cfRule type="expression" dxfId="210" priority="397">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G704:G705">
-    <cfRule type="expression" dxfId="204" priority="380">
+    <cfRule type="expression" dxfId="209" priority="386">
       <formula>$C704=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G710">
-    <cfRule type="expression" dxfId="203" priority="376">
+    <cfRule type="expression" dxfId="208" priority="382">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G712:G714">
-    <cfRule type="expression" dxfId="202" priority="366">
+    <cfRule type="expression" dxfId="207" priority="372">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G719">
-    <cfRule type="expression" dxfId="201" priority="361">
+    <cfRule type="expression" dxfId="206" priority="367">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G721:G723">
-    <cfRule type="expression" dxfId="200" priority="356">
+    <cfRule type="expression" dxfId="205" priority="362">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G728">
-    <cfRule type="expression" dxfId="199" priority="349">
+    <cfRule type="expression" dxfId="204" priority="355">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G730:G732">
-    <cfRule type="expression" dxfId="198" priority="336">
+    <cfRule type="expression" dxfId="203" priority="342">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G737">
-    <cfRule type="expression" dxfId="197" priority="329">
+    <cfRule type="expression" dxfId="202" priority="335">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G739:G741">
-    <cfRule type="expression" dxfId="196" priority="315">
+    <cfRule type="expression" dxfId="201" priority="321">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G746">
-    <cfRule type="expression" dxfId="195" priority="306">
+    <cfRule type="expression" dxfId="200" priority="312">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G749:G750">
-    <cfRule type="expression" dxfId="194" priority="283">
+    <cfRule type="expression" dxfId="199" priority="289">
       <formula>$C749=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G755">
-    <cfRule type="expression" dxfId="193" priority="277">
+    <cfRule type="expression" dxfId="198" priority="283">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G757:G759">
-    <cfRule type="expression" dxfId="192" priority="249">
+    <cfRule type="expression" dxfId="197" priority="255">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G764">
-    <cfRule type="expression" dxfId="191" priority="246">
+    <cfRule type="expression" dxfId="196" priority="252">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G766:G768">
-    <cfRule type="expression" dxfId="190" priority="219">
+    <cfRule type="expression" dxfId="195" priority="225">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G773">
-    <cfRule type="expression" dxfId="189" priority="211">
+    <cfRule type="expression" dxfId="194" priority="217">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G775:G777">
-    <cfRule type="expression" dxfId="188" priority="194">
+    <cfRule type="expression" dxfId="193" priority="200">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G782">
-    <cfRule type="expression" dxfId="187" priority="177">
+    <cfRule type="expression" dxfId="192" priority="183">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G784:G786">
-    <cfRule type="expression" dxfId="186" priority="155">
+    <cfRule type="expression" dxfId="191" priority="161">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:I47">
-    <cfRule type="expression" dxfId="185" priority="446">
+    <cfRule type="expression" dxfId="190" priority="452">
       <formula>$B4=TEXT(TODAY(),"ДДД")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="expression" dxfId="184" priority="450">
+    <cfRule type="expression" dxfId="189" priority="456">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I685">
-    <cfRule type="expression" dxfId="183" priority="408">
+    <cfRule type="expression" dxfId="188" priority="414">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I694:I695">
-    <cfRule type="expression" dxfId="182" priority="395">
+    <cfRule type="expression" dxfId="187" priority="401">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I703:I704">
-    <cfRule type="expression" dxfId="181" priority="382">
+    <cfRule type="expression" dxfId="186" priority="388">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I712:I714">
-    <cfRule type="expression" dxfId="180" priority="365">
+    <cfRule type="expression" dxfId="185" priority="371">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I721:I723">
-    <cfRule type="expression" dxfId="179" priority="354">
+    <cfRule type="expression" dxfId="184" priority="360">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I730:I732">
-    <cfRule type="expression" dxfId="178" priority="332">
+    <cfRule type="expression" dxfId="183" priority="338">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I739:I741">
-    <cfRule type="expression" dxfId="177" priority="312">
+    <cfRule type="expression" dxfId="182" priority="318">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I748:I749">
-    <cfRule type="expression" dxfId="176" priority="291">
+    <cfRule type="expression" dxfId="181" priority="297">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I755">
-    <cfRule type="expression" dxfId="175" priority="275">
+    <cfRule type="expression" dxfId="180" priority="281">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I757:I758">
-    <cfRule type="expression" dxfId="174" priority="258">
+    <cfRule type="expression" dxfId="179" priority="264">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I766:I768">
-    <cfRule type="expression" dxfId="173" priority="215">
+    <cfRule type="expression" dxfId="178" priority="221">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I773">
-    <cfRule type="expression" dxfId="172" priority="209">
+    <cfRule type="expression" dxfId="177" priority="215">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I775:I777">
-    <cfRule type="expression" dxfId="171" priority="187">
+    <cfRule type="expression" dxfId="176" priority="193">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I782">
-    <cfRule type="expression" dxfId="170" priority="175">
+    <cfRule type="expression" dxfId="175" priority="181">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I784:I786">
-    <cfRule type="expression" dxfId="169" priority="149">
+    <cfRule type="expression" dxfId="174" priority="155">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="168" priority="425">
+    <cfRule type="expression" dxfId="173" priority="431">
       <formula>$C13=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K685">
-    <cfRule type="expression" dxfId="167" priority="407">
+    <cfRule type="expression" dxfId="172" priority="413">
       <formula>$C685=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K692">
-    <cfRule type="expression" dxfId="166" priority="404">
+    <cfRule type="expression" dxfId="171" priority="410">
       <formula>$C692=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K694:K695">
-    <cfRule type="expression" dxfId="165" priority="394">
+    <cfRule type="expression" dxfId="170" priority="400">
       <formula>$C694=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K701">
-    <cfRule type="expression" dxfId="164" priority="389">
+    <cfRule type="expression" dxfId="169" priority="395">
       <formula>$C701=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K703:K705">
-    <cfRule type="expression" dxfId="163" priority="379">
+    <cfRule type="expression" dxfId="168" priority="385">
       <formula>$C703=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K710">
-    <cfRule type="expression" dxfId="162" priority="374">
+    <cfRule type="expression" dxfId="167" priority="380">
       <formula>$C710=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K712:K714">
-    <cfRule type="expression" dxfId="161" priority="364">
+    <cfRule type="expression" dxfId="166" priority="370">
       <formula>$C712=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K719">
-    <cfRule type="expression" dxfId="160" priority="359">
+    <cfRule type="expression" dxfId="165" priority="365">
       <formula>$C719=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K721:K723">
-    <cfRule type="expression" dxfId="159" priority="352">
+    <cfRule type="expression" dxfId="164" priority="358">
       <formula>$C721=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K728">
-    <cfRule type="expression" dxfId="158" priority="347">
+    <cfRule type="expression" dxfId="163" priority="353">
       <formula>$C728=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K730:K732">
-    <cfRule type="expression" dxfId="157" priority="334">
+    <cfRule type="expression" dxfId="162" priority="340">
       <formula>$C730=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K737">
-    <cfRule type="expression" dxfId="156" priority="327">
+    <cfRule type="expression" dxfId="161" priority="333">
       <formula>$C737=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K739:K741">
-    <cfRule type="expression" dxfId="155" priority="309">
+    <cfRule type="expression" dxfId="160" priority="315">
       <formula>$C739=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K746">
-    <cfRule type="expression" dxfId="154" priority="304">
+    <cfRule type="expression" dxfId="159" priority="310">
       <formula>$C746=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K748:K750">
-    <cfRule type="expression" dxfId="153" priority="280">
+    <cfRule type="expression" dxfId="158" priority="286">
       <formula>$C748=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K755">
-    <cfRule type="expression" dxfId="152" priority="273">
+    <cfRule type="expression" dxfId="157" priority="279">
       <formula>$C755=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K757:K758">
-    <cfRule type="expression" dxfId="151" priority="255">
+    <cfRule type="expression" dxfId="156" priority="261">
       <formula>$C757=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K764">
-    <cfRule type="expression" dxfId="150" priority="244">
+    <cfRule type="expression" dxfId="155" priority="250">
       <formula>$C764=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K766:K767">
-    <cfRule type="expression" dxfId="149" priority="226">
+    <cfRule type="expression" dxfId="154" priority="232">
       <formula>$C766=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K773">
-    <cfRule type="expression" dxfId="148" priority="207">
+    <cfRule type="expression" dxfId="153" priority="213">
       <formula>$C773=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K775:K777">
-    <cfRule type="expression" dxfId="147" priority="180">
+    <cfRule type="expression" dxfId="152" priority="186">
       <formula>$C775=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K782">
-    <cfRule type="expression" dxfId="146" priority="173">
+    <cfRule type="expression" dxfId="151" priority="179">
       <formula>$C782=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K784:K786">
-    <cfRule type="expression" dxfId="145" priority="143">
+    <cfRule type="expression" dxfId="150" priority="149">
       <formula>$C784=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E792:E793">
-    <cfRule type="expression" dxfId="144" priority="142">
+    <cfRule type="expression" dxfId="149" priority="148">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="143" priority="141">
+    <cfRule type="expression" dxfId="148" priority="147">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G792:G793">
-    <cfRule type="expression" dxfId="142" priority="140">
+    <cfRule type="expression" dxfId="147" priority="146">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="141" priority="139">
+    <cfRule type="expression" dxfId="146" priority="145">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I792:I793">
-    <cfRule type="expression" dxfId="140" priority="138">
+    <cfRule type="expression" dxfId="145" priority="144">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="139" priority="137">
+    <cfRule type="expression" dxfId="144" priority="143">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K792:K793">
-    <cfRule type="expression" dxfId="138" priority="136">
+    <cfRule type="expression" dxfId="143" priority="142">
       <formula>$C792=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E794:E795">
-    <cfRule type="expression" dxfId="137" priority="135">
+    <cfRule type="expression" dxfId="142" priority="141">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="136" priority="134">
+    <cfRule type="expression" dxfId="141" priority="140">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G794:G795">
-    <cfRule type="expression" dxfId="135" priority="133">
+    <cfRule type="expression" dxfId="140" priority="139">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="134" priority="132">
+    <cfRule type="expression" dxfId="139" priority="138">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I794:I795">
-    <cfRule type="expression" dxfId="133" priority="131">
+    <cfRule type="expression" dxfId="138" priority="137">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="132" priority="130">
+    <cfRule type="expression" dxfId="137" priority="136">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K794:K795">
-    <cfRule type="expression" dxfId="131" priority="129">
+    <cfRule type="expression" dxfId="136" priority="135">
       <formula>$C794=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E801:E802">
-    <cfRule type="expression" dxfId="130" priority="128">
+    <cfRule type="expression" dxfId="135" priority="134">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E803:E805">
-    <cfRule type="expression" dxfId="129" priority="127">
+    <cfRule type="expression" dxfId="134" priority="133">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G805">
-    <cfRule type="expression" dxfId="128" priority="126">
+    <cfRule type="expression" dxfId="133" priority="132">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G801:G802">
-    <cfRule type="expression" dxfId="127" priority="125">
+    <cfRule type="expression" dxfId="132" priority="131">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G803:G805">
-    <cfRule type="expression" dxfId="126" priority="124">
+    <cfRule type="expression" dxfId="131" priority="130">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I805">
-    <cfRule type="expression" dxfId="125" priority="123">
+    <cfRule type="expression" dxfId="130" priority="129">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I801:I802">
-    <cfRule type="expression" dxfId="124" priority="122">
+    <cfRule type="expression" dxfId="129" priority="128">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I803:I805">
-    <cfRule type="expression" dxfId="123" priority="121">
+    <cfRule type="expression" dxfId="128" priority="127">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K805">
-    <cfRule type="expression" dxfId="122" priority="120">
+    <cfRule type="expression" dxfId="127" priority="126">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K801:K802">
-    <cfRule type="expression" dxfId="121" priority="119">
+    <cfRule type="expression" dxfId="126" priority="125">
       <formula>$C801=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K803:K805">
-    <cfRule type="expression" dxfId="120" priority="118">
+    <cfRule type="expression" dxfId="125" priority="124">
       <formula>$C803=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E809:E810">
-    <cfRule type="expression" dxfId="119" priority="117">
+    <cfRule type="expression" dxfId="124" priority="123">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E811:E812">
-    <cfRule type="expression" dxfId="118" priority="116">
+    <cfRule type="expression" dxfId="123" priority="122">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G812">
-    <cfRule type="expression" dxfId="117" priority="115">
+    <cfRule type="expression" dxfId="122" priority="121">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G809:G810">
-    <cfRule type="expression" dxfId="116" priority="114">
+    <cfRule type="expression" dxfId="121" priority="120">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G811:G812">
-    <cfRule type="expression" dxfId="115" priority="113">
+    <cfRule type="expression" dxfId="120" priority="119">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I812">
-    <cfRule type="expression" dxfId="114" priority="112">
+    <cfRule type="expression" dxfId="119" priority="118">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I809:I810">
-    <cfRule type="expression" dxfId="113" priority="111">
+    <cfRule type="expression" dxfId="118" priority="117">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I811:I812">
-    <cfRule type="expression" dxfId="112" priority="110">
+    <cfRule type="expression" dxfId="117" priority="116">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K812">
-    <cfRule type="expression" dxfId="111" priority="109">
+    <cfRule type="expression" dxfId="116" priority="115">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K809:K810">
-    <cfRule type="expression" dxfId="110" priority="108">
+    <cfRule type="expression" dxfId="115" priority="114">
       <formula>$C809=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K811:K812">
-    <cfRule type="expression" dxfId="109" priority="107">
+    <cfRule type="expression" dxfId="114" priority="113">
       <formula>$C811=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E818:E822 G818:G822 K818:K822 I818:I822">
-    <cfRule type="expression" dxfId="108" priority="106">
+    <cfRule type="expression" dxfId="113" priority="112">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K818:K822 G818:G822 I818:I822">
-    <cfRule type="expression" dxfId="107" priority="105">
+    <cfRule type="expression" dxfId="112" priority="111">
       <formula>$C818=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E820:E821">
-    <cfRule type="expression" dxfId="106" priority="104">
+    <cfRule type="expression" dxfId="111" priority="110">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="105" priority="103">
+    <cfRule type="expression" dxfId="110" priority="109">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G820:G821">
-    <cfRule type="expression" dxfId="104" priority="102">
+    <cfRule type="expression" dxfId="109" priority="108">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="103" priority="101">
+    <cfRule type="expression" dxfId="108" priority="107">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K820:K821">
-    <cfRule type="expression" dxfId="102" priority="100">
+    <cfRule type="expression" dxfId="107" priority="106">
       <formula>$C820=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K822 G822">
-    <cfRule type="expression" dxfId="101" priority="99">
+    <cfRule type="expression" dxfId="106" priority="105">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I822">
-    <cfRule type="expression" dxfId="100" priority="98">
+    <cfRule type="expression" dxfId="105" priority="104">
       <formula>$C822=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E828:E831">
-    <cfRule type="expression" dxfId="99" priority="97">
+    <cfRule type="expression" dxfId="104" priority="103">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="98" priority="96">
+    <cfRule type="expression" dxfId="103" priority="102">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K828:K831 I828:I831 G828:G831">
-    <cfRule type="expression" dxfId="97" priority="95">
+    <cfRule type="expression" dxfId="102" priority="101">
       <formula>$C828=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="96" priority="94">
+    <cfRule type="expression" dxfId="101" priority="100">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E830:E831">
-    <cfRule type="expression" dxfId="95" priority="93">
+    <cfRule type="expression" dxfId="100" priority="99">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="94" priority="92">
+    <cfRule type="expression" dxfId="99" priority="98">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="93" priority="91">
+    <cfRule type="expression" dxfId="98" priority="97">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G830:G831">
-    <cfRule type="expression" dxfId="92" priority="90">
+    <cfRule type="expression" dxfId="97" priority="96">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="91" priority="89">
+    <cfRule type="expression" dxfId="96" priority="95">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="90" priority="88">
+    <cfRule type="expression" dxfId="95" priority="94">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I830:I831">
-    <cfRule type="expression" dxfId="89" priority="87">
+    <cfRule type="expression" dxfId="94" priority="93">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="88" priority="86">
+    <cfRule type="expression" dxfId="93" priority="92">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="87" priority="85">
+    <cfRule type="expression" dxfId="92" priority="91">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K830:K831">
-    <cfRule type="expression" dxfId="86" priority="84">
+    <cfRule type="expression" dxfId="91" priority="90">
       <formula>$C830=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837">
-    <cfRule type="expression" dxfId="85" priority="83">
+    <cfRule type="expression" dxfId="90" priority="89">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="84" priority="82">
+    <cfRule type="expression" dxfId="89" priority="88">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G837">
-    <cfRule type="expression" dxfId="83" priority="81">
+    <cfRule type="expression" dxfId="88" priority="87">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="82" priority="80">
+    <cfRule type="expression" dxfId="87" priority="86">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I837">
-    <cfRule type="expression" dxfId="81" priority="79">
+    <cfRule type="expression" dxfId="86" priority="85">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="80" priority="78">
+    <cfRule type="expression" dxfId="85" priority="84">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K837">
-    <cfRule type="expression" dxfId="79" priority="77">
+    <cfRule type="expression" dxfId="84" priority="83">
       <formula>$C837=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E845:E847">
-    <cfRule type="expression" dxfId="78" priority="76">
+    <cfRule type="expression" dxfId="83" priority="82">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="77" priority="75">
+    <cfRule type="expression" dxfId="82" priority="81">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E846:E847">
-    <cfRule type="expression" dxfId="76" priority="74">
+    <cfRule type="expression" dxfId="81" priority="80">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="75" priority="73">
+    <cfRule type="expression" dxfId="80" priority="79">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G847">
-    <cfRule type="expression" dxfId="74" priority="72">
+    <cfRule type="expression" dxfId="79" priority="78">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="73" priority="71">
+    <cfRule type="expression" dxfId="78" priority="77">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846:G847">
-    <cfRule type="expression" dxfId="72" priority="70">
+    <cfRule type="expression" dxfId="77" priority="76">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="71" priority="69">
+    <cfRule type="expression" dxfId="76" priority="75">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I845:I847">
-    <cfRule type="expression" dxfId="70" priority="68">
+    <cfRule type="expression" dxfId="75" priority="74">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="69" priority="67">
+    <cfRule type="expression" dxfId="74" priority="73">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846:I847">
-    <cfRule type="expression" dxfId="68" priority="66">
+    <cfRule type="expression" dxfId="73" priority="72">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="67" priority="65">
+    <cfRule type="expression" dxfId="72" priority="71">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="66" priority="64">
+    <cfRule type="expression" dxfId="71" priority="70">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="65" priority="63">
+    <cfRule type="expression" dxfId="70" priority="69">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="64" priority="62">
+    <cfRule type="expression" dxfId="69" priority="68">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="63" priority="61">
+    <cfRule type="expression" dxfId="68" priority="67">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K845:K847">
-    <cfRule type="expression" dxfId="62" priority="60">
+    <cfRule type="expression" dxfId="67" priority="66">
       <formula>$C845=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="61" priority="59">
+    <cfRule type="expression" dxfId="66" priority="65">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846:K847">
-    <cfRule type="expression" dxfId="60" priority="58">
+    <cfRule type="expression" dxfId="65" priority="64">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="59" priority="57">
+    <cfRule type="expression" dxfId="64" priority="63">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="58" priority="56">
+    <cfRule type="expression" dxfId="63" priority="62">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="57" priority="55">
+    <cfRule type="expression" dxfId="62" priority="61">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G846">
-    <cfRule type="expression" dxfId="56" priority="54">
+    <cfRule type="expression" dxfId="61" priority="60">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="55" priority="53">
+    <cfRule type="expression" dxfId="60" priority="59">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="54" priority="52">
+    <cfRule type="expression" dxfId="59" priority="58">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="53" priority="51">
+    <cfRule type="expression" dxfId="58" priority="57">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I846">
-    <cfRule type="expression" dxfId="52" priority="50">
+    <cfRule type="expression" dxfId="57" priority="56">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="51" priority="49">
+    <cfRule type="expression" dxfId="56" priority="55">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="50" priority="48">
+    <cfRule type="expression" dxfId="55" priority="54">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="49" priority="47">
+    <cfRule type="expression" dxfId="54" priority="53">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K846">
-    <cfRule type="expression" dxfId="48" priority="46">
+    <cfRule type="expression" dxfId="53" priority="52">
       <formula>$C846=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E836">
-    <cfRule type="expression" dxfId="47" priority="45">
+    <cfRule type="expression" dxfId="52" priority="51">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="46" priority="44">
+    <cfRule type="expression" dxfId="51" priority="50">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G836">
-    <cfRule type="expression" dxfId="45" priority="43">
+    <cfRule type="expression" dxfId="50" priority="49">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="44" priority="42">
+    <cfRule type="expression" dxfId="49" priority="48">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I836">
-    <cfRule type="expression" dxfId="43" priority="41">
+    <cfRule type="expression" dxfId="48" priority="47">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="42" priority="40">
+    <cfRule type="expression" dxfId="47" priority="46">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K836">
-    <cfRule type="expression" dxfId="41" priority="39">
+    <cfRule type="expression" dxfId="46" priority="45">
       <formula>$C836=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853 E853">
-    <cfRule type="expression" dxfId="40" priority="38">
+    <cfRule type="expression" dxfId="45" priority="44">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K853 I853 G853">
-    <cfRule type="expression" dxfId="39" priority="37">
+    <cfRule type="expression" dxfId="44" priority="43">
       <formula>$C853=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854 E854">
-    <cfRule type="expression" dxfId="38" priority="36">
+    <cfRule type="expression" dxfId="43" priority="42">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K854 I854 G854">
-    <cfRule type="expression" dxfId="37" priority="35">
+    <cfRule type="expression" dxfId="42" priority="41">
       <formula>$C854=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="36" priority="34">
+    <cfRule type="expression" dxfId="41" priority="40">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="35" priority="33">
+    <cfRule type="expression" dxfId="40" priority="39">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856 E855:E856">
-    <cfRule type="expression" dxfId="34" priority="32">
+    <cfRule type="expression" dxfId="39" priority="38">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K855:K856 I855:I856 G855:G856">
-    <cfRule type="expression" dxfId="33" priority="31">
+    <cfRule type="expression" dxfId="38" priority="37">
       <formula>$C855=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K862 I862 G862 E862">
-    <cfRule type="expression" dxfId="32" priority="30">
+    <cfRule type="expression" dxfId="37" priority="36">
       <formula>$C862=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K862 I862 G862">
-    <cfRule type="expression" dxfId="31" priority="29">
+    <cfRule type="expression" dxfId="36" priority="35">
       <formula>$C862=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K863 I863 G863 E863">
-    <cfRule type="expression" dxfId="30" priority="28">
+    <cfRule type="expression" dxfId="35" priority="34">
       <formula>$C863=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="29" priority="27">
+    <cfRule type="expression" dxfId="34" priority="33">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="28" priority="26">
+    <cfRule type="expression" dxfId="33" priority="32">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K864:K865 I864:I865 G864:G865 E864:E865">
-    <cfRule type="expression" dxfId="27" priority="25">
+    <cfRule type="expression" dxfId="32" priority="31">
       <formula>$C864=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K863:K865 I863:I865 G863:G865">
-    <cfRule type="expression" dxfId="26" priority="24">
+    <cfRule type="expression" dxfId="31" priority="30">
       <formula>$C863=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E871">
-    <cfRule type="expression" dxfId="25" priority="23">
+    <cfRule type="expression" dxfId="30" priority="29">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E872">
-    <cfRule type="expression" dxfId="24" priority="22">
+    <cfRule type="expression" dxfId="29" priority="28">
       <formula>$C872=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E873:E874">
-    <cfRule type="expression" dxfId="23" priority="21">
+    <cfRule type="expression" dxfId="28" priority="27">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E873:E874">
-    <cfRule type="expression" dxfId="22" priority="20">
+    <cfRule type="expression" dxfId="27" priority="26">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E873:E874">
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="26" priority="25">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G871:G874">
-    <cfRule type="expression" dxfId="20" priority="18">
+    <cfRule type="expression" dxfId="25" priority="24">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G871">
-    <cfRule type="expression" dxfId="19" priority="17">
+    <cfRule type="expression" dxfId="24" priority="23">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G872">
-    <cfRule type="expression" dxfId="18" priority="16">
+    <cfRule type="expression" dxfId="23" priority="22">
       <formula>$C872=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G873:G874">
-    <cfRule type="expression" dxfId="17" priority="15">
+    <cfRule type="expression" dxfId="22" priority="21">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G873:G874">
-    <cfRule type="expression" dxfId="16" priority="14">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G873:G874">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I871:I874">
-    <cfRule type="expression" dxfId="14" priority="12">
+    <cfRule type="expression" dxfId="19" priority="18">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I871">
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I872">
-    <cfRule type="expression" dxfId="12" priority="10">
+    <cfRule type="expression" dxfId="17" priority="16">
       <formula>$C872=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I873:I874">
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="16" priority="15">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I873:I874">
-    <cfRule type="expression" dxfId="10" priority="8">
+    <cfRule type="expression" dxfId="15" priority="14">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I873:I874">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="14" priority="13">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K871:K874">
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="13" priority="12">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K871">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="12" priority="11">
       <formula>$C871=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K872">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>$C872=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K873:K874">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K873:K874">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="9" priority="8">
       <formula>$C873=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K873:K874">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>$C873=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K880 I880 G880 E880">
+    <cfRule type="expression" dxfId="7" priority="6">
+      <formula>$C880=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K881 I881 G881 E881">
+    <cfRule type="expression" dxfId="6" priority="5">
+      <formula>$C881=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K882:K883 I882:I883 G882:G883 E882:E883">
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>$C882=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K882:K883 I882:I883 G882:G883 E882:E883">
+    <cfRule type="expression" dxfId="4" priority="3">
+      <formula>$C882=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K882:K883 I882:I883 G882:G883 E882:E883">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>$C882=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K880:K883 I880:I883 G880:G883">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$C880=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
